--- a/생산실적현황(설비운영현황).xlsx
+++ b/생산실적현황(설비운영현황).xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -601,11 +601,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Metha</t>
+          <t>(UV_NEW)CS30_8.60</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rose_color_원형</t>
+          <t>Gray Bunny_PIA_M_(중)_14.2</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
     </row>
@@ -705,47 +705,47 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>T38_금캡(UV포함)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
     </row>
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
     </row>
@@ -785,23 +785,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
         </is>
       </c>
     </row>
@@ -813,23 +813,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>FLAMINGO_PIA_M(Y)</t>
         </is>
       </c>
     </row>
@@ -849,15 +849,15 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
     </row>
@@ -869,23 +869,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
     </row>
@@ -897,11 +897,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -909,11 +909,11 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1-Day_58_M</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
     </row>
@@ -925,15 +925,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -941,79 +941,79 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sincere_2week UV_Clear</t>
+          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>PIA D Toric CP-1.25_Dazzle Gray_55% UV</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>1-Day_58_M</t>
         </is>
       </c>
     </row>
@@ -1037,23 +1037,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Sincere D_Clear_38%</t>
         </is>
       </c>
     </row>
@@ -1065,15 +1065,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
     </row>
@@ -1093,23 +1093,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Clalen D_Mimosa Brown</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1133,11 +1133,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Clalen oneday A(O2 Edition)</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
     </row>
@@ -1149,11 +1149,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1161,11 +1161,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
     </row>
@@ -1177,21 +1177,133 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C27" t="n">
+        <v>13</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
         <v>6</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>BELLA D_Cedar</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Clalen oneday A(O2 Edition)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>6</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Si_1-Day_Sph</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
@@ -1208,16 +1320,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G271"/>
+  <dimension ref="A1:G302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1284,7 +1396,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>94208</v>
+        <v>45418</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1317,10 +1429,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>48235</v>
+        <v>102271</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="4">
@@ -1350,10 +1462,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>34932</v>
+        <v>30907</v>
       </c>
       <c r="G4" t="n">
-        <v>570</v>
+        <v>770</v>
       </c>
     </row>
     <row r="5">
@@ -1379,14 +1491,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Metha_55</t>
+          <t>S55_8.60</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>35900</v>
+        <v>17531</v>
       </c>
       <c r="G5" t="n">
-        <v>1424</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="6">
@@ -1407,19 +1519,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>조립8호기</t>
+          <t>조립3호기</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.2</t>
+          <t>S55_8.80</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>39871</v>
+        <v>17837</v>
       </c>
       <c r="G6" t="n">
-        <v>1614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1435,24 +1547,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>조립2호기</t>
+          <t>조립8호기</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>T38_(UV포함)</t>
+          <t>(NEW)S43-HD-Dry-14.2</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3313</v>
+        <v>40514</v>
       </c>
       <c r="G7" t="n">
-        <v>2038</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1478,14 +1590,14 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>T38_(UV포함)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3153</v>
+        <v>7128</v>
       </c>
       <c r="G8" t="n">
-        <v>1031</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="9">
@@ -1515,10 +1627,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7448</v>
+        <v>6173</v>
       </c>
       <c r="G9" t="n">
-        <v>1089</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="10">
@@ -1548,10 +1660,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>13202</v>
+        <v>13757</v>
       </c>
       <c r="G10" t="n">
-        <v>1934</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="11">
@@ -1581,10 +1693,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>11639</v>
+        <v>14152</v>
       </c>
       <c r="G11" t="n">
-        <v>1834</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="12">
@@ -1614,10 +1726,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>25844</v>
+        <v>8168</v>
       </c>
       <c r="G12" t="n">
-        <v>4665</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="13">
@@ -1647,10 +1759,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3657</v>
+        <v>17600</v>
       </c>
       <c r="G13" t="n">
-        <v>850</v>
+        <v>4173</v>
       </c>
     </row>
     <row r="14">
@@ -1680,10 +1792,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5170</v>
+        <v>12648</v>
       </c>
       <c r="G14" t="n">
-        <v>1360</v>
+        <v>4819</v>
       </c>
     </row>
     <row r="15">
@@ -1699,24 +1811,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>분리4호기</t>
+          <t>분리3호기</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS30-Dry</t>
+          <t>T38_(UV포함)</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5993</v>
+        <v>12705</v>
       </c>
       <c r="G15" t="n">
-        <v>885</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="16">
@@ -1732,24 +1844,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>분리5호기</t>
+          <t>분리3호기</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>US55-2(M)</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2015</v>
+        <v>514</v>
       </c>
       <c r="G16" t="n">
-        <v>587</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -1760,29 +1872,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>분리3호기</t>
+          <t>검사15호기</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>T38_(UV포함)</t>
+          <t>Chuulens M_Mellow Hazel_After Glow_(중)</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>9511</v>
+        <v>1756</v>
       </c>
       <c r="G17" t="n">
-        <v>2142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1803,19 +1915,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>Bella Diamond_14.5_중사각</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>850</v>
+        <v>448</v>
       </c>
       <c r="G18" t="n">
-        <v>197</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -1836,19 +1948,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3574</v>
+        <v>4262</v>
       </c>
       <c r="G19" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20">
@@ -1869,19 +1981,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cihan Elegance_중사각</t>
+          <t>Gray Bunny_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>81</v>
+        <v>4406</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21">
@@ -1902,19 +2014,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Clalen Iris_Claire Brown_원형</t>
+          <t>BELLA M_Moon_14.5_(중)</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3755</v>
+        <v>82</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22">
@@ -1935,19 +2047,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Clalen Iris_Claire Gray_원형</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4386</v>
+        <v>2524</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23">
@@ -1968,19 +2080,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Neon Color_원형</t>
+          <t>Gray Bunny_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>3906</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24">
@@ -2006,14 +2118,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NewFusion_원형</t>
+          <t>Bella-SnowWhite_14.5_원형</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>392</v>
+        <v>552</v>
       </c>
       <c r="G24" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2039,14 +2151,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rose_color_원형</t>
+          <t>Clalen Iris_BRW_3304_원형</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7458</v>
+        <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2067,16 +2179,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BELLA M_Moon_14.5_(중)</t>
+          <t>Clalen Iris_Claire Brown_원형</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>59</v>
+        <v>887</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2100,16 +2212,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bella-Elite_14.5_중사각</t>
+          <t>Clalen Iris_Claire Gray_원형</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>575</v>
+        <v>2583</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2133,16 +2245,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bella-Natural_14.5_중사각</t>
+          <t>Clalen Iris_VIO_3303_원형</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>928</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2166,19 +2278,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bella-Natural_중사각</t>
+          <t>Rose_color_원형</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>329</v>
+        <v>5628</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30">
@@ -2204,14 +2316,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>Affogato_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5696</v>
+        <v>1161</v>
       </c>
       <c r="G30" t="n">
-        <v>416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2237,11 +2349,11 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Clalen Iris_Claire Gray_원형</t>
+          <t>BELLA M_Moon_14.5_(중)</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>221</v>
+        <v>58</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2270,14 +2382,14 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2758</v>
+        <v>1592</v>
       </c>
       <c r="G32" t="n">
-        <v>265</v>
+        <v>687</v>
       </c>
     </row>
     <row r="33">
@@ -2298,19 +2410,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>Gray Bunny_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2108</v>
+        <v>3268</v>
       </c>
       <c r="G33" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34">
@@ -2331,19 +2443,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>NewFusion_소사각</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>6264</v>
+        <v>33</v>
       </c>
       <c r="G34" t="n">
-        <v>446</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35">
@@ -2364,19 +2476,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>NewFusion_원형</t>
+          <t>BELLA M_Moon_14.5_(중)</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>9</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36">
@@ -2397,19 +2509,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rose_color_원형</t>
+          <t>Bella-Contour_중사각</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>5561</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>161</v>
+        <v>499</v>
       </c>
     </row>
     <row r="37">
@@ -2430,19 +2542,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CLC-30_바이알</t>
+          <t>Bella-Natural_중사각</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38">
@@ -2463,19 +2575,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Crazy_은캡</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>419</v>
+        <v>2656</v>
       </c>
       <c r="G38" t="n">
-        <v>56</v>
+        <v>925</v>
       </c>
     </row>
     <row r="39">
@@ -2496,19 +2608,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Festival-II-Color_은캡</t>
+          <t>Gray Bunny_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>915</v>
+        <v>6819</v>
       </c>
       <c r="G39" t="n">
-        <v>85</v>
+        <v>320</v>
       </c>
     </row>
     <row r="40">
@@ -2524,24 +2636,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사7호기</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>Bella-Contour_중사각</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>4832</v>
+        <v>184</v>
       </c>
       <c r="G40" t="n">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
@@ -2557,24 +2669,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>검사7호기</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>Gray Bunny_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>4184</v>
+        <v>2060</v>
       </c>
       <c r="G41" t="n">
-        <v>91</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42">
@@ -2595,19 +2707,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1831</v>
+        <v>4246</v>
       </c>
       <c r="G42" t="n">
-        <v>96</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43">
@@ -2628,19 +2740,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>S38_은캡(BLUE TINT)</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>80</v>
+        <v>748</v>
       </c>
       <c r="G43" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44">
@@ -2656,7 +2768,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2666,14 +2778,14 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>US55-2(M)_소사각</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>688</v>
+        <v>2108</v>
       </c>
       <c r="G44" t="n">
-        <v>241</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
@@ -2689,24 +2801,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>US55-2(M)_소사각</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>300</v>
+        <v>1550</v>
       </c>
       <c r="G45" t="n">
-        <v>228</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46">
@@ -2722,24 +2834,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1942</v>
+        <v>990</v>
       </c>
       <c r="G46" t="n">
-        <v>441</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
@@ -2755,24 +2867,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>T38_금캡(UV포함)</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>837</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>408</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="48">
@@ -2788,24 +2900,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>Metha_55_금캡</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>6449</v>
+        <v>1068</v>
       </c>
       <c r="G48" t="n">
-        <v>912</v>
+        <v>230</v>
       </c>
     </row>
     <row r="49">
@@ -2821,24 +2933,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1344</v>
+        <v>532</v>
       </c>
       <c r="G49" t="n">
-        <v>432</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50">
@@ -2854,24 +2966,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>4750</v>
+        <v>368</v>
       </c>
       <c r="G50" t="n">
-        <v>1383</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51">
@@ -2887,24 +2999,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Si_FRP_Toric</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>O2O2 M_UV_Toric_SMD_(소)</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="G51" t="n">
-        <v>203</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52">
@@ -2920,24 +3032,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Si_FRP_Toric</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>O2O2 M_UV_Toric_SMD_(소)</t>
+          <t>T38_금캡</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>250</v>
+        <v>514</v>
       </c>
       <c r="G52" t="n">
-        <v>108</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53">
@@ -2953,24 +3065,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Si_FRP_Toric</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>O2O2 M_UV_Toric_SMD_(소)</t>
+          <t>T38_금캡(UV포함)</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>228</v>
+        <v>1695</v>
       </c>
       <c r="G53" t="n">
-        <v>57</v>
+        <v>384</v>
       </c>
     </row>
     <row r="54">
@@ -2986,21 +3098,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Si_FRP_Toric</t>
+          <t>Si_FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>O2O2 M_UV_Toric_SMD_(소)</t>
+          <t>O2O2 M_Mysti Gray EX_(중)</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>631</v>
+        <v>80</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -3009,232 +3121,232 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>조립10호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>O2O2 M_Natural Brown EX_(중)</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>28904</v>
+        <v>52</v>
       </c>
       <c r="G55" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>조립12호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>O2O2 M_Natural Gray EX_(중)</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>22980</v>
+        <v>56</v>
       </c>
       <c r="G56" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>조립13호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>Silicone relax_소사각</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>51562</v>
+        <v>2963</v>
       </c>
       <c r="G57" t="n">
-        <v>6352</v>
+        <v>387</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>조립14호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>57158</v>
+        <v>2584</v>
       </c>
       <c r="G58" t="n">
-        <v>940</v>
+        <v>492</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>조립15호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>29530</v>
+        <v>5754</v>
       </c>
       <c r="G59" t="n">
-        <v>100</v>
+        <v>395</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Toric</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>조립16호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>O2O2 M_UV_Toric_SMD_(소)</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>55331</v>
+        <v>1776</v>
       </c>
       <c r="G60" t="n">
-        <v>412</v>
+        <v>236</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Toric</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>조립20호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>O2O2 M_UV_Toric_SMD_(소)</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>43601</v>
+        <v>403</v>
       </c>
       <c r="G61" t="n">
-        <v>8885</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62">
@@ -3255,19 +3367,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>조립25호기</t>
+          <t>조립10호기</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>30260</v>
+        <v>5133</v>
       </c>
       <c r="G62" t="n">
-        <v>30</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="63">
@@ -3288,19 +3400,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>조립26호기</t>
+          <t>조립11호기</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>10380</v>
+        <v>51239</v>
       </c>
       <c r="G63" t="n">
-        <v>1789</v>
+        <v>6611</v>
       </c>
     </row>
     <row r="64">
@@ -3321,19 +3433,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>조립27호기</t>
+          <t>조립12호기</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>BELLA D_VENUS 55%</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>14890</v>
+        <v>25902</v>
       </c>
       <c r="G64" t="n">
-        <v>158</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="65">
@@ -3354,19 +3466,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>조립40호기</t>
+          <t>조립13호기</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>4696</v>
+        <v>23337</v>
       </c>
       <c r="G65" t="n">
-        <v>1611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -3387,7 +3499,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>조립44호기</t>
+          <t>조립14호기</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3396,10 +3508,10 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>49253</v>
+        <v>27377</v>
       </c>
       <c r="G66" t="n">
-        <v>179</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="67">
@@ -3420,19 +3532,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>조립45호기</t>
+          <t>조립15호기</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>28491</v>
+        <v>28304</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>444</v>
       </c>
     </row>
     <row r="68">
@@ -3453,19 +3565,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>조립46호기</t>
+          <t>조립16호기</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BELLA_1-Day_Hazel Honey</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>7108</v>
+        <v>23426</v>
       </c>
       <c r="G68" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -3486,19 +3598,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>조립47호기</t>
+          <t>조립20호기</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>51366</v>
+        <v>9983</v>
       </c>
       <c r="G69" t="n">
-        <v>2150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3519,19 +3631,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>조립48호기</t>
+          <t>조립25호기</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>47684</v>
+        <v>25301</v>
       </c>
       <c r="G70" t="n">
-        <v>5548</v>
+        <v>829</v>
       </c>
     </row>
     <row r="71">
@@ -3552,19 +3664,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>조립50호기</t>
+          <t>조립26호기</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>21831</v>
+        <v>29524</v>
       </c>
       <c r="G71" t="n">
-        <v>2330</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="72">
@@ -3585,19 +3697,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>조립51호기</t>
+          <t>조립27호기</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>BELLA D_VENUS 55%</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>29280</v>
+        <v>24730</v>
       </c>
       <c r="G72" t="n">
-        <v>300</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="73">
@@ -3618,19 +3730,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>조립53호기</t>
+          <t>조립40호기</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>49998</v>
+        <v>48038</v>
       </c>
       <c r="G73" t="n">
-        <v>66</v>
+        <v>5642</v>
       </c>
     </row>
     <row r="74">
@@ -3651,19 +3763,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>조립54호기</t>
+          <t>조립44호기</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sincere D_Air Beige_ITFA_38% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>24348</v>
+        <v>22488</v>
       </c>
       <c r="G74" t="n">
-        <v>55</v>
+        <v>188</v>
       </c>
     </row>
     <row r="75">
@@ -3684,19 +3796,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>조립57호기</t>
+          <t>조립45호기</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>BELLA D_Siren Bronze 55%</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>20887</v>
+        <v>30926</v>
       </c>
       <c r="G75" t="n">
-        <v>2364</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="76">
@@ -3717,19 +3829,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>조립58호기</t>
+          <t>조립46호기</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>27104</v>
+        <v>30215</v>
       </c>
       <c r="G76" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -3750,19 +3862,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>조립59호기</t>
+          <t>조립47호기</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>26229</v>
+        <v>29481</v>
       </c>
       <c r="G77" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -3778,24 +3890,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립48호기</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>12026</v>
+        <v>28305</v>
       </c>
       <c r="G78" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -3811,24 +3923,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립49호기</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>32374</v>
+        <v>26387</v>
       </c>
       <c r="G79" t="n">
-        <v>1871</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="80">
@@ -3844,24 +3956,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립50호기</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>10681</v>
+        <v>61010</v>
       </c>
       <c r="G80" t="n">
-        <v>4</v>
+        <v>160</v>
       </c>
     </row>
     <row r="81">
@@ -3877,24 +3989,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립51호기</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Gray</t>
+          <t>PIA D_Cherish Brown_55% UV 14.2</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>12851</v>
+        <v>10469</v>
       </c>
       <c r="G81" t="n">
-        <v>2300</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="82">
@@ -3910,24 +4022,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립52호기</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>8822</v>
+        <v>47720</v>
       </c>
       <c r="G82" t="n">
-        <v>300</v>
+        <v>4380</v>
       </c>
     </row>
     <row r="83">
@@ -3943,24 +4055,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>조립24호기</t>
+          <t>조립55호기</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PIA_Opal CP-0.75 Toric_UV</t>
+          <t>PIA D_Pomme Canele_38% UV</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>28321</v>
+        <v>24267</v>
       </c>
       <c r="G83" t="n">
-        <v>2325</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="84">
@@ -3976,24 +4088,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>조립24호기</t>
+          <t>조립57호기</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PIA_Opal CP-1.25 Toric_UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>9183</v>
+        <v>23659</v>
       </c>
       <c r="G84" t="n">
-        <v>910</v>
+        <v>434</v>
       </c>
     </row>
     <row r="85">
@@ -4004,7 +4116,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4014,19 +4126,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>조립58호기</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>5309</v>
+        <v>52422</v>
       </c>
       <c r="G85" t="n">
-        <v>622</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86">
@@ -4037,29 +4149,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>BELLA D_Siren Bronze 55%</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>18198</v>
+        <v>9835</v>
       </c>
       <c r="G86" t="n">
-        <v>1980</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="87">
@@ -4070,29 +4182,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>23762</v>
+        <v>5420</v>
       </c>
       <c r="G87" t="n">
-        <v>2399</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4103,29 +4215,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>35788</v>
+        <v>5478</v>
       </c>
       <c r="G88" t="n">
-        <v>4481</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4136,29 +4248,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>Toric_CP-0.75_Halo Gray</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>8908</v>
+        <v>2508</v>
       </c>
       <c r="G89" t="n">
-        <v>1176</v>
+        <v>652</v>
       </c>
     </row>
     <row r="90">
@@ -4169,29 +4281,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>PIA D_Teddy Brown_55% UV</t>
+          <t>Toric_CP-1.25_Halo Gray</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>38328</v>
+        <v>11004</v>
       </c>
       <c r="G90" t="n">
-        <v>4329</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="91">
@@ -4202,29 +4314,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>BELLA D_MARS 55%</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>32046</v>
+        <v>8993</v>
       </c>
       <c r="G91" t="n">
-        <v>7414</v>
+        <v>496</v>
       </c>
     </row>
     <row r="92">
@@ -4235,29 +4347,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>조립24호기</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>PIA D_Dorayaki_55% UV</t>
+          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>21758</v>
+        <v>15405</v>
       </c>
       <c r="G92" t="n">
-        <v>3437</v>
+        <v>250</v>
       </c>
     </row>
     <row r="93">
@@ -4268,29 +4380,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>조립24호기</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>PIA_Tulle Brown_1D_55%_14.2</t>
+          <t>PIA_Brown Fondue CP-1.25 Toric_UV</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>21703</v>
+        <v>5252</v>
       </c>
       <c r="G93" t="n">
-        <v>3304</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -4301,29 +4413,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>분리19호기</t>
+          <t>조립53호기</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>FLAMINGO_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>15403</v>
+        <v>9976</v>
       </c>
       <c r="G94" t="n">
-        <v>1971</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="95">
@@ -4344,19 +4456,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>분리19호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>22485</v>
+        <v>44226</v>
       </c>
       <c r="G95" t="n">
-        <v>2570</v>
+        <v>4572</v>
       </c>
     </row>
     <row r="96">
@@ -4377,19 +4489,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>6449</v>
+        <v>5366</v>
       </c>
       <c r="G96" t="n">
-        <v>984</v>
+        <v>569</v>
       </c>
     </row>
     <row r="97">
@@ -4410,19 +4522,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>29590</v>
+        <v>41742</v>
       </c>
       <c r="G97" t="n">
-        <v>5996</v>
+        <v>4886</v>
       </c>
     </row>
     <row r="98">
@@ -4443,19 +4555,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>42148</v>
+        <v>5615</v>
       </c>
       <c r="G98" t="n">
-        <v>4597</v>
+        <v>938</v>
       </c>
     </row>
     <row r="99">
@@ -4476,19 +4588,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>46397</v>
+        <v>19196</v>
       </c>
       <c r="G99" t="n">
-        <v>4840</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="100">
@@ -4509,19 +4621,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>13980</v>
+        <v>13194</v>
       </c>
       <c r="G100" t="n">
-        <v>2310</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="101">
@@ -4542,19 +4654,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Teddy Brown_55% UV</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>28423</v>
+        <v>6168</v>
       </c>
       <c r="G101" t="n">
-        <v>3874</v>
+        <v>565</v>
       </c>
     </row>
     <row r="102">
@@ -4575,7 +4687,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4584,10 +4696,10 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>39235</v>
+        <v>18508</v>
       </c>
       <c r="G102" t="n">
-        <v>6222</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="103">
@@ -4608,19 +4720,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>BELLA D_MARS 55%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>15544</v>
+        <v>5028</v>
       </c>
       <c r="G103" t="n">
-        <v>2051</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="104">
@@ -4641,19 +4753,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Clalen D_FUGUANG_55%</t>
+          <t>PIA D_Dorayaki_55% UV</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>10248</v>
+        <v>8365</v>
       </c>
       <c r="G104" t="n">
-        <v>2107</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="105">
@@ -4674,19 +4786,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>13168</v>
+        <v>15475</v>
       </c>
       <c r="G105" t="n">
-        <v>1357</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="106">
@@ -4707,19 +4819,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>BELLA D_VENUS 55%</t>
+          <t>Rina_Crystal Gray_1-Day</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>19642</v>
+        <v>1863</v>
       </c>
       <c r="G106" t="n">
-        <v>3308</v>
+        <v>194</v>
       </c>
     </row>
     <row r="107">
@@ -4740,19 +4852,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리19호기</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>5197</v>
+        <v>16158</v>
       </c>
       <c r="G107" t="n">
-        <v>549</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="108">
@@ -4773,19 +4885,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리19호기</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>47589</v>
+        <v>27596</v>
       </c>
       <c r="G108" t="n">
-        <v>4592</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="109">
@@ -4806,19 +4918,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>37109</v>
+        <v>39050</v>
       </c>
       <c r="G109" t="n">
-        <v>6460</v>
+        <v>5741</v>
       </c>
     </row>
     <row r="110">
@@ -4839,19 +4951,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>9417</v>
+        <v>4003</v>
       </c>
       <c r="G110" t="n">
-        <v>913</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="111">
@@ -4872,19 +4984,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Alcon D_Chic Smoke_W4</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1107</v>
+        <v>23039</v>
       </c>
       <c r="G111" t="n">
-        <v>178</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="112">
@@ -4905,19 +5017,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>12061</v>
+        <v>19958</v>
       </c>
       <c r="G112" t="n">
-        <v>1150</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="113">
@@ -4938,19 +5050,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>PIA D_Sugar Donut_38% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>9411</v>
+        <v>45333</v>
       </c>
       <c r="G113" t="n">
-        <v>1912</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="114">
@@ -4971,19 +5083,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sincere D_Air Beige_ITFA_38% UV</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>5671</v>
+        <v>39778</v>
       </c>
       <c r="G114" t="n">
-        <v>1390</v>
+        <v>4951</v>
       </c>
     </row>
     <row r="115">
@@ -5004,19 +5116,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sincere D_Neutral Brown_UV_38% 14.2</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>12349</v>
+        <v>37871</v>
       </c>
       <c r="G115" t="n">
-        <v>3164</v>
+        <v>7093</v>
       </c>
     </row>
     <row r="116">
@@ -5037,19 +5149,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>sincere_Lavender Nude_1-Day 38%</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1518</v>
+        <v>9616</v>
       </c>
       <c r="G116" t="n">
-        <v>1200</v>
+        <v>944</v>
       </c>
     </row>
     <row r="117">
@@ -5070,19 +5182,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>43972</v>
+        <v>23112</v>
       </c>
       <c r="G117" t="n">
-        <v>3693</v>
+        <v>3189</v>
       </c>
     </row>
     <row r="118">
@@ -5103,19 +5215,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>BELLA_1-Day_Hazel Honey</t>
+          <t>Alcon D_Chic Smoke_W4</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>5589</v>
+        <v>1667</v>
       </c>
       <c r="G118" t="n">
-        <v>401</v>
+        <v>178</v>
       </c>
     </row>
     <row r="119">
@@ -5136,19 +5248,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Freedom380</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>7101</v>
+        <v>15747</v>
       </c>
       <c r="G119" t="n">
-        <v>1690</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="120">
@@ -5169,19 +5281,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>36779</v>
+        <v>4880</v>
       </c>
       <c r="G120" t="n">
-        <v>4054</v>
+        <v>497</v>
       </c>
     </row>
     <row r="121">
@@ -5202,19 +5314,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Cherish Brown_55% UV 14.2</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>22082</v>
+        <v>9702</v>
       </c>
       <c r="G121" t="n">
-        <v>2683</v>
+        <v>767</v>
       </c>
     </row>
     <row r="122">
@@ -5235,19 +5347,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>BELLA D_Siren Bronze 55%</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>22051</v>
+        <v>26455</v>
       </c>
       <c r="G122" t="n">
-        <v>1690</v>
+        <v>4095</v>
       </c>
     </row>
     <row r="123">
@@ -5268,19 +5380,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>분리43호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>33467</v>
+        <v>34042</v>
       </c>
       <c r="G123" t="n">
-        <v>5044</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="124">
@@ -5301,19 +5413,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>분리43호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>PIA D_Cherish Brown_55% UV 14.2</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>9421</v>
+        <v>15414</v>
       </c>
       <c r="G124" t="n">
-        <v>1039</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="125">
@@ -5329,24 +5441,24 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>PIA D_Sugar Donut_38% UV</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>5018</v>
+        <v>12475</v>
       </c>
       <c r="G125" t="n">
-        <v>892</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="126">
@@ -5362,24 +5474,24 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>28791</v>
+        <v>22892</v>
       </c>
       <c r="G126" t="n">
-        <v>4684</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="127">
@@ -5395,24 +5507,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>Sincere D_Air Beige_ITFA_38% UV</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>5952</v>
+        <v>4443</v>
       </c>
       <c r="G127" t="n">
-        <v>1342</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="128">
@@ -5428,24 +5540,24 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>PIA D Toric CP-0.75_Dollish Brown_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3564</v>
+        <v>1520</v>
       </c>
       <c r="G128" t="n">
-        <v>2127</v>
+        <v>192</v>
       </c>
     </row>
     <row r="129">
@@ -5461,24 +5573,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>PIA D Toric CP-1.25_Dazzle Gray_55% UV</t>
+          <t>BELLA_1-Day_Hazel Honey</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2413</v>
+        <v>12114</v>
       </c>
       <c r="G129" t="n">
-        <v>834</v>
+        <v>882</v>
       </c>
     </row>
     <row r="130">
@@ -5494,24 +5606,24 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-0.75 Dollish Gray_55% UV</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3369</v>
+        <v>23112</v>
       </c>
       <c r="G130" t="n">
-        <v>646</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="131">
@@ -5527,24 +5639,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-1.25 Dollish Gray_55% UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>7975</v>
+        <v>20787</v>
       </c>
       <c r="G131" t="n">
-        <v>1550</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="132">
@@ -5560,24 +5672,24 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>PIA_Opal CP-0.75 Toric_UV</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>5025</v>
+        <v>24572</v>
       </c>
       <c r="G132" t="n">
-        <v>940</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="133">
@@ -5593,24 +5705,24 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Gray</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>7142</v>
+        <v>41567</v>
       </c>
       <c r="G133" t="n">
-        <v>1871</v>
+        <v>4253</v>
       </c>
     </row>
     <row r="134">
@@ -5626,24 +5738,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리43호기</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Gray</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>9831</v>
+        <v>18969</v>
       </c>
       <c r="G134" t="n">
-        <v>2397</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="135">
@@ -5659,24 +5771,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>분리22호기</t>
+          <t>분리43호기</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>37777</v>
+        <v>24481</v>
       </c>
       <c r="G135" t="n">
-        <v>6668</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="136">
@@ -5692,24 +5804,24 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>분리23호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D Toric_CP-0.75 Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>35782</v>
+        <v>2722</v>
       </c>
       <c r="G136" t="n">
-        <v>10011</v>
+        <v>661</v>
       </c>
     </row>
     <row r="137">
@@ -5725,24 +5837,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>분리25호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>43588</v>
+        <v>2403</v>
       </c>
       <c r="G137" t="n">
-        <v>8184</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="138">
@@ -5758,24 +5870,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Coffee Jelly_PIA_M(Y)</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>3508</v>
+        <v>10366</v>
       </c>
       <c r="G138" t="n">
-        <v>2092</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="139">
@@ -5791,24 +5903,24 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Cream Rose_PIA_M</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>819</v>
+        <v>18897</v>
       </c>
       <c r="G139" t="n">
-        <v>691</v>
+        <v>3139</v>
       </c>
     </row>
     <row r="140">
@@ -5824,24 +5936,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Date Topaz_PIA_M(Y)</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>417</v>
+        <v>5675</v>
       </c>
       <c r="G140" t="n">
-        <v>132</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="141">
@@ -5857,24 +5969,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Garnet_PIA_M(Y)</t>
+          <t>PIA D Toric CP-0.75_Dollish Brown_55% UV</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1875</v>
+        <v>608</v>
       </c>
       <c r="G141" t="n">
-        <v>959</v>
+        <v>308</v>
       </c>
     </row>
     <row r="142">
@@ -5890,24 +6002,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Lady Black_PIA_M_(중)_14.5</t>
+          <t>PIA D Toric_CP-1.25 Dollish Gray_55% UV</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1844</v>
+        <v>1769</v>
       </c>
       <c r="G142" t="n">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="143">
@@ -5923,24 +6035,24 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Princess Chocolat_PIA_M_(중)_14.5</t>
+          <t>PIA_Opal CP-0.75 Toric_UV</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>2246</v>
+        <v>12289</v>
       </c>
       <c r="G143" t="n">
-        <v>630</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="144">
@@ -5951,29 +6063,29 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA_Opal CP-1.25 Toric_UV</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>3440</v>
+        <v>4802</v>
       </c>
       <c r="G144" t="n">
-        <v>45</v>
+        <v>941</v>
       </c>
     </row>
     <row r="145">
@@ -5984,29 +6096,29 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>PIA D_Cherish Brown_55% UV 14.2</t>
+          <t>Toric_CP-1.25_Halo Gray</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>5800</v>
+        <v>11762</v>
       </c>
       <c r="G145" t="n">
-        <v>85</v>
+        <v>3803</v>
       </c>
     </row>
     <row r="146">
@@ -6017,29 +6129,29 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>PIA D_MELON PAN_55% UV</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>2865</v>
+        <v>9537</v>
       </c>
       <c r="G146" t="n">
-        <v>50</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="147">
@@ -6050,29 +6162,29 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리22호기</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Smore_55% UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>3010</v>
+        <v>32529</v>
       </c>
       <c r="G147" t="n">
-        <v>75</v>
+        <v>6194</v>
       </c>
     </row>
     <row r="148">
@@ -6083,29 +6195,29 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리23호기</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>PIA_BROWN MANEGE</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>9450</v>
+        <v>26386</v>
       </c>
       <c r="G148" t="n">
-        <v>150</v>
+        <v>6849</v>
       </c>
     </row>
     <row r="149">
@@ -6116,29 +6228,29 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리25호기</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PIA_Cider_1-DAY 55%</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>43543</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>8232</v>
       </c>
     </row>
     <row r="150">
@@ -6149,29 +6261,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PIA_MS5 Tint Brown_1T</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>4550</v>
+        <v>2108</v>
       </c>
       <c r="G150" t="n">
-        <v>235</v>
+        <v>169</v>
       </c>
     </row>
     <row r="151">
@@ -6182,29 +6294,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PIA_SARANG BROWN</t>
+          <t>Coral Brown_2T_(PBT)PIA_M</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2605</v>
+        <v>4591</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>4849</v>
       </c>
     </row>
     <row r="152">
@@ -6215,29 +6327,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>PIA D_Teddy Brown_55% UV</t>
+          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2710</v>
+        <v>11653</v>
       </c>
       <c r="G152" t="n">
-        <v>395</v>
+        <v>3629</v>
       </c>
     </row>
     <row r="153">
@@ -6258,19 +6370,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>PIA_BROWN MANEGE</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>15870</v>
+        <v>6192</v>
       </c>
       <c r="G153" t="n">
-        <v>325</v>
+        <v>248</v>
       </c>
     </row>
     <row r="154">
@@ -6291,19 +6403,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>PIA_Cider_1-DAY 55%</t>
+          <t>PIA D_Cherish Brown_55% UV 14.2</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>6885</v>
+        <v>1620</v>
       </c>
       <c r="G154" t="n">
-        <v>140</v>
+        <v>45</v>
       </c>
     </row>
     <row r="155">
@@ -6324,19 +6436,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>PIA_KEOPI BROWN</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>3090</v>
+        <v>1435</v>
       </c>
       <c r="G155" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="156">
@@ -6357,19 +6469,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>PIA_LILY BLACK</t>
+          <t>PIA D_Teddy Brown_55% UV</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>3380</v>
+        <v>3290</v>
       </c>
       <c r="G156" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="157">
@@ -6390,19 +6502,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>PIA_MS5 Tint Brown_1T</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>3058</v>
+        <v>2010</v>
       </c>
       <c r="G157" t="n">
-        <v>487</v>
+        <v>135</v>
       </c>
     </row>
     <row r="158">
@@ -6423,19 +6535,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>PIA_Cider_1-DAY 55%</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>2770</v>
+        <v>550</v>
       </c>
       <c r="G158" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="159">
@@ -6456,19 +6568,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA_Coconut_55%_1-DAY</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>8835</v>
+        <v>1070</v>
       </c>
       <c r="G159" t="n">
-        <v>110</v>
+        <v>20</v>
       </c>
     </row>
     <row r="160">
@@ -6489,19 +6601,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA_KEOPI BROWN</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>25675</v>
+        <v>2810</v>
       </c>
       <c r="G160" t="n">
-        <v>295</v>
+        <v>90</v>
       </c>
     </row>
     <row r="161">
@@ -6522,19 +6634,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>BELLA D_MARS 55%</t>
+          <t>PIA_LILY BLACK</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>6545</v>
+        <v>3340</v>
       </c>
       <c r="G161" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
     </row>
     <row r="162">
@@ -6555,19 +6667,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>BELLA D_Siren Bronze 55%</t>
+          <t>PIA_MS5 Tint Brown_1T</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>22600</v>
+        <v>1440</v>
       </c>
       <c r="G162" t="n">
-        <v>345</v>
+        <v>40</v>
       </c>
     </row>
     <row r="163">
@@ -6588,19 +6700,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>BELLA D_VENUS 55%</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>17224</v>
+        <v>3755</v>
       </c>
       <c r="G163" t="n">
-        <v>1151</v>
+        <v>50</v>
       </c>
     </row>
     <row r="164">
@@ -6621,19 +6733,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>PIA D_MELON PAN_55% UV</t>
+          <t>PIA D_Teddy Brown_55% UV</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1705</v>
+        <v>8355</v>
       </c>
       <c r="G164" t="n">
-        <v>60</v>
+        <v>195</v>
       </c>
     </row>
     <row r="165">
@@ -6654,19 +6766,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1460</v>
+        <v>5680</v>
       </c>
       <c r="G165" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="166">
@@ -6687,19 +6799,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Smore_55% UV</t>
+          <t>PIA_BROWN MANEGE</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>2640</v>
+        <v>6760</v>
       </c>
       <c r="G166" t="n">
-        <v>60</v>
+        <v>105</v>
       </c>
     </row>
     <row r="167">
@@ -6720,19 +6832,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA_Cider_1-DAY 55%</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>2585</v>
+        <v>4330</v>
       </c>
       <c r="G167" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
     </row>
     <row r="168">
@@ -6753,19 +6865,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PIA_BROWN MANEGE</t>
+          <t>PIA_Coconut_55%_1-DAY</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>14830</v>
+        <v>970</v>
       </c>
       <c r="G168" t="n">
-        <v>205</v>
+        <v>25</v>
       </c>
     </row>
     <row r="169">
@@ -6786,19 +6898,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PIA_Cider_1-DAY 55%</t>
+          <t>PIA_LILY BLACK</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>905</v>
+        <v>3315</v>
       </c>
       <c r="G169" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="170">
@@ -6819,19 +6931,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>PIA_KEOPI BROWN</t>
+          <t>PIA_MS4 Mirror Gray_3T</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>2220</v>
+        <v>815</v>
       </c>
       <c r="G170" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
     </row>
     <row r="171">
@@ -6852,19 +6964,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PIA_LILY BLACK</t>
+          <t>PIA_MS5 Tint Brown_1T</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>24965</v>
+        <v>3640</v>
       </c>
       <c r="G171" t="n">
-        <v>300</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="172">
@@ -6885,7 +6997,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -6894,10 +7006,10 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>10530</v>
+        <v>17225</v>
       </c>
       <c r="G172" t="n">
-        <v>275</v>
+        <v>200</v>
       </c>
     </row>
     <row r="173">
@@ -6918,7 +7030,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -6927,10 +7039,10 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>38945</v>
+        <v>30770</v>
       </c>
       <c r="G173" t="n">
-        <v>1060</v>
+        <v>765</v>
       </c>
     </row>
     <row r="174">
@@ -6951,19 +7063,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>BELLA D_MARS 55%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2520</v>
+        <v>19493</v>
       </c>
       <c r="G174" t="n">
-        <v>55</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="175">
@@ -6984,19 +7096,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>PIA D_Cherish Brown_55% UV 14.2</t>
+          <t>BELLA D_Siren Bronze 55%</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>31715</v>
+        <v>23052</v>
       </c>
       <c r="G175" t="n">
-        <v>595</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="176">
@@ -7017,19 +7129,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>PIA D_Gray Bunny_55% UV 14.2</t>
+          <t>BELLA D_VENUS 55%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>6855</v>
+        <v>7580</v>
       </c>
       <c r="G176" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
     </row>
     <row r="177">
@@ -7050,19 +7162,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>2760</v>
+        <v>12870</v>
       </c>
       <c r="G177" t="n">
-        <v>75</v>
+        <v>750</v>
       </c>
     </row>
     <row r="178">
@@ -7083,19 +7195,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>PIA D_Gray Bunny_55% UV 14.2</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>3500</v>
+        <v>1465</v>
       </c>
       <c r="G178" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="179">
@@ -7116,19 +7228,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_MELON PAN_55% UV</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>4155</v>
+        <v>2875</v>
       </c>
       <c r="G179" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="180">
@@ -7149,19 +7261,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>29435</v>
+        <v>1435</v>
       </c>
       <c r="G180" t="n">
-        <v>555</v>
+        <v>10</v>
       </c>
     </row>
     <row r="181">
@@ -7182,19 +7294,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Sakura Smore_55% UV</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>9340</v>
+        <v>2085</v>
       </c>
       <c r="G181" t="n">
-        <v>130</v>
+        <v>45</v>
       </c>
     </row>
     <row r="182">
@@ -7215,19 +7327,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Teddy Brown_55% UV</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2015</v>
+        <v>975</v>
       </c>
       <c r="G182" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="183">
@@ -7248,19 +7360,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2175</v>
+        <v>4973</v>
       </c>
       <c r="G183" t="n">
-        <v>35</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="184">
@@ -7281,19 +7393,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA_BROWN MANEGE</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>12165</v>
+        <v>3400</v>
       </c>
       <c r="G184" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
     </row>
     <row r="185">
@@ -7314,19 +7426,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA_Cider_1-DAY 55%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>31415</v>
+        <v>1560</v>
       </c>
       <c r="G185" t="n">
-        <v>640</v>
+        <v>10</v>
       </c>
     </row>
     <row r="186">
@@ -7347,19 +7459,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA_Coconut_55%_1-DAY</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>3235</v>
+        <v>3840</v>
       </c>
       <c r="G186" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="187">
@@ -7380,19 +7492,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA_LILY BLACK</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1415</v>
+        <v>4495</v>
       </c>
       <c r="G187" t="n">
-        <v>30</v>
+        <v>575</v>
       </c>
     </row>
     <row r="188">
@@ -7413,19 +7525,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA_MS5 Tint Brown_1T</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1972</v>
+        <v>6989</v>
       </c>
       <c r="G188" t="n">
-        <v>843</v>
+        <v>631</v>
       </c>
     </row>
     <row r="189">
@@ -7446,19 +7558,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>PIA_BROWN MANEGE</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>22330</v>
+        <v>3395</v>
       </c>
       <c r="G189" t="n">
-        <v>390</v>
+        <v>75</v>
       </c>
     </row>
     <row r="190">
@@ -7479,19 +7591,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>PIA_KEOPI BROWN</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>2985</v>
+        <v>27494</v>
       </c>
       <c r="G190" t="n">
-        <v>50</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="191">
@@ -7512,19 +7624,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>PIA_LILY BLACK</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>6870</v>
+        <v>17445</v>
       </c>
       <c r="G191" t="n">
-        <v>85</v>
+        <v>365</v>
       </c>
     </row>
     <row r="192">
@@ -7545,19 +7657,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>PIA_Tulle Brown_1D_55%_14.2</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>7070</v>
+        <v>13044</v>
       </c>
       <c r="G192" t="n">
-        <v>665</v>
+        <v>731</v>
       </c>
     </row>
     <row r="193">
@@ -7578,19 +7690,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>ClearBeige Mini UV 14.2</t>
+          <t>PIA D_Cherish Brown_55% UV 14.2</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>5300</v>
+        <v>4865</v>
       </c>
       <c r="G193" t="n">
-        <v>140</v>
+        <v>55</v>
       </c>
     </row>
     <row r="194">
@@ -7611,19 +7723,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>From D_(UV)Clear Beige Coral_38%</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1690</v>
+        <v>3620</v>
       </c>
       <c r="G194" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="195">
@@ -7644,19 +7756,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>From D_(UV)Clear Beige_38%</t>
+          <t>PIA D_Dorayaki_55% UV</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>2695</v>
+        <v>3120</v>
       </c>
       <c r="G195" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="196">
@@ -7677,19 +7789,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Sakura Smore_55% UV</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>2529</v>
+        <v>2200</v>
       </c>
       <c r="G196" t="n">
-        <v>701</v>
+        <v>30</v>
       </c>
     </row>
     <row r="197">
@@ -7710,19 +7822,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Clalen D_FUGUANG_55%</t>
+          <t>PIA D_Teddy Brown_55% UV</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>4625</v>
+        <v>995</v>
       </c>
       <c r="G197" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="198">
@@ -7743,19 +7855,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Clalen D_LANDIAO_55%</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>2165</v>
+        <v>6832</v>
       </c>
       <c r="G198" t="n">
-        <v>80</v>
+        <v>813</v>
       </c>
     </row>
     <row r="199">
@@ -7776,19 +7888,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Clalen D_XUYU(PINK)55%(TW)</t>
+          <t>PIA_BROWN MANEGE</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>33900</v>
+        <v>1690</v>
       </c>
       <c r="G199" t="n">
-        <v>575</v>
+        <v>20</v>
       </c>
     </row>
     <row r="200">
@@ -7809,19 +7921,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>IRIS_Jazz black(NEW)</t>
+          <t>PIA_Coconut_55%_1-DAY</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>2580</v>
+        <v>3610</v>
       </c>
       <c r="G200" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="201">
@@ -7842,19 +7954,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>BELLA_1-Day_Hazel Honey(8년)</t>
+          <t>PIA_LILY BLACK</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>9010</v>
+        <v>2680</v>
       </c>
       <c r="G201" t="n">
-        <v>180</v>
+        <v>55</v>
       </c>
     </row>
     <row r="202">
@@ -7875,19 +7987,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>PIA_MS5 Tint Brown_1T</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>31659</v>
+        <v>10332</v>
       </c>
       <c r="G202" t="n">
-        <v>941</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="203">
@@ -7908,19 +8020,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>PIA_Matcha Latte_55%_1-DAY</t>
+          <t>PIA_Tulle Brown_1D_55%_14.2</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1875</v>
+        <v>1045</v>
       </c>
       <c r="G203" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="204">
@@ -7936,24 +8048,24 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-0.75 Brown Bunny_55% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>2660</v>
+        <v>30726</v>
       </c>
       <c r="G204" t="n">
-        <v>195</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="205">
@@ -7969,24 +8081,24 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-0.75 Dollish Gray_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>4210</v>
+        <v>20991</v>
       </c>
       <c r="G205" t="n">
-        <v>75</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="206">
@@ -8002,24 +8114,24 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-0.75 TOPARDS Baby Espresso_55%_UV</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>1845</v>
+        <v>5470</v>
       </c>
       <c r="G206" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
     </row>
     <row r="207">
@@ -8035,24 +8147,24 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>970</v>
+        <v>21295</v>
       </c>
       <c r="G207" t="n">
-        <v>780</v>
+        <v>390</v>
       </c>
     </row>
     <row r="208">
@@ -8068,24 +8180,24 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-1.25 Dollish Gray_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>3760</v>
+        <v>18535</v>
       </c>
       <c r="G208" t="n">
-        <v>95</v>
+        <v>310</v>
       </c>
     </row>
     <row r="209">
@@ -8101,24 +8213,24 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-1.25 TOPARDS Baby Espresso_55%_UV</t>
+          <t>Clalen D_FUGUANG(GRAY)55%(TW)</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>1355</v>
+        <v>2765</v>
       </c>
       <c r="G209" t="n">
-        <v>195</v>
+        <v>15</v>
       </c>
     </row>
     <row r="210">
@@ -8134,24 +8246,24 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>Clalen D_FUGUANG_55%</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>13905</v>
+        <v>3386</v>
       </c>
       <c r="G210" t="n">
-        <v>170</v>
+        <v>554</v>
       </c>
     </row>
     <row r="211">
@@ -8167,7 +8279,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -8177,14 +8289,14 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>5375</v>
+        <v>36820</v>
       </c>
       <c r="G211" t="n">
-        <v>90</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="212">
@@ -8200,24 +8312,24 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>PIA D Toric CP-0.75_Dollish Brown_55% UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>3860</v>
+        <v>10490</v>
       </c>
       <c r="G212" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
     </row>
     <row r="213">
@@ -8233,24 +8345,24 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>PIA D Toric CP-1.25_Dazzle Gray_55% UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>12890</v>
+        <v>4019</v>
       </c>
       <c r="G213" t="n">
-        <v>290</v>
+        <v>346</v>
       </c>
     </row>
     <row r="214">
@@ -8266,24 +8378,24 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>1-Day_58_M</t>
+          <t>PIA D_Cherish Brown_55% UV 14.2</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>45655</v>
+        <v>2295</v>
       </c>
       <c r="G214" t="n">
-        <v>1475</v>
+        <v>65</v>
       </c>
     </row>
     <row r="215">
@@ -8299,24 +8411,24 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>1-DAY58_Micure</t>
+          <t>PIA D_Sakura Smore_55% UV</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>14335</v>
+        <v>2220</v>
       </c>
       <c r="G215" t="n">
-        <v>445</v>
+        <v>30</v>
       </c>
     </row>
     <row r="216">
@@ -8332,24 +8444,24 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Teddy Brown_55% UV</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>14650</v>
+        <v>8835</v>
       </c>
       <c r="G216" t="n">
-        <v>430</v>
+        <v>185</v>
       </c>
     </row>
     <row r="217">
@@ -8365,24 +8477,24 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>1-Day_58_M</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>31610</v>
+        <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>1120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -8398,24 +8510,24 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>1-DAY_58_공용_MD로고</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>9095</v>
+        <v>5895</v>
       </c>
       <c r="G218" t="n">
-        <v>200</v>
+        <v>75</v>
       </c>
     </row>
     <row r="219">
@@ -8431,24 +8543,24 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>1-Day_58(NEW)</t>
+          <t>PIA_Cider_1-DAY 55%</t>
         </is>
       </c>
       <c r="F219" t="n">
-        <v>16065</v>
+        <v>1895</v>
       </c>
       <c r="G219" t="n">
-        <v>350</v>
+        <v>50</v>
       </c>
     </row>
     <row r="220">
@@ -8464,24 +8576,24 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>1-Day_58(수출용_파랑)</t>
+          <t>PIA_Coconut_55%_1-DAY</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>18995</v>
+        <v>1830</v>
       </c>
       <c r="G220" t="n">
-        <v>565</v>
+        <v>10</v>
       </c>
     </row>
     <row r="221">
@@ -8497,816 +8609,816 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Sincere_2week UV_Clear</t>
+          <t>PIA_LILY BLACK</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>29502</v>
+        <v>2535</v>
       </c>
       <c r="G221" t="n">
-        <v>930</v>
+        <v>20</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>B형 조립중합4호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>PIA_MS5 Tint Brown_1T</t>
         </is>
       </c>
       <c r="F222" t="n">
-        <v>13969</v>
+        <v>3885</v>
       </c>
       <c r="G222" t="n">
-        <v>2671</v>
+        <v>145</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>B형 조립중합5호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>PIA_Matcha Latte_55%_1-DAY</t>
         </is>
       </c>
       <c r="F223" t="n">
-        <v>16740</v>
+        <v>6613</v>
       </c>
       <c r="G223" t="n">
-        <v>932</v>
+        <v>567</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>B형 조립중합6호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Brown EX</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F224" t="n">
-        <v>10010</v>
+        <v>2785</v>
       </c>
       <c r="G224" t="n">
-        <v>6006</v>
+        <v>30</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>B형 조립중합7호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>6783</v>
+        <v>21805</v>
       </c>
       <c r="G225" t="n">
-        <v>977</v>
+        <v>255</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>57257</v>
+        <v>26827</v>
       </c>
       <c r="G226" t="n">
-        <v>0</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>22795</v>
+        <v>17734</v>
       </c>
       <c r="G227" t="n">
-        <v>0</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>CAM분리1호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>8560</v>
+        <v>20290</v>
       </c>
       <c r="G228" t="n">
-        <v>1735</v>
+        <v>170</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>CAM분리2호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>PIA_Cider_1-DAY 55%</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>8649</v>
+        <v>875</v>
       </c>
       <c r="G229" t="n">
-        <v>1630</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>CAM분리3호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>PIA D Toric_CP-1.25 Dollish Gray_55% UV</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>8630</v>
+        <v>1306</v>
       </c>
       <c r="G230" t="n">
-        <v>1790</v>
+        <v>749</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>CAM분리4호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>Hapa D Toric_Glazed choco_CP-1.75</t>
         </is>
       </c>
       <c r="F231" t="n">
-        <v>5109</v>
+        <v>1113</v>
       </c>
       <c r="G231" t="n">
-        <v>1023</v>
+        <v>292</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F232" t="n">
-        <v>1380</v>
+        <v>2220</v>
       </c>
       <c r="G232" t="n">
-        <v>665</v>
+        <v>40</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F233" t="n">
-        <v>11179</v>
+        <v>2580</v>
       </c>
       <c r="G233" t="n">
-        <v>4064</v>
+        <v>5</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Gray EX</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F234" t="n">
-        <v>3529</v>
+        <v>2525</v>
       </c>
       <c r="G234" t="n">
-        <v>873</v>
+        <v>10</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F235" t="n">
-        <v>9682</v>
+        <v>1065</v>
       </c>
       <c r="G235" t="n">
-        <v>2748</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>PIA D Toric CP-0.75_Dazzle Gray_55% UV</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>6806</v>
+        <v>4260</v>
       </c>
       <c r="G236" t="n">
-        <v>1085</v>
+        <v>35</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>B형 분리수화접착6호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>PIA D Toric CP-0.75_Dollish Brown_55% UV</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>10369</v>
+        <v>3854</v>
       </c>
       <c r="G237" t="n">
-        <v>1917</v>
+        <v>151</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>B형 분리수화접착6호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>PIA D Toric CP-1.25_Dazzle Gray_55% UV</t>
         </is>
       </c>
       <c r="F238" t="n">
-        <v>4769</v>
+        <v>12895</v>
       </c>
       <c r="G238" t="n">
-        <v>2460</v>
+        <v>160</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>PIA D Toric CP-1.25_Dollish Brown_55% UV</t>
         </is>
       </c>
       <c r="F239" t="n">
-        <v>7763</v>
+        <v>3785</v>
       </c>
       <c r="G239" t="n">
-        <v>2389</v>
+        <v>255</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>PIA_Opal CP-0.75 Toric_UV</t>
         </is>
       </c>
       <c r="F240" t="n">
-        <v>3417</v>
+        <v>1930</v>
       </c>
       <c r="G240" t="n">
-        <v>815</v>
+        <v>600</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>1-Day_58_M</t>
         </is>
       </c>
       <c r="F241" t="n">
-        <v>6701</v>
+        <v>34525</v>
       </c>
       <c r="G241" t="n">
-        <v>1546</v>
+        <v>850</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>1-Day_58_M</t>
         </is>
       </c>
       <c r="F242" t="n">
-        <v>958</v>
+        <v>50791</v>
       </c>
       <c r="G242" t="n">
-        <v>1077</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>1-Day_58_M</t>
         </is>
       </c>
       <c r="F243" t="n">
-        <v>15592</v>
+        <v>38831</v>
       </c>
       <c r="G243" t="n">
-        <v>1323</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F244" t="n">
-        <v>19893</v>
+        <v>18965</v>
       </c>
       <c r="G244" t="n">
-        <v>1416</v>
+        <v>470</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>1-Day_58(NEW)</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>22308</v>
+        <v>14635</v>
       </c>
       <c r="G245" t="n">
-        <v>3312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="246">
@@ -9317,29 +9429,29 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Clalen D_Canola Brown</t>
+          <t>Sincere D_Clear_38%</t>
         </is>
       </c>
       <c r="F246" t="n">
-        <v>8510</v>
+        <v>16354</v>
       </c>
       <c r="G246" t="n">
-        <v>681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -9350,29 +9462,29 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>B형 조립중합4호기</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Clalen D_Mimosa Brown</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F247" t="n">
-        <v>14740</v>
+        <v>14841</v>
       </c>
       <c r="G247" t="n">
-        <v>683</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="248">
@@ -9383,29 +9495,29 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>B형 조립중합5호기</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>BELLA D_Cedar</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F248" t="n">
-        <v>0</v>
+        <v>22129</v>
       </c>
       <c r="G248" t="n">
-        <v>0</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="249">
@@ -9416,29 +9528,29 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>B형 조립중합6호기</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Clalen D_Mimosa Brown</t>
+          <t>O2O2 D_Ash Brown EX</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2220</v>
+        <v>12275</v>
       </c>
       <c r="G249" t="n">
-        <v>27</v>
+        <v>4269</v>
       </c>
     </row>
     <row r="250">
@@ -9449,12 +9561,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -9464,14 +9576,14 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Clalen oneday A(O2 Edition)</t>
+          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>25185</v>
+        <v>18253</v>
       </c>
       <c r="G250" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -9482,29 +9594,29 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Clalen oneday A(O2 Edition)</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>1710</v>
+        <v>40473</v>
       </c>
       <c r="G251" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -9515,29 +9627,29 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Clalen oneday A(O2 Edition)</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2860</v>
+        <v>43870</v>
       </c>
       <c r="G252" t="n">
-        <v>616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -9548,29 +9660,29 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>5399</v>
+        <v>25831</v>
       </c>
       <c r="G253" t="n">
-        <v>1105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -9581,29 +9693,29 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>CAM분리2호기</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>BELLA D_Cedar</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>6144</v>
+        <v>1857</v>
       </c>
       <c r="G254" t="n">
-        <v>925</v>
+        <v>671</v>
       </c>
     </row>
     <row r="255">
@@ -9614,29 +9726,29 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>CAM분리2호기</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>DYE D_ALORA</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>7745</v>
+        <v>1499</v>
       </c>
       <c r="G255" t="n">
-        <v>1570</v>
+        <v>713</v>
       </c>
     </row>
     <row r="256">
@@ -9647,29 +9759,29 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>CAM분리1호기</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>2631</v>
+        <v>12330</v>
       </c>
       <c r="G256" t="n">
-        <v>699</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="257">
@@ -9680,29 +9792,29 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>CAM분리2호기</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F257" t="n">
-        <v>4148</v>
+        <v>5508</v>
       </c>
       <c r="G257" t="n">
-        <v>1144</v>
+        <v>617</v>
       </c>
     </row>
     <row r="258">
@@ -9713,29 +9825,29 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>CAM분리3호기</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F258" t="n">
-        <v>824</v>
+        <v>11937</v>
       </c>
       <c r="G258" t="n">
-        <v>76</v>
+        <v>915</v>
       </c>
     </row>
     <row r="259">
@@ -9746,29 +9858,29 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>CAM분리4호기</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F259" t="n">
-        <v>7661</v>
+        <v>4294</v>
       </c>
       <c r="G259" t="n">
-        <v>360</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="260">
@@ -9779,7 +9891,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9789,19 +9901,19 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>B형 분리수화접착4호기</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F260" t="n">
-        <v>872</v>
+        <v>4736</v>
       </c>
       <c r="G260" t="n">
-        <v>143</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="261">
@@ -9812,7 +9924,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9822,19 +9934,19 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>B형 분리수화접착4호기</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F261" t="n">
-        <v>985</v>
+        <v>1093</v>
       </c>
       <c r="G261" t="n">
-        <v>19</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="262">
@@ -9845,7 +9957,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9855,19 +9967,19 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F262" t="n">
-        <v>12710</v>
+        <v>7603</v>
       </c>
       <c r="G262" t="n">
-        <v>347</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="263">
@@ -9878,7 +9990,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9888,7 +10000,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -9897,10 +10009,10 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>11900</v>
+        <v>6011</v>
       </c>
       <c r="G263" t="n">
-        <v>465</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="264">
@@ -9911,29 +10023,29 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>B형 분리수화접착6호기</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMDH_WHITE_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F264" t="n">
-        <v>1440</v>
+        <v>7562</v>
       </c>
       <c r="G264" t="n">
-        <v>44</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="265">
@@ -9944,29 +10056,29 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>B형 분리수화접착6호기</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMDH_WHITE_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F265" t="n">
-        <v>2930</v>
+        <v>8341</v>
       </c>
       <c r="G265" t="n">
-        <v>58</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="266">
@@ -9977,29 +10089,29 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>O2O2 D_UV_Spherical_FGC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F266" t="n">
-        <v>22550</v>
+        <v>13209</v>
       </c>
       <c r="G266" t="n">
-        <v>501</v>
+        <v>4961</v>
       </c>
     </row>
     <row r="267">
@@ -10010,29 +10122,29 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F267" t="n">
-        <v>9665</v>
+        <v>1536</v>
       </c>
       <c r="G267" t="n">
-        <v>125</v>
+        <v>270</v>
       </c>
     </row>
     <row r="268">
@@ -10043,29 +10155,29 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>14510</v>
+        <v>13368</v>
       </c>
       <c r="G268" t="n">
-        <v>193</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="269">
@@ -10076,29 +10188,29 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>20630</v>
+        <v>1288</v>
       </c>
       <c r="G269" t="n">
-        <v>230</v>
+        <v>541</v>
       </c>
     </row>
     <row r="270">
@@ -10109,29 +10221,29 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>9455</v>
+        <v>1432</v>
       </c>
       <c r="G270" t="n">
-        <v>207</v>
+        <v>476</v>
       </c>
     </row>
     <row r="271">
@@ -10142,29 +10254,1052 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
+          <t>Si_1-Day_M/F</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>B형 분리수화접착3호기</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>3941</v>
+      </c>
+      <c r="G271" t="n">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>[20] 분리</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Si_1-Day_M/F</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>B형 분리수화접착4호기</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>3933</v>
+      </c>
+      <c r="G272" t="n">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>[20] 분리</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
           <t>Si_1-Day_Sph</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>56659</v>
+      </c>
+      <c r="G273" t="n">
+        <v>5156</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>[20] 분리</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>A형 인라인2호기</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>35686</v>
+      </c>
+      <c r="G274" t="n">
+        <v>3935</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>[20] 분리</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>A형 인라인3호기</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>14024</v>
+      </c>
+      <c r="G275" t="n">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>[20] 분리</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>B형 분리수화접착3호기</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>16808</v>
+      </c>
+      <c r="G276" t="n">
+        <v>4486</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>[20] 분리</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>B형 분리수화접착4호기</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>11862</v>
+      </c>
+      <c r="G277" t="n">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>A형 인라인4호기</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>BELLA D_Cedar</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
+        <v>7195</v>
+      </c>
+      <c r="G278" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>A형 인라인4호기</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>BELLA D_Pine</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>8245</v>
+      </c>
+      <c r="G279" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>A형 인라인4호기</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Clalen D_Canola Brown</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>6730</v>
+      </c>
+      <c r="G280" t="n">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>A형 인라인4호기</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Clalen D_Mimosa Brown</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>3945</v>
+      </c>
+      <c r="G281" t="n">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>A형 인라인6호기</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>BELLA D_Cedar</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>19145</v>
+      </c>
+      <c r="G282" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>A형 인라인6호기</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Clalen D_Mimosa Brown</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>2070</v>
+      </c>
+      <c r="G283" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
         <is>
           <t>A형 인라인5호기</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Clalen oneday A(O2 Edition)</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>26530</v>
+      </c>
+      <c r="G284" t="n">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G285" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>2900</v>
+      </c>
+      <c r="G286" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>2755</v>
+      </c>
+      <c r="G287" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>A형 인라인2호기</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>1590</v>
+      </c>
+      <c r="G288" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>A형 인라인2호기</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>1770</v>
+      </c>
+      <c r="G289" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>A형 인라인3호기</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>7181</v>
+      </c>
+      <c r="G290" t="n">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>A형 인라인3호기</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>25961</v>
+      </c>
+      <c r="G291" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>A형 인라인3호기</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>7560</v>
+      </c>
+      <c r="G292" t="n">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>A형 인라인4호기</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>A형 인라인4호기</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>4530</v>
+      </c>
+      <c r="G294" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>A형 인라인5호기</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>4040</v>
+      </c>
+      <c r="G295" t="n">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>A형 인라인5호기</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>3085</v>
+      </c>
+      <c r="G296" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>A형 인라인6호기</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>2210</v>
+      </c>
+      <c r="G297" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>A형 인라인6호기</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G298" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
         <is>
           <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
-      <c r="F271" t="n">
-        <v>33170</v>
-      </c>
-      <c r="G271" t="n">
-        <v>663</v>
+      <c r="F299" t="n">
+        <v>33286</v>
+      </c>
+      <c r="G299" t="n">
+        <v>4317</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>A형 인라인2호기</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>25372</v>
+      </c>
+      <c r="G300" t="n">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>A형 인라인4호기</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>1675</v>
+      </c>
+      <c r="G301" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>A형 인라인6호기</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>17265</v>
+      </c>
+      <c r="G302" t="n">
+        <v>408</v>
       </c>
     </row>
   </sheetData>

--- a/생산실적현황(설비운영현황).xlsx
+++ b/생산실적현황(설비운영현황).xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.2</t>
+          <t>S55_8.60</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -549,7 +549,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>T38_(UV포함)</t>
+          <t>O2O2 Spherical(DK70)_K2-SMD</t>
         </is>
       </c>
     </row>
@@ -561,23 +561,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Si_1-Day_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>O2O2 D_UV_Toric_SMD</t>
+          <t>S55</t>
         </is>
       </c>
     </row>
@@ -597,15 +597,15 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>(UV_NEW)CS30_8.60</t>
+          <t>T38_(UV포함)</t>
         </is>
       </c>
     </row>
@@ -617,23 +617,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>T38_(UV포함)</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
     </row>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>S55_소사각</t>
         </is>
       </c>
     </row>
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>Silicone relax_소사각</t>
         </is>
       </c>
     </row>
@@ -705,47 +705,47 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>T38_금캡(UV포함)</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
     </row>
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
     </row>
@@ -789,19 +789,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
+          <t>Gray Bunny_PIA_M_(중)_14.2</t>
         </is>
       </c>
     </row>
@@ -813,23 +813,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FLAMINGO_PIA_M(Y)</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
     </row>
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
         </is>
       </c>
     </row>
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
     </row>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
     </row>
@@ -925,23 +925,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
     </row>
@@ -961,35 +961,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-Day_58(수출용_파랑)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -997,23 +997,23 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PIA D Toric CP-1.25_Dazzle Gray_55% UV</t>
+          <t>BELLA D_Star</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1021,11 +1021,11 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1-Day_58_M</t>
+          <t>Sincere D_Clear_38%</t>
         </is>
       </c>
     </row>
@@ -1045,15 +1045,15 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sincere D_Clear_38%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
     </row>
@@ -1073,15 +1073,15 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1093,23 +1093,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>DYE D_LAVA</t>
         </is>
       </c>
     </row>
@@ -1125,11 +1125,11 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
     </row>
@@ -1153,11 +1153,11 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Toric</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>O2O2 D_UV_Toric_SMD</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1241,15 +1241,15 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Clalen oneday A(O2 Edition)</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
     </row>
@@ -1269,41 +1269,13 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>6</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>2</v>
-      </c>
-      <c r="F31" t="inlineStr">
         <is>
           <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
@@ -1320,14 +1292,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G302"/>
+  <dimension ref="A1:G278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1396,10 +1368,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>45418</v>
+        <v>48942</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="3">
@@ -1429,10 +1401,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>102271</v>
+        <v>105808</v>
       </c>
       <c r="G3" t="n">
-        <v>1412</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1448,24 +1420,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>조립1호기</t>
+          <t>조립32호기</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(UV_NEW)CS30_8.60</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>30907</v>
+        <v>50994</v>
       </c>
       <c r="G4" t="n">
-        <v>770</v>
+        <v>613</v>
       </c>
     </row>
     <row r="5">
@@ -1486,19 +1458,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>조립3호기</t>
+          <t>조립1호기</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S55_8.60</t>
+          <t>CS30-Dry</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>17531</v>
+        <v>18621</v>
       </c>
       <c r="G5" t="n">
-        <v>1841</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="6">
@@ -1519,16 +1491,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>조립3호기</t>
+          <t>조립1호기</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S55_8.80</t>
+          <t>S38-2_Blue</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>17837</v>
+        <v>19000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1552,19 +1524,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>조립8호기</t>
+          <t>조립3호기</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.2</t>
+          <t>S55_8.60</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>40514</v>
+        <v>36628</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>453</v>
       </c>
     </row>
     <row r="8">
@@ -1580,24 +1552,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>조립2호기</t>
+          <t>조립8호기</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>T38_(UV포함)</t>
+          <t>(NEW)S43-HD-Dry-14.4</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7128</v>
+        <v>35317</v>
       </c>
       <c r="G8" t="n">
-        <v>1612</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -1613,24 +1585,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Si_1-Day_Toric</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>조립7호기</t>
+          <t>조립4호기</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>O2O2 D_UV_Toric_SMD</t>
+          <t>O2O2 Spherical(DK70)_K2-SMD</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6173</v>
+        <v>31180</v>
       </c>
       <c r="G9" t="n">
-        <v>1739</v>
+        <v>538</v>
       </c>
     </row>
     <row r="10">
@@ -1660,10 +1632,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>13757</v>
+        <v>12333</v>
       </c>
       <c r="G10" t="n">
-        <v>1772</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="11">
@@ -1693,10 +1665,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>14152</v>
+        <v>14134</v>
       </c>
       <c r="G11" t="n">
-        <v>2183</v>
+        <v>3672</v>
       </c>
     </row>
     <row r="12">
@@ -1722,14 +1694,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Metha</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>8168</v>
+        <v>30444</v>
       </c>
       <c r="G12" t="n">
-        <v>1994</v>
+        <v>5201</v>
       </c>
     </row>
     <row r="13">
@@ -1750,19 +1722,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>분리14호기</t>
+          <t>분리4호기</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>(NEW)S43-HD-Dry-14.2</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>17600</v>
+        <v>14776</v>
       </c>
       <c r="G13" t="n">
-        <v>4173</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="14">
@@ -1778,24 +1750,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>분리4호기</t>
+          <t>분리3호기</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.2</t>
+          <t>T38_(UV포함)</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12648</v>
+        <v>10302</v>
       </c>
       <c r="G14" t="n">
-        <v>4819</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="15">
@@ -1821,14 +1793,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>T38_(UV포함)</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12705</v>
+        <v>1323</v>
       </c>
       <c r="G15" t="n">
-        <v>3485</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16">
@@ -1839,29 +1811,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>분리3호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>514</v>
+        <v>6192</v>
       </c>
       <c r="G16" t="n">
-        <v>15</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="17">
@@ -1882,19 +1854,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>검사15호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chuulens M_Mellow Hazel_After Glow_(중)</t>
+          <t>Gray Bunny_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1756</v>
+        <v>2946</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18">
@@ -1915,19 +1887,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bella Diamond_14.5_중사각</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>448</v>
+        <v>6542</v>
       </c>
       <c r="G18" t="n">
-        <v>50</v>
+        <v>617</v>
       </c>
     </row>
     <row r="19">
@@ -1948,19 +1920,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>Gray Bunny_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4262</v>
+        <v>2636</v>
       </c>
       <c r="G19" t="n">
-        <v>220</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20">
@@ -1981,19 +1953,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>Advance_CB_원형</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4406</v>
+        <v>1294</v>
       </c>
       <c r="G20" t="n">
-        <v>153</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21">
@@ -2014,19 +1986,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BELLA M_Moon_14.5_(중)</t>
+          <t>Advance_EO_원형</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="G21" t="n">
-        <v>118</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
@@ -2047,19 +2019,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>Clalen Iris_Claire Brown_원형</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2524</v>
+        <v>120</v>
       </c>
       <c r="G22" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2080,19 +2052,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>Clalen Iris_Claire Gray_원형</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3906</v>
+        <v>304</v>
       </c>
       <c r="G23" t="n">
-        <v>272</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2118,14 +2090,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bella-SnowWhite_14.5_원형</t>
+          <t>Festival-II-Color_원형</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>552</v>
+        <v>348</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
@@ -2151,11 +2123,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Clalen Iris_BRW_3304_원형</t>
+          <t>Neon Color_원형</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2184,14 +2156,14 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Clalen Iris_Claire Brown_원형</t>
+          <t>NewFusion_원형</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>887</v>
+        <v>2664</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>656</v>
       </c>
     </row>
     <row r="27">
@@ -2217,14 +2189,14 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Clalen Iris_Claire Gray_원형</t>
+          <t>Rose_color_원형</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2583</v>
+        <v>1008</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
     </row>
     <row r="28">
@@ -2245,19 +2217,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Clalen Iris_VIO_3303_원형</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>928</v>
+        <v>4768</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
     </row>
     <row r="29">
@@ -2278,19 +2250,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rose_color_원형</t>
+          <t>Clalen 1M_Planet_Mercury Blue</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5628</v>
+        <v>176</v>
       </c>
       <c r="G29" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2316,14 +2288,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Affogato_PIA_M_(중)(Y)</t>
+          <t>Gray Bunny_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1161</v>
+        <v>5388</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>552</v>
       </c>
     </row>
     <row r="31">
@@ -2344,19 +2316,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BELLA M_Moon_14.5_(중)</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>58</v>
+        <v>3716</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="32">
@@ -2377,19 +2349,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>Gray Bunny_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1592</v>
+        <v>5834</v>
       </c>
       <c r="G32" t="n">
-        <v>687</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33">
@@ -2410,19 +2382,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사7호기</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3268</v>
+        <v>6300</v>
       </c>
       <c r="G33" t="n">
-        <v>83</v>
+        <v>503</v>
       </c>
     </row>
     <row r="34">
@@ -2443,19 +2415,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사7호기</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>NewFusion_소사각</t>
+          <t>Gray Bunny_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>33</v>
+        <v>2696</v>
       </c>
       <c r="G34" t="n">
-        <v>65</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35">
@@ -2476,19 +2448,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BELLA M_Moon_14.5_(중)</t>
+          <t>APIA-(Look at me)_원형</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1022</v>
       </c>
       <c r="G35" t="n">
-        <v>197</v>
+        <v>665</v>
       </c>
     </row>
     <row r="36">
@@ -2509,19 +2481,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bella-Contour_중사각</t>
+          <t>Advance_CB_원형</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="G36" t="n">
-        <v>499</v>
+        <v>444</v>
       </c>
     </row>
     <row r="37">
@@ -2542,19 +2514,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bella-Natural_중사각</t>
+          <t>Festival-II-Color_원형</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="G37" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38">
@@ -2575,19 +2547,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>NewFusion_원형</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2656</v>
+        <v>926</v>
       </c>
       <c r="G38" t="n">
-        <v>925</v>
+        <v>991</v>
       </c>
     </row>
     <row r="39">
@@ -2608,19 +2580,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>Rose_color_원형</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>6819</v>
+        <v>376</v>
       </c>
       <c r="G39" t="n">
-        <v>320</v>
+        <v>148</v>
       </c>
     </row>
     <row r="40">
@@ -2636,24 +2608,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>검사7호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bella-Contour_중사각</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>184</v>
+        <v>3309</v>
       </c>
       <c r="G40" t="n">
-        <v>9</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41">
@@ -2669,24 +2641,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>검사7호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>US55-2(M)_소사각</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2060</v>
+        <v>1948</v>
       </c>
       <c r="G41" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
@@ -2707,19 +2679,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>S38_은캡(BLUE TINT)</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>4246</v>
+        <v>1578</v>
       </c>
       <c r="G42" t="n">
-        <v>66</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43">
@@ -2735,24 +2707,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>748</v>
+        <v>632</v>
       </c>
       <c r="G43" t="n">
-        <v>42</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44">
@@ -2768,24 +2740,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>T38_금캡(UV포함)</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2108</v>
+        <v>640</v>
       </c>
       <c r="G44" t="n">
-        <v>11</v>
+        <v>147</v>
       </c>
     </row>
     <row r="45">
@@ -2801,24 +2773,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>Silicone relax_소사각</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1550</v>
+        <v>8446</v>
       </c>
       <c r="G45" t="n">
-        <v>218</v>
+        <v>660</v>
       </c>
     </row>
     <row r="46">
@@ -2834,24 +2806,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>990</v>
+        <v>2882</v>
       </c>
       <c r="G46" t="n">
-        <v>10</v>
+        <v>469</v>
       </c>
     </row>
     <row r="47">
@@ -2867,24 +2839,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>2907</v>
       </c>
       <c r="G47" t="n">
-        <v>1050</v>
+        <v>548</v>
       </c>
     </row>
     <row r="48">
@@ -2900,24 +2872,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>Si_FRP_Toric</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Metha_55_금캡</t>
+          <t>O2O2 M_UV_Toric_SMD_(소)</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1068</v>
+        <v>306</v>
       </c>
       <c r="G48" t="n">
-        <v>230</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49">
@@ -2933,420 +2905,420 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>Si_FRP_Toric</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>O2O2 M_UV_Toric_SMD_(소)</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="G49" t="n">
-        <v>119</v>
+        <v>461</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>조립10호기</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>368</v>
+        <v>29489</v>
       </c>
       <c r="G50" t="n">
-        <v>28</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>조립11호기</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>290</v>
+        <v>18455</v>
       </c>
       <c r="G51" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>조립12호기</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>T38_금캡</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>514</v>
+        <v>59017</v>
       </c>
       <c r="G52" t="n">
-        <v>61</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>조립13호기</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>T38_금캡(UV포함)</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1695</v>
+        <v>51545</v>
       </c>
       <c r="G53" t="n">
-        <v>384</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Si_FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>조립14호기</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>O2O2 M_Mysti Gray EX_(중)</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>80</v>
+        <v>25160</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Si_FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>조립15호기</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>O2O2 M_Natural Brown EX_(중)</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>52</v>
+        <v>27941</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Si_FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>조립16호기</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>O2O2 M_Natural Gray EX_(중)</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>56</v>
+        <v>26948</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>338</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>조립20호기</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Silicone relax_소사각</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2963</v>
+        <v>26029</v>
       </c>
       <c r="G57" t="n">
-        <v>387</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>조립24호기</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2584</v>
+        <v>25559</v>
       </c>
       <c r="G58" t="n">
-        <v>492</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>조립25호기</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>5754</v>
+        <v>27067</v>
       </c>
       <c r="G59" t="n">
-        <v>395</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Si_FRP_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>조립26호기</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>O2O2 M_UV_Toric_SMD_(소)</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1776</v>
+        <v>23807</v>
       </c>
       <c r="G60" t="n">
-        <v>236</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Si_FRP_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>조립40호기</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>O2O2 M_UV_Toric_SMD_(소)</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>403</v>
+        <v>25284</v>
       </c>
       <c r="G61" t="n">
-        <v>67</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="62">
@@ -3367,19 +3339,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>조립10호기</t>
+          <t>조립47호기</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>5133</v>
+        <v>62637</v>
       </c>
       <c r="G62" t="n">
-        <v>2224</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="63">
@@ -3400,19 +3372,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>조립11호기</t>
+          <t>조립48호기</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>51239</v>
+        <v>28743</v>
       </c>
       <c r="G63" t="n">
-        <v>6611</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="64">
@@ -3433,19 +3405,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>조립12호기</t>
+          <t>조립49호기</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>25902</v>
+        <v>23137</v>
       </c>
       <c r="G64" t="n">
-        <v>1592</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="65">
@@ -3466,19 +3438,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>조립13호기</t>
+          <t>조립50호기</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>23337</v>
+        <v>45611</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="66">
@@ -3499,19 +3471,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>조립14호기</t>
+          <t>조립51호기</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>27377</v>
+        <v>46313</v>
       </c>
       <c r="G66" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="67">
@@ -3532,19 +3504,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>조립15호기</t>
+          <t>조립52호기</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>28304</v>
+        <v>28458</v>
       </c>
       <c r="G67" t="n">
-        <v>444</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="68">
@@ -3565,19 +3537,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>조립16호기</t>
+          <t>조립54호기</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Grege Quartz 38% UV</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>23426</v>
+        <v>25781</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>884</v>
       </c>
     </row>
     <row r="69">
@@ -3598,19 +3570,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>조립20호기</t>
+          <t>조립55호기</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA D_Jelly Gray_38% UV</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>9983</v>
+        <v>25481</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="70">
@@ -3631,19 +3603,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>조립25호기</t>
+          <t>조립56호기</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>25301</v>
+        <v>23590</v>
       </c>
       <c r="G70" t="n">
-        <v>829</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="71">
@@ -3664,19 +3636,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>조립26호기</t>
+          <t>조립58호기</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Cherish Brown_55% UV 14.2</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>29524</v>
+        <v>29840</v>
       </c>
       <c r="G71" t="n">
-        <v>1100</v>
+        <v>866</v>
       </c>
     </row>
     <row r="72">
@@ -3697,19 +3669,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>조립27호기</t>
+          <t>조립59호기</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>BELLA D_VENUS 55%</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>24730</v>
+        <v>50979</v>
       </c>
       <c r="G72" t="n">
-        <v>1621</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="73">
@@ -3725,24 +3697,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>조립40호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>48038</v>
+        <v>18323</v>
       </c>
       <c r="G73" t="n">
-        <v>5642</v>
+        <v>508</v>
       </c>
     </row>
     <row r="74">
@@ -3758,24 +3730,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>조립44호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>22488</v>
+        <v>17989</v>
       </c>
       <c r="G74" t="n">
-        <v>188</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="75">
@@ -3791,24 +3763,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>조립45호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>30926</v>
+        <v>4825</v>
       </c>
       <c r="G75" t="n">
-        <v>1230</v>
+        <v>751</v>
       </c>
     </row>
     <row r="76">
@@ -3824,24 +3796,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>조립46호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Toric_CP-0.75_Halo Gray</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>30215</v>
+        <v>7494</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
     </row>
     <row r="77">
@@ -3857,21 +3829,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>조립47호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>Toric_CP-1.25_Halo Gray</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>29481</v>
+        <v>7382</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -3890,24 +3862,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>조립48호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>28305</v>
+        <v>33776</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="79">
@@ -3923,24 +3895,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>조립49호기</t>
+          <t>조립45호기</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>26387</v>
+        <v>33347</v>
       </c>
       <c r="G79" t="n">
-        <v>1900</v>
+        <v>7802</v>
       </c>
     </row>
     <row r="80">
@@ -3956,24 +3928,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>조립50호기</t>
+          <t>조립46호기</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Gray Bunny_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>61010</v>
+        <v>39841</v>
       </c>
       <c r="G80" t="n">
-        <v>160</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="81">
@@ -3984,7 +3956,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3994,19 +3966,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>조립51호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PIA D_Cherish Brown_55% UV 14.2</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>10469</v>
+        <v>10867</v>
       </c>
       <c r="G81" t="n">
-        <v>1500</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="82">
@@ -4017,7 +3989,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4027,19 +3999,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>조립52호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>47720</v>
+        <v>11846</v>
       </c>
       <c r="G82" t="n">
-        <v>4380</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="83">
@@ -4050,7 +4022,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4060,19 +4032,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>조립55호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PIA D_Pomme Canele_38% UV</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>24267</v>
+        <v>10852</v>
       </c>
       <c r="G83" t="n">
-        <v>1800</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="84">
@@ -4083,7 +4055,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4093,19 +4065,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>조립57호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>23659</v>
+        <v>16696</v>
       </c>
       <c r="G84" t="n">
-        <v>434</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="85">
@@ -4116,7 +4088,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4126,19 +4098,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>조립58호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>52422</v>
+        <v>5584</v>
       </c>
       <c r="G85" t="n">
-        <v>23</v>
+        <v>995</v>
       </c>
     </row>
     <row r="86">
@@ -4149,29 +4121,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>9835</v>
+        <v>23406</v>
       </c>
       <c r="G86" t="n">
-        <v>1100</v>
+        <v>4281</v>
       </c>
     </row>
     <row r="87">
@@ -4182,29 +4154,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>5420</v>
+        <v>30892</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>3264</v>
       </c>
     </row>
     <row r="88">
@@ -4215,29 +4187,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>5478</v>
+        <v>13241</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="89">
@@ -4248,29 +4220,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Gray</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>2508</v>
+        <v>11038</v>
       </c>
       <c r="G89" t="n">
-        <v>652</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="90">
@@ -4281,29 +4253,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Gray</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>11004</v>
+        <v>42101</v>
       </c>
       <c r="G90" t="n">
-        <v>1657</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="91">
@@ -4314,29 +4286,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>BELLA D_VENUS 55%</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>8993</v>
+        <v>17113</v>
       </c>
       <c r="G91" t="n">
-        <v>496</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="92">
@@ -4347,29 +4319,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>조립24호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>15405</v>
+        <v>29595</v>
       </c>
       <c r="G92" t="n">
-        <v>250</v>
+        <v>4693</v>
       </c>
     </row>
     <row r="93">
@@ -4380,29 +4352,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>조립24호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>PIA_Brown Fondue CP-1.25 Toric_UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>5252</v>
+        <v>15718</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>3799</v>
       </c>
     </row>
     <row r="94">
@@ -4413,29 +4385,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>조립53호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>FLAMINGO_PIA_M(Y)</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>9976</v>
+        <v>23835</v>
       </c>
       <c r="G94" t="n">
-        <v>3950</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="95">
@@ -4456,7 +4428,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4465,10 +4437,10 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>44226</v>
+        <v>23814</v>
       </c>
       <c r="G95" t="n">
-        <v>4572</v>
+        <v>4111</v>
       </c>
     </row>
     <row r="96">
@@ -4489,19 +4461,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>5366</v>
+        <v>45201</v>
       </c>
       <c r="G96" t="n">
-        <v>569</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="97">
@@ -4522,19 +4494,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>41742</v>
+        <v>19250</v>
       </c>
       <c r="G97" t="n">
-        <v>4886</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="98">
@@ -4555,19 +4527,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>5615</v>
+        <v>7739</v>
       </c>
       <c r="G98" t="n">
-        <v>938</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="99">
@@ -4588,19 +4560,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>19196</v>
+        <v>9492</v>
       </c>
       <c r="G99" t="n">
-        <v>2665</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="100">
@@ -4621,19 +4593,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
+          <t>HAPA(PIA) D_One&amp;Only Kristin Plus Brown 14.2_38%</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>13194</v>
+        <v>10214</v>
       </c>
       <c r="G100" t="n">
-        <v>1579</v>
+        <v>4465</v>
       </c>
     </row>
     <row r="101">
@@ -4654,19 +4626,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PIA D_Teddy Brown_55% UV</t>
+          <t>PIA D_Puree Greige_38% UV</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>6168</v>
+        <v>12424</v>
       </c>
       <c r="G101" t="n">
-        <v>565</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="102">
@@ -4687,19 +4659,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>18508</v>
+        <v>23829</v>
       </c>
       <c r="G102" t="n">
-        <v>3002</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="103">
@@ -4720,19 +4692,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>BELLA D_MARS 55%</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>5028</v>
+        <v>3503</v>
       </c>
       <c r="G103" t="n">
-        <v>1447</v>
+        <v>315</v>
       </c>
     </row>
     <row r="104">
@@ -4753,19 +4725,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PIA D_Dorayaki_55% UV</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>8365</v>
+        <v>24337</v>
       </c>
       <c r="G104" t="n">
-        <v>1371</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="105">
@@ -4786,7 +4758,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4795,10 +4767,10 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>15475</v>
+        <v>6206</v>
       </c>
       <c r="G105" t="n">
-        <v>2718</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="106">
@@ -4819,19 +4791,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>분리43호기</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Rina_Crystal Gray_1-Day</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1863</v>
+        <v>11891</v>
       </c>
       <c r="G106" t="n">
-        <v>194</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="107">
@@ -4852,19 +4824,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>분리19호기</t>
+          <t>분리43호기</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Cherish Brown_55% UV 14.2</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>16158</v>
+        <v>19400</v>
       </c>
       <c r="G107" t="n">
-        <v>2187</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="108">
@@ -4880,24 +4852,24 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>분리19호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>27596</v>
+        <v>2711</v>
       </c>
       <c r="G108" t="n">
-        <v>2664</v>
+        <v>582</v>
       </c>
     </row>
     <row r="109">
@@ -4913,24 +4885,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA_Brown Fondue CP-1.25 Toric_UV</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>39050</v>
+        <v>3695</v>
       </c>
       <c r="G109" t="n">
-        <v>5741</v>
+        <v>843</v>
       </c>
     </row>
     <row r="110">
@@ -4946,24 +4918,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>4003</v>
+        <v>3015</v>
       </c>
       <c r="G110" t="n">
-        <v>1077</v>
+        <v>434</v>
       </c>
     </row>
     <row r="111">
@@ -4979,24 +4951,24 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Toric_CP-0.75_Halo Gray</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>23039</v>
+        <v>2593</v>
       </c>
       <c r="G111" t="n">
-        <v>2230</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="112">
@@ -5012,24 +4984,24 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>19958</v>
+        <v>11291</v>
       </c>
       <c r="G112" t="n">
-        <v>1672</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="113">
@@ -5045,24 +5017,24 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>45333</v>
+        <v>2803</v>
       </c>
       <c r="G113" t="n">
-        <v>3397</v>
+        <v>657</v>
       </c>
     </row>
     <row r="114">
@@ -5078,24 +5050,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>39778</v>
+        <v>9172</v>
       </c>
       <c r="G114" t="n">
-        <v>4951</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="115">
@@ -5111,24 +5083,24 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D Toric_CP-0.75 Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>37871</v>
+        <v>1738</v>
       </c>
       <c r="G115" t="n">
-        <v>7093</v>
+        <v>313</v>
       </c>
     </row>
     <row r="116">
@@ -5144,24 +5116,24 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>9616</v>
+        <v>1607</v>
       </c>
       <c r="G116" t="n">
-        <v>944</v>
+        <v>3998</v>
       </c>
     </row>
     <row r="117">
@@ -5177,24 +5149,24 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>23112</v>
+        <v>9613</v>
       </c>
       <c r="G117" t="n">
-        <v>3189</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="118">
@@ -5210,24 +5182,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Alcon D_Chic Smoke_W4</t>
+          <t>PIA_Brown Fondue CP-1.25 Toric_UV</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1667</v>
+        <v>1341</v>
       </c>
       <c r="G118" t="n">
-        <v>178</v>
+        <v>395</v>
       </c>
     </row>
     <row r="119">
@@ -5243,24 +5215,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>PIA_Opal CP-0.75 Toric_UV</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>15747</v>
+        <v>3872</v>
       </c>
       <c r="G119" t="n">
-        <v>1474</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="120">
@@ -5276,24 +5248,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA_Opal CP-1.25 Toric_UV</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>4880</v>
+        <v>1108</v>
       </c>
       <c r="G120" t="n">
-        <v>497</v>
+        <v>269</v>
       </c>
     </row>
     <row r="121">
@@ -5309,24 +5281,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리22호기</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>PIA D_Cherish Brown_55% UV 14.2</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>9702</v>
+        <v>40625</v>
       </c>
       <c r="G121" t="n">
-        <v>767</v>
+        <v>6518</v>
       </c>
     </row>
     <row r="122">
@@ -5342,24 +5314,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리23호기</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>26455</v>
+        <v>40406</v>
       </c>
       <c r="G122" t="n">
-        <v>4095</v>
+        <v>9071</v>
       </c>
     </row>
     <row r="123">
@@ -5375,24 +5347,24 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리25호기</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>34042</v>
+        <v>44955</v>
       </c>
       <c r="G123" t="n">
-        <v>2615</v>
+        <v>9447</v>
       </c>
     </row>
     <row r="124">
@@ -5408,24 +5380,24 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>15414</v>
+        <v>4406</v>
       </c>
       <c r="G124" t="n">
-        <v>1775</v>
+        <v>966</v>
       </c>
     </row>
     <row r="125">
@@ -5441,24 +5413,24 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>PIA D_Sugar Donut_38% UV</t>
+          <t>FLAMINGO_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>12475</v>
+        <v>1533</v>
       </c>
       <c r="G125" t="n">
-        <v>2758</v>
+        <v>218</v>
       </c>
     </row>
     <row r="126">
@@ -5474,24 +5446,24 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>Gray Bunny_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>22892</v>
+        <v>3968</v>
       </c>
       <c r="G126" t="n">
-        <v>2995</v>
+        <v>545</v>
       </c>
     </row>
     <row r="127">
@@ -5502,7 +5474,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5512,19 +5484,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sincere D_Air Beige_ITFA_38% UV</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>4443</v>
+        <v>2885</v>
       </c>
       <c r="G127" t="n">
-        <v>1655</v>
+        <v>140</v>
       </c>
     </row>
     <row r="128">
@@ -5535,7 +5507,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5545,19 +5517,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1520</v>
+        <v>4435</v>
       </c>
       <c r="G128" t="n">
-        <v>192</v>
+        <v>430</v>
       </c>
     </row>
     <row r="129">
@@ -5568,7 +5540,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5578,19 +5550,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>BELLA_1-Day_Hazel Honey</t>
+          <t>PIA D_Teddy Brown_55% UV</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>12114</v>
+        <v>5980</v>
       </c>
       <c r="G129" t="n">
-        <v>882</v>
+        <v>350</v>
       </c>
     </row>
     <row r="130">
@@ -5601,7 +5573,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5611,19 +5583,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>23112</v>
+        <v>8855</v>
       </c>
       <c r="G130" t="n">
-        <v>1703</v>
+        <v>695</v>
       </c>
     </row>
     <row r="131">
@@ -5634,7 +5606,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5644,19 +5616,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA_LILY BLACK</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>20787</v>
+        <v>2915</v>
       </c>
       <c r="G131" t="n">
-        <v>3084</v>
+        <v>125</v>
       </c>
     </row>
     <row r="132">
@@ -5667,7 +5639,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5677,19 +5649,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>24572</v>
+        <v>3240</v>
       </c>
       <c r="G132" t="n">
-        <v>1985</v>
+        <v>225</v>
       </c>
     </row>
     <row r="133">
@@ -5700,7 +5672,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5710,19 +5682,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA_Tulle Brown_1D_55%_14.2</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>41567</v>
+        <v>845</v>
       </c>
       <c r="G133" t="n">
-        <v>4253</v>
+        <v>210</v>
       </c>
     </row>
     <row r="134">
@@ -5733,7 +5705,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5743,19 +5715,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>분리43호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>18969</v>
+        <v>9080</v>
       </c>
       <c r="G134" t="n">
-        <v>3054</v>
+        <v>375</v>
       </c>
     </row>
     <row r="135">
@@ -5766,7 +5738,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5776,19 +5748,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>분리43호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>24481</v>
+        <v>2956</v>
       </c>
       <c r="G135" t="n">
-        <v>2577</v>
+        <v>464</v>
       </c>
     </row>
     <row r="136">
@@ -5799,29 +5771,29 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-0.75 Brown Bunny_55% UV</t>
+          <t>PIA D_Dorayaki_55% UV</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>2722</v>
+        <v>2845</v>
       </c>
       <c r="G136" t="n">
-        <v>661</v>
+        <v>40</v>
       </c>
     </row>
     <row r="137">
@@ -5832,29 +5804,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
+          <t>PIA D_Teddy Brown_55% UV</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>2403</v>
+        <v>6055</v>
       </c>
       <c r="G137" t="n">
-        <v>2192</v>
+        <v>90</v>
       </c>
     </row>
     <row r="138">
@@ -5865,29 +5837,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>10366</v>
+        <v>6065</v>
       </c>
       <c r="G138" t="n">
-        <v>1616</v>
+        <v>445</v>
       </c>
     </row>
     <row r="139">
@@ -5898,29 +5870,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>18897</v>
+        <v>2285</v>
       </c>
       <c r="G139" t="n">
-        <v>3139</v>
+        <v>30</v>
       </c>
     </row>
     <row r="140">
@@ -5931,29 +5903,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>PIA_Cider_1-DAY 55%</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>5675</v>
+        <v>2780</v>
       </c>
       <c r="G140" t="n">
-        <v>1106</v>
+        <v>315</v>
       </c>
     </row>
     <row r="141">
@@ -5964,29 +5936,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>PIA D Toric CP-0.75_Dollish Brown_55% UV</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>608</v>
+        <v>3170</v>
       </c>
       <c r="G141" t="n">
-        <v>308</v>
+        <v>245</v>
       </c>
     </row>
     <row r="142">
@@ -5997,29 +5969,29 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-1.25 Dollish Gray_55% UV</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1769</v>
+        <v>3962</v>
       </c>
       <c r="G142" t="n">
-        <v>519</v>
+        <v>363</v>
       </c>
     </row>
     <row r="143">
@@ -6030,29 +6002,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>PIA_Opal CP-0.75 Toric_UV</t>
+          <t>PIA_Tulle Brown_1D_55%_14.2</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>12289</v>
+        <v>863</v>
       </c>
       <c r="G143" t="n">
-        <v>2442</v>
+        <v>207</v>
       </c>
     </row>
     <row r="144">
@@ -6063,29 +6035,29 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>PIA_Opal CP-1.25 Toric_UV</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>4802</v>
+        <v>6145</v>
       </c>
       <c r="G144" t="n">
-        <v>941</v>
+        <v>75</v>
       </c>
     </row>
     <row r="145">
@@ -6096,29 +6068,29 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Gray</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>11762</v>
+        <v>4610</v>
       </c>
       <c r="G145" t="n">
-        <v>3803</v>
+        <v>75</v>
       </c>
     </row>
     <row r="146">
@@ -6129,29 +6101,29 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>9537</v>
+        <v>10385</v>
       </c>
       <c r="G146" t="n">
-        <v>2492</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="147">
@@ -6162,29 +6134,29 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>분리22호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>32529</v>
+        <v>3380</v>
       </c>
       <c r="G147" t="n">
-        <v>6194</v>
+        <v>40</v>
       </c>
     </row>
     <row r="148">
@@ -6195,29 +6167,29 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>분리23호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>26386</v>
+        <v>12055</v>
       </c>
       <c r="G148" t="n">
-        <v>6849</v>
+        <v>225</v>
       </c>
     </row>
     <row r="149">
@@ -6228,29 +6200,29 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>분리25호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA_Matcha Latte_55%_1-DAY</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>43543</v>
+        <v>1320</v>
       </c>
       <c r="G149" t="n">
-        <v>8232</v>
+        <v>15</v>
       </c>
     </row>
     <row r="150">
@@ -6261,29 +6233,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2108</v>
+        <v>2925</v>
       </c>
       <c r="G150" t="n">
-        <v>169</v>
+        <v>25</v>
       </c>
     </row>
     <row r="151">
@@ -6294,29 +6266,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Coral Brown_2T_(PBT)PIA_M</t>
+          <t>PIA_Tulle Brown_1D_55%_14.2</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>4591</v>
+        <v>2725</v>
       </c>
       <c r="G151" t="n">
-        <v>4849</v>
+        <v>55</v>
       </c>
     </row>
     <row r="152">
@@ -6327,29 +6299,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
+          <t>BELLA D_MARS 55%</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>11653</v>
+        <v>12313</v>
       </c>
       <c r="G152" t="n">
-        <v>3629</v>
+        <v>567</v>
       </c>
     </row>
     <row r="153">
@@ -6370,19 +6342,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>BELLA D_Siren Bronze 55%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>6192</v>
+        <v>12615</v>
       </c>
       <c r="G153" t="n">
-        <v>248</v>
+        <v>175</v>
       </c>
     </row>
     <row r="154">
@@ -6403,19 +6375,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>PIA D_Cherish Brown_55% UV 14.2</t>
+          <t>BELLA D_VENUS 55%</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1620</v>
+        <v>18790</v>
       </c>
       <c r="G154" t="n">
-        <v>45</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="155">
@@ -6436,19 +6408,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1435</v>
+        <v>7830</v>
       </c>
       <c r="G155" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
     </row>
     <row r="156">
@@ -6469,19 +6441,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>PIA D_Teddy Brown_55% UV</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>3290</v>
+        <v>3110</v>
       </c>
       <c r="G156" t="n">
-        <v>95</v>
+        <v>35</v>
       </c>
     </row>
     <row r="157">
@@ -6502,19 +6474,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>2010</v>
+        <v>1470</v>
       </c>
       <c r="G157" t="n">
-        <v>135</v>
+        <v>35</v>
       </c>
     </row>
     <row r="158">
@@ -6535,19 +6507,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>PIA_Cider_1-DAY 55%</t>
+          <t>PIA D_Dorayaki_55% UV</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>550</v>
+        <v>5944</v>
       </c>
       <c r="G158" t="n">
-        <v>10</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="159">
@@ -6568,16 +6540,16 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>PIA_Coconut_55%_1-DAY</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1070</v>
+        <v>2675</v>
       </c>
       <c r="G159" t="n">
         <v>20</v>
@@ -6601,19 +6573,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>PIA_KEOPI BROWN</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>2810</v>
+        <v>4000</v>
       </c>
       <c r="G160" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
     </row>
     <row r="161">
@@ -6634,19 +6606,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>PIA_LILY BLACK</t>
+          <t>PIA_KEOPI BROWN</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>3340</v>
+        <v>8850</v>
       </c>
       <c r="G161" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="162">
@@ -6667,19 +6639,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>PIA_MS5 Tint Brown_1T</t>
+          <t>PIA_LILY BLACK</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1440</v>
+        <v>5145</v>
       </c>
       <c r="G162" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="163">
@@ -6700,19 +6672,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>3755</v>
+        <v>7525</v>
       </c>
       <c r="G163" t="n">
-        <v>50</v>
+        <v>215</v>
       </c>
     </row>
     <row r="164">
@@ -6733,19 +6705,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>PIA D_Teddy Brown_55% UV</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>8355</v>
+        <v>10585</v>
       </c>
       <c r="G164" t="n">
-        <v>195</v>
+        <v>130</v>
       </c>
     </row>
     <row r="165">
@@ -6766,19 +6738,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA_Tulle Brown_1D_55%_14.2</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>5680</v>
+        <v>2273</v>
       </c>
       <c r="G165" t="n">
-        <v>75</v>
+        <v>407</v>
       </c>
     </row>
     <row r="166">
@@ -6799,19 +6771,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>PIA_BROWN MANEGE</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>6760</v>
+        <v>18745</v>
       </c>
       <c r="G166" t="n">
-        <v>105</v>
+        <v>415</v>
       </c>
     </row>
     <row r="167">
@@ -6832,19 +6804,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>PIA_Cider_1-DAY 55%</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>4330</v>
+        <v>18839</v>
       </c>
       <c r="G167" t="n">
-        <v>95</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="168">
@@ -6865,19 +6837,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PIA_Coconut_55%_1-DAY</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>970</v>
+        <v>2507</v>
       </c>
       <c r="G168" t="n">
-        <v>25</v>
+        <v>583</v>
       </c>
     </row>
     <row r="169">
@@ -6898,19 +6870,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PIA_LILY BLACK</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>3315</v>
+        <v>1235</v>
       </c>
       <c r="G169" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
     </row>
     <row r="170">
@@ -6931,19 +6903,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>PIA_MS4 Mirror Gray_3T</t>
+          <t>PIA D_Dorayaki_55% UV</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>815</v>
+        <v>4455</v>
       </c>
       <c r="G170" t="n">
-        <v>40</v>
+        <v>125</v>
       </c>
     </row>
     <row r="171">
@@ -6964,19 +6936,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PIA_MS5 Tint Brown_1T</t>
+          <t>PIA D_Teddy Brown_55% UV</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>3640</v>
+        <v>5955</v>
       </c>
       <c r="G171" t="n">
-        <v>2265</v>
+        <v>80</v>
       </c>
     </row>
     <row r="172">
@@ -6997,19 +6969,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>17225</v>
+        <v>8205</v>
       </c>
       <c r="G172" t="n">
-        <v>200</v>
+        <v>145</v>
       </c>
     </row>
     <row r="173">
@@ -7030,19 +7002,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>30770</v>
+        <v>2610</v>
       </c>
       <c r="G173" t="n">
-        <v>765</v>
+        <v>60</v>
       </c>
     </row>
     <row r="174">
@@ -7063,19 +7035,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>BELLA D_MARS 55%</t>
+          <t>PIA_KEOPI BROWN</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>19493</v>
+        <v>3055</v>
       </c>
       <c r="G174" t="n">
-        <v>2072</v>
+        <v>55</v>
       </c>
     </row>
     <row r="175">
@@ -7096,19 +7068,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>BELLA D_Siren Bronze 55%</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>23052</v>
+        <v>3395</v>
       </c>
       <c r="G175" t="n">
-        <v>2658</v>
+        <v>80</v>
       </c>
     </row>
     <row r="176">
@@ -7129,19 +7101,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>BELLA D_VENUS 55%</t>
+          <t>PIA_Tulle Brown_1D_55%_14.2</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>7580</v>
+        <v>15085</v>
       </c>
       <c r="G176" t="n">
-        <v>150</v>
+        <v>465</v>
       </c>
     </row>
     <row r="177">
@@ -7162,19 +7134,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>12870</v>
+        <v>2610</v>
       </c>
       <c r="G177" t="n">
-        <v>750</v>
+        <v>40</v>
       </c>
     </row>
     <row r="178">
@@ -7195,19 +7167,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>PIA D_Gray Bunny_55% UV 14.2</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1465</v>
+        <v>19866</v>
       </c>
       <c r="G178" t="n">
-        <v>15</v>
+        <v>834</v>
       </c>
     </row>
     <row r="179">
@@ -7228,19 +7200,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>PIA D_MELON PAN_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>2875</v>
+        <v>32367</v>
       </c>
       <c r="G179" t="n">
-        <v>55</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="180">
@@ -7261,19 +7233,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1435</v>
+        <v>5860</v>
       </c>
       <c r="G180" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
     </row>
     <row r="181">
@@ -7294,19 +7266,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Smore_55% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2085</v>
+        <v>15440</v>
       </c>
       <c r="G181" t="n">
-        <v>45</v>
+        <v>285</v>
       </c>
     </row>
     <row r="182">
@@ -7327,19 +7299,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>PIA D_Teddy Brown_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>975</v>
+        <v>31402</v>
       </c>
       <c r="G182" t="n">
-        <v>25</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="183">
@@ -7360,19 +7332,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>4973</v>
+        <v>17200</v>
       </c>
       <c r="G183" t="n">
-        <v>1042</v>
+        <v>990</v>
       </c>
     </row>
     <row r="184">
@@ -7393,19 +7365,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PIA_BROWN MANEGE</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3400</v>
+        <v>14465</v>
       </c>
       <c r="G184" t="n">
-        <v>55</v>
+        <v>115</v>
       </c>
     </row>
     <row r="185">
@@ -7426,19 +7398,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>PIA_Cider_1-DAY 55%</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1560</v>
+        <v>8150</v>
       </c>
       <c r="G185" t="n">
-        <v>10</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="186">
@@ -7459,19 +7431,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>PIA_Coconut_55%_1-DAY</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>3840</v>
+        <v>5858</v>
       </c>
       <c r="G186" t="n">
-        <v>50</v>
+        <v>327</v>
       </c>
     </row>
     <row r="187">
@@ -7492,19 +7464,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>PIA_LILY BLACK</t>
+          <t>PIA D_Cherish Brown_55% UV 14.2</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>4495</v>
+        <v>1575</v>
       </c>
       <c r="G187" t="n">
-        <v>575</v>
+        <v>20</v>
       </c>
     </row>
     <row r="188">
@@ -7525,19 +7497,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>PIA_MS5 Tint Brown_1T</t>
+          <t>PIA D_Dollish Brown_55% UV</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>6989</v>
+        <v>2680</v>
       </c>
       <c r="G188" t="n">
-        <v>631</v>
+        <v>80</v>
       </c>
     </row>
     <row r="189">
@@ -7558,19 +7530,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>PIA D_Dorayaki_55% UV</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>3395</v>
+        <v>1240</v>
       </c>
       <c r="G189" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
     </row>
     <row r="190">
@@ -7591,19 +7563,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Teddy Brown_55% UV</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>27494</v>
+        <v>2630</v>
       </c>
       <c r="G190" t="n">
-        <v>2136</v>
+        <v>70</v>
       </c>
     </row>
     <row r="191">
@@ -7624,19 +7596,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>17445</v>
+        <v>9840</v>
       </c>
       <c r="G191" t="n">
-        <v>365</v>
+        <v>160</v>
       </c>
     </row>
     <row r="192">
@@ -7657,19 +7629,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>13044</v>
+        <v>13945</v>
       </c>
       <c r="G192" t="n">
-        <v>731</v>
+        <v>240</v>
       </c>
     </row>
     <row r="193">
@@ -7690,19 +7662,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>PIA D_Cherish Brown_55% UV 14.2</t>
+          <t>PIA_BROWN MANEGE</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>4865</v>
+        <v>1905</v>
       </c>
       <c r="G193" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="194">
@@ -7723,19 +7695,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>3620</v>
+        <v>2017</v>
       </c>
       <c r="G194" t="n">
-        <v>50</v>
+        <v>408</v>
       </c>
     </row>
     <row r="195">
@@ -7756,19 +7728,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>PIA D_Dorayaki_55% UV</t>
+          <t>PIA_Matcha Latte_55%_1-DAY</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>3120</v>
+        <v>6200</v>
       </c>
       <c r="G195" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
     </row>
     <row r="196">
@@ -7789,19 +7761,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Smore_55% UV</t>
+          <t>PIA_SARANG BROWN</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>2200</v>
+        <v>2465</v>
       </c>
       <c r="G196" t="n">
-        <v>30</v>
+        <v>135</v>
       </c>
     </row>
     <row r="197">
@@ -7822,19 +7794,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>PIA D_Teddy Brown_55% UV</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>995</v>
+        <v>47184</v>
       </c>
       <c r="G197" t="n">
-        <v>25</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="198">
@@ -7855,19 +7827,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>6832</v>
+        <v>1930</v>
       </c>
       <c r="G198" t="n">
-        <v>813</v>
+        <v>35</v>
       </c>
     </row>
     <row r="199">
@@ -7888,19 +7860,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>PIA_BROWN MANEGE</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1690</v>
+        <v>6460</v>
       </c>
       <c r="G199" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="200">
@@ -7921,19 +7893,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>PIA_Coconut_55%_1-DAY</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>3610</v>
+        <v>7770</v>
       </c>
       <c r="G200" t="n">
-        <v>55</v>
+        <v>135</v>
       </c>
     </row>
     <row r="201">
@@ -7954,19 +7926,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>PIA_LILY BLACK</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>2680</v>
+        <v>11925</v>
       </c>
       <c r="G201" t="n">
-        <v>55</v>
+        <v>140</v>
       </c>
     </row>
     <row r="202">
@@ -7987,19 +7959,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>PIA_MS5 Tint Brown_1T</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>10332</v>
+        <v>6290</v>
       </c>
       <c r="G202" t="n">
-        <v>1718</v>
+        <v>105</v>
       </c>
     </row>
     <row r="203">
@@ -8020,19 +7992,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>PIA_Tulle Brown_1D_55%_14.2</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1045</v>
+        <v>9380</v>
       </c>
       <c r="G203" t="n">
-        <v>50</v>
+        <v>905</v>
       </c>
     </row>
     <row r="204">
@@ -8053,19 +8025,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA_Matcha Latte_55%_1-DAY</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>30726</v>
+        <v>3800</v>
       </c>
       <c r="G204" t="n">
-        <v>1799</v>
+        <v>80</v>
       </c>
     </row>
     <row r="205">
@@ -8086,19 +8058,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA_SARANG BROWN</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>20991</v>
+        <v>3095</v>
       </c>
       <c r="G205" t="n">
-        <v>1049</v>
+        <v>150</v>
       </c>
     </row>
     <row r="206">
@@ -8119,19 +8091,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>5470</v>
+        <v>11970</v>
       </c>
       <c r="G206" t="n">
-        <v>130</v>
+        <v>245</v>
       </c>
     </row>
     <row r="207">
@@ -8152,19 +8124,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>21295</v>
+        <v>4645</v>
       </c>
       <c r="G207" t="n">
-        <v>390</v>
+        <v>270</v>
       </c>
     </row>
     <row r="208">
@@ -8185,19 +8157,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>BELLA_1-Day_Hazel Honey(8년)</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>18535</v>
+        <v>7990</v>
       </c>
       <c r="G208" t="n">
-        <v>310</v>
+        <v>220</v>
       </c>
     </row>
     <row r="209">
@@ -8218,19 +8190,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Clalen D_FUGUANG(GRAY)55%(TW)</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>2765</v>
+        <v>28205</v>
       </c>
       <c r="G209" t="n">
-        <v>15</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="210">
@@ -8251,19 +8223,19 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Clalen D_FUGUANG_55%</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>3386</v>
+        <v>3438</v>
       </c>
       <c r="G210" t="n">
-        <v>554</v>
+        <v>247</v>
       </c>
     </row>
     <row r="211">
@@ -8284,19 +8256,19 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>36820</v>
+        <v>1718</v>
       </c>
       <c r="G211" t="n">
-        <v>3820</v>
+        <v>842</v>
       </c>
     </row>
     <row r="212">
@@ -8317,19 +8289,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>10490</v>
+        <v>18567</v>
       </c>
       <c r="G212" t="n">
-        <v>220</v>
+        <v>673</v>
       </c>
     </row>
     <row r="213">
@@ -8350,19 +8322,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>4019</v>
+        <v>3845</v>
       </c>
       <c r="G213" t="n">
-        <v>346</v>
+        <v>175</v>
       </c>
     </row>
     <row r="214">
@@ -8383,19 +8355,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>PIA D_Cherish Brown_55% UV 14.2</t>
+          <t>PIA_Tulle Brown_1D_55%_14.2</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>2295</v>
+        <v>3680</v>
       </c>
       <c r="G214" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="215">
@@ -8411,24 +8383,24 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Smore_55% UV</t>
+          <t>PIA D Toric_CP-0.75 Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>2220</v>
+        <v>4510</v>
       </c>
       <c r="G215" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
     </row>
     <row r="216">
@@ -8444,24 +8416,24 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>PIA D_Teddy Brown_55% UV</t>
+          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>8835</v>
+        <v>5960</v>
       </c>
       <c r="G216" t="n">
-        <v>185</v>
+        <v>320</v>
       </c>
     </row>
     <row r="217">
@@ -8477,24 +8449,24 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>0</v>
+        <v>9055</v>
       </c>
       <c r="G217" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
     </row>
     <row r="218">
@@ -8510,24 +8482,24 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>Toric_CP-1.25_Halo Gray</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>5895</v>
+        <v>3719</v>
       </c>
       <c r="G218" t="n">
-        <v>75</v>
+        <v>706</v>
       </c>
     </row>
     <row r="219">
@@ -8543,24 +8515,24 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>PIA_Cider_1-DAY 55%</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1895</v>
+        <v>2765</v>
       </c>
       <c r="G219" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="220">
@@ -8576,24 +8548,24 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>PIA_Coconut_55%_1-DAY</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1830</v>
+        <v>4274</v>
       </c>
       <c r="G220" t="n">
-        <v>10</v>
+        <v>3141</v>
       </c>
     </row>
     <row r="221">
@@ -8609,24 +8581,24 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>PIA_LILY BLACK</t>
+          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>2535</v>
+        <v>1640</v>
       </c>
       <c r="G221" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
     <row r="222">
@@ -8642,24 +8614,24 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>PIA_MS5 Tint Brown_1T</t>
+          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
         </is>
       </c>
       <c r="F222" t="n">
-        <v>3885</v>
+        <v>10465</v>
       </c>
       <c r="G222" t="n">
-        <v>145</v>
+        <v>175</v>
       </c>
     </row>
     <row r="223">
@@ -8675,24 +8647,24 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>PIA_Matcha Latte_55%_1-DAY</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F223" t="n">
-        <v>6613</v>
+        <v>2965</v>
       </c>
       <c r="G223" t="n">
-        <v>567</v>
+        <v>50</v>
       </c>
     </row>
     <row r="224">
@@ -8708,24 +8680,24 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F224" t="n">
-        <v>2785</v>
+        <v>2375</v>
       </c>
       <c r="G224" t="n">
-        <v>30</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="225">
@@ -8741,24 +8713,24 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA_Opal CP-0.75 Toric_UV</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>21805</v>
+        <v>11930</v>
       </c>
       <c r="G225" t="n">
-        <v>255</v>
+        <v>305</v>
       </c>
     </row>
     <row r="226">
@@ -8774,24 +8746,24 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA_Opal CP-1.25 Toric_UV</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>26827</v>
+        <v>4690</v>
       </c>
       <c r="G226" t="n">
-        <v>1518</v>
+        <v>95</v>
       </c>
     </row>
     <row r="227">
@@ -8807,24 +8779,24 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>1-Day_58(수출용_파랑)</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>17734</v>
+        <v>9650</v>
       </c>
       <c r="G227" t="n">
-        <v>2441</v>
+        <v>320</v>
       </c>
     </row>
     <row r="228">
@@ -8840,24 +8812,24 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>20290</v>
+        <v>17510</v>
       </c>
       <c r="G228" t="n">
-        <v>170</v>
+        <v>335</v>
       </c>
     </row>
     <row r="229">
@@ -8873,24 +8845,24 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>PIA_Cider_1-DAY 55%</t>
+          <t>1-Day_58(수출용_파랑)</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>875</v>
+        <v>8665</v>
       </c>
       <c r="G229" t="n">
-        <v>5</v>
+        <v>360</v>
       </c>
     </row>
     <row r="230">
@@ -8906,519 +8878,519 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-1.25 Dollish Gray_55% UV</t>
+          <t>1-Day_SOLEKO(5년)</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>1306</v>
+        <v>16610</v>
       </c>
       <c r="G230" t="n">
-        <v>749</v>
+        <v>510</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>B형 조립중합8호기</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Hapa D Toric_Glazed choco_CP-1.75</t>
+          <t>BELLA D_Star</t>
         </is>
       </c>
       <c r="F231" t="n">
-        <v>1113</v>
+        <v>9344</v>
       </c>
       <c r="G231" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>Sincere D_Clear_38%</t>
         </is>
       </c>
       <c r="F232" t="n">
-        <v>2220</v>
+        <v>34954</v>
       </c>
       <c r="G232" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>B형 조립중합4호기</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F233" t="n">
-        <v>2580</v>
+        <v>34816</v>
       </c>
       <c r="G233" t="n">
-        <v>5</v>
+        <v>120</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>B형 조립중합5호기</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F234" t="n">
-        <v>2525</v>
+        <v>39920</v>
       </c>
       <c r="G234" t="n">
-        <v>10</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>B형 조립중합6호기</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>O2O2 D_Ash Gray EX</t>
         </is>
       </c>
       <c r="F235" t="n">
-        <v>1065</v>
+        <v>28844</v>
       </c>
       <c r="G235" t="n">
-        <v>2285</v>
+        <v>3404</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>PIA D Toric CP-0.75_Dazzle Gray_55% UV</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>4260</v>
+        <v>42682</v>
       </c>
       <c r="G236" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>PIA D Toric CP-0.75_Dollish Brown_55% UV</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>3854</v>
+        <v>40518</v>
       </c>
       <c r="G237" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>PIA D Toric CP-1.25_Dazzle Gray_55% UV</t>
+          <t>DYE D_LAVA</t>
         </is>
       </c>
       <c r="F238" t="n">
-        <v>12895</v>
+        <v>1968</v>
       </c>
       <c r="G238" t="n">
-        <v>160</v>
+        <v>262</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>CAM분리2호기</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>PIA D Toric CP-1.25_Dollish Brown_55% UV</t>
+          <t>BELLA D_Star</t>
         </is>
       </c>
       <c r="F239" t="n">
-        <v>3785</v>
+        <v>8460</v>
       </c>
       <c r="G239" t="n">
-        <v>255</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>CAM분리2호기</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>PIA_Opal CP-0.75 Toric_UV</t>
+          <t>DYE D_ALORA</t>
         </is>
       </c>
       <c r="F240" t="n">
-        <v>1930</v>
+        <v>1707</v>
       </c>
       <c r="G240" t="n">
-        <v>600</v>
+        <v>533</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>CAM분리2호기</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>1-Day_58_M</t>
+          <t>DYE D_LAVA</t>
         </is>
       </c>
       <c r="F241" t="n">
-        <v>34525</v>
+        <v>4276</v>
       </c>
       <c r="G241" t="n">
-        <v>850</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>CAM분리3호기</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>1-Day_58_M</t>
+          <t>BELLA D_Star</t>
         </is>
       </c>
       <c r="F242" t="n">
-        <v>50791</v>
+        <v>564</v>
       </c>
       <c r="G242" t="n">
-        <v>2544</v>
+        <v>359</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>CAM분리3호기</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>1-Day_58_M</t>
+          <t>DYE D_LAVA</t>
         </is>
       </c>
       <c r="F243" t="n">
-        <v>38831</v>
+        <v>8052</v>
       </c>
       <c r="G243" t="n">
-        <v>1754</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>1-DAY58_Micure</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F244" t="n">
-        <v>18965</v>
+        <v>1748</v>
       </c>
       <c r="G244" t="n">
-        <v>470</v>
+        <v>203</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>1-Day_58(NEW)</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>14635</v>
+        <v>12892</v>
       </c>
       <c r="G245" t="n">
-        <v>320</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="246">
@@ -9429,29 +9401,29 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>B형 분리수화접착6호기</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Sincere D_Clear_38%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F246" t="n">
-        <v>16354</v>
+        <v>17026</v>
       </c>
       <c r="G246" t="n">
-        <v>0</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="247">
@@ -9462,7 +9434,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9472,7 +9444,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>B형 조립중합4호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -9481,10 +9453,10 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>14841</v>
+        <v>2122</v>
       </c>
       <c r="G247" t="n">
-        <v>2023</v>
+        <v>926</v>
       </c>
     </row>
     <row r="248">
@@ -9495,7 +9467,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9505,19 +9477,19 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>B형 조립중합5호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F248" t="n">
-        <v>22129</v>
+        <v>12734</v>
       </c>
       <c r="G248" t="n">
-        <v>2503</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="249">
@@ -9528,7 +9500,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9538,19 +9510,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>B형 조립중합6호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Brown EX</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>12275</v>
+        <v>2530</v>
       </c>
       <c r="G249" t="n">
-        <v>4269</v>
+        <v>767</v>
       </c>
     </row>
     <row r="250">
@@ -9561,29 +9533,29 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>18253</v>
+        <v>11867</v>
       </c>
       <c r="G250" t="n">
-        <v>0</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="251">
@@ -9594,29 +9566,29 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착3호기</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>40473</v>
+        <v>3794</v>
       </c>
       <c r="G251" t="n">
-        <v>0</v>
+        <v>818</v>
       </c>
     </row>
     <row r="252">
@@ -9627,7 +9599,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9637,7 +9609,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -9646,10 +9618,10 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>43870</v>
+        <v>29486</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="253">
@@ -9660,7 +9632,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9670,7 +9642,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -9679,10 +9651,10 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>25831</v>
+        <v>26298</v>
       </c>
       <c r="G253" t="n">
-        <v>0</v>
+        <v>748</v>
       </c>
     </row>
     <row r="254">
@@ -9698,24 +9670,24 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>CAM분리2호기</t>
+          <t>B형 분리수화접착3호기</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>BELLA D_Cedar</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>1857</v>
+        <v>7910</v>
       </c>
       <c r="G254" t="n">
-        <v>671</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="255">
@@ -9731,24 +9703,24 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>CAM분리2호기</t>
+          <t>B형 분리수화접착4호기</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>DYE D_ALORA</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>1499</v>
+        <v>20675</v>
       </c>
       <c r="G255" t="n">
-        <v>713</v>
+        <v>4312</v>
       </c>
     </row>
     <row r="256">
@@ -9764,24 +9736,24 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Toric</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>CAM분리1호기</t>
+          <t>B형 분리수화접착1호기</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>O2O2 D_UV_Toric_SMD</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>12330</v>
+        <v>376</v>
       </c>
       <c r="G256" t="n">
-        <v>2104</v>
+        <v>30</v>
       </c>
     </row>
     <row r="257">
@@ -9792,29 +9764,29 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>CAM분리2호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>BELLA D_Star</t>
         </is>
       </c>
       <c r="F257" t="n">
-        <v>5508</v>
+        <v>850</v>
       </c>
       <c r="G257" t="n">
-        <v>617</v>
+        <v>34</v>
       </c>
     </row>
     <row r="258">
@@ -9825,29 +9797,29 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>CAM분리3호기</t>
+          <t>A형 인라인6호기</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>BELLA D_Cedar</t>
         </is>
       </c>
       <c r="F258" t="n">
-        <v>11937</v>
+        <v>15090</v>
       </c>
       <c r="G258" t="n">
-        <v>915</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="259">
@@ -9858,29 +9830,29 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>CAM분리4호기</t>
+          <t>A형 인라인6호기</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>BELLA D_Pine</t>
         </is>
       </c>
       <c r="F259" t="n">
-        <v>4294</v>
+        <v>5925</v>
       </c>
       <c r="G259" t="n">
-        <v>2093</v>
+        <v>153</v>
       </c>
     </row>
     <row r="260">
@@ -9891,29 +9863,29 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>A형 인라인6호기</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>BELLA D_Star</t>
         </is>
       </c>
       <c r="F260" t="n">
-        <v>4736</v>
+        <v>3555</v>
       </c>
       <c r="G260" t="n">
-        <v>1928</v>
+        <v>262</v>
       </c>
     </row>
     <row r="261">
@@ -9924,29 +9896,29 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>A형 인라인6호기</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>DYE D_CAPRI</t>
         </is>
       </c>
       <c r="F261" t="n">
-        <v>1093</v>
+        <v>2145</v>
       </c>
       <c r="G261" t="n">
-        <v>1054</v>
+        <v>51</v>
       </c>
     </row>
     <row r="262">
@@ -9957,29 +9929,29 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>A형 인라인6호기</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>DYE D_LAVA</t>
         </is>
       </c>
       <c r="F262" t="n">
-        <v>7603</v>
+        <v>3535</v>
       </c>
       <c r="G262" t="n">
-        <v>1899</v>
+        <v>142</v>
       </c>
     </row>
     <row r="263">
@@ -9990,29 +9962,29 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen oneday A(O2 Edition)</t>
         </is>
       </c>
       <c r="F263" t="n">
-        <v>6011</v>
+        <v>5230</v>
       </c>
       <c r="G263" t="n">
-        <v>1441</v>
+        <v>181</v>
       </c>
     </row>
     <row r="264">
@@ -10023,7 +9995,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -10033,7 +10005,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>B형 분리수화접착6호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -10042,10 +10014,10 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>7562</v>
+        <v>15459</v>
       </c>
       <c r="G264" t="n">
-        <v>2123</v>
+        <v>5771</v>
       </c>
     </row>
     <row r="265">
@@ -10056,7 +10028,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -10066,19 +10038,19 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>B형 분리수화접착6호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F265" t="n">
-        <v>8341</v>
+        <v>7525</v>
       </c>
       <c r="G265" t="n">
-        <v>1652</v>
+        <v>126</v>
       </c>
     </row>
     <row r="266">
@@ -10089,7 +10061,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -10099,19 +10071,19 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F266" t="n">
-        <v>13209</v>
+        <v>12928</v>
       </c>
       <c r="G266" t="n">
-        <v>4961</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="267">
@@ -10122,7 +10094,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -10132,19 +10104,19 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F267" t="n">
-        <v>1536</v>
+        <v>4770</v>
       </c>
       <c r="G267" t="n">
-        <v>270</v>
+        <v>88</v>
       </c>
     </row>
     <row r="268">
@@ -10155,7 +10127,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -10165,7 +10137,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -10174,10 +10146,10 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>13368</v>
+        <v>5533</v>
       </c>
       <c r="G268" t="n">
-        <v>3893</v>
+        <v>528</v>
       </c>
     </row>
     <row r="269">
@@ -10188,7 +10160,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -10198,19 +10170,19 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>1288</v>
+        <v>5198</v>
       </c>
       <c r="G269" t="n">
-        <v>541</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="270">
@@ -10221,7 +10193,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -10231,19 +10203,19 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>1432</v>
+        <v>17429</v>
       </c>
       <c r="G270" t="n">
-        <v>476</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="271">
@@ -10254,29 +10226,29 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>3941</v>
+        <v>1710</v>
       </c>
       <c r="G271" t="n">
-        <v>711</v>
+        <v>17</v>
       </c>
     </row>
     <row r="272">
@@ -10287,29 +10259,29 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>3933</v>
+        <v>6705</v>
       </c>
       <c r="G272" t="n">
-        <v>428</v>
+        <v>158</v>
       </c>
     </row>
     <row r="273">
@@ -10320,29 +10292,29 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>A형 인라인6호기</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F273" t="n">
-        <v>56659</v>
+        <v>0</v>
       </c>
       <c r="G273" t="n">
-        <v>5156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -10353,29 +10325,29 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>A형 인라인6호기</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>35686</v>
+        <v>6490</v>
       </c>
       <c r="G274" t="n">
-        <v>3935</v>
+        <v>265</v>
       </c>
     </row>
     <row r="275">
@@ -10386,7 +10358,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -10396,19 +10368,19 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
       <c r="F275" t="n">
-        <v>14024</v>
+        <v>42182</v>
       </c>
       <c r="G275" t="n">
-        <v>1192</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="276">
@@ -10419,7 +10391,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10429,19 +10401,19 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>16808</v>
+        <v>29150</v>
       </c>
       <c r="G276" t="n">
-        <v>4486</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="277">
@@ -10452,7 +10424,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -10462,19 +10434,19 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
       <c r="F277" t="n">
-        <v>11862</v>
+        <v>32645</v>
       </c>
       <c r="G277" t="n">
-        <v>1564</v>
+        <v>812</v>
       </c>
     </row>
     <row r="278">
@@ -10490,816 +10462,24 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>BELLA D_Cedar</t>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>7195</v>
+        <v>12616</v>
       </c>
       <c r="G278" t="n">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>A형 인라인4호기</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>BELLA D_Pine</t>
-        </is>
-      </c>
-      <c r="F279" t="n">
-        <v>8245</v>
-      </c>
-      <c r="G279" t="n">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>A형 인라인4호기</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>Clalen D_Canola Brown</t>
-        </is>
-      </c>
-      <c r="F280" t="n">
-        <v>6730</v>
-      </c>
-      <c r="G280" t="n">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>A형 인라인4호기</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>Clalen D_Mimosa Brown</t>
-        </is>
-      </c>
-      <c r="F281" t="n">
-        <v>3945</v>
-      </c>
-      <c r="G281" t="n">
-        <v>2080</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>A형 인라인6호기</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>BELLA D_Cedar</t>
-        </is>
-      </c>
-      <c r="F282" t="n">
-        <v>19145</v>
-      </c>
-      <c r="G282" t="n">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>A형 인라인6호기</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>Clalen D_Mimosa Brown</t>
-        </is>
-      </c>
-      <c r="F283" t="n">
-        <v>2070</v>
-      </c>
-      <c r="G283" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>A형 인라인5호기</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>Clalen oneday A(O2 Edition)</t>
-        </is>
-      </c>
-      <c r="F284" t="n">
-        <v>26530</v>
-      </c>
-      <c r="G284" t="n">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>A형 인라인1호기</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
-        </is>
-      </c>
-      <c r="F285" t="n">
-        <v>2015</v>
-      </c>
-      <c r="G285" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>A형 인라인1호기</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
-        </is>
-      </c>
-      <c r="F286" t="n">
-        <v>2900</v>
-      </c>
-      <c r="G286" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>A형 인라인1호기</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
-        </is>
-      </c>
-      <c r="F287" t="n">
-        <v>2755</v>
-      </c>
-      <c r="G287" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>A형 인라인2호기</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
-        </is>
-      </c>
-      <c r="F288" t="n">
-        <v>1590</v>
-      </c>
-      <c r="G288" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>A형 인라인2호기</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
-        </is>
-      </c>
-      <c r="F289" t="n">
-        <v>1770</v>
-      </c>
-      <c r="G289" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>A형 인라인3호기</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
-        </is>
-      </c>
-      <c r="F290" t="n">
-        <v>7181</v>
-      </c>
-      <c r="G290" t="n">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>A형 인라인3호기</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
-        </is>
-      </c>
-      <c r="F291" t="n">
-        <v>25961</v>
-      </c>
-      <c r="G291" t="n">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>A형 인라인3호기</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
-        </is>
-      </c>
-      <c r="F292" t="n">
-        <v>7560</v>
-      </c>
-      <c r="G292" t="n">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>A형 인라인4호기</t>
-        </is>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
-        </is>
-      </c>
-      <c r="F293" t="n">
-        <v>0</v>
-      </c>
-      <c r="G293" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>A형 인라인4호기</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
-        </is>
-      </c>
-      <c r="F294" t="n">
-        <v>4530</v>
-      </c>
-      <c r="G294" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>A형 인라인5호기</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
-        </is>
-      </c>
-      <c r="F295" t="n">
-        <v>4040</v>
-      </c>
-      <c r="G295" t="n">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>A형 인라인5호기</t>
-        </is>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
-        </is>
-      </c>
-      <c r="F296" t="n">
-        <v>3085</v>
-      </c>
-      <c r="G296" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>A형 인라인6호기</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
-        </is>
-      </c>
-      <c r="F297" t="n">
-        <v>2210</v>
-      </c>
-      <c r="G297" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>A형 인라인6호기</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
-        </is>
-      </c>
-      <c r="F298" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G298" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>A형 인라인1호기</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
-        </is>
-      </c>
-      <c r="F299" t="n">
-        <v>33286</v>
-      </c>
-      <c r="G299" t="n">
-        <v>4317</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>A형 인라인2호기</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
-        </is>
-      </c>
-      <c r="F300" t="n">
-        <v>25372</v>
-      </c>
-      <c r="G300" t="n">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>A형 인라인4호기</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
-        </is>
-      </c>
-      <c r="F301" t="n">
-        <v>1675</v>
-      </c>
-      <c r="G301" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>A형 인라인6호기</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
-        </is>
-      </c>
-      <c r="F302" t="n">
-        <v>17265</v>
-      </c>
-      <c r="G302" t="n">
-        <v>408</v>
+        <v>2356</v>
       </c>
     </row>
   </sheetData>

--- a/생산실적현황(설비운영현황).xlsx
+++ b/생산실적현황(설비운영현황).xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -521,7 +521,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S55_8.60</t>
+          <t>(NEW)S38-HD-Dry-14.0</t>
         </is>
       </c>
     </row>
@@ -565,15 +565,15 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FRP_Sph</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>5</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>FRP_Sph</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>T38_(UV포함)</t>
+          <t>T55_소사각</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>US55-2(M)_소사각</t>
         </is>
       </c>
     </row>
@@ -677,11 +677,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -689,7 +689,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Silicone relax_소사각</t>
+          <t>T38_금캡(UV포함)</t>
         </is>
       </c>
     </row>
@@ -705,47 +705,47 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>Silicone relax_소사각</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
     </row>
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
     </row>
@@ -789,11 +789,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
     </row>
@@ -813,23 +813,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
     </row>
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
     </row>
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Toric_CP-1.25_Halo Gray</t>
         </is>
       </c>
     </row>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -961,15 +961,15 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1-Day_58(수출용_파랑)</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
     </row>
@@ -985,11 +985,11 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -997,7 +997,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BELLA D_Star</t>
+          <t>Sincere D_Clear_38%</t>
         </is>
       </c>
     </row>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sincere D_Clear_38%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
     </row>
@@ -1041,19 +1041,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1065,15 +1065,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Sincere D_Clear_38%</t>
         </is>
       </c>
     </row>
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DYE D_LAVA</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
     </row>
@@ -1125,11 +1125,11 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1149,23 +1149,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>BELLA D_Star</t>
         </is>
       </c>
     </row>
@@ -1177,15 +1177,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Si_1-Day_Toric</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>O2O2 D_UV_Toric_SMD</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
     </row>
@@ -1213,69 +1213,13 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F28" t="inlineStr">
-        <is>
-          <t>BELLA D_Cedar</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>6</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>2</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>6</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>3</v>
-      </c>
-      <c r="F30" t="inlineStr">
         <is>
           <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
@@ -1292,15 +1236,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G278"/>
+  <dimension ref="A1:G292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1368,10 +1312,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>48942</v>
+        <v>99031</v>
       </c>
       <c r="G2" t="n">
-        <v>1089</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1401,7 +1345,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>105808</v>
+        <v>45382</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1434,10 +1378,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>50994</v>
+        <v>54779</v>
       </c>
       <c r="G4" t="n">
-        <v>613</v>
+        <v>2968</v>
       </c>
     </row>
     <row r="5">
@@ -1463,14 +1407,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CS30-Dry</t>
+          <t>US55-2(M)</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>18621</v>
+        <v>13912</v>
       </c>
       <c r="G5" t="n">
-        <v>2819</v>
+        <v>683</v>
       </c>
     </row>
     <row r="6">
@@ -1491,16 +1435,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>조립1호기</t>
+          <t>조립3호기</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S38-2_Blue</t>
+          <t>S55_8.60</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>19000</v>
+        <v>19456</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1524,19 +1468,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>조립3호기</t>
+          <t>조립8호기</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S55_8.60</t>
+          <t>(NEW)S38-HD-Dry-14.0</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>36628</v>
+        <v>29812</v>
       </c>
       <c r="G7" t="n">
-        <v>453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1552,24 +1496,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>조립8호기</t>
+          <t>조립4호기</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.4</t>
+          <t>O2O2 Spherical(DK70)_K2-SMD</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>35317</v>
+        <v>36724</v>
       </c>
       <c r="G8" t="n">
-        <v>422</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1580,29 +1524,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>조립4호기</t>
+          <t>분리10호기</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>O2O2 Spherical(DK70)_K2-SMD</t>
+          <t>(UV_NEW)CS30_8.60</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>31180</v>
+        <v>11780</v>
       </c>
       <c r="G9" t="n">
-        <v>538</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="10">
@@ -1623,7 +1567,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>분리10호기</t>
+          <t>분리11호기</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1632,10 +1576,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12333</v>
+        <v>10860</v>
       </c>
       <c r="G10" t="n">
-        <v>1683</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="11">
@@ -1656,19 +1600,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>분리11호기</t>
+          <t>분리14호기</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(UV_NEW)CS30_8.60</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>14134</v>
+        <v>31121</v>
       </c>
       <c r="G11" t="n">
-        <v>3672</v>
+        <v>5808</v>
       </c>
     </row>
     <row r="12">
@@ -1689,19 +1633,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>분리14호기</t>
+          <t>분리4호기</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>(NEW)S43-HD-Dry-14.2</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>30444</v>
+        <v>11890</v>
       </c>
       <c r="G12" t="n">
-        <v>5201</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="13">
@@ -1722,19 +1666,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>분리4호기</t>
+          <t>분리5호기</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.2</t>
+          <t>US55-2(M)</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>14776</v>
+        <v>10223</v>
       </c>
       <c r="G13" t="n">
-        <v>3065</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="14">
@@ -1764,10 +1708,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>10302</v>
+        <v>1065</v>
       </c>
       <c r="G14" t="n">
-        <v>2938</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15">
@@ -1797,10 +1741,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1323</v>
+        <v>1282</v>
       </c>
       <c r="G15" t="n">
-        <v>345</v>
+        <v>468</v>
       </c>
     </row>
     <row r="16">
@@ -1821,19 +1765,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>NewFusion_소사각</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6192</v>
+        <v>346</v>
       </c>
       <c r="G16" t="n">
-        <v>1303</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17">
@@ -1854,19 +1798,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>NewFusion_소사각</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2946</v>
+        <v>270</v>
       </c>
       <c r="G17" t="n">
-        <v>162</v>
+        <v>367</v>
       </c>
     </row>
     <row r="18">
@@ -1887,19 +1831,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>NewFusion_소사각</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6542</v>
+        <v>94</v>
       </c>
       <c r="G18" t="n">
-        <v>617</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
@@ -1920,19 +1864,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>NewFusion_소사각</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2636</v>
+        <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>194</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
@@ -1953,19 +1897,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Advance_CB_원형</t>
+          <t>Bella-Elite_14.5_중사각</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1294</v>
+        <v>1114</v>
       </c>
       <c r="G20" t="n">
-        <v>252</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21">
@@ -1986,19 +1930,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Advance_EO_원형</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>64</v>
+        <v>2298</v>
       </c>
       <c r="G21" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22">
@@ -2019,19 +1963,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Clalen Iris_Claire Brown_원형</t>
+          <t>Gray Bunny_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>120</v>
+        <v>1666</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>422</v>
       </c>
     </row>
     <row r="23">
@@ -2052,16 +1996,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Clalen Iris_Claire Gray_원형</t>
+          <t>NewFusion_원형</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>304</v>
+        <v>14</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2090,14 +2034,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Festival-II-Color_원형</t>
+          <t>Bella-Natural_14.5_중사각</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>348</v>
+        <v>92</v>
       </c>
       <c r="G24" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -2123,11 +2067,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Neon Color_원형</t>
+          <t>Clalen Iris_Claire Brown_원형</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2156,14 +2100,14 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NewFusion_원형</t>
+          <t>Clalen Iris_Claire Gray_원형</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2664</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
-        <v>656</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2189,14 +2133,14 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rose_color_원형</t>
+          <t>Neon Color_원형</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1008</v>
+        <v>151</v>
       </c>
       <c r="G27" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2217,19 +2161,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>NewFusion_원형</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4768</v>
+        <v>111</v>
       </c>
       <c r="G28" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2255,11 +2199,11 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Clalen 1M_Planet_Mercury Blue</t>
+          <t>Bella-Contour_중사각</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>176</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2288,14 +2232,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>Bella-Elite_14.5_중사각</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5388</v>
+        <v>286</v>
       </c>
       <c r="G30" t="n">
-        <v>552</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -2316,19 +2260,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>Bella-Natural_14.5_중사각</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3716</v>
+        <v>86</v>
       </c>
       <c r="G31" t="n">
-        <v>1239</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
@@ -2349,19 +2293,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>Bella-Natural_중사각</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5834</v>
+        <v>13</v>
       </c>
       <c r="G32" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2382,19 +2326,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>검사7호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>Clalen 6M_KUTAO_38%_(중)</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6300</v>
+        <v>920</v>
       </c>
       <c r="G33" t="n">
-        <v>503</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34">
@@ -2415,19 +2359,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>검사7호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>Clalen 6M_WEIGUANG_38%_(중)</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2696</v>
+        <v>1688</v>
       </c>
       <c r="G34" t="n">
-        <v>194</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35">
@@ -2448,19 +2392,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>APIA-(Look at me)_원형</t>
+          <t>Clalen 6M_YOUYU_38%_(중)</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1022</v>
+        <v>2246</v>
       </c>
       <c r="G35" t="n">
-        <v>665</v>
+        <v>253</v>
       </c>
     </row>
     <row r="36">
@@ -2481,19 +2425,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Advance_CB_원형</t>
+          <t>Coral Brown_2T_(PBT)PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>280</v>
+        <v>129</v>
       </c>
       <c r="G36" t="n">
-        <v>444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2514,19 +2458,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Festival-II-Color_원형</t>
+          <t>DYE M_NOLA_14.5_중사각</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>336</v>
+        <v>976</v>
       </c>
       <c r="G37" t="n">
-        <v>104</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38">
@@ -2547,19 +2491,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>NewFusion_원형</t>
+          <t>Gray Bunny_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>926</v>
+        <v>1838</v>
       </c>
       <c r="G38" t="n">
-        <v>991</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39">
@@ -2580,19 +2524,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rose_color_원형</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>376</v>
+        <v>3393</v>
       </c>
       <c r="G39" t="n">
-        <v>148</v>
+        <v>225</v>
       </c>
     </row>
     <row r="40">
@@ -2608,24 +2552,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>Clalen 6M_KUTAO_38%_(중)</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3309</v>
+        <v>734</v>
       </c>
       <c r="G40" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41">
@@ -2641,24 +2585,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>Clalen 6M_WEIGUANG_38%_(중)</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1948</v>
+        <v>618</v>
       </c>
       <c r="G41" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
@@ -2679,19 +2623,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>S38_은캡(BLUE TINT)</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1578</v>
+        <v>2237</v>
       </c>
       <c r="G42" t="n">
-        <v>120</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43">
@@ -2707,24 +2651,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>632</v>
+        <v>1891</v>
       </c>
       <c r="G43" t="n">
-        <v>186</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44">
@@ -2740,24 +2684,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>T38_금캡(UV포함)</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>640</v>
+        <v>3138</v>
       </c>
       <c r="G44" t="n">
-        <v>147</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45">
@@ -2773,24 +2717,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Silicone relax_소사각</t>
+          <t>US55-2(M)_소사각</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>8446</v>
+        <v>7606</v>
       </c>
       <c r="G45" t="n">
-        <v>660</v>
+        <v>455</v>
       </c>
     </row>
     <row r="46">
@@ -2806,24 +2750,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>Metha_55_중사각</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2882</v>
+        <v>3946</v>
       </c>
       <c r="G46" t="n">
-        <v>469</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47">
@@ -2839,24 +2783,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2907</v>
+        <v>358</v>
       </c>
       <c r="G47" t="n">
-        <v>548</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48">
@@ -2872,24 +2816,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Si_FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>O2O2 M_UV_Toric_SMD_(소)</t>
+          <t>US55-2(M)_소사각</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>306</v>
+        <v>5330</v>
       </c>
       <c r="G48" t="n">
-        <v>91</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49">
@@ -2905,387 +2849,387 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Si_FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>O2O2 M_UV_Toric_SMD_(소)</t>
+          <t>Metha_55_중사각</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>540</v>
+        <v>3338</v>
       </c>
       <c r="G49" t="n">
-        <v>461</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>조립10호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>29489</v>
+        <v>3312</v>
       </c>
       <c r="G50" t="n">
-        <v>2400</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>조립11호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
+          <t>Metha_55_중사각</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>18455</v>
+        <v>1793</v>
       </c>
       <c r="G51" t="n">
-        <v>9</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>조립12호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Metha_55_중사각</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>59017</v>
+        <v>1950</v>
       </c>
       <c r="G52" t="n">
-        <v>1650</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>조립13호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>S38_은캡(BLUE TINT)</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>51545</v>
+        <v>176</v>
       </c>
       <c r="G53" t="n">
-        <v>2337</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>조립14호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>T38_금캡(UV포함)</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>25160</v>
+        <v>2846</v>
       </c>
       <c r="G54" t="n">
-        <v>2293</v>
+        <v>585</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>조립15호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>Silicone relax_소사각</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>27941</v>
+        <v>3670</v>
       </c>
       <c r="G55" t="n">
-        <v>2350</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>조립16호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>Silicone relax_소사각</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>26948</v>
+        <v>3563</v>
       </c>
       <c r="G56" t="n">
-        <v>338</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>조립20호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>26029</v>
+        <v>5058</v>
       </c>
       <c r="G57" t="n">
-        <v>2450</v>
+        <v>719</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>조립24호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>25559</v>
+        <v>3015</v>
       </c>
       <c r="G58" t="n">
-        <v>2800</v>
+        <v>854</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>조립25호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>27067</v>
+        <v>9178</v>
       </c>
       <c r="G59" t="n">
-        <v>2400</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Toric</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>조립26호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>O2O2 M_UV_Toric_SMD_(소)</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>23807</v>
+        <v>2500</v>
       </c>
       <c r="G60" t="n">
-        <v>1350</v>
+        <v>731</v>
       </c>
     </row>
     <row r="61">
@@ -3306,19 +3250,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>조립40호기</t>
+          <t>조립10호기</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>25284</v>
+        <v>29641</v>
       </c>
       <c r="G61" t="n">
-        <v>1000</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="62">
@@ -3339,19 +3283,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>조립47호기</t>
+          <t>조립11호기</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>62637</v>
+        <v>37096</v>
       </c>
       <c r="G62" t="n">
-        <v>1492</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="63">
@@ -3372,19 +3316,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>조립48호기</t>
+          <t>조립12호기</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>28743</v>
+        <v>25660</v>
       </c>
       <c r="G63" t="n">
-        <v>1200</v>
+        <v>356</v>
       </c>
     </row>
     <row r="64">
@@ -3405,19 +3349,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>조립49호기</t>
+          <t>조립13호기</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>23137</v>
+        <v>22929</v>
       </c>
       <c r="G64" t="n">
-        <v>1330</v>
+        <v>846</v>
       </c>
     </row>
     <row r="65">
@@ -3438,19 +3382,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>조립50호기</t>
+          <t>조립14호기</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>45611</v>
+        <v>41681</v>
       </c>
       <c r="G65" t="n">
-        <v>3578</v>
+        <v>5615</v>
       </c>
     </row>
     <row r="66">
@@ -3471,19 +3415,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>조립51호기</t>
+          <t>조립15호기</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>46313</v>
+        <v>30189</v>
       </c>
       <c r="G66" t="n">
-        <v>1000</v>
+        <v>783</v>
       </c>
     </row>
     <row r="67">
@@ -3504,19 +3448,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>조립52호기</t>
+          <t>조립16호기</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>28458</v>
+        <v>49694</v>
       </c>
       <c r="G67" t="n">
-        <v>1490</v>
+        <v>3422</v>
       </c>
     </row>
     <row r="68">
@@ -3537,19 +3481,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>조립54호기</t>
+          <t>조립20호기</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PIA D_Grege Quartz 38% UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>25781</v>
+        <v>41040</v>
       </c>
       <c r="G68" t="n">
-        <v>884</v>
+        <v>7345</v>
       </c>
     </row>
     <row r="69">
@@ -3570,19 +3514,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>조립55호기</t>
+          <t>조립24호기</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Gray_38% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>25481</v>
+        <v>10570</v>
       </c>
       <c r="G69" t="n">
-        <v>500</v>
+        <v>367</v>
       </c>
     </row>
     <row r="70">
@@ -3603,19 +3547,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>조립56호기</t>
+          <t>조립25호기</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>23590</v>
+        <v>47135</v>
       </c>
       <c r="G70" t="n">
-        <v>2050</v>
+        <v>4386</v>
       </c>
     </row>
     <row r="71">
@@ -3636,19 +3580,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>조립58호기</t>
+          <t>조립26호기</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PIA D_Cherish Brown_55% UV 14.2</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>29840</v>
+        <v>38428</v>
       </c>
       <c r="G71" t="n">
-        <v>866</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="72">
@@ -3669,19 +3613,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>조립59호기</t>
+          <t>조립27호기</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>50979</v>
+        <v>18291</v>
       </c>
       <c r="G72" t="n">
-        <v>1370</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="73">
@@ -3697,24 +3641,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립40호기</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>18323</v>
+        <v>37122</v>
       </c>
       <c r="G73" t="n">
-        <v>508</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="74">
@@ -3730,24 +3674,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립44호기</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Plus Gray 14.2_55% UV</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>17989</v>
+        <v>42884</v>
       </c>
       <c r="G74" t="n">
-        <v>1961</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="75">
@@ -3763,24 +3707,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립47호기</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>4825</v>
+        <v>30904</v>
       </c>
       <c r="G75" t="n">
-        <v>751</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="76">
@@ -3796,24 +3740,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립49호기</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Gray</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>7494</v>
+        <v>22673</v>
       </c>
       <c r="G76" t="n">
-        <v>525</v>
+        <v>2982</v>
       </c>
     </row>
     <row r="77">
@@ -3829,24 +3773,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립50호기</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Gray</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>7382</v>
+        <v>28435</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78">
@@ -3862,24 +3806,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립51호기</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>33776</v>
+        <v>28448</v>
       </c>
       <c r="G78" t="n">
-        <v>1900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -3895,24 +3839,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>조립45호기</t>
+          <t>조립52호기</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>33347</v>
+        <v>48186</v>
       </c>
       <c r="G79" t="n">
-        <v>7802</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="80">
@@ -3928,24 +3872,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>조립46호기</t>
+          <t>조립54호기</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>PIA D_Garnet_38% UV</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>39841</v>
+        <v>14099</v>
       </c>
       <c r="G80" t="n">
-        <v>2106</v>
+        <v>5095</v>
       </c>
     </row>
     <row r="81">
@@ -3956,7 +3900,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3966,19 +3910,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>조립55호기</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Cream Rose_38% UV</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>10867</v>
+        <v>20721</v>
       </c>
       <c r="G81" t="n">
-        <v>1070</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="82">
@@ -3989,7 +3933,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3999,19 +3943,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>조립56호기</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>11846</v>
+        <v>59729</v>
       </c>
       <c r="G82" t="n">
-        <v>1677</v>
+        <v>419</v>
       </c>
     </row>
     <row r="83">
@@ -4022,7 +3966,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4032,19 +3976,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>조립57호기</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>BELLA D_Silent Gray 55%</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>10852</v>
+        <v>27294</v>
       </c>
       <c r="G83" t="n">
-        <v>1127</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="84">
@@ -4055,7 +3999,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4065,19 +4009,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>조립58호기</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>16696</v>
+        <v>27283</v>
       </c>
       <c r="G84" t="n">
-        <v>2018</v>
+        <v>933</v>
       </c>
     </row>
     <row r="85">
@@ -4088,7 +4032,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4098,19 +4042,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>조립59호기</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>5584</v>
+        <v>28973</v>
       </c>
       <c r="G85" t="n">
-        <v>995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -4121,29 +4065,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>23406</v>
+        <v>13799</v>
       </c>
       <c r="G86" t="n">
-        <v>4281</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="87">
@@ -4154,29 +4098,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>30892</v>
+        <v>4181</v>
       </c>
       <c r="G87" t="n">
-        <v>3264</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="88">
@@ -4187,29 +4131,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>13241</v>
+        <v>3161</v>
       </c>
       <c r="G88" t="n">
-        <v>2103</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89">
@@ -4220,29 +4164,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>Toric_CP-0.75_Halo Gray</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>11038</v>
+        <v>3087</v>
       </c>
       <c r="G89" t="n">
-        <v>1707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -4253,29 +4197,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>42101</v>
+        <v>21640</v>
       </c>
       <c r="G90" t="n">
-        <v>4198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -4286,29 +4230,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>조립45호기</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>BELLA D_VENUS 55%</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>17113</v>
+        <v>15662</v>
       </c>
       <c r="G91" t="n">
-        <v>1755</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="92">
@@ -4319,29 +4263,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>조립46호기</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>Gray Bunny_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>29595</v>
+        <v>13099</v>
       </c>
       <c r="G92" t="n">
-        <v>4693</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="93">
@@ -4352,29 +4296,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>조립53호기</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>Princess Chocolat_PIA_M_(중)_14.5</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>15718</v>
+        <v>9343</v>
       </c>
       <c r="G93" t="n">
-        <v>3799</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="94">
@@ -4385,29 +4329,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>조립53호기</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>Uniform Black_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>23835</v>
+        <v>9878</v>
       </c>
       <c r="G94" t="n">
-        <v>2662</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="95">
@@ -4428,19 +4372,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>23814</v>
+        <v>43883</v>
       </c>
       <c r="G95" t="n">
-        <v>4111</v>
+        <v>4348</v>
       </c>
     </row>
     <row r="96">
@@ -4461,19 +4405,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>45201</v>
+        <v>1988</v>
       </c>
       <c r="G96" t="n">
-        <v>2777</v>
+        <v>216</v>
       </c>
     </row>
     <row r="97">
@@ -4494,19 +4438,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>19250</v>
+        <v>28090</v>
       </c>
       <c r="G97" t="n">
-        <v>1550</v>
+        <v>3821</v>
       </c>
     </row>
     <row r="98">
@@ -4527,19 +4471,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>7739</v>
+        <v>38801</v>
       </c>
       <c r="G98" t="n">
-        <v>1777</v>
+        <v>5375</v>
       </c>
     </row>
     <row r="99">
@@ -4560,19 +4504,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>9492</v>
+        <v>40838</v>
       </c>
       <c r="G99" t="n">
-        <v>1121</v>
+        <v>5046</v>
       </c>
     </row>
     <row r="100">
@@ -4593,19 +4537,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_One&amp;Only Kristin Plus Brown 14.2_38%</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>10214</v>
+        <v>37722</v>
       </c>
       <c r="G100" t="n">
-        <v>4465</v>
+        <v>3989</v>
       </c>
     </row>
     <row r="101">
@@ -4626,19 +4570,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PIA D_Puree Greige_38% UV</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>12424</v>
+        <v>6138</v>
       </c>
       <c r="G101" t="n">
-        <v>2254</v>
+        <v>508</v>
       </c>
     </row>
     <row r="102">
@@ -4659,19 +4603,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리19호기</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>23829</v>
+        <v>24448</v>
       </c>
       <c r="G102" t="n">
-        <v>1456</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="103">
@@ -4692,19 +4636,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리19호기</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3503</v>
+        <v>3183</v>
       </c>
       <c r="G103" t="n">
-        <v>315</v>
+        <v>275</v>
       </c>
     </row>
     <row r="104">
@@ -4725,19 +4669,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Plus Gray 14.2_55% UV</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>24337</v>
+        <v>8566</v>
       </c>
       <c r="G104" t="n">
-        <v>2121</v>
+        <v>877</v>
       </c>
     </row>
     <row r="105">
@@ -4758,19 +4702,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>6206</v>
+        <v>8582</v>
       </c>
       <c r="G105" t="n">
-        <v>1188</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="106">
@@ -4791,19 +4735,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>분리43호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>11891</v>
+        <v>21337</v>
       </c>
       <c r="G106" t="n">
-        <v>1397</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="107">
@@ -4824,19 +4768,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>분리43호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>PIA D_Cherish Brown_55% UV 14.2</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>19400</v>
+        <v>40914</v>
       </c>
       <c r="G107" t="n">
-        <v>2853</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="108">
@@ -4852,24 +4796,24 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2711</v>
+        <v>10509</v>
       </c>
       <c r="G108" t="n">
-        <v>582</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="109">
@@ -4885,24 +4829,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>PIA_Brown Fondue CP-1.25 Toric_UV</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3695</v>
+        <v>10882</v>
       </c>
       <c r="G109" t="n">
-        <v>843</v>
+        <v>885</v>
       </c>
     </row>
     <row r="110">
@@ -4918,24 +4862,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3015</v>
+        <v>15164</v>
       </c>
       <c r="G110" t="n">
-        <v>434</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="111">
@@ -4951,24 +4895,24 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Gray</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2593</v>
+        <v>23887</v>
       </c>
       <c r="G111" t="n">
-        <v>1039</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="112">
@@ -4984,24 +4928,24 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>11291</v>
+        <v>18071</v>
       </c>
       <c r="G112" t="n">
-        <v>2587</v>
+        <v>5045</v>
       </c>
     </row>
     <row r="113">
@@ -5017,24 +4961,24 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>2803</v>
+        <v>12385</v>
       </c>
       <c r="G113" t="n">
-        <v>657</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="114">
@@ -5050,24 +4994,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>9172</v>
+        <v>15038</v>
       </c>
       <c r="G114" t="n">
-        <v>2595</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="115">
@@ -5083,24 +5027,24 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-0.75 Brown Bunny_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1738</v>
+        <v>23014</v>
       </c>
       <c r="G115" t="n">
-        <v>313</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="116">
@@ -5116,24 +5060,24 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1607</v>
+        <v>3492</v>
       </c>
       <c r="G116" t="n">
-        <v>3998</v>
+        <v>332</v>
       </c>
     </row>
     <row r="117">
@@ -5149,24 +5093,24 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>9613</v>
+        <v>25494</v>
       </c>
       <c r="G117" t="n">
-        <v>1964</v>
+        <v>3722</v>
       </c>
     </row>
     <row r="118">
@@ -5182,24 +5126,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>PIA_Brown Fondue CP-1.25 Toric_UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1341</v>
+        <v>40181</v>
       </c>
       <c r="G118" t="n">
-        <v>395</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="119">
@@ -5215,24 +5159,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>PIA_Opal CP-0.75 Toric_UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>3872</v>
+        <v>8205</v>
       </c>
       <c r="G119" t="n">
-        <v>1333</v>
+        <v>600</v>
       </c>
     </row>
     <row r="120">
@@ -5248,24 +5192,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>PIA_Opal CP-1.25 Toric_UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1108</v>
+        <v>19740</v>
       </c>
       <c r="G120" t="n">
-        <v>269</v>
+        <v>5798</v>
       </c>
     </row>
     <row r="121">
@@ -5281,24 +5225,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>분리22호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>40625</v>
+        <v>18700</v>
       </c>
       <c r="G121" t="n">
-        <v>6518</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="122">
@@ -5314,24 +5258,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>분리23호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Grege Quartz 38% UV</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>40406</v>
+        <v>21088</v>
       </c>
       <c r="G122" t="n">
-        <v>9071</v>
+        <v>4693</v>
       </c>
     </row>
     <row r="123">
@@ -5347,24 +5291,24 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>분리25호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Jelly Gray_38% UV</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>44955</v>
+        <v>14184</v>
       </c>
       <c r="G123" t="n">
-        <v>9447</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="124">
@@ -5380,24 +5324,24 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>Sincere D_Neutral Brown_UV_38% 14.2</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>4406</v>
+        <v>621</v>
       </c>
       <c r="G124" t="n">
-        <v>966</v>
+        <v>275</v>
       </c>
     </row>
     <row r="125">
@@ -5413,24 +5357,24 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>FLAMINGO_PIA_M(Y)</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1533</v>
+        <v>48006</v>
       </c>
       <c r="G125" t="n">
-        <v>218</v>
+        <v>3468</v>
       </c>
     </row>
     <row r="126">
@@ -5446,24 +5390,24 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>3968</v>
+        <v>24179</v>
       </c>
       <c r="G126" t="n">
-        <v>545</v>
+        <v>4825</v>
       </c>
     </row>
     <row r="127">
@@ -5474,7 +5418,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5484,19 +5428,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>2885</v>
+        <v>5072</v>
       </c>
       <c r="G127" t="n">
-        <v>140</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="128">
@@ -5507,7 +5451,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5517,19 +5461,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>4435</v>
+        <v>3493</v>
       </c>
       <c r="G128" t="n">
-        <v>430</v>
+        <v>273</v>
       </c>
     </row>
     <row r="129">
@@ -5540,7 +5484,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5550,19 +5494,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>PIA D_Teddy Brown_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>5980</v>
+        <v>9826</v>
       </c>
       <c r="G129" t="n">
-        <v>350</v>
+        <v>821</v>
       </c>
     </row>
     <row r="130">
@@ -5573,7 +5517,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5583,19 +5527,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>8855</v>
+        <v>23935</v>
       </c>
       <c r="G130" t="n">
-        <v>695</v>
+        <v>4434</v>
       </c>
     </row>
     <row r="131">
@@ -5606,7 +5550,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5616,19 +5560,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리43호기</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>PIA_LILY BLACK</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2915</v>
+        <v>10635</v>
       </c>
       <c r="G131" t="n">
-        <v>125</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="132">
@@ -5639,7 +5583,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5649,19 +5593,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리43호기</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA D_Cherish Brown_55% UV 14.2</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3240</v>
+        <v>6298</v>
       </c>
       <c r="G132" t="n">
-        <v>225</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="133">
@@ -5672,7 +5616,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5682,19 +5626,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리43호기</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>PIA_Tulle Brown_1D_55%_14.2</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>845</v>
+        <v>21322</v>
       </c>
       <c r="G133" t="n">
-        <v>210</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="134">
@@ -5705,29 +5649,29 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>9080</v>
+        <v>529</v>
       </c>
       <c r="G134" t="n">
-        <v>375</v>
+        <v>102</v>
       </c>
     </row>
     <row r="135">
@@ -5738,29 +5682,29 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>2956</v>
+        <v>1872</v>
       </c>
       <c r="G135" t="n">
-        <v>464</v>
+        <v>359</v>
       </c>
     </row>
     <row r="136">
@@ -5771,29 +5715,29 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>PIA D_Dorayaki_55% UV</t>
+          <t>PIA_Brown Fondue CP-1.25 Toric_UV</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>2845</v>
+        <v>1249</v>
       </c>
       <c r="G136" t="n">
-        <v>40</v>
+        <v>114</v>
       </c>
     </row>
     <row r="137">
@@ -5804,29 +5748,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>PIA D_Teddy Brown_55% UV</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>6055</v>
+        <v>11140</v>
       </c>
       <c r="G137" t="n">
-        <v>90</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="138">
@@ -5837,29 +5781,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>Toric_CP-0.75_Halo Gray</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>6065</v>
+        <v>5952</v>
       </c>
       <c r="G138" t="n">
-        <v>445</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="139">
@@ -5870,29 +5814,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>2285</v>
+        <v>10610</v>
       </c>
       <c r="G139" t="n">
-        <v>30</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="140">
@@ -5903,29 +5847,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>PIA_Cider_1-DAY 55%</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>2780</v>
+        <v>2295</v>
       </c>
       <c r="G140" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="141">
@@ -5936,29 +5880,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>3170</v>
+        <v>10745</v>
       </c>
       <c r="G141" t="n">
-        <v>245</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="142">
@@ -5969,29 +5913,29 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>Toric_CP-1.25_Halo Gray</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>3962</v>
+        <v>11234</v>
       </c>
       <c r="G142" t="n">
-        <v>363</v>
+        <v>4662</v>
       </c>
     </row>
     <row r="143">
@@ -6002,29 +5946,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리22호기</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>PIA_Tulle Brown_1D_55%_14.2</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>863</v>
+        <v>38312</v>
       </c>
       <c r="G143" t="n">
-        <v>207</v>
+        <v>8267</v>
       </c>
     </row>
     <row r="144">
@@ -6035,29 +5979,29 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>분리23호기</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>6145</v>
+        <v>39542</v>
       </c>
       <c r="G144" t="n">
-        <v>75</v>
+        <v>6997</v>
       </c>
     </row>
     <row r="145">
@@ -6068,29 +6012,29 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>분리25호기</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>4610</v>
+        <v>45271</v>
       </c>
       <c r="G145" t="n">
-        <v>75</v>
+        <v>7048</v>
       </c>
     </row>
     <row r="146">
@@ -6101,29 +6045,29 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>10385</v>
+        <v>25898</v>
       </c>
       <c r="G146" t="n">
-        <v>1680</v>
+        <v>6403</v>
       </c>
     </row>
     <row r="147">
@@ -6134,29 +6078,29 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>3380</v>
+        <v>2118</v>
       </c>
       <c r="G147" t="n">
-        <v>40</v>
+        <v>568</v>
       </c>
     </row>
     <row r="148">
@@ -6167,29 +6111,29 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>Princess Chocolat_PIA_M_(중)_14.5</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>12055</v>
+        <v>1007</v>
       </c>
       <c r="G148" t="n">
-        <v>225</v>
+        <v>268</v>
       </c>
     </row>
     <row r="149">
@@ -6210,19 +6154,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PIA_Matcha Latte_55%_1-DAY</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1320</v>
+        <v>4935</v>
       </c>
       <c r="G149" t="n">
-        <v>15</v>
+        <v>110</v>
       </c>
     </row>
     <row r="150">
@@ -6243,19 +6187,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2925</v>
+        <v>5855</v>
       </c>
       <c r="G150" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
     </row>
     <row r="151">
@@ -6276,19 +6220,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PIA_Tulle Brown_1D_55%_14.2</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2725</v>
+        <v>1160</v>
       </c>
       <c r="G151" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="152">
@@ -6309,19 +6253,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>BELLA D_MARS 55%</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>12313</v>
+        <v>8614</v>
       </c>
       <c r="G152" t="n">
-        <v>567</v>
+        <v>681</v>
       </c>
     </row>
     <row r="153">
@@ -6342,19 +6286,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>BELLA D_Siren Bronze 55%</t>
+          <t>PIA_LILY BLACK</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>12615</v>
+        <v>3125</v>
       </c>
       <c r="G153" t="n">
-        <v>175</v>
+        <v>50</v>
       </c>
     </row>
     <row r="154">
@@ -6375,19 +6319,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>BELLA D_VENUS 55%</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>18790</v>
+        <v>5400</v>
       </c>
       <c r="G154" t="n">
-        <v>1685</v>
+        <v>65</v>
       </c>
     </row>
     <row r="155">
@@ -6408,19 +6352,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>7830</v>
+        <v>3355</v>
       </c>
       <c r="G155" t="n">
-        <v>90</v>
+        <v>225</v>
       </c>
     </row>
     <row r="156">
@@ -6441,19 +6385,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>3110</v>
+        <v>2640</v>
       </c>
       <c r="G156" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="157">
@@ -6474,19 +6418,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1470</v>
+        <v>6670</v>
       </c>
       <c r="G157" t="n">
-        <v>35</v>
+        <v>155</v>
       </c>
     </row>
     <row r="158">
@@ -6507,19 +6451,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>PIA D_Dorayaki_55% UV</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>5944</v>
+        <v>9890</v>
       </c>
       <c r="G158" t="n">
-        <v>1776</v>
+        <v>260</v>
       </c>
     </row>
     <row r="159">
@@ -6540,19 +6484,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>PIA D_Dorayaki_55% UV</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>2675</v>
+        <v>2555</v>
       </c>
       <c r="G159" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="160">
@@ -6573,19 +6517,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>4000</v>
+        <v>3270</v>
       </c>
       <c r="G160" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="161">
@@ -6606,19 +6550,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>PIA_KEOPI BROWN</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>8850</v>
+        <v>9645</v>
       </c>
       <c r="G161" t="n">
-        <v>115</v>
+        <v>190</v>
       </c>
     </row>
     <row r="162">
@@ -6639,19 +6583,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>PIA_LILY BLACK</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>5145</v>
+        <v>3263</v>
       </c>
       <c r="G162" t="n">
-        <v>60</v>
+        <v>577</v>
       </c>
     </row>
     <row r="163">
@@ -6672,19 +6616,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA_LILY BLACK</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>7525</v>
+        <v>2940</v>
       </c>
       <c r="G163" t="n">
-        <v>215</v>
+        <v>35</v>
       </c>
     </row>
     <row r="164">
@@ -6705,19 +6649,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>10585</v>
+        <v>3010</v>
       </c>
       <c r="G164" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
     </row>
     <row r="165">
@@ -6738,19 +6682,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>PIA_Tulle Brown_1D_55%_14.2</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>2273</v>
+        <v>2810</v>
       </c>
       <c r="G165" t="n">
-        <v>407</v>
+        <v>35</v>
       </c>
     </row>
     <row r="166">
@@ -6771,7 +6715,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6780,10 +6724,10 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>18745</v>
+        <v>5140</v>
       </c>
       <c r="G166" t="n">
-        <v>415</v>
+        <v>75</v>
       </c>
     </row>
     <row r="167">
@@ -6804,7 +6748,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6813,10 +6757,10 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>18839</v>
+        <v>7360</v>
       </c>
       <c r="G167" t="n">
-        <v>2091</v>
+        <v>390</v>
       </c>
     </row>
     <row r="168">
@@ -6837,7 +6781,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6846,10 +6790,10 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>2507</v>
+        <v>10285</v>
       </c>
       <c r="G168" t="n">
-        <v>583</v>
+        <v>100</v>
       </c>
     </row>
     <row r="169">
@@ -6870,7 +6814,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6879,10 +6823,10 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1235</v>
+        <v>2246</v>
       </c>
       <c r="G169" t="n">
-        <v>85</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="170">
@@ -6903,19 +6847,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>PIA D_Dorayaki_55% UV</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>4455</v>
+        <v>6495</v>
       </c>
       <c r="G170" t="n">
-        <v>125</v>
+        <v>45</v>
       </c>
     </row>
     <row r="171">
@@ -6936,19 +6880,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PIA D_Teddy Brown_55% UV</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>5955</v>
+        <v>4190</v>
       </c>
       <c r="G171" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="172">
@@ -6969,19 +6913,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>8205</v>
+        <v>6260</v>
       </c>
       <c r="G172" t="n">
-        <v>145</v>
+        <v>95</v>
       </c>
     </row>
     <row r="173">
@@ -7002,19 +6946,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2610</v>
+        <v>2065</v>
       </c>
       <c r="G173" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="174">
@@ -7035,19 +6979,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PIA_KEOPI BROWN</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3055</v>
+        <v>1180</v>
       </c>
       <c r="G174" t="n">
-        <v>55</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="175">
@@ -7068,19 +7012,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3395</v>
+        <v>6070</v>
       </c>
       <c r="G175" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="176">
@@ -7101,19 +7045,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>PIA_Tulle Brown_1D_55%_14.2</t>
+          <t>BELLA D_MARS 55%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>15085</v>
+        <v>10985</v>
       </c>
       <c r="G176" t="n">
-        <v>465</v>
+        <v>590</v>
       </c>
     </row>
     <row r="177">
@@ -7134,19 +7078,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>BELLA D_Siren Bronze 55%</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>2610</v>
+        <v>4665</v>
       </c>
       <c r="G177" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="178">
@@ -7167,19 +7111,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>BELLA D_VENUS 55%</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>19866</v>
+        <v>21325</v>
       </c>
       <c r="G178" t="n">
-        <v>834</v>
+        <v>400</v>
       </c>
     </row>
     <row r="179">
@@ -7200,19 +7144,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>32367</v>
+        <v>4065</v>
       </c>
       <c r="G179" t="n">
-        <v>1288</v>
+        <v>45</v>
       </c>
     </row>
     <row r="180">
@@ -7233,19 +7177,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>5860</v>
+        <v>8105</v>
       </c>
       <c r="G180" t="n">
-        <v>90</v>
+        <v>135</v>
       </c>
     </row>
     <row r="181">
@@ -7266,19 +7210,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>15440</v>
+        <v>6335</v>
       </c>
       <c r="G181" t="n">
-        <v>285</v>
+        <v>530</v>
       </c>
     </row>
     <row r="182">
@@ -7299,19 +7243,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>31402</v>
+        <v>6660</v>
       </c>
       <c r="G182" t="n">
-        <v>1003</v>
+        <v>90</v>
       </c>
     </row>
     <row r="183">
@@ -7332,19 +7276,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>17200</v>
+        <v>3370</v>
       </c>
       <c r="G183" t="n">
-        <v>990</v>
+        <v>20</v>
       </c>
     </row>
     <row r="184">
@@ -7365,19 +7309,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>PIA D_Dorayaki_55% UV</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>14465</v>
+        <v>2810</v>
       </c>
       <c r="G184" t="n">
-        <v>115</v>
+        <v>40</v>
       </c>
     </row>
     <row r="185">
@@ -7398,19 +7342,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>8150</v>
+        <v>3160</v>
       </c>
       <c r="G185" t="n">
-        <v>1195</v>
+        <v>110</v>
       </c>
     </row>
     <row r="186">
@@ -7431,19 +7375,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>5858</v>
+        <v>5530</v>
       </c>
       <c r="G186" t="n">
-        <v>327</v>
+        <v>75</v>
       </c>
     </row>
     <row r="187">
@@ -7464,19 +7408,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>PIA D_Cherish Brown_55% UV 14.2</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1575</v>
+        <v>8865</v>
       </c>
       <c r="G187" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
     </row>
     <row r="188">
@@ -7497,19 +7441,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>PIA D_Dollish Brown_55% UV</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>2680</v>
+        <v>4795</v>
       </c>
       <c r="G188" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="189">
@@ -7530,19 +7474,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>PIA D_Dorayaki_55% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1240</v>
+        <v>28790</v>
       </c>
       <c r="G189" t="n">
-        <v>15</v>
+        <v>345</v>
       </c>
     </row>
     <row r="190">
@@ -7563,19 +7507,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>PIA D_Teddy Brown_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>2630</v>
+        <v>24565</v>
       </c>
       <c r="G190" t="n">
-        <v>70</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="191">
@@ -7596,19 +7540,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>9840</v>
+        <v>9510</v>
       </c>
       <c r="G191" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="192">
@@ -7629,19 +7573,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>13945</v>
+        <v>2920</v>
       </c>
       <c r="G192" t="n">
-        <v>240</v>
+        <v>10</v>
       </c>
     </row>
     <row r="193">
@@ -7662,19 +7606,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>PIA_BROWN MANEGE</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1905</v>
+        <v>3925</v>
       </c>
       <c r="G193" t="n">
-        <v>35</v>
+        <v>140</v>
       </c>
     </row>
     <row r="194">
@@ -7695,19 +7639,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA D_Dollish Gray_55% UV</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>2017</v>
+        <v>3010</v>
       </c>
       <c r="G194" t="n">
-        <v>408</v>
+        <v>55</v>
       </c>
     </row>
     <row r="195">
@@ -7728,19 +7672,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>PIA_Matcha Latte_55%_1-DAY</t>
+          <t>PIA D_Dorayaki_55% UV</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>6200</v>
+        <v>925</v>
       </c>
       <c r="G195" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
     </row>
     <row r="196">
@@ -7761,19 +7705,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>PIA_SARANG BROWN</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>2465</v>
+        <v>3450</v>
       </c>
       <c r="G196" t="n">
-        <v>135</v>
+        <v>20</v>
       </c>
     </row>
     <row r="197">
@@ -7794,19 +7738,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>47184</v>
+        <v>8720</v>
       </c>
       <c r="G197" t="n">
-        <v>1426</v>
+        <v>760</v>
       </c>
     </row>
     <row r="198">
@@ -7827,19 +7771,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1930</v>
+        <v>10200</v>
       </c>
       <c r="G198" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
     </row>
     <row r="199">
@@ -7860,19 +7804,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>6460</v>
+        <v>10060</v>
       </c>
       <c r="G199" t="n">
-        <v>50</v>
+        <v>210</v>
       </c>
     </row>
     <row r="200">
@@ -7893,19 +7837,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>7770</v>
+        <v>2500</v>
       </c>
       <c r="G200" t="n">
-        <v>135</v>
+        <v>715</v>
       </c>
     </row>
     <row r="201">
@@ -7926,16 +7870,16 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>11925</v>
+        <v>9215</v>
       </c>
       <c r="G201" t="n">
         <v>140</v>
@@ -7959,19 +7903,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>6290</v>
+        <v>13905</v>
       </c>
       <c r="G202" t="n">
-        <v>105</v>
+        <v>245</v>
       </c>
     </row>
     <row r="203">
@@ -7992,19 +7936,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>Hapakristin D_Quiet Kristin Glow Brown</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>9380</v>
+        <v>3030</v>
       </c>
       <c r="G203" t="n">
-        <v>905</v>
+        <v>75</v>
       </c>
     </row>
     <row r="204">
@@ -8025,19 +7969,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>PIA_Matcha Latte_55%_1-DAY</t>
+          <t>IRIS_Rhapsody(NEW)</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>3800</v>
+        <v>13865</v>
       </c>
       <c r="G204" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="205">
@@ -8058,19 +8002,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>PIA_SARANG BROWN</t>
+          <t>IRIS_Soul Brown(NEW)</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>3095</v>
+        <v>9015</v>
       </c>
       <c r="G205" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
     </row>
     <row r="206">
@@ -8091,19 +8035,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>11970</v>
+        <v>6300</v>
       </c>
       <c r="G206" t="n">
-        <v>245</v>
+        <v>85</v>
       </c>
     </row>
     <row r="207">
@@ -8124,16 +8068,16 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>4645</v>
+        <v>21205</v>
       </c>
       <c r="G207" t="n">
         <v>270</v>
@@ -8157,19 +8101,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>BELLA_1-Day_Hazel Honey(8년)</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>7990</v>
+        <v>24122</v>
       </c>
       <c r="G208" t="n">
-        <v>220</v>
+        <v>768</v>
       </c>
     </row>
     <row r="209">
@@ -8190,19 +8134,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>Hapakristin D_CREME BROWN_Secretive Kristin</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>28205</v>
+        <v>4165</v>
       </c>
       <c r="G209" t="n">
-        <v>1235</v>
+        <v>125</v>
       </c>
     </row>
     <row r="210">
@@ -8223,19 +8167,19 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>3438</v>
+        <v>12409</v>
       </c>
       <c r="G210" t="n">
-        <v>247</v>
+        <v>771</v>
       </c>
     </row>
     <row r="211">
@@ -8256,19 +8200,19 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>1718</v>
+        <v>3890</v>
       </c>
       <c r="G211" t="n">
-        <v>842</v>
+        <v>105</v>
       </c>
     </row>
     <row r="212">
@@ -8289,19 +8233,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>18567</v>
+        <v>17835</v>
       </c>
       <c r="G212" t="n">
-        <v>673</v>
+        <v>260</v>
       </c>
     </row>
     <row r="213">
@@ -8322,19 +8266,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>3845</v>
+        <v>1840</v>
       </c>
       <c r="G213" t="n">
-        <v>175</v>
+        <v>20</v>
       </c>
     </row>
     <row r="214">
@@ -8355,19 +8299,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>PIA_Tulle Brown_1D_55%_14.2</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>3680</v>
+        <v>4205</v>
       </c>
       <c r="G214" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="215">
@@ -8383,24 +8327,24 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-0.75 Brown Bunny_55% UV</t>
+          <t>PIA D_Sugar Donut_38% UV</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>4510</v>
+        <v>14107</v>
       </c>
       <c r="G215" t="n">
-        <v>75</v>
+        <v>623</v>
       </c>
     </row>
     <row r="216">
@@ -8416,24 +8360,24 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>5960</v>
+        <v>3300</v>
       </c>
       <c r="G216" t="n">
-        <v>320</v>
+        <v>45</v>
       </c>
     </row>
     <row r="217">
@@ -8449,24 +8393,24 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>9055</v>
+        <v>8830</v>
       </c>
       <c r="G217" t="n">
-        <v>225</v>
+        <v>190</v>
       </c>
     </row>
     <row r="218">
@@ -8482,24 +8426,24 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Gray</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>3719</v>
+        <v>8655</v>
       </c>
       <c r="G218" t="n">
-        <v>706</v>
+        <v>135</v>
       </c>
     </row>
     <row r="219">
@@ -8515,24 +8459,24 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F219" t="n">
-        <v>2765</v>
+        <v>58339</v>
       </c>
       <c r="G219" t="n">
-        <v>65</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="220">
@@ -8548,24 +8492,24 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>4274</v>
+        <v>24621</v>
       </c>
       <c r="G220" t="n">
-        <v>3141</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="221">
@@ -8581,24 +8525,24 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1640</v>
+        <v>2795</v>
       </c>
       <c r="G221" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
     <row r="222">
@@ -8614,24 +8558,24 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F222" t="n">
-        <v>10465</v>
+        <v>12345</v>
       </c>
       <c r="G222" t="n">
-        <v>175</v>
+        <v>145</v>
       </c>
     </row>
     <row r="223">
@@ -8647,24 +8591,24 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F223" t="n">
-        <v>2965</v>
+        <v>9195</v>
       </c>
       <c r="G223" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
     </row>
     <row r="224">
@@ -8680,24 +8624,24 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>PIA_KEOPI BROWN</t>
         </is>
       </c>
       <c r="F224" t="n">
-        <v>2375</v>
+        <v>2360</v>
       </c>
       <c r="G224" t="n">
-        <v>1190</v>
+        <v>30</v>
       </c>
     </row>
     <row r="225">
@@ -8713,24 +8657,24 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>PIA_Opal CP-0.75 Toric_UV</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>11930</v>
+        <v>3070</v>
       </c>
       <c r="G225" t="n">
-        <v>305</v>
+        <v>15</v>
       </c>
     </row>
     <row r="226">
@@ -8746,24 +8690,24 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>PIA_Opal CP-1.25 Toric_UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>4690</v>
+        <v>2927</v>
       </c>
       <c r="G226" t="n">
-        <v>95</v>
+        <v>453</v>
       </c>
     </row>
     <row r="227">
@@ -8779,24 +8723,24 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1-Day_58(수출용_파랑)</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>9650</v>
+        <v>3070</v>
       </c>
       <c r="G227" t="n">
-        <v>320</v>
+        <v>40</v>
       </c>
     </row>
     <row r="228">
@@ -8812,24 +8756,24 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>1-DAY58_Micure</t>
+          <t>Alcon D_Chic Caramel_W4(KR)</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>17510</v>
+        <v>1110</v>
       </c>
       <c r="G228" t="n">
-        <v>335</v>
+        <v>25</v>
       </c>
     </row>
     <row r="229">
@@ -8845,24 +8789,24 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>1-Day_58(수출용_파랑)</t>
+          <t>Alcon D_Chic Smoke_W4(KR)</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>8665</v>
+        <v>6670</v>
       </c>
       <c r="G229" t="n">
-        <v>360</v>
+        <v>135</v>
       </c>
     </row>
     <row r="230">
@@ -8878,35 +8822,35 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>Alcon D_Jewel Black_W3(KR)</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>16610</v>
+        <v>2965</v>
       </c>
       <c r="G230" t="n">
-        <v>510</v>
+        <v>45</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8916,646 +8860,646 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>B형 조립중합8호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>BELLA D_Star</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F231" t="n">
-        <v>9344</v>
+        <v>47678</v>
       </c>
       <c r="G231" t="n">
-        <v>0</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Sincere D_Clear_38%</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F232" t="n">
-        <v>34954</v>
+        <v>6365</v>
       </c>
       <c r="G232" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>B형 조립중합4호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F233" t="n">
-        <v>34816</v>
+        <v>955</v>
       </c>
       <c r="G233" t="n">
-        <v>120</v>
+        <v>15</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>B형 조립중합5호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F234" t="n">
-        <v>39920</v>
+        <v>40549</v>
       </c>
       <c r="G234" t="n">
-        <v>3496</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>B형 조립중합6호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Gray EX</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F235" t="n">
-        <v>28844</v>
+        <v>3470</v>
       </c>
       <c r="G235" t="n">
-        <v>3404</v>
+        <v>55</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>PIA D Toric_CP-0.75 Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>42682</v>
+        <v>1705</v>
       </c>
       <c r="G236" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>40518</v>
+        <v>762</v>
       </c>
       <c r="G237" t="n">
-        <v>0</v>
+        <v>788</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>DYE D_LAVA</t>
+          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
         </is>
       </c>
       <c r="F238" t="n">
-        <v>1968</v>
+        <v>6205</v>
       </c>
       <c r="G238" t="n">
-        <v>262</v>
+        <v>130</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>CAM분리2호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>BELLA D_Star</t>
+          <t>PIA_Brown Fondue CP-1.25 Toric_UV</t>
         </is>
       </c>
       <c r="F239" t="n">
-        <v>8460</v>
+        <v>9185</v>
       </c>
       <c r="G239" t="n">
-        <v>2678</v>
+        <v>195</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>CAM분리2호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>DYE D_ALORA</t>
+          <t>Toric_CP-0.75_Halo Gray</t>
         </is>
       </c>
       <c r="F240" t="n">
-        <v>1707</v>
+        <v>4495</v>
       </c>
       <c r="G240" t="n">
-        <v>533</v>
+        <v>65</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>CAM분리2호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>DYE D_LAVA</t>
+          <t>Toric_CP-1.25_Halo Gray</t>
         </is>
       </c>
       <c r="F241" t="n">
-        <v>4276</v>
+        <v>12095</v>
       </c>
       <c r="G241" t="n">
-        <v>1244</v>
+        <v>180</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>CAM분리3호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>BELLA D_Star</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F242" t="n">
-        <v>564</v>
+        <v>6750</v>
       </c>
       <c r="G242" t="n">
-        <v>359</v>
+        <v>75</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>CAM분리3호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>DYE D_LAVA</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F243" t="n">
-        <v>8052</v>
+        <v>12350</v>
       </c>
       <c r="G243" t="n">
-        <v>2177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F244" t="n">
-        <v>1748</v>
+        <v>20587</v>
       </c>
       <c r="G244" t="n">
-        <v>203</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>12892</v>
+        <v>4895</v>
       </c>
       <c r="G245" t="n">
-        <v>2785</v>
+        <v>50</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>B형 분리수화접착6호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>PIA_Opal CP-1.25 Toric_UV</t>
         </is>
       </c>
       <c r="F246" t="n">
-        <v>17026</v>
+        <v>1085</v>
       </c>
       <c r="G246" t="n">
-        <v>2589</v>
+        <v>15</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>1-Day_58(NEW)</t>
         </is>
       </c>
       <c r="F247" t="n">
-        <v>2122</v>
+        <v>6395</v>
       </c>
       <c r="G247" t="n">
-        <v>926</v>
+        <v>215</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>1-Day_58(수출용_파랑)</t>
         </is>
       </c>
       <c r="F248" t="n">
-        <v>12734</v>
+        <v>9055</v>
       </c>
       <c r="G248" t="n">
-        <v>2786</v>
+        <v>470</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>1-Day_Contakt-HA</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2530</v>
+        <v>12505</v>
       </c>
       <c r="G249" t="n">
-        <v>767</v>
+        <v>330</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>1-Day_SOLEKO(5년)</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>11867</v>
+        <v>20480</v>
       </c>
       <c r="G250" t="n">
-        <v>2390</v>
+        <v>715</v>
       </c>
     </row>
     <row r="251">
@@ -9566,29 +9510,29 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
+          <t>Sincere D_Clear_38%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3794</v>
+        <v>32641</v>
       </c>
       <c r="G251" t="n">
-        <v>818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -9599,29 +9543,29 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 조립중합4호기</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>29486</v>
+        <v>15371</v>
       </c>
       <c r="G252" t="n">
-        <v>1278</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="253">
@@ -9632,29 +9576,29 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>B형 조립중합6호기</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>O2O2 D_Ash Gray EX</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>26298</v>
+        <v>11025</v>
       </c>
       <c r="G253" t="n">
-        <v>748</v>
+        <v>6615</v>
       </c>
     </row>
     <row r="254">
@@ -9665,7 +9609,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9675,7 +9619,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -9684,10 +9628,10 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>7910</v>
+        <v>42730</v>
       </c>
       <c r="G254" t="n">
-        <v>1351</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -9698,7 +9642,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9708,7 +9652,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -9717,10 +9661,10 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>20675</v>
+        <v>42848</v>
       </c>
       <c r="G255" t="n">
-        <v>4312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -9736,24 +9680,24 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Si_1-Day_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>B형 분리수화접착1호기</t>
+          <t>CAM분리3호기</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>O2O2 D_UV_Toric_SMD</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>376</v>
+        <v>4170</v>
       </c>
       <c r="G256" t="n">
-        <v>30</v>
+        <v>401</v>
       </c>
     </row>
     <row r="257">
@@ -9764,29 +9708,29 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>CAM분리4호기</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>BELLA D_Star</t>
+          <t>Sincere D_Clear_38%</t>
         </is>
       </c>
       <c r="F257" t="n">
-        <v>850</v>
+        <v>18079</v>
       </c>
       <c r="G257" t="n">
-        <v>34</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="258">
@@ -9797,29 +9741,29 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>BELLA D_Cedar</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F258" t="n">
-        <v>15090</v>
+        <v>10859</v>
       </c>
       <c r="G258" t="n">
-        <v>1575</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="259">
@@ -9830,29 +9774,29 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>BELLA D_Pine</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F259" t="n">
-        <v>5925</v>
+        <v>5291</v>
       </c>
       <c r="G259" t="n">
-        <v>153</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="260">
@@ -9863,29 +9807,29 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>BELLA D_Star</t>
+          <t>O2O2 D_Ash Gray EX</t>
         </is>
       </c>
       <c r="F260" t="n">
-        <v>3555</v>
+        <v>2023</v>
       </c>
       <c r="G260" t="n">
-        <v>262</v>
+        <v>183</v>
       </c>
     </row>
     <row r="261">
@@ -9896,29 +9840,29 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>B형 분리수화접착6호기</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>DYE D_CAPRI</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F261" t="n">
-        <v>2145</v>
+        <v>1508</v>
       </c>
       <c r="G261" t="n">
-        <v>51</v>
+        <v>633</v>
       </c>
     </row>
     <row r="262">
@@ -9929,29 +9873,29 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>B형 분리수화접착6호기</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>DYE D_LAVA</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F262" t="n">
-        <v>3535</v>
+        <v>14173</v>
       </c>
       <c r="G262" t="n">
-        <v>142</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="263">
@@ -9962,29 +9906,29 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Clalen oneday A(O2 Edition)</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F263" t="n">
-        <v>5230</v>
+        <v>9890</v>
       </c>
       <c r="G263" t="n">
-        <v>181</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="264">
@@ -9995,7 +9939,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -10005,19 +9949,19 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F264" t="n">
-        <v>15459</v>
+        <v>2877</v>
       </c>
       <c r="G264" t="n">
-        <v>5771</v>
+        <v>959</v>
       </c>
     </row>
     <row r="265">
@@ -10028,7 +9972,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -10038,19 +9982,19 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F265" t="n">
-        <v>7525</v>
+        <v>4350</v>
       </c>
       <c r="G265" t="n">
-        <v>126</v>
+        <v>876</v>
       </c>
     </row>
     <row r="266">
@@ -10061,7 +10005,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -10071,19 +10015,19 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F266" t="n">
-        <v>12928</v>
+        <v>11683</v>
       </c>
       <c r="G266" t="n">
-        <v>3011</v>
+        <v>3391</v>
       </c>
     </row>
     <row r="267">
@@ -10094,7 +10038,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -10104,19 +10048,19 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F267" t="n">
-        <v>4770</v>
+        <v>3520</v>
       </c>
       <c r="G267" t="n">
-        <v>88</v>
+        <v>361</v>
       </c>
     </row>
     <row r="268">
@@ -10127,7 +10071,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -10137,19 +10081,19 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>5533</v>
+        <v>3864</v>
       </c>
       <c r="G268" t="n">
-        <v>528</v>
+        <v>558</v>
       </c>
     </row>
     <row r="269">
@@ -10160,29 +10104,29 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>5198</v>
+        <v>29636</v>
       </c>
       <c r="G269" t="n">
-        <v>1259</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="270">
@@ -10193,29 +10137,29 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>17429</v>
+        <v>27235</v>
       </c>
       <c r="G270" t="n">
-        <v>1564</v>
+        <v>732</v>
       </c>
     </row>
     <row r="271">
@@ -10226,29 +10170,29 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>B형 분리수화접착3호기</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>1710</v>
+        <v>12589</v>
       </c>
       <c r="G271" t="n">
-        <v>17</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="272">
@@ -10259,29 +10203,29 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>B형 분리수화접착4호기</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>6705</v>
+        <v>10588</v>
       </c>
       <c r="G272" t="n">
-        <v>158</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="273">
@@ -10297,7 +10241,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -10307,14 +10251,14 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>BELLA D_Star</t>
         </is>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>6720</v>
       </c>
       <c r="G273" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
     </row>
     <row r="274">
@@ -10330,7 +10274,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -10340,14 +10284,14 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>DYE D_LAVA</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>6490</v>
+        <v>6665</v>
       </c>
       <c r="G274" t="n">
-        <v>265</v>
+        <v>167</v>
       </c>
     </row>
     <row r="275">
@@ -10363,24 +10307,24 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+          <t>Clalen oneday A(O2 Edition)</t>
         </is>
       </c>
       <c r="F275" t="n">
-        <v>42182</v>
+        <v>12100</v>
       </c>
       <c r="G275" t="n">
-        <v>1564</v>
+        <v>659</v>
       </c>
     </row>
     <row r="276">
@@ -10396,24 +10340,24 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>29150</v>
+        <v>17240</v>
       </c>
       <c r="G276" t="n">
-        <v>1104</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="277">
@@ -10429,24 +10373,24 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F277" t="n">
-        <v>32645</v>
+        <v>12355</v>
       </c>
       <c r="G277" t="n">
-        <v>812</v>
+        <v>176</v>
       </c>
     </row>
     <row r="278">
@@ -10462,24 +10406,486 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
+        <v>23610</v>
+      </c>
+      <c r="G278" t="n">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>A형 인라인3호기</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>4250</v>
+      </c>
+      <c r="G279" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>A형 인라인3호기</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G280" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>A형 인라인5호기</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>3130</v>
+      </c>
+      <c r="G281" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>A형 인라인5호기</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>1775</v>
+      </c>
+      <c r="G282" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>A형 인라인5호기</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>8105</v>
+      </c>
+      <c r="G283" t="n">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>A형 인라인6호기</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G284" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>A형 인라인6호기</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>5540</v>
+      </c>
+      <c r="G285" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Si_1-Day_M/F</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>A형 인라인5호기</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>O2O2_Multifocal_K2_SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>2095</v>
+      </c>
+      <c r="G286" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
           <t>Si_1-Day_Sph</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr">
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>7350</v>
+      </c>
+      <c r="G287" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>A형 인라인2호기</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>36318</v>
+      </c>
+      <c r="G288" t="n">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>A형 인라인3호기</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>39967</v>
+      </c>
+      <c r="G289" t="n">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>A형 인라인4호기</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>31760</v>
+      </c>
+      <c r="G290" t="n">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
         <is>
           <t>A형 인라인5호기</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr">
+      <c r="E291" t="inlineStr">
         <is>
           <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
-      <c r="F278" t="n">
-        <v>12616</v>
-      </c>
-      <c r="G278" t="n">
-        <v>2356</v>
+      <c r="F291" t="n">
+        <v>30577</v>
+      </c>
+      <c r="G291" t="n">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>A형 인라인6호기</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>2270</v>
+      </c>
+      <c r="G292" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/생산실적현황(설비운영현황).xlsx
+++ b/생산실적현황(설비운영현황).xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -577,7 +577,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>(UV_NEW)CS30_8.60</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>T38_(UV포함)</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>Bella-Elite_14.5_중사각</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>S55_소사각</t>
         </is>
       </c>
     </row>
@@ -769,11 +769,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
     </row>
@@ -825,11 +825,11 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>Date Topaz_PIA_M(Y)</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Gray</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
     </row>
@@ -965,27 +965,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sincere D_Clear_38%</t>
+          <t>1-Day_SOLEKO(5년)</t>
         </is>
       </c>
     </row>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Sincere D_Clear_38%</t>
         </is>
       </c>
     </row>
@@ -1041,19 +1041,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
     </row>
@@ -1065,15 +1065,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sincere D_Clear_38%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1101,15 +1101,15 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Sincere D_Clear_38%</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
     </row>
@@ -1149,23 +1149,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BELLA D_Star</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>sincere Natural 1day</t>
         </is>
       </c>
     </row>
@@ -1213,13 +1213,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>Si_1-Day_Sph</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E29" t="n">
         <v>4</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
@@ -1236,7 +1264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G292"/>
+  <dimension ref="A1:G287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1245,7 +1273,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="56" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1312,7 +1340,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>99031</v>
+        <v>45513</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1345,7 +1373,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>45382</v>
+        <v>95692</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1378,10 +1406,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>54779</v>
+        <v>94079</v>
       </c>
       <c r="G4" t="n">
-        <v>2968</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="5">
@@ -1411,10 +1439,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>13912</v>
+        <v>19925</v>
       </c>
       <c r="G5" t="n">
-        <v>683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1444,10 +1472,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>19456</v>
+        <v>34130</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>959</v>
       </c>
     </row>
     <row r="7">
@@ -1477,10 +1505,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>29812</v>
+        <v>35761</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>857</v>
       </c>
     </row>
     <row r="8">
@@ -1510,7 +1538,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>36724</v>
+        <v>38501</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1543,10 +1571,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>11780</v>
+        <v>8759</v>
       </c>
       <c r="G9" t="n">
-        <v>1804</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="10">
@@ -1567,19 +1595,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>분리11호기</t>
+          <t>분리10호기</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(UV_NEW)CS30_8.60</t>
+          <t>CS30-Dry</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10860</v>
+        <v>3886</v>
       </c>
       <c r="G10" t="n">
-        <v>1293</v>
+        <v>664</v>
       </c>
     </row>
     <row r="11">
@@ -1600,19 +1628,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>분리14호기</t>
+          <t>분리11호기</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>(UV_NEW)CS30_8.60</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>31121</v>
+        <v>9666</v>
       </c>
       <c r="G11" t="n">
-        <v>5808</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="12">
@@ -1633,19 +1661,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>분리4호기</t>
+          <t>분리14호기</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.2</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>11890</v>
+        <v>4549</v>
       </c>
       <c r="G12" t="n">
-        <v>3021</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="13">
@@ -1666,19 +1694,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>분리5호기</t>
+          <t>분리4호기</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>US55-2(M)</t>
+          <t>(NEW)S38-HD-Dry-14.0</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>10223</v>
+        <v>8074</v>
       </c>
       <c r="G13" t="n">
-        <v>1875</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="14">
@@ -1694,24 +1722,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>분리3호기</t>
+          <t>분리4호기</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>T38_(UV포함)</t>
+          <t>(NEW)S43-HD-Dry-14.2</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1065</v>
+        <v>5885</v>
       </c>
       <c r="G14" t="n">
-        <v>129</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="15">
@@ -1727,24 +1755,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>분리3호기</t>
+          <t>분리5호기</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1282</v>
+        <v>2090</v>
       </c>
       <c r="G15" t="n">
-        <v>468</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="16">
@@ -1755,29 +1783,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>분리5호기</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NewFusion_소사각</t>
+          <t>US55-2(M)</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>346</v>
+        <v>5450</v>
       </c>
       <c r="G16" t="n">
-        <v>238</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="17">
@@ -1788,29 +1816,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>분리3호기</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NewFusion_소사각</t>
+          <t>T38_(UV포함)</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>270</v>
+        <v>3275</v>
       </c>
       <c r="G17" t="n">
-        <v>367</v>
+        <v>924</v>
       </c>
     </row>
     <row r="18">
@@ -1821,29 +1849,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>분리3호기</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NewFusion_소사각</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>94</v>
+        <v>403</v>
       </c>
       <c r="G18" t="n">
-        <v>30</v>
+        <v>972</v>
       </c>
     </row>
     <row r="19">
@@ -1873,10 +1901,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="G19" t="n">
-        <v>50</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20">
@@ -1902,14 +1930,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bella-Elite_14.5_중사각</t>
+          <t>Clalen 6M_KUTAO_38%_(중)</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1114</v>
+        <v>1350</v>
       </c>
       <c r="G20" t="n">
-        <v>84</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21">
@@ -1935,14 +1963,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>Clalen 6M_WEIGUANG_38%_(중)</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2298</v>
+        <v>912</v>
       </c>
       <c r="G21" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22">
@@ -1968,14 +1996,14 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>Clalen 6M_YOUYU_38%_(중)</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1666</v>
+        <v>610</v>
       </c>
       <c r="G22" t="n">
-        <v>422</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23">
@@ -1996,16 +2024,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>NewFusion_원형</t>
+          <t>CLC-30_원형</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2034,14 +2062,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bella-Natural_14.5_중사각</t>
+          <t>Intensive 55_원형</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2067,11 +2095,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Clalen Iris_Claire Brown_원형</t>
+          <t>NewFusion_원형</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2095,19 +2123,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Clalen Iris_Claire Gray_원형</t>
+          <t>Bella-Contour_중사각</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27">
@@ -2128,19 +2156,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Neon Color_원형</t>
+          <t>Bella-Elite_14.5_중사각</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>151</v>
+        <v>1988</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28">
@@ -2161,19 +2189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NewFusion_원형</t>
+          <t>Bella-Natural_14.5_중사각</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>111</v>
+        <v>942</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
@@ -2199,11 +2227,11 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bella-Contour_중사각</t>
+          <t>Cihan Elegance_중사각</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2232,14 +2260,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bella-Elite_14.5_중사각</t>
+          <t>DYE M_NOLA_14.5_중사각</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>286</v>
+        <v>2100</v>
       </c>
       <c r="G30" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31">
@@ -2265,14 +2293,14 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bella-Natural_14.5_중사각</t>
+          <t>DYE M_SILVER LACE_14.5_중사각</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="G31" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2298,11 +2326,11 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bella-Natural_중사각</t>
+          <t>DYE M_START DUST_14.5_중사각</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -2326,19 +2354,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Clalen 6M_KUTAO_38%_(중)</t>
+          <t>Bella Diamond_14.5_중사각</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>920</v>
+        <v>272</v>
       </c>
       <c r="G33" t="n">
-        <v>64</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
@@ -2359,19 +2387,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Clalen 6M_WEIGUANG_38%_(중)</t>
+          <t>Bella Glow_중사각</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1688</v>
+        <v>438</v>
       </c>
       <c r="G34" t="n">
-        <v>106</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35">
@@ -2392,19 +2420,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Clalen 6M_YOUYU_38%_(중)</t>
+          <t>Bella-Contour_중사각</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2246</v>
+        <v>176</v>
       </c>
       <c r="G35" t="n">
-        <v>253</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36">
@@ -2425,19 +2453,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Coral Brown_2T_(PBT)PIA_M_(중)(Y)</t>
+          <t>Bella-Elite_14.5_중사각</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>129</v>
+        <v>1626</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37">
@@ -2458,19 +2486,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>DYE M_NOLA_14.5_중사각</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>976</v>
+        <v>3172</v>
       </c>
       <c r="G37" t="n">
-        <v>24</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="38">
@@ -2491,19 +2519,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>Oolong Tea_PIA_M_중사각(Y)</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1838</v>
+        <v>894</v>
       </c>
       <c r="G38" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
@@ -2524,19 +2552,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>Advance_CB_원형</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3393</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>225</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="40">
@@ -2557,19 +2585,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Clalen 6M_KUTAO_38%_(중)</t>
+          <t>Bella-SnowWhite_14.5_원형</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>734</v>
+        <v>244</v>
       </c>
       <c r="G40" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41">
@@ -2590,19 +2618,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Clalen 6M_WEIGUANG_38%_(중)</t>
+          <t>CLC-30_원형</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>618</v>
+        <v>1580</v>
       </c>
       <c r="G41" t="n">
-        <v>30</v>
+        <v>671</v>
       </c>
     </row>
     <row r="42">
@@ -2618,24 +2646,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>NewFusion_원형</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2237</v>
+        <v>42</v>
       </c>
       <c r="G42" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43">
@@ -2651,24 +2679,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>CLC-30_바이알</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1891</v>
+        <v>275</v>
       </c>
       <c r="G43" t="n">
-        <v>124</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
@@ -2689,19 +2717,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3138</v>
+        <v>2176</v>
       </c>
       <c r="G44" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45">
@@ -2722,19 +2750,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>7606</v>
+        <v>1936</v>
       </c>
       <c r="G45" t="n">
-        <v>455</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46">
@@ -2755,19 +2783,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Metha_55_중사각</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3946</v>
+        <v>304</v>
       </c>
       <c r="G46" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="47">
@@ -2788,19 +2816,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>US55-2(M)_소사각</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>358</v>
+        <v>907</v>
       </c>
       <c r="G47" t="n">
-        <v>18</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48">
@@ -2821,19 +2849,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>Metha_55_중사각</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>5330</v>
+        <v>6162</v>
       </c>
       <c r="G48" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="49">
@@ -2854,19 +2882,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Metha_55_중사각</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3338</v>
+        <v>4340</v>
       </c>
       <c r="G49" t="n">
-        <v>13</v>
+        <v>549</v>
       </c>
     </row>
     <row r="50">
@@ -2887,19 +2915,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>US55-2(M)_소사각</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>3312</v>
+        <v>1362</v>
       </c>
       <c r="G50" t="n">
-        <v>90</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51">
@@ -2920,7 +2948,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2929,10 +2957,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1793</v>
+        <v>324</v>
       </c>
       <c r="G51" t="n">
-        <v>186</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -2953,19 +2981,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Metha_55_중사각</t>
+          <t>US55-2(M)_소사각</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1950</v>
+        <v>2050</v>
       </c>
       <c r="G52" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53">
@@ -2986,19 +3014,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>S38_은캡(BLUE TINT)</t>
+          <t>Metha_55_원형</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>176</v>
+        <v>2654</v>
       </c>
       <c r="G53" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54">
@@ -3019,19 +3047,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>T38_금캡(UV포함)</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2846</v>
+        <v>760</v>
       </c>
       <c r="G54" t="n">
-        <v>585</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55">
@@ -3047,24 +3075,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Silicone relax_소사각</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3670</v>
+        <v>851</v>
       </c>
       <c r="G55" t="n">
-        <v>90</v>
+        <v>333</v>
       </c>
     </row>
     <row r="56">
@@ -3080,24 +3108,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Silicone relax_소사각</t>
+          <t>T38_금캡</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3563</v>
+        <v>837</v>
       </c>
       <c r="G56" t="n">
-        <v>119</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57">
@@ -3113,24 +3141,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>T38_금캡(UV포함)</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>5058</v>
+        <v>5627</v>
       </c>
       <c r="G57" t="n">
-        <v>719</v>
+        <v>847</v>
       </c>
     </row>
     <row r="58">
@@ -3146,24 +3174,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>Silicone relax_소사각</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3015</v>
+        <v>4428</v>
       </c>
       <c r="G58" t="n">
-        <v>854</v>
+        <v>473</v>
       </c>
     </row>
     <row r="59">
@@ -3179,24 +3207,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>9178</v>
+        <v>480</v>
       </c>
       <c r="G59" t="n">
-        <v>2015</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60">
@@ -3212,156 +3240,156 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Si_FRP_Toric</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>O2O2 M_UV_Toric_SMD_(소)</t>
+          <t>Silicone relax_소사각</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2500</v>
+        <v>3452</v>
       </c>
       <c r="G60" t="n">
-        <v>731</v>
+        <v>199</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>조립10호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>29641</v>
+        <v>5254</v>
       </c>
       <c r="G61" t="n">
-        <v>2179</v>
+        <v>453</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>조립11호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>37096</v>
+        <v>2888</v>
       </c>
       <c r="G62" t="n">
-        <v>3235</v>
+        <v>746</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>조립12호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>25660</v>
+        <v>10201</v>
       </c>
       <c r="G63" t="n">
-        <v>356</v>
+        <v>932</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Toric</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>조립13호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>O2O2 M_UV_Toric_SMD_(소)</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>22929</v>
+        <v>2388</v>
       </c>
       <c r="G64" t="n">
-        <v>846</v>
+        <v>816</v>
       </c>
     </row>
     <row r="65">
@@ -3382,19 +3410,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>조립14호기</t>
+          <t>조립10호기</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_Latin</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>41681</v>
+        <v>48582</v>
       </c>
       <c r="G65" t="n">
-        <v>5615</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="66">
@@ -3415,19 +3443,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>조립15호기</t>
+          <t>조립11호기</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Sakana_55% UV</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>30189</v>
+        <v>23074</v>
       </c>
       <c r="G66" t="n">
-        <v>783</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="67">
@@ -3448,19 +3476,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>조립16호기</t>
+          <t>조립12호기</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>49694</v>
+        <v>29147</v>
       </c>
       <c r="G67" t="n">
-        <v>3422</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="68">
@@ -3481,19 +3509,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>조립20호기</t>
+          <t>조립13호기</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>41040</v>
+        <v>52170</v>
       </c>
       <c r="G68" t="n">
-        <v>7345</v>
+        <v>408</v>
       </c>
     </row>
     <row r="69">
@@ -3514,19 +3542,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>조립24호기</t>
+          <t>조립14호기</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>10570</v>
+        <v>22061</v>
       </c>
       <c r="G69" t="n">
-        <v>367</v>
+        <v>3364</v>
       </c>
     </row>
     <row r="70">
@@ -3547,19 +3575,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>조립25호기</t>
+          <t>조립15호기</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>47135</v>
+        <v>21828</v>
       </c>
       <c r="G70" t="n">
-        <v>4386</v>
+        <v>5113</v>
       </c>
     </row>
     <row r="71">
@@ -3580,19 +3608,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>조립26호기</t>
+          <t>조립16호기</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>38428</v>
+        <v>23579</v>
       </c>
       <c r="G71" t="n">
-        <v>1839</v>
+        <v>4187</v>
       </c>
     </row>
     <row r="72">
@@ -3613,19 +3641,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>조립27호기</t>
+          <t>조립20호기</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>18291</v>
+        <v>16013</v>
       </c>
       <c r="G72" t="n">
-        <v>2505</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="73">
@@ -3646,19 +3674,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>조립40호기</t>
+          <t>조립24호기</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>37122</v>
+        <v>27719</v>
       </c>
       <c r="G73" t="n">
-        <v>5580</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="74">
@@ -3679,19 +3707,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>조립44호기</t>
+          <t>조립25호기</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Plus Gray 14.2_55% UV</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>42884</v>
+        <v>17306</v>
       </c>
       <c r="G74" t="n">
-        <v>2708</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="75">
@@ -3712,19 +3740,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>조립47호기</t>
+          <t>조립26호기</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>30904</v>
+        <v>28659</v>
       </c>
       <c r="G75" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3745,19 +3773,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>조립49호기</t>
+          <t>조립27호기</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>22673</v>
+        <v>28628</v>
       </c>
       <c r="G76" t="n">
-        <v>2982</v>
+        <v>8943</v>
       </c>
     </row>
     <row r="77">
@@ -3778,19 +3806,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>조립50호기</t>
+          <t>조립40호기</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>28435</v>
+        <v>4751</v>
       </c>
       <c r="G77" t="n">
-        <v>87</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78">
@@ -3811,19 +3839,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>조립51호기</t>
+          <t>조립44호기</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>HAPA(PIA) D_First Love Kristin Brown 14.2_38% UV</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>28448</v>
+        <v>12842</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>6091</v>
       </c>
     </row>
     <row r="79">
@@ -3844,19 +3872,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>조립52호기</t>
+          <t>조립45호기</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>1-Day_iris_Latin</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>48186</v>
+        <v>50109</v>
       </c>
       <c r="G79" t="n">
-        <v>5859</v>
+        <v>7298</v>
       </c>
     </row>
     <row r="80">
@@ -3877,19 +3905,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>조립54호기</t>
+          <t>조립47호기</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>PIA D_Garnet_38% UV</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>14099</v>
+        <v>29854</v>
       </c>
       <c r="G80" t="n">
-        <v>5095</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="81">
@@ -3910,19 +3938,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>조립55호기</t>
+          <t>조립48호기</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PIA D_Cream Rose_38% UV</t>
+          <t>PIA D_Sakura Mousse_55% UV</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>20721</v>
+        <v>21781</v>
       </c>
       <c r="G81" t="n">
-        <v>6260</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="82">
@@ -3943,19 +3971,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>조립56호기</t>
+          <t>조립49호기</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>59729</v>
+        <v>22952</v>
       </c>
       <c r="G82" t="n">
-        <v>419</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="83">
@@ -3976,19 +4004,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>조립57호기</t>
+          <t>조립50호기</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>BELLA D_Silent Gray 55%</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>27294</v>
+        <v>57685</v>
       </c>
       <c r="G83" t="n">
-        <v>2306</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="84">
@@ -4009,19 +4037,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>조립58호기</t>
+          <t>조립52호기</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>27283</v>
+        <v>27379</v>
       </c>
       <c r="G84" t="n">
-        <v>933</v>
+        <v>4386</v>
       </c>
     </row>
     <row r="85">
@@ -4042,19 +4070,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>조립59호기</t>
+          <t>조립54호기</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>PIA D_Glow Brown_38% UV</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>28973</v>
+        <v>18857</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>3760</v>
       </c>
     </row>
     <row r="86">
@@ -4070,24 +4098,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립55호기</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>PIA D_Cream Rose_38% UV</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>13799</v>
+        <v>8434</v>
       </c>
       <c r="G86" t="n">
-        <v>2205</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="87">
@@ -4103,24 +4131,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립56호기</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>PIA D_Uniform Black_55% UV</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>4181</v>
+        <v>18900</v>
       </c>
       <c r="G87" t="n">
-        <v>2110</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="88">
@@ -4136,24 +4164,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립57호기</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>BELLA D_Nerelle 55%</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3161</v>
+        <v>22700</v>
       </c>
       <c r="G88" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89">
@@ -4169,24 +4197,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립58호기</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Gray</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3087</v>
+        <v>47048</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>4019</v>
       </c>
     </row>
     <row r="90">
@@ -4202,24 +4230,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립59호기</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>21640</v>
+        <v>27210</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="91">
@@ -4235,24 +4263,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>조립45호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>15662</v>
+        <v>9301</v>
       </c>
       <c r="G91" t="n">
-        <v>2276</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92">
@@ -4268,24 +4296,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>조립46호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Gray Bunny_PIA_M_(중)_14.2</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>13099</v>
+        <v>5751</v>
       </c>
       <c r="G92" t="n">
-        <v>1645</v>
+        <v>448</v>
       </c>
     </row>
     <row r="93">
@@ -4301,24 +4329,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>조립53호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Princess Chocolat_PIA_M_(중)_14.5</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>9343</v>
+        <v>6489</v>
       </c>
       <c r="G93" t="n">
-        <v>1020</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="94">
@@ -4334,24 +4362,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>조립53호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Uniform Black_PIA_M(Y)</t>
+          <t>Toric_CP-0.75_Halo Gray</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>9878</v>
+        <v>2804</v>
       </c>
       <c r="G94" t="n">
-        <v>1400</v>
+        <v>701</v>
       </c>
     </row>
     <row r="95">
@@ -4362,29 +4390,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>Toric_CP-1.25_Halo Gray</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>43883</v>
+        <v>6269</v>
       </c>
       <c r="G95" t="n">
-        <v>4348</v>
+        <v>715</v>
       </c>
     </row>
     <row r="96">
@@ -4395,29 +4423,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1988</v>
+        <v>16283</v>
       </c>
       <c r="G96" t="n">
-        <v>216</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="97">
@@ -4428,29 +4456,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>조립46호기</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>Date Topaz_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>28090</v>
+        <v>18452</v>
       </c>
       <c r="G97" t="n">
-        <v>3821</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="98">
@@ -4461,29 +4489,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>조립53호기</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
+          <t>Tarte Tatin_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>38801</v>
+        <v>17907</v>
       </c>
       <c r="G98" t="n">
-        <v>5375</v>
+        <v>700</v>
       </c>
     </row>
     <row r="99">
@@ -4504,19 +4532,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_Latin</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>40838</v>
+        <v>24369</v>
       </c>
       <c r="G99" t="n">
-        <v>5046</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="100">
@@ -4537,19 +4565,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>37722</v>
+        <v>9224</v>
       </c>
       <c r="G100" t="n">
-        <v>3989</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="101">
@@ -4570,19 +4598,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>6138</v>
+        <v>9766</v>
       </c>
       <c r="G101" t="n">
-        <v>508</v>
+        <v>927</v>
       </c>
     </row>
     <row r="102">
@@ -4603,19 +4631,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>분리19호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>24448</v>
+        <v>13186</v>
       </c>
       <c r="G102" t="n">
-        <v>3817</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="103">
@@ -4636,19 +4664,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>분리19호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>Gemhour D_Liz Brown_Keira</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3183</v>
+        <v>13082</v>
       </c>
       <c r="G103" t="n">
-        <v>275</v>
+        <v>3245</v>
       </c>
     </row>
     <row r="104">
@@ -4669,19 +4697,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Plus Gray 14.2_55% UV</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>8566</v>
+        <v>18579</v>
       </c>
       <c r="G104" t="n">
-        <v>877</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="105">
@@ -4702,19 +4730,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>8582</v>
+        <v>21216</v>
       </c>
       <c r="G105" t="n">
-        <v>1964</v>
+        <v>4315</v>
       </c>
     </row>
     <row r="106">
@@ -4735,19 +4763,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Plus Gray 14.2_55% UV</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>21337</v>
+        <v>14657</v>
       </c>
       <c r="G106" t="n">
-        <v>2335</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="107">
@@ -4768,19 +4796,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>40914</v>
+        <v>3081</v>
       </c>
       <c r="G107" t="n">
-        <v>4800</v>
+        <v>386</v>
       </c>
     </row>
     <row r="108">
@@ -4801,19 +4829,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>10509</v>
+        <v>11930</v>
       </c>
       <c r="G108" t="n">
-        <v>2679</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="109">
@@ -4834,19 +4862,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>10882</v>
+        <v>20697</v>
       </c>
       <c r="G109" t="n">
-        <v>885</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="110">
@@ -4867,19 +4895,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>15164</v>
+        <v>11338</v>
       </c>
       <c r="G110" t="n">
-        <v>1897</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="111">
@@ -4900,19 +4928,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>23887</v>
+        <v>19197</v>
       </c>
       <c r="G111" t="n">
-        <v>2757</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="112">
@@ -4933,19 +4961,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>18071</v>
+        <v>20484</v>
       </c>
       <c r="G112" t="n">
-        <v>5045</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="113">
@@ -4966,19 +4994,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>분리19호기</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>12385</v>
+        <v>43293</v>
       </c>
       <c r="G113" t="n">
-        <v>1379</v>
+        <v>5732</v>
       </c>
     </row>
     <row r="114">
@@ -4999,19 +5027,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Gemhour D_Liz Brown_Keira</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>15038</v>
+        <v>2895</v>
       </c>
       <c r="G114" t="n">
-        <v>1243</v>
+        <v>852</v>
       </c>
     </row>
     <row r="115">
@@ -5032,19 +5060,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Plus Gray 14.2_55% UV</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>23014</v>
+        <v>14228</v>
       </c>
       <c r="G115" t="n">
-        <v>2146</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="116">
@@ -5065,19 +5093,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>3492</v>
+        <v>27228</v>
       </c>
       <c r="G116" t="n">
-        <v>332</v>
+        <v>4052</v>
       </c>
     </row>
     <row r="117">
@@ -5098,19 +5126,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>1-Day_iris_Latin</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>25494</v>
+        <v>19181</v>
       </c>
       <c r="G117" t="n">
-        <v>3722</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="118">
@@ -5131,19 +5159,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>40181</v>
+        <v>22927</v>
       </c>
       <c r="G118" t="n">
-        <v>2955</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="119">
@@ -5164,19 +5192,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>8205</v>
+        <v>3059</v>
       </c>
       <c r="G119" t="n">
-        <v>600</v>
+        <v>399</v>
       </c>
     </row>
     <row r="120">
@@ -5197,19 +5225,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>19740</v>
+        <v>25293</v>
       </c>
       <c r="G120" t="n">
-        <v>5798</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="121">
@@ -5230,19 +5258,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>18700</v>
+        <v>9912</v>
       </c>
       <c r="G121" t="n">
-        <v>2530</v>
+        <v>994</v>
       </c>
     </row>
     <row r="122">
@@ -5263,19 +5291,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>PIA D_Grege Quartz 38% UV</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>21088</v>
+        <v>41752</v>
       </c>
       <c r="G122" t="n">
-        <v>4693</v>
+        <v>6567</v>
       </c>
     </row>
     <row r="123">
@@ -5296,19 +5324,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Gray_38% UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>14184</v>
+        <v>28886</v>
       </c>
       <c r="G123" t="n">
-        <v>2033</v>
+        <v>6009</v>
       </c>
     </row>
     <row r="124">
@@ -5329,19 +5357,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sincere D_Neutral Brown_UV_38% 14.2</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>621</v>
+        <v>7927</v>
       </c>
       <c r="G124" t="n">
-        <v>275</v>
+        <v>925</v>
       </c>
     </row>
     <row r="125">
@@ -5362,19 +5390,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>48006</v>
+        <v>11463</v>
       </c>
       <c r="G125" t="n">
-        <v>3468</v>
+        <v>995</v>
       </c>
     </row>
     <row r="126">
@@ -5395,19 +5423,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>24179</v>
+        <v>8328</v>
       </c>
       <c r="G126" t="n">
-        <v>4825</v>
+        <v>643</v>
       </c>
     </row>
     <row r="127">
@@ -5428,19 +5456,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>Astra Glitter</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>5072</v>
+        <v>1336</v>
       </c>
       <c r="G127" t="n">
-        <v>1556</v>
+        <v>8732</v>
       </c>
     </row>
     <row r="128">
@@ -5461,19 +5489,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>Gemhour D_Liz Brown_Keira</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3493</v>
+        <v>7191</v>
       </c>
       <c r="G128" t="n">
-        <v>273</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="129">
@@ -5494,7 +5522,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5503,10 +5531,10 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>9826</v>
+        <v>20827</v>
       </c>
       <c r="G129" t="n">
-        <v>821</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="130">
@@ -5527,7 +5555,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5536,10 +5564,10 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>23935</v>
+        <v>36202</v>
       </c>
       <c r="G130" t="n">
-        <v>4434</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="131">
@@ -5560,19 +5588,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>분리43호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>10635</v>
+        <v>7521</v>
       </c>
       <c r="G131" t="n">
-        <v>2556</v>
+        <v>481</v>
       </c>
     </row>
     <row r="132">
@@ -5593,19 +5621,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>분리43호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>PIA D_Cherish Brown_55% UV 14.2</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>6298</v>
+        <v>47037</v>
       </c>
       <c r="G132" t="n">
-        <v>1289</v>
+        <v>3361</v>
       </c>
     </row>
     <row r="133">
@@ -5626,19 +5654,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>분리43호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>21322</v>
+        <v>3146</v>
       </c>
       <c r="G133" t="n">
-        <v>3353</v>
+        <v>328</v>
       </c>
     </row>
     <row r="134">
@@ -5654,24 +5682,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
+          <t>Gemhour D_Liz Brown_Keira</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>529</v>
+        <v>2195</v>
       </c>
       <c r="G134" t="n">
-        <v>102</v>
+        <v>350</v>
       </c>
     </row>
     <row r="135">
@@ -5687,24 +5715,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
+          <t>HAPA(PIA) D_First Love Kristin Brown 14.2_38% UV</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1872</v>
+        <v>2615</v>
       </c>
       <c r="G135" t="n">
-        <v>359</v>
+        <v>754</v>
       </c>
     </row>
     <row r="136">
@@ -5720,24 +5748,24 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>PIA_Brown Fondue CP-1.25 Toric_UV</t>
+          <t>PIA D_Cream Rose_38% UV</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1249</v>
+        <v>17100</v>
       </c>
       <c r="G136" t="n">
-        <v>114</v>
+        <v>3083</v>
       </c>
     </row>
     <row r="137">
@@ -5753,24 +5781,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>PIA D_Garnet_38% UV</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>11140</v>
+        <v>12548</v>
       </c>
       <c r="G137" t="n">
-        <v>1178</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="138">
@@ -5786,24 +5814,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Gray</t>
+          <t>PIA D_Jelly Gray_38% UV</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>5952</v>
+        <v>7977</v>
       </c>
       <c r="G138" t="n">
-        <v>1542</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="139">
@@ -5819,24 +5847,24 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>10610</v>
+        <v>9206</v>
       </c>
       <c r="G139" t="n">
-        <v>1343</v>
+        <v>659</v>
       </c>
     </row>
     <row r="140">
@@ -5852,24 +5880,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>2295</v>
+        <v>38466</v>
       </c>
       <c r="G140" t="n">
-        <v>316</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="141">
@@ -5885,24 +5913,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>PIA D_Sakura Mousse_55% UV</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>10745</v>
+        <v>14714</v>
       </c>
       <c r="G141" t="n">
-        <v>2302</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="142">
@@ -5918,24 +5946,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Gray</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>11234</v>
+        <v>23348</v>
       </c>
       <c r="G142" t="n">
-        <v>4662</v>
+        <v>6538</v>
       </c>
     </row>
     <row r="143">
@@ -5951,24 +5979,24 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>분리22호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>38312</v>
+        <v>12509</v>
       </c>
       <c r="G143" t="n">
-        <v>8267</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="144">
@@ -5984,24 +6012,24 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>분리23호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Astra Estelle Gray</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>39542</v>
+        <v>2236</v>
       </c>
       <c r="G144" t="n">
-        <v>6997</v>
+        <v>845</v>
       </c>
     </row>
     <row r="145">
@@ -6017,24 +6045,24 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>분리25호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>BELLA D_Nerelle 55%</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>45271</v>
+        <v>2292</v>
       </c>
       <c r="G145" t="n">
-        <v>7048</v>
+        <v>533</v>
       </c>
     </row>
     <row r="146">
@@ -6050,24 +6078,24 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>BELLA D_Silent Gray 55%</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>25898</v>
+        <v>24628</v>
       </c>
       <c r="G146" t="n">
-        <v>6403</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="147">
@@ -6083,24 +6111,24 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리43호기</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2118</v>
+        <v>33022</v>
       </c>
       <c r="G147" t="n">
-        <v>568</v>
+        <v>7183</v>
       </c>
     </row>
     <row r="148">
@@ -6116,24 +6144,24 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리43호기</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Princess Chocolat_PIA_M_(중)_14.5</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1007</v>
+        <v>3129</v>
       </c>
       <c r="G148" t="n">
-        <v>268</v>
+        <v>420</v>
       </c>
     </row>
     <row r="149">
@@ -6144,29 +6172,29 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>4935</v>
+        <v>1550</v>
       </c>
       <c r="G149" t="n">
-        <v>110</v>
+        <v>387</v>
       </c>
     </row>
     <row r="150">
@@ -6177,29 +6205,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA_Brown Fondue CP-1.25 Toric_UV</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>5855</v>
+        <v>8064</v>
       </c>
       <c r="G150" t="n">
-        <v>55</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="151">
@@ -6210,29 +6238,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1160</v>
+        <v>19507</v>
       </c>
       <c r="G151" t="n">
-        <v>65</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="152">
@@ -6243,29 +6271,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>8614</v>
+        <v>12090</v>
       </c>
       <c r="G152" t="n">
-        <v>681</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="153">
@@ -6276,29 +6304,29 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>PIA_LILY BLACK</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>3125</v>
+        <v>4584</v>
       </c>
       <c r="G153" t="n">
-        <v>50</v>
+        <v>807</v>
       </c>
     </row>
     <row r="154">
@@ -6309,29 +6337,29 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>5400</v>
+        <v>1229</v>
       </c>
       <c r="G154" t="n">
-        <v>65</v>
+        <v>462</v>
       </c>
     </row>
     <row r="155">
@@ -6342,29 +6370,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리22호기</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>3355</v>
+        <v>36367</v>
       </c>
       <c r="G155" t="n">
-        <v>225</v>
+        <v>6765</v>
       </c>
     </row>
     <row r="156">
@@ -6375,29 +6403,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리23호기</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>2640</v>
+        <v>35503</v>
       </c>
       <c r="G156" t="n">
-        <v>50</v>
+        <v>9606</v>
       </c>
     </row>
     <row r="157">
@@ -6408,29 +6436,29 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리25호기</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>6670</v>
+        <v>36267</v>
       </c>
       <c r="G157" t="n">
-        <v>155</v>
+        <v>7884</v>
       </c>
     </row>
     <row r="158">
@@ -6441,29 +6469,29 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>9890</v>
+        <v>41946</v>
       </c>
       <c r="G158" t="n">
-        <v>260</v>
+        <v>10013</v>
       </c>
     </row>
     <row r="159">
@@ -6474,29 +6502,29 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>PIA D_Dorayaki_55% UV</t>
+          <t>Cherish Brown_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>2555</v>
+        <v>3437</v>
       </c>
       <c r="G159" t="n">
-        <v>60</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="160">
@@ -6507,29 +6535,29 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>Date Topaz_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>3270</v>
+        <v>8506</v>
       </c>
       <c r="G160" t="n">
-        <v>25</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="161">
@@ -6540,29 +6568,29 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>MARIGOLD_PIA_M</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>9645</v>
+        <v>791</v>
       </c>
       <c r="G161" t="n">
-        <v>190</v>
+        <v>4186</v>
       </c>
     </row>
     <row r="162">
@@ -6573,29 +6601,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>Uniform Black_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>3263</v>
+        <v>2414</v>
       </c>
       <c r="G162" t="n">
-        <v>577</v>
+        <v>366</v>
       </c>
     </row>
     <row r="163">
@@ -6616,19 +6644,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>PIA_LILY BLACK</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>2940</v>
+        <v>3325</v>
       </c>
       <c r="G163" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
     </row>
     <row r="164">
@@ -6649,19 +6677,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>3010</v>
+        <v>9865</v>
       </c>
       <c r="G164" t="n">
-        <v>210</v>
+        <v>85</v>
       </c>
     </row>
     <row r="165">
@@ -6682,19 +6710,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>2810</v>
+        <v>4795</v>
       </c>
       <c r="G165" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="166">
@@ -6715,19 +6743,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>5140</v>
+        <v>2673</v>
       </c>
       <c r="G166" t="n">
-        <v>75</v>
+        <v>632</v>
       </c>
     </row>
     <row r="167">
@@ -6748,19 +6776,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>7360</v>
+        <v>4620</v>
       </c>
       <c r="G167" t="n">
-        <v>390</v>
+        <v>70</v>
       </c>
     </row>
     <row r="168">
@@ -6781,19 +6809,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>10285</v>
+        <v>2370</v>
       </c>
       <c r="G168" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="169">
@@ -6814,19 +6842,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>2246</v>
+        <v>4565</v>
       </c>
       <c r="G169" t="n">
-        <v>1099</v>
+        <v>105</v>
       </c>
     </row>
     <row r="170">
@@ -6847,19 +6875,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>6495</v>
+        <v>3820</v>
       </c>
       <c r="G170" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="171">
@@ -6880,19 +6908,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>4190</v>
+        <v>1060</v>
       </c>
       <c r="G171" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
     </row>
     <row r="172">
@@ -6913,19 +6941,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>6260</v>
+        <v>6373</v>
       </c>
       <c r="G172" t="n">
-        <v>95</v>
+        <v>572</v>
       </c>
     </row>
     <row r="173">
@@ -6946,19 +6974,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2065</v>
+        <v>10655</v>
       </c>
       <c r="G173" t="n">
-        <v>55</v>
+        <v>185</v>
       </c>
     </row>
     <row r="174">
@@ -6979,19 +7007,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1180</v>
+        <v>3450</v>
       </c>
       <c r="G174" t="n">
-        <v>1955</v>
+        <v>65</v>
       </c>
     </row>
     <row r="175">
@@ -7012,19 +7040,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>6070</v>
+        <v>2920</v>
       </c>
       <c r="G175" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="176">
@@ -7045,19 +7073,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>BELLA D_MARS 55%</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>10985</v>
+        <v>10850</v>
       </c>
       <c r="G176" t="n">
-        <v>590</v>
+        <v>100</v>
       </c>
     </row>
     <row r="177">
@@ -7078,19 +7106,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>BELLA D_Siren Bronze 55%</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>4665</v>
+        <v>5245</v>
       </c>
       <c r="G177" t="n">
-        <v>45</v>
+        <v>130</v>
       </c>
     </row>
     <row r="178">
@@ -7111,19 +7139,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>BELLA D_VENUS 55%</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>21325</v>
+        <v>990</v>
       </c>
       <c r="G178" t="n">
-        <v>400</v>
+        <v>35</v>
       </c>
     </row>
     <row r="179">
@@ -7144,19 +7172,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>4065</v>
+        <v>2900</v>
       </c>
       <c r="G179" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
     </row>
     <row r="180">
@@ -7177,19 +7205,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>8105</v>
+        <v>8290</v>
       </c>
       <c r="G180" t="n">
-        <v>135</v>
+        <v>360</v>
       </c>
     </row>
     <row r="181">
@@ -7210,19 +7238,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Cherish Brown_55% UV 14.2</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>6335</v>
+        <v>18635</v>
       </c>
       <c r="G181" t="n">
-        <v>530</v>
+        <v>285</v>
       </c>
     </row>
     <row r="182">
@@ -7243,19 +7271,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>6660</v>
+        <v>1751</v>
       </c>
       <c r="G182" t="n">
-        <v>90</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="183">
@@ -7276,19 +7304,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3370</v>
+        <v>15540</v>
       </c>
       <c r="G183" t="n">
-        <v>20</v>
+        <v>135</v>
       </c>
     </row>
     <row r="184">
@@ -7309,16 +7337,16 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PIA D_Dorayaki_55% UV</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2810</v>
+        <v>3265</v>
       </c>
       <c r="G184" t="n">
         <v>40</v>
@@ -7342,19 +7370,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3160</v>
+        <v>5770</v>
       </c>
       <c r="G185" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
     </row>
     <row r="186">
@@ -7375,19 +7403,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>BELLA D_MARS 55%</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>5530</v>
+        <v>5550</v>
       </c>
       <c r="G186" t="n">
-        <v>75</v>
+        <v>305</v>
       </c>
     </row>
     <row r="187">
@@ -7408,19 +7436,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>BELLA D_Silent Gray 55%</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>8865</v>
+        <v>6690</v>
       </c>
       <c r="G187" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
     </row>
     <row r="188">
@@ -7441,19 +7469,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>BELLA D_Siren Bronze 55%</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>4795</v>
+        <v>1940</v>
       </c>
       <c r="G188" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="189">
@@ -7474,19 +7502,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>BELLA D_VENUS 55%</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>28790</v>
+        <v>4867</v>
       </c>
       <c r="G189" t="n">
-        <v>345</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="190">
@@ -7507,19 +7535,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>HAPA(PIA) D_One&amp;Only Kristin Plus Brown 14.2_38%</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>24565</v>
+        <v>9935</v>
       </c>
       <c r="G190" t="n">
-        <v>1120</v>
+        <v>230</v>
       </c>
     </row>
     <row r="191">
@@ -7540,19 +7568,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>Sincere D_Neutral Brown_UV_38% 14.2</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>9510</v>
+        <v>595</v>
       </c>
       <c r="G191" t="n">
-        <v>170</v>
+        <v>20</v>
       </c>
     </row>
     <row r="192">
@@ -7573,19 +7601,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>2920</v>
+        <v>33285</v>
       </c>
       <c r="G192" t="n">
-        <v>10</v>
+        <v>470</v>
       </c>
     </row>
     <row r="193">
@@ -7606,19 +7634,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>3925</v>
+        <v>25274</v>
       </c>
       <c r="G193" t="n">
-        <v>140</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="194">
@@ -7639,19 +7667,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>PIA D_Dollish Gray_55% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>3010</v>
+        <v>38934</v>
       </c>
       <c r="G194" t="n">
-        <v>55</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="195">
@@ -7672,19 +7700,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>PIA D_Dorayaki_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>925</v>
+        <v>20710</v>
       </c>
       <c r="G195" t="n">
-        <v>45</v>
+        <v>310</v>
       </c>
     </row>
     <row r="196">
@@ -7710,14 +7738,14 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>3450</v>
+        <v>4325</v>
       </c>
       <c r="G196" t="n">
-        <v>20</v>
+        <v>220</v>
       </c>
     </row>
     <row r="197">
@@ -7743,14 +7771,14 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>8720</v>
+        <v>10570</v>
       </c>
       <c r="G197" t="n">
-        <v>760</v>
+        <v>95</v>
       </c>
     </row>
     <row r="198">
@@ -7776,14 +7804,14 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>10200</v>
+        <v>7015</v>
       </c>
       <c r="G198" t="n">
-        <v>100</v>
+        <v>315</v>
       </c>
     </row>
     <row r="199">
@@ -7809,14 +7837,14 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>10060</v>
+        <v>8010</v>
       </c>
       <c r="G199" t="n">
-        <v>210</v>
+        <v>65</v>
       </c>
     </row>
     <row r="200">
@@ -7837,19 +7865,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>2500</v>
+        <v>9450</v>
       </c>
       <c r="G200" t="n">
-        <v>715</v>
+        <v>185</v>
       </c>
     </row>
     <row r="201">
@@ -7870,19 +7898,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>9215</v>
+        <v>2494</v>
       </c>
       <c r="G201" t="n">
-        <v>140</v>
+        <v>831</v>
       </c>
     </row>
     <row r="202">
@@ -7903,19 +7931,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>13905</v>
+        <v>5925</v>
       </c>
       <c r="G202" t="n">
-        <v>245</v>
+        <v>75</v>
       </c>
     </row>
     <row r="203">
@@ -7936,19 +7964,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Hapakristin D_Quiet Kristin Glow Brown</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>3030</v>
+        <v>6425</v>
       </c>
       <c r="G203" t="n">
-        <v>75</v>
+        <v>115</v>
       </c>
     </row>
     <row r="204">
@@ -7974,14 +8002,14 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>IRIS_Rhapsody(NEW)</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>13865</v>
+        <v>2915</v>
       </c>
       <c r="G204" t="n">
-        <v>115</v>
+        <v>55</v>
       </c>
     </row>
     <row r="205">
@@ -8007,14 +8035,14 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>IRIS_Soul Brown(NEW)</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>9015</v>
+        <v>29498</v>
       </c>
       <c r="G205" t="n">
-        <v>210</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="206">
@@ -8035,19 +8063,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>6300</v>
+        <v>21908</v>
       </c>
       <c r="G206" t="n">
-        <v>85</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="207">
@@ -8073,14 +8101,14 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>21205</v>
+        <v>5965</v>
       </c>
       <c r="G207" t="n">
-        <v>270</v>
+        <v>70</v>
       </c>
     </row>
     <row r="208">
@@ -8106,14 +8134,14 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>24122</v>
+        <v>19935</v>
       </c>
       <c r="G208" t="n">
-        <v>768</v>
+        <v>300</v>
       </c>
     </row>
     <row r="209">
@@ -8134,19 +8162,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Hapakristin D_CREME BROWN_Secretive Kristin</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>4165</v>
+        <v>21905</v>
       </c>
       <c r="G209" t="n">
-        <v>125</v>
+        <v>650</v>
       </c>
     </row>
     <row r="210">
@@ -8176,10 +8204,10 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>12409</v>
+        <v>15279</v>
       </c>
       <c r="G210" t="n">
-        <v>771</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="211">
@@ -8209,10 +8237,10 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>3890</v>
+        <v>30405</v>
       </c>
       <c r="G211" t="n">
-        <v>105</v>
+        <v>435</v>
       </c>
     </row>
     <row r="212">
@@ -8242,10 +8270,10 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>17835</v>
+        <v>9915</v>
       </c>
       <c r="G212" t="n">
-        <v>260</v>
+        <v>145</v>
       </c>
     </row>
     <row r="213">
@@ -8271,14 +8299,14 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>IRIS_Soul Brown(NEW)</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1840</v>
+        <v>6135</v>
       </c>
       <c r="G213" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="214">
@@ -8304,14 +8332,14 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA D_Jelly Gray_38% UV</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>4205</v>
+        <v>13690</v>
       </c>
       <c r="G214" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
     </row>
     <row r="215">
@@ -8337,14 +8365,14 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>PIA D_Sugar Donut_38% UV</t>
+          <t>PIA D_Pomme Canele_38% UV</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>14107</v>
+        <v>17960</v>
       </c>
       <c r="G215" t="n">
-        <v>623</v>
+        <v>315</v>
       </c>
     </row>
     <row r="216">
@@ -8370,14 +8398,14 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>PIA D_Puree Greige_38% UV</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>3300</v>
+        <v>12195</v>
       </c>
       <c r="G216" t="n">
-        <v>45</v>
+        <v>190</v>
       </c>
     </row>
     <row r="217">
@@ -8403,14 +8431,14 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Sugar Donut_38% UV</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>8830</v>
+        <v>2785</v>
       </c>
       <c r="G217" t="n">
-        <v>190</v>
+        <v>50</v>
       </c>
     </row>
     <row r="218">
@@ -8431,19 +8459,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>8655</v>
+        <v>16925</v>
       </c>
       <c r="G218" t="n">
-        <v>135</v>
+        <v>260</v>
       </c>
     </row>
     <row r="219">
@@ -8464,19 +8492,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F219" t="n">
-        <v>58339</v>
+        <v>2770</v>
       </c>
       <c r="G219" t="n">
-        <v>1661</v>
+        <v>55</v>
       </c>
     </row>
     <row r="220">
@@ -8502,14 +8530,14 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>24621</v>
+        <v>15235</v>
       </c>
       <c r="G220" t="n">
-        <v>1409</v>
+        <v>265</v>
       </c>
     </row>
     <row r="221">
@@ -8535,14 +8563,14 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>2795</v>
+        <v>29386</v>
       </c>
       <c r="G221" t="n">
-        <v>70</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="222">
@@ -8563,19 +8591,19 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F222" t="n">
-        <v>12345</v>
+        <v>5890</v>
       </c>
       <c r="G222" t="n">
-        <v>145</v>
+        <v>65</v>
       </c>
     </row>
     <row r="223">
@@ -8596,16 +8624,16 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F223" t="n">
-        <v>9195</v>
+        <v>5750</v>
       </c>
       <c r="G223" t="n">
         <v>140</v>
@@ -8629,19 +8657,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>PIA_KEOPI BROWN</t>
+          <t>Gemhour D_Liz Brown_Keira</t>
         </is>
       </c>
       <c r="F224" t="n">
-        <v>2360</v>
+        <v>2815</v>
       </c>
       <c r="G224" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="225">
@@ -8667,14 +8695,14 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>3070</v>
+        <v>9605</v>
       </c>
       <c r="G225" t="n">
-        <v>15</v>
+        <v>205</v>
       </c>
     </row>
     <row r="226">
@@ -8700,14 +8728,14 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>2927</v>
+        <v>8790</v>
       </c>
       <c r="G226" t="n">
-        <v>453</v>
+        <v>115</v>
       </c>
     </row>
     <row r="227">
@@ -8728,19 +8756,19 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>3070</v>
+        <v>55935</v>
       </c>
       <c r="G227" t="n">
-        <v>40</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="228">
@@ -8761,19 +8789,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Alcon D_Chic Caramel_W4(KR)</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>1110</v>
+        <v>2720</v>
       </c>
       <c r="G228" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="229">
@@ -8794,19 +8822,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Alcon D_Chic Smoke_W4(KR)</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>6670</v>
+        <v>8805</v>
       </c>
       <c r="G229" t="n">
-        <v>135</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="230">
@@ -8827,19 +8855,19 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Black_W3(KR)</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>2965</v>
+        <v>3830</v>
       </c>
       <c r="G230" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="231">
@@ -8860,19 +8888,19 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F231" t="n">
-        <v>47678</v>
+        <v>1305</v>
       </c>
       <c r="G231" t="n">
-        <v>1537</v>
+        <v>20</v>
       </c>
     </row>
     <row r="232">
@@ -8893,19 +8921,19 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F232" t="n">
-        <v>6365</v>
+        <v>25451</v>
       </c>
       <c r="G232" t="n">
-        <v>80</v>
+        <v>574</v>
       </c>
     </row>
     <row r="233">
@@ -8931,14 +8959,14 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F233" t="n">
-        <v>955</v>
+        <v>2965</v>
       </c>
       <c r="G233" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="234">
@@ -8964,14 +8992,14 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F234" t="n">
-        <v>40549</v>
+        <v>2265</v>
       </c>
       <c r="G234" t="n">
-        <v>1151</v>
+        <v>35</v>
       </c>
     </row>
     <row r="235">
@@ -8987,24 +9015,24 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F235" t="n">
-        <v>3470</v>
+        <v>0</v>
       </c>
       <c r="G235" t="n">
-        <v>55</v>
+        <v>825</v>
       </c>
     </row>
     <row r="236">
@@ -9025,19 +9053,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-0.75 Brown Bunny_55% UV</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>1705</v>
+        <v>9250</v>
       </c>
       <c r="G236" t="n">
-        <v>25</v>
+        <v>155</v>
       </c>
     </row>
     <row r="237">
@@ -9058,19 +9086,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>762</v>
+        <v>2915</v>
       </c>
       <c r="G237" t="n">
-        <v>788</v>
+        <v>45</v>
       </c>
     </row>
     <row r="238">
@@ -9100,10 +9128,10 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>6205</v>
+        <v>3150</v>
       </c>
       <c r="G238" t="n">
-        <v>130</v>
+        <v>75</v>
       </c>
     </row>
     <row r="239">
@@ -9133,10 +9161,10 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>9185</v>
+        <v>1220</v>
       </c>
       <c r="G239" t="n">
-        <v>195</v>
+        <v>20</v>
       </c>
     </row>
     <row r="240">
@@ -9157,7 +9185,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -9166,10 +9194,10 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>4495</v>
+        <v>11090</v>
       </c>
       <c r="G240" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
     </row>
     <row r="241">
@@ -9190,7 +9218,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -9199,10 +9227,10 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>12095</v>
+        <v>11060</v>
       </c>
       <c r="G241" t="n">
-        <v>180</v>
+        <v>155</v>
       </c>
     </row>
     <row r="242">
@@ -9223,7 +9251,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -9232,10 +9260,10 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>6750</v>
+        <v>13525</v>
       </c>
       <c r="G242" t="n">
-        <v>75</v>
+        <v>185</v>
       </c>
     </row>
     <row r="243">
@@ -9265,10 +9293,10 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>12350</v>
+        <v>6170</v>
       </c>
       <c r="G243" t="n">
-        <v>170</v>
+        <v>105</v>
       </c>
     </row>
     <row r="244">
@@ -9298,10 +9326,10 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>20587</v>
+        <v>8310</v>
       </c>
       <c r="G244" t="n">
-        <v>1143</v>
+        <v>225</v>
       </c>
     </row>
     <row r="245">
@@ -9331,10 +9359,10 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>4895</v>
+        <v>2755</v>
       </c>
       <c r="G245" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="246">
@@ -9360,14 +9388,14 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>PIA_Opal CP-1.25 Toric_UV</t>
+          <t>PIA_Opal CP-0.75 Toric_UV</t>
         </is>
       </c>
       <c r="F246" t="n">
-        <v>1085</v>
+        <v>7405</v>
       </c>
       <c r="G246" t="n">
-        <v>15</v>
+        <v>250</v>
       </c>
     </row>
     <row r="247">
@@ -9383,24 +9411,24 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>1-Day_58(NEW)</t>
+          <t>PIA_Opal CP-1.25 Toric_UV</t>
         </is>
       </c>
       <c r="F247" t="n">
-        <v>6395</v>
+        <v>1505</v>
       </c>
       <c r="G247" t="n">
-        <v>215</v>
+        <v>40</v>
       </c>
     </row>
     <row r="248">
@@ -9421,19 +9449,19 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>1-Day_58(수출용_파랑)</t>
+          <t>1-Day_SOLEKO(5년)</t>
         </is>
       </c>
       <c r="F248" t="n">
-        <v>9055</v>
+        <v>19540</v>
       </c>
       <c r="G248" t="n">
-        <v>470</v>
+        <v>430</v>
       </c>
     </row>
     <row r="249">
@@ -9454,30 +9482,30 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>1-Day_Contakt-HA</t>
+          <t>1-Day_SOLEKO(5년)</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>12505</v>
+        <v>23895</v>
       </c>
       <c r="G249" t="n">
-        <v>330</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9487,19 +9515,19 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>Sincere D_Clear_38%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>20480</v>
+        <v>17456</v>
       </c>
       <c r="G250" t="n">
-        <v>715</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -9515,24 +9543,24 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>B형 조립중합4호기</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Sincere D_Clear_38%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>32641</v>
+        <v>11236</v>
       </c>
       <c r="G251" t="n">
-        <v>0</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="252">
@@ -9553,19 +9581,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>B형 조립중합4호기</t>
+          <t>B형 조립중합5호기</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>15371</v>
+        <v>43666</v>
       </c>
       <c r="G252" t="n">
-        <v>1237</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="253">
@@ -9595,10 +9623,10 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>11025</v>
+        <v>7870</v>
       </c>
       <c r="G253" t="n">
-        <v>6615</v>
+        <v>4722</v>
       </c>
     </row>
     <row r="254">
@@ -9628,7 +9656,7 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>42730</v>
+        <v>39861</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
@@ -9661,7 +9689,7 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>42848</v>
+        <v>41135</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -9685,19 +9713,19 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>CAM분리3호기</t>
+          <t>CAM분리1호기</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>Sincere D_Clear_38%</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>4170</v>
+        <v>12697</v>
       </c>
       <c r="G256" t="n">
-        <v>401</v>
+        <v>4031</v>
       </c>
     </row>
     <row r="257">
@@ -9727,10 +9755,10 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>18079</v>
+        <v>19161</v>
       </c>
       <c r="G257" t="n">
-        <v>3611</v>
+        <v>4097</v>
       </c>
     </row>
     <row r="258">
@@ -9756,14 +9784,14 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F258" t="n">
-        <v>10859</v>
+        <v>7077</v>
       </c>
       <c r="G258" t="n">
-        <v>1739</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="259">
@@ -9789,14 +9817,14 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F259" t="n">
-        <v>5291</v>
+        <v>4275</v>
       </c>
       <c r="G259" t="n">
-        <v>1088</v>
+        <v>527</v>
       </c>
     </row>
     <row r="260">
@@ -9822,14 +9850,14 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Gray EX</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F260" t="n">
-        <v>2023</v>
+        <v>4798</v>
       </c>
       <c r="G260" t="n">
-        <v>183</v>
+        <v>951</v>
       </c>
     </row>
     <row r="261">
@@ -9859,10 +9887,10 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>1508</v>
+        <v>2122</v>
       </c>
       <c r="G261" t="n">
-        <v>633</v>
+        <v>377</v>
       </c>
     </row>
     <row r="262">
@@ -9892,10 +9920,10 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>14173</v>
+        <v>12582</v>
       </c>
       <c r="G262" t="n">
-        <v>2614</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="263">
@@ -9925,10 +9953,10 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>9890</v>
+        <v>8773</v>
       </c>
       <c r="G263" t="n">
-        <v>4020</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="264">
@@ -9954,14 +9982,14 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F264" t="n">
-        <v>2877</v>
+        <v>553</v>
       </c>
       <c r="G264" t="n">
-        <v>959</v>
+        <v>484</v>
       </c>
     </row>
     <row r="265">
@@ -9982,19 +10010,19 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F265" t="n">
-        <v>4350</v>
+        <v>18481</v>
       </c>
       <c r="G265" t="n">
-        <v>876</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="266">
@@ -10010,24 +10038,24 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F266" t="n">
-        <v>11683</v>
+        <v>13338</v>
       </c>
       <c r="G266" t="n">
-        <v>3391</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="267">
@@ -10043,24 +10071,24 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F267" t="n">
-        <v>3520</v>
+        <v>14299</v>
       </c>
       <c r="G267" t="n">
-        <v>361</v>
+        <v>882</v>
       </c>
     </row>
     <row r="268">
@@ -10076,24 +10104,24 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>B형 분리수화접착3호기</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>3864</v>
+        <v>10206</v>
       </c>
       <c r="G268" t="n">
-        <v>558</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="269">
@@ -10114,7 +10142,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착4호기</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -10123,10 +10151,10 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>29636</v>
+        <v>13341</v>
       </c>
       <c r="G269" t="n">
-        <v>1080</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="270">
@@ -10137,29 +10165,29 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen D_Canola Brown</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>27235</v>
+        <v>2800</v>
       </c>
       <c r="G270" t="n">
-        <v>732</v>
+        <v>50</v>
       </c>
     </row>
     <row r="271">
@@ -10170,29 +10198,29 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen D_Mimosa Brown</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>12589</v>
+        <v>4855</v>
       </c>
       <c r="G271" t="n">
-        <v>2370</v>
+        <v>90</v>
       </c>
     </row>
     <row r="272">
@@ -10203,29 +10231,29 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>sincere Natural 1day</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>10588</v>
+        <v>5625</v>
       </c>
       <c r="G272" t="n">
-        <v>2457</v>
+        <v>45</v>
       </c>
     </row>
     <row r="273">
@@ -10241,24 +10269,24 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>BELLA D_Star</t>
+          <t>sincere Natural 1day</t>
         </is>
       </c>
       <c r="F273" t="n">
-        <v>6720</v>
+        <v>16446</v>
       </c>
       <c r="G273" t="n">
-        <v>238</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="274">
@@ -10274,24 +10302,24 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>DYE D_LAVA</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>6665</v>
+        <v>6962</v>
       </c>
       <c r="G274" t="n">
-        <v>167</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="275">
@@ -10307,24 +10335,24 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Clalen oneday A(O2 Edition)</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F275" t="n">
-        <v>12100</v>
+        <v>6290</v>
       </c>
       <c r="G275" t="n">
-        <v>659</v>
+        <v>650</v>
       </c>
     </row>
     <row r="276">
@@ -10350,14 +10378,14 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>17240</v>
+        <v>26840</v>
       </c>
       <c r="G276" t="n">
-        <v>1364</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="277">
@@ -10378,19 +10406,19 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F277" t="n">
-        <v>12355</v>
+        <v>3295</v>
       </c>
       <c r="G277" t="n">
-        <v>176</v>
+        <v>118</v>
       </c>
     </row>
     <row r="278">
@@ -10411,19 +10439,19 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>23610</v>
+        <v>2854</v>
       </c>
       <c r="G278" t="n">
-        <v>1097</v>
+        <v>535</v>
       </c>
     </row>
     <row r="279">
@@ -10444,19 +10472,19 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>4250</v>
+        <v>2359</v>
       </c>
       <c r="G279" t="n">
-        <v>208</v>
+        <v>305</v>
       </c>
     </row>
     <row r="280">
@@ -10477,19 +10505,19 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>A형 인라인6호기</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>2800</v>
+        <v>2640</v>
       </c>
       <c r="G280" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
     </row>
     <row r="281">
@@ -10510,19 +10538,19 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>A형 인라인6호기</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>3130</v>
+        <v>1730</v>
       </c>
       <c r="G281" t="n">
-        <v>192</v>
+        <v>29</v>
       </c>
     </row>
     <row r="282">
@@ -10543,19 +10571,19 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>A형 인라인6호기</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F282" t="n">
-        <v>1775</v>
+        <v>7035</v>
       </c>
       <c r="G282" t="n">
-        <v>18</v>
+        <v>379</v>
       </c>
     </row>
     <row r="283">
@@ -10571,24 +10599,24 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
       <c r="F283" t="n">
-        <v>8105</v>
+        <v>38423</v>
       </c>
       <c r="G283" t="n">
-        <v>431</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="284">
@@ -10604,24 +10632,24 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
       <c r="F284" t="n">
-        <v>1120</v>
+        <v>45712</v>
       </c>
       <c r="G284" t="n">
-        <v>61</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="285">
@@ -10637,24 +10665,24 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
       <c r="F285" t="n">
-        <v>5540</v>
+        <v>11830</v>
       </c>
       <c r="G285" t="n">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
     <row r="286">
@@ -10670,7 +10698,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -10680,14 +10708,14 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMDH_WHITE_OPHTALMIC</t>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
       <c r="F286" t="n">
-        <v>2095</v>
+        <v>7215</v>
       </c>
       <c r="G286" t="n">
-        <v>31</v>
+        <v>123</v>
       </c>
     </row>
     <row r="287">
@@ -10708,7 +10736,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>A형 인라인6호기</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -10717,175 +10745,10 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>7350</v>
+        <v>22630</v>
       </c>
       <c r="G287" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>A형 인라인2호기</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
-        </is>
-      </c>
-      <c r="F288" t="n">
-        <v>36318</v>
-      </c>
-      <c r="G288" t="n">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>A형 인라인3호기</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
-        </is>
-      </c>
-      <c r="F289" t="n">
-        <v>39967</v>
-      </c>
-      <c r="G289" t="n">
-        <v>2649</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>A형 인라인4호기</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
-        </is>
-      </c>
-      <c r="F290" t="n">
-        <v>31760</v>
-      </c>
-      <c r="G290" t="n">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>A형 인라인5호기</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
-        </is>
-      </c>
-      <c r="F291" t="n">
-        <v>30577</v>
-      </c>
-      <c r="G291" t="n">
-        <v>1796</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>A형 인라인6호기</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
-        </is>
-      </c>
-      <c r="F292" t="n">
-        <v>2270</v>
-      </c>
-      <c r="G292" t="n">
-        <v>15</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>

--- a/생산실적현황(설비운영현황).xlsx
+++ b/생산실적현황(설비운영현황).xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>(NEW)S38-HD-Dry-14.0</t>
+          <t>US55-2(M)</t>
         </is>
       </c>
     </row>
@@ -537,11 +537,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -549,7 +549,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>O2O2 Spherical(DK70)_K2-SMD</t>
+          <t>T55_소사각</t>
         </is>
       </c>
     </row>
@@ -561,23 +561,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>(UV_NEW)CS30_8.60</t>
+          <t>O2O2 Spherical(DK70)_K2-SMD</t>
         </is>
       </c>
     </row>
@@ -589,15 +589,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>Si_1-Day_Toric</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -605,7 +605,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>T38_(UV포함)</t>
+          <t>O2O2 D_UV_Toric_SMD</t>
         </is>
       </c>
     </row>
@@ -617,23 +617,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bella-Elite_14.5_중사각</t>
+          <t>S55</t>
         </is>
       </c>
     </row>
@@ -645,23 +645,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>T55_소사각</t>
         </is>
       </c>
     </row>
@@ -681,15 +681,15 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>T38_금캡(UV포함)</t>
+          <t>Bella-Natural_중사각</t>
         </is>
       </c>
     </row>
@@ -709,15 +709,15 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Silicone relax_소사각</t>
+          <t>Metha_55_중사각</t>
         </is>
       </c>
     </row>
@@ -737,63 +737,63 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>T38_금캡(UV포함)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Silicone relax_소사각</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
     </row>
@@ -817,19 +817,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Date Topaz_PIA_M(Y)</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
     </row>
@@ -841,23 +841,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
     </row>
@@ -869,23 +869,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>Cream Rose_PIA_M</t>
         </is>
       </c>
     </row>
@@ -905,15 +905,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
     </row>
@@ -925,23 +925,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
     </row>
@@ -953,23 +953,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
     </row>
@@ -989,35 +989,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1025,27 +1025,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sincere D_Clear_38%</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>1-Day_SOLEKO(5년)</t>
         </is>
       </c>
     </row>
@@ -1073,15 +1073,15 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen D_Pink Tulip Brown</t>
         </is>
       </c>
     </row>
@@ -1093,11 +1093,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1133,11 +1133,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 D_Ash Brown EX</t>
         </is>
       </c>
     </row>
@@ -1149,11 +1149,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1177,23 +1177,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>sincere Natural 1day</t>
+          <t>Clalen D_Pink Tulip Brown</t>
         </is>
       </c>
     </row>
@@ -1205,15 +1205,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Sincere D_Clear_38%</t>
         </is>
       </c>
     </row>
@@ -1233,21 +1233,133 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>4</v>
       </c>
       <c r="F29" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>[20] 분리</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>11</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>sincere Natural 1day</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
@@ -1264,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G287"/>
+  <dimension ref="A1:G286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1340,10 +1452,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>45513</v>
+        <v>96527</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>582</v>
       </c>
     </row>
     <row r="3">
@@ -1373,10 +1485,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>95692</v>
+        <v>44984</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="4">
@@ -1406,10 +1518,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>94079</v>
+        <v>47065</v>
       </c>
       <c r="G4" t="n">
-        <v>1581</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="5">
@@ -1439,7 +1551,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>19925</v>
+        <v>20180</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1472,10 +1584,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>34130</v>
+        <v>18927</v>
       </c>
       <c r="G6" t="n">
-        <v>959</v>
+        <v>576</v>
       </c>
     </row>
     <row r="7">
@@ -1501,14 +1613,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(NEW)S38-HD-Dry-14.0</t>
+          <t>(NEW)S38-Dry-14.2</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>35761</v>
+        <v>19166</v>
       </c>
       <c r="G7" t="n">
-        <v>857</v>
+        <v>404</v>
       </c>
     </row>
     <row r="8">
@@ -1524,21 +1636,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>조립4호기</t>
+          <t>조립8호기</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>O2O2 Spherical(DK70)_K2-SMD</t>
+          <t>(NEW)S38-HD-Dry-14.0</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>38501</v>
+        <v>17766</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1552,29 +1664,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>분리10호기</t>
+          <t>조립2호기</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(UV_NEW)CS30_8.60</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8759</v>
+        <v>3208</v>
       </c>
       <c r="G9" t="n">
-        <v>1425</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="10">
@@ -1585,29 +1697,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>분리10호기</t>
+          <t>조립4호기</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS30-Dry</t>
+          <t>O2O2 Spherical(DK70)_K2-SMD</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3886</v>
+        <v>18256</v>
       </c>
       <c r="G10" t="n">
-        <v>664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1618,29 +1730,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>Si_1-Day_Toric</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>분리11호기</t>
+          <t>조립7호기</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(UV_NEW)CS30_8.60</t>
+          <t>O2O2 D_UV_Toric_SMD</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>9666</v>
+        <v>4177</v>
       </c>
       <c r="G11" t="n">
-        <v>2074</v>
+        <v>597</v>
       </c>
     </row>
     <row r="12">
@@ -1661,19 +1773,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>분리14호기</t>
+          <t>분리10호기</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>CS30-Dry</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4549</v>
+        <v>12882</v>
       </c>
       <c r="G12" t="n">
-        <v>1987</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="13">
@@ -1694,19 +1806,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>분리4호기</t>
+          <t>분리11호기</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(NEW)S38-HD-Dry-14.0</t>
+          <t>(UV_NEW)CS30_8.60</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>8074</v>
+        <v>14893</v>
       </c>
       <c r="G13" t="n">
-        <v>2412</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="14">
@@ -1727,19 +1839,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>분리4호기</t>
+          <t>분리14호기</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.2</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5885</v>
+        <v>5882</v>
       </c>
       <c r="G14" t="n">
-        <v>1327</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="15">
@@ -1760,19 +1872,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>분리5호기</t>
+          <t>분리4호기</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>(NEW)S38-HD-Dry-14.0</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2090</v>
+        <v>9998</v>
       </c>
       <c r="G15" t="n">
-        <v>1792</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="16">
@@ -1798,14 +1910,14 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>US55-2(M)</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5450</v>
+        <v>10778</v>
       </c>
       <c r="G16" t="n">
-        <v>1366</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="17">
@@ -1821,24 +1933,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>분리3호기</t>
+          <t>분리5호기</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>T38_(UV포함)</t>
+          <t>US55-2(M)</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3275</v>
+        <v>1740</v>
       </c>
       <c r="G17" t="n">
-        <v>924</v>
+        <v>727</v>
       </c>
     </row>
     <row r="18">
@@ -1868,10 +1980,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>403</v>
+        <v>2107</v>
       </c>
       <c r="G18" t="n">
-        <v>972</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="19">
@@ -1892,19 +2004,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NewFusion_소사각</t>
+          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>104</v>
+        <v>1274</v>
       </c>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -1925,19 +2037,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Clalen 6M_KUTAO_38%_(중)</t>
+          <t>FLAMINGO_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1350</v>
+        <v>1479</v>
       </c>
       <c r="G20" t="n">
-        <v>103</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21">
@@ -1958,19 +2070,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Clalen 6M_WEIGUANG_38%_(중)</t>
+          <t>Oolong Tea_PIA_M_중사각(Y)</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>912</v>
+        <v>940</v>
       </c>
       <c r="G21" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22">
@@ -1991,19 +2103,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Clalen 6M_YOUYU_38%_(중)</t>
+          <t>Princess Chocolat_PIA_M_(중)_14.5</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>610</v>
+        <v>948</v>
       </c>
       <c r="G22" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
@@ -2024,19 +2136,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CLC-30_원형</t>
+          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>29</v>
+        <v>934</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
@@ -2057,19 +2169,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Intensive 55_원형</t>
+          <t>Date Topaz_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>84</v>
+        <v>1882</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25">
@@ -2090,19 +2202,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NewFusion_원형</t>
+          <t>Sakura Smore_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>402</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
@@ -2123,19 +2235,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bella-Contour_중사각</t>
+          <t>Tiramisu Ring_PIA_M_중사각(Y)</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>52</v>
+        <v>1436</v>
       </c>
       <c r="G26" t="n">
-        <v>157</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
@@ -2156,19 +2268,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bella-Elite_14.5_중사각</t>
+          <t>CLC-30_원형</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1988</v>
+        <v>82</v>
       </c>
       <c r="G27" t="n">
-        <v>95</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
@@ -2189,19 +2301,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bella-Natural_14.5_중사각</t>
+          <t>NewFusion_원형</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>942</v>
+        <v>54</v>
       </c>
       <c r="G28" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
@@ -2227,14 +2339,14 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cihan Elegance_중사각</t>
+          <t>Bella Diamond_14.5_중사각</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>18</v>
+        <v>420</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30">
@@ -2260,14 +2372,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DYE M_NOLA_14.5_중사각</t>
+          <t>Bella Glow_중사각</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2100</v>
+        <v>466</v>
       </c>
       <c r="G30" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
@@ -2293,14 +2405,14 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>DYE M_SILVER LACE_14.5_중사각</t>
+          <t>Bella-Contour_중사각</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>125</v>
+        <v>402</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32">
@@ -2326,14 +2438,14 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DYE M_START DUST_14.5_중사각</t>
+          <t>Bella-Elite_14.5_중사각</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>132</v>
+        <v>968</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33">
@@ -2354,19 +2466,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bella Diamond_14.5_중사각</t>
+          <t>Bella-Natural_중사각</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>272</v>
+        <v>2200</v>
       </c>
       <c r="G33" t="n">
-        <v>26</v>
+        <v>759</v>
       </c>
     </row>
     <row r="34">
@@ -2387,19 +2499,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bella Glow_중사각</t>
+          <t>Clalen 6M_WEIGUANG_38%_(중)</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>438</v>
+        <v>136</v>
       </c>
       <c r="G34" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35">
@@ -2420,19 +2532,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bella-Contour_중사각</t>
+          <t>Dazzle Beige_2T_(PBT)PIA_M(Y)</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>176</v>
+        <v>400</v>
       </c>
       <c r="G35" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2453,19 +2565,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bella-Elite_14.5_중사각</t>
+          <t>MARIGOLD_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1626</v>
+        <v>72</v>
       </c>
       <c r="G36" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2486,19 +2598,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>Tiramisu Ring_PIA_M_중사각(Y)</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3172</v>
+        <v>349</v>
       </c>
       <c r="G37" t="n">
-        <v>2185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2524,14 +2636,14 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oolong Tea_PIA_M_중사각(Y)</t>
+          <t>Bella Diamond_14.5_중사각</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>894</v>
+        <v>768</v>
       </c>
       <c r="G38" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39">
@@ -2552,19 +2664,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Advance_CB_원형</t>
+          <t>Bella Glow_중사각</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="G39" t="n">
-        <v>1220</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
@@ -2585,19 +2697,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bella-SnowWhite_14.5_원형</t>
+          <t>Bella-Contour_중사각</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>244</v>
+        <v>514</v>
       </c>
       <c r="G40" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41">
@@ -2618,19 +2730,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CLC-30_원형</t>
+          <t>Bella-Natural_14.5_중사각</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1580</v>
+        <v>1180</v>
       </c>
       <c r="G41" t="n">
-        <v>671</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
@@ -2651,19 +2763,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>NewFusion_원형</t>
+          <t>Bella-Natural_중사각</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>42</v>
+        <v>576</v>
       </c>
       <c r="G42" t="n">
-        <v>57</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43">
@@ -2684,19 +2796,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CLC-30_바이알</t>
+          <t>CLC-30_원형</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>275</v>
+        <v>776</v>
       </c>
       <c r="G43" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -2712,24 +2824,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>KBS-C_원형</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2176</v>
+        <v>180</v>
       </c>
       <c r="G44" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
@@ -2745,24 +2857,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>NewFusion_원형</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1936</v>
+        <v>708</v>
       </c>
       <c r="G45" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46">
@@ -2778,24 +2890,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>CLC-30_바이알</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>304</v>
+        <v>1249</v>
       </c>
       <c r="G46" t="n">
-        <v>188</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47">
@@ -2811,24 +2923,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>Festival-II-Color_은캡</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>907</v>
+        <v>1629</v>
       </c>
       <c r="G47" t="n">
-        <v>128</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48">
@@ -2849,19 +2961,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Metha_55_중사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>6162</v>
+        <v>4176</v>
       </c>
       <c r="G48" t="n">
-        <v>192</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49">
@@ -2882,7 +2994,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2891,10 +3003,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>4340</v>
+        <v>4686</v>
       </c>
       <c r="G49" t="n">
-        <v>549</v>
+        <v>329</v>
       </c>
     </row>
     <row r="50">
@@ -2920,14 +3032,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1362</v>
+        <v>3590</v>
       </c>
       <c r="G50" t="n">
-        <v>136</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
@@ -2948,19 +3060,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Metha_55_중사각</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>324</v>
+        <v>2024</v>
       </c>
       <c r="G51" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
@@ -2981,19 +3093,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>Metha_55_중사각</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2050</v>
+        <v>1200</v>
       </c>
       <c r="G52" t="n">
-        <v>57</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53">
@@ -3014,19 +3126,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Metha_55_원형</t>
+          <t>Metha_55_중사각</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2654</v>
+        <v>11476</v>
       </c>
       <c r="G53" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54">
@@ -3042,24 +3154,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>760</v>
+        <v>1744</v>
       </c>
       <c r="G54" t="n">
-        <v>149</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55">
@@ -3075,24 +3187,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>Metha_55_원형</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>851</v>
+        <v>1784</v>
       </c>
       <c r="G55" t="n">
-        <v>333</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56">
@@ -3113,19 +3225,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>T38_금캡</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>837</v>
+        <v>680</v>
       </c>
       <c r="G56" t="n">
-        <v>94</v>
+        <v>467</v>
       </c>
     </row>
     <row r="57">
@@ -3146,19 +3258,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>T38_금캡(UV포함)</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>5627</v>
+        <v>1132</v>
       </c>
       <c r="G57" t="n">
-        <v>847</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58">
@@ -3174,24 +3286,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Silicone relax_소사각</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>4428</v>
+        <v>440</v>
       </c>
       <c r="G58" t="n">
-        <v>473</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59">
@@ -3207,24 +3319,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>480</v>
+        <v>964</v>
       </c>
       <c r="G59" t="n">
-        <v>319</v>
+        <v>238</v>
       </c>
     </row>
     <row r="60">
@@ -3240,24 +3352,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Silicone relax_소사각</t>
+          <t>T38_금캡(UV포함)</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3452</v>
+        <v>3457</v>
       </c>
       <c r="G60" t="n">
-        <v>199</v>
+        <v>756</v>
       </c>
     </row>
     <row r="61">
@@ -3273,7 +3385,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3283,14 +3395,14 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>5254</v>
+        <v>1034</v>
       </c>
       <c r="G61" t="n">
-        <v>453</v>
+        <v>297</v>
       </c>
     </row>
     <row r="62">
@@ -3306,24 +3418,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2888</v>
+        <v>396</v>
       </c>
       <c r="G62" t="n">
-        <v>746</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63">
@@ -3339,7 +3451,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3349,14 +3461,14 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>10201</v>
+        <v>1674</v>
       </c>
       <c r="G63" t="n">
-        <v>932</v>
+        <v>179</v>
       </c>
     </row>
     <row r="64">
@@ -3372,156 +3484,156 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Si_FRP_Toric</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>O2O2 M_UV_Toric_SMD_(소)</t>
+          <t>Silicone relax_소사각</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2388</v>
+        <v>3788</v>
       </c>
       <c r="G64" t="n">
-        <v>816</v>
+        <v>497</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>조립10호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1-Day_iris_Latin</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>48582</v>
+        <v>6074</v>
       </c>
       <c r="G65" t="n">
-        <v>3273</v>
+        <v>933</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>조립11호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PIA D_Sakana_55% UV</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>23074</v>
+        <v>1060</v>
       </c>
       <c r="G66" t="n">
-        <v>2460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>조립12호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>29147</v>
+        <v>3263</v>
       </c>
       <c r="G67" t="n">
-        <v>3387</v>
+        <v>525</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Toric</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>조립13호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>O2O2 M_UV_Toric_SMD_(소)</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>52170</v>
+        <v>673</v>
       </c>
       <c r="G68" t="n">
-        <v>408</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69">
@@ -3542,19 +3654,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>조립14호기</t>
+          <t>조립10호기</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_Latin</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>22061</v>
+        <v>27174</v>
       </c>
       <c r="G69" t="n">
-        <v>3364</v>
+        <v>665</v>
       </c>
     </row>
     <row r="70">
@@ -3575,19 +3687,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>조립15호기</t>
+          <t>조립11호기</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>PIA D_Sakana_55% UV</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>21828</v>
+        <v>27901</v>
       </c>
       <c r="G70" t="n">
-        <v>5113</v>
+        <v>550</v>
       </c>
     </row>
     <row r="71">
@@ -3608,19 +3720,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>조립16호기</t>
+          <t>조립12호기</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>23579</v>
+        <v>27332</v>
       </c>
       <c r="G71" t="n">
-        <v>4187</v>
+        <v>921</v>
       </c>
     </row>
     <row r="72">
@@ -3641,19 +3753,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>조립20호기</t>
+          <t>조립14호기</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>16013</v>
+        <v>23280</v>
       </c>
       <c r="G72" t="n">
-        <v>1048</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="73">
@@ -3674,19 +3786,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>조립24호기</t>
+          <t>조립14호기</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>27719</v>
+        <v>22147</v>
       </c>
       <c r="G73" t="n">
-        <v>2954</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="74">
@@ -3707,19 +3819,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>조립25호기</t>
+          <t>조립15호기</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>17306</v>
+        <v>19654</v>
       </c>
       <c r="G74" t="n">
-        <v>2523</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="75">
@@ -3740,19 +3852,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>조립26호기</t>
+          <t>조립16호기</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>28659</v>
+        <v>26495</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="76">
@@ -3773,19 +3885,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>조립27호기</t>
+          <t>조립19호기</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>28628</v>
+        <v>23921</v>
       </c>
       <c r="G76" t="n">
-        <v>8943</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="77">
@@ -3806,19 +3918,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>조립40호기</t>
+          <t>조립20호기</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>4751</v>
+        <v>20704</v>
       </c>
       <c r="G77" t="n">
-        <v>35</v>
+        <v>3939</v>
       </c>
     </row>
     <row r="78">
@@ -3839,19 +3951,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>조립44호기</t>
+          <t>조립24호기</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_First Love Kristin Brown 14.2_38% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>12842</v>
+        <v>32851</v>
       </c>
       <c r="G78" t="n">
-        <v>6091</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="79">
@@ -3872,19 +3984,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>조립45호기</t>
+          <t>조립25호기</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1-Day_iris_Latin</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>50109</v>
+        <v>25668</v>
       </c>
       <c r="G79" t="n">
-        <v>7298</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="80">
@@ -3905,19 +4017,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>조립47호기</t>
+          <t>조립26호기</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>BELLA D_VENUS 55%</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>29854</v>
+        <v>14945</v>
       </c>
       <c r="G80" t="n">
-        <v>1519</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="81">
@@ -3938,19 +4050,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>조립48호기</t>
+          <t>조립27호기</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>21781</v>
+        <v>23764</v>
       </c>
       <c r="G81" t="n">
-        <v>2007</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="82">
@@ -3971,19 +4083,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>조립49호기</t>
+          <t>조립40호기</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>22952</v>
+        <v>38711</v>
       </c>
       <c r="G82" t="n">
-        <v>2745</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="83">
@@ -4004,19 +4116,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>조립50호기</t>
+          <t>조립42호기</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>57685</v>
+        <v>26094</v>
       </c>
       <c r="G83" t="n">
-        <v>1218</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="84">
@@ -4037,19 +4149,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>조립52호기</t>
+          <t>조립44호기</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>HAPA(PIA) D_First Love Kristin Brown 14.2_38% UV</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>27379</v>
+        <v>7066</v>
       </c>
       <c r="G84" t="n">
-        <v>4386</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="85">
@@ -4070,19 +4182,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>조립54호기</t>
+          <t>조립45호기</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PIA D_Glow Brown_38% UV</t>
+          <t>1-Day_iris_Latin</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>18857</v>
+        <v>28357</v>
       </c>
       <c r="G85" t="n">
-        <v>3760</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="86">
@@ -4103,19 +4215,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>조립55호기</t>
+          <t>조립47호기</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PIA D_Cream Rose_38% UV</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>8434</v>
+        <v>22481</v>
       </c>
       <c r="G86" t="n">
-        <v>6100</v>
+        <v>5402</v>
       </c>
     </row>
     <row r="87">
@@ -4136,19 +4248,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>조립56호기</t>
+          <t>조립48호기</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PIA D_Uniform Black_55% UV</t>
+          <t>PIA D_Sakura Mousse_55% UV</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>18900</v>
+        <v>25120</v>
       </c>
       <c r="G87" t="n">
-        <v>3800</v>
+        <v>75</v>
       </c>
     </row>
     <row r="88">
@@ -4169,19 +4281,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>조립57호기</t>
+          <t>조립49호기</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>BELLA D_Nerelle 55%</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>22700</v>
+        <v>38488</v>
       </c>
       <c r="G88" t="n">
-        <v>8</v>
+        <v>9827</v>
       </c>
     </row>
     <row r="89">
@@ -4202,19 +4314,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>조립58호기</t>
+          <t>조립50호기</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>47048</v>
+        <v>27917</v>
       </c>
       <c r="G89" t="n">
-        <v>4019</v>
+        <v>172</v>
       </c>
     </row>
     <row r="90">
@@ -4235,19 +4347,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>조립59호기</t>
+          <t>조립51호기</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>27210</v>
+        <v>57451</v>
       </c>
       <c r="G90" t="n">
-        <v>1502</v>
+        <v>50</v>
       </c>
     </row>
     <row r="91">
@@ -4263,24 +4375,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립52호기</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>9301</v>
+        <v>37000</v>
       </c>
       <c r="G91" t="n">
-        <v>11</v>
+        <v>5858</v>
       </c>
     </row>
     <row r="92">
@@ -4296,24 +4408,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립54호기</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>PIA D_Glow Brown_38% UV</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>5751</v>
+        <v>17274</v>
       </c>
       <c r="G92" t="n">
-        <v>448</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="93">
@@ -4329,24 +4441,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립56호기</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>6489</v>
+        <v>28796</v>
       </c>
       <c r="G93" t="n">
-        <v>2664</v>
+        <v>534</v>
       </c>
     </row>
     <row r="94">
@@ -4362,24 +4474,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립57호기</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Gray</t>
+          <t>PIA D_Air Gray_55% UV</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2804</v>
+        <v>28628</v>
       </c>
       <c r="G94" t="n">
-        <v>701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -4395,24 +4507,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립58호기</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Gray</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>6269</v>
+        <v>19513</v>
       </c>
       <c r="G95" t="n">
-        <v>715</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="96">
@@ -4428,24 +4540,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립59호기</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>16283</v>
+        <v>30208</v>
       </c>
       <c r="G96" t="n">
-        <v>1138</v>
+        <v>594</v>
       </c>
     </row>
     <row r="97">
@@ -4461,24 +4573,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>조립46호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Date Topaz_PIA_M(Y)</t>
+          <t>PIA D Toric_CP-0.75 Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>18452</v>
+        <v>1370</v>
       </c>
       <c r="G97" t="n">
-        <v>2454</v>
+        <v>604</v>
       </c>
     </row>
     <row r="98">
@@ -4494,24 +4606,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>조립53호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tarte Tatin_PIA_M(Y)</t>
+          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>17907</v>
+        <v>11920</v>
       </c>
       <c r="G98" t="n">
-        <v>700</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="99">
@@ -4522,29 +4634,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1-Day_iris_Latin</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>24369</v>
+        <v>12797</v>
       </c>
       <c r="G99" t="n">
-        <v>2654</v>
+        <v>800</v>
       </c>
     </row>
     <row r="100">
@@ -4555,29 +4667,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>9224</v>
+        <v>7783</v>
       </c>
       <c r="G100" t="n">
-        <v>2111</v>
+        <v>400</v>
       </c>
     </row>
     <row r="101">
@@ -4588,29 +4700,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>Toric_CP-0.75_Halo Gray</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>9766</v>
+        <v>9404</v>
       </c>
       <c r="G101" t="n">
-        <v>927</v>
+        <v>689</v>
       </c>
     </row>
     <row r="102">
@@ -4621,29 +4733,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Toric_CP-1.25_Halo Gray</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>13186</v>
+        <v>4886</v>
       </c>
       <c r="G102" t="n">
-        <v>1290</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="103">
@@ -4654,29 +4766,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Gemhour D_Liz Brown_Keira</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>13082</v>
+        <v>11868</v>
       </c>
       <c r="G103" t="n">
-        <v>3245</v>
+        <v>500</v>
       </c>
     </row>
     <row r="104">
@@ -4687,29 +4799,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>18579</v>
+        <v>10886</v>
       </c>
       <c r="G104" t="n">
-        <v>2175</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="105">
@@ -4720,29 +4832,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>조립46호기</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Coffee Jelly_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>21216</v>
+        <v>5178</v>
       </c>
       <c r="G105" t="n">
-        <v>4315</v>
+        <v>6834</v>
       </c>
     </row>
     <row r="106">
@@ -4753,29 +4865,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>조립53호기</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Plus Gray 14.2_55% UV</t>
+          <t>Oolong Tea_PIA_M_중사각(Y)</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>14657</v>
+        <v>9910</v>
       </c>
       <c r="G106" t="n">
-        <v>2496</v>
+        <v>600</v>
       </c>
     </row>
     <row r="107">
@@ -4786,29 +4898,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>조립55호기</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
+          <t>Cream Rose_PIA_M</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3081</v>
+        <v>13598</v>
       </c>
       <c r="G107" t="n">
-        <v>386</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="108">
@@ -4829,19 +4941,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>11930</v>
+        <v>37218</v>
       </c>
       <c r="G108" t="n">
-        <v>1831</v>
+        <v>4341</v>
       </c>
     </row>
     <row r="109">
@@ -4862,19 +4974,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>20697</v>
+        <v>17188</v>
       </c>
       <c r="G109" t="n">
-        <v>3300</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="110">
@@ -4895,19 +5007,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>BELLA D_VENUS 55%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>11338</v>
+        <v>10366</v>
       </c>
       <c r="G110" t="n">
-        <v>1284</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="111">
@@ -4928,19 +5040,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>19197</v>
+        <v>20416</v>
       </c>
       <c r="G111" t="n">
-        <v>2245</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="112">
@@ -4961,19 +5073,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>PIA D_Sakana_55% UV</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>20484</v>
+        <v>20266</v>
       </c>
       <c r="G112" t="n">
-        <v>2511</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="113">
@@ -4994,19 +5106,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>분리19호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>43293</v>
+        <v>30262</v>
       </c>
       <c r="G113" t="n">
-        <v>5732</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="114">
@@ -5027,19 +5139,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Gemhour D_Liz Brown_Keira</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>2895</v>
+        <v>7986</v>
       </c>
       <c r="G114" t="n">
-        <v>852</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="115">
@@ -5060,19 +5172,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Plus Gray 14.2_55% UV</t>
+          <t>1-Day_iris_Latin</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>14228</v>
+        <v>25020</v>
       </c>
       <c r="G115" t="n">
-        <v>2001</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="116">
@@ -5093,19 +5205,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>27228</v>
+        <v>14899</v>
       </c>
       <c r="G116" t="n">
-        <v>4052</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="117">
@@ -5126,19 +5238,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>분리19호기</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1-Day_iris_Latin</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>19181</v>
+        <v>27443</v>
       </c>
       <c r="G117" t="n">
-        <v>1632</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="118">
@@ -5159,19 +5271,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>분리19호기</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>22927</v>
+        <v>9554</v>
       </c>
       <c r="G118" t="n">
-        <v>1951</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="119">
@@ -5192,19 +5304,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>3059</v>
+        <v>42142</v>
       </c>
       <c r="G119" t="n">
-        <v>399</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="120">
@@ -5225,19 +5337,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>25293</v>
+        <v>37847</v>
       </c>
       <c r="G120" t="n">
-        <v>3098</v>
+        <v>5742</v>
       </c>
     </row>
     <row r="121">
@@ -5263,14 +5375,14 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>1-Day_iris_Latin</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>9912</v>
+        <v>19229</v>
       </c>
       <c r="G121" t="n">
-        <v>994</v>
+        <v>3927</v>
       </c>
     </row>
     <row r="122">
@@ -5291,19 +5403,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>41752</v>
+        <v>16844</v>
       </c>
       <c r="G122" t="n">
-        <v>6567</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="123">
@@ -5324,19 +5436,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>28886</v>
+        <v>2635</v>
       </c>
       <c r="G123" t="n">
-        <v>6009</v>
+        <v>426</v>
       </c>
     </row>
     <row r="124">
@@ -5357,19 +5469,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>7927</v>
+        <v>21097</v>
       </c>
       <c r="G124" t="n">
-        <v>925</v>
+        <v>4478</v>
       </c>
     </row>
     <row r="125">
@@ -5390,19 +5502,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>HOYA_Casual Ash</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>11463</v>
+        <v>3650</v>
       </c>
       <c r="G125" t="n">
-        <v>995</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="126">
@@ -5423,19 +5535,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>8328</v>
+        <v>30855</v>
       </c>
       <c r="G126" t="n">
-        <v>643</v>
+        <v>9516</v>
       </c>
     </row>
     <row r="127">
@@ -5461,14 +5573,14 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Astra Glitter</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1336</v>
+        <v>39093</v>
       </c>
       <c r="G127" t="n">
-        <v>8732</v>
+        <v>6233</v>
       </c>
     </row>
     <row r="128">
@@ -5489,19 +5601,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Gemhour D_Liz Brown_Keira</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>7191</v>
+        <v>2671</v>
       </c>
       <c r="G128" t="n">
-        <v>1206</v>
+        <v>547</v>
       </c>
     </row>
     <row r="129">
@@ -5527,14 +5639,14 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>20827</v>
+        <v>9657</v>
       </c>
       <c r="G129" t="n">
-        <v>2320</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="130">
@@ -5555,19 +5667,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>HOYA_Maquia Brown</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>36202</v>
+        <v>129</v>
       </c>
       <c r="G130" t="n">
-        <v>3240</v>
+        <v>626</v>
       </c>
     </row>
     <row r="131">
@@ -5588,19 +5700,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>7521</v>
+        <v>14389</v>
       </c>
       <c r="G131" t="n">
-        <v>481</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="132">
@@ -5621,19 +5733,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>47037</v>
+        <v>24318</v>
       </c>
       <c r="G132" t="n">
-        <v>3361</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="133">
@@ -5654,19 +5766,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3146</v>
+        <v>18636</v>
       </c>
       <c r="G133" t="n">
-        <v>328</v>
+        <v>931</v>
       </c>
     </row>
     <row r="134">
@@ -5687,19 +5799,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Gemhour D_Liz Brown_Keira</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2195</v>
+        <v>19792</v>
       </c>
       <c r="G134" t="n">
-        <v>350</v>
+        <v>3986</v>
       </c>
     </row>
     <row r="135">
@@ -5720,19 +5832,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_First Love Kristin Brown 14.2_38% UV</t>
+          <t>PIA D_Uniform Black_55% UV</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>2615</v>
+        <v>14173</v>
       </c>
       <c r="G135" t="n">
-        <v>754</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="136">
@@ -5758,14 +5870,14 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>PIA D_Cream Rose_38% UV</t>
+          <t>HAPA(PIA) D_First Love Kristin Brown 14.2_38% UV</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>17100</v>
+        <v>9912</v>
       </c>
       <c r="G136" t="n">
-        <v>3083</v>
+        <v>4891</v>
       </c>
     </row>
     <row r="137">
@@ -5791,14 +5903,14 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>PIA D_Garnet_38% UV</t>
+          <t>PIA D_Cream Rose_38% UV</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>12548</v>
+        <v>6811</v>
       </c>
       <c r="G137" t="n">
-        <v>1551</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="138">
@@ -5824,14 +5936,14 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Gray_38% UV</t>
+          <t>PIA D_Glow Brown_38% UV</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>7977</v>
+        <v>15449</v>
       </c>
       <c r="G138" t="n">
-        <v>1348</v>
+        <v>3408</v>
       </c>
     </row>
     <row r="139">
@@ -5861,10 +5973,10 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>9206</v>
+        <v>17864</v>
       </c>
       <c r="G139" t="n">
-        <v>659</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="140">
@@ -5890,14 +6002,14 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>HOYA_Casual Ash</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>38466</v>
+        <v>1610</v>
       </c>
       <c r="G140" t="n">
-        <v>4088</v>
+        <v>702</v>
       </c>
     </row>
     <row r="141">
@@ -5918,19 +6030,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>HOYA_Maquia Brown</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>14714</v>
+        <v>374</v>
       </c>
       <c r="G141" t="n">
-        <v>2318</v>
+        <v>719</v>
       </c>
     </row>
     <row r="142">
@@ -5951,19 +6063,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>23348</v>
+        <v>7902</v>
       </c>
       <c r="G142" t="n">
-        <v>6538</v>
+        <v>593</v>
       </c>
     </row>
     <row r="143">
@@ -5984,19 +6096,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>HOYA_Maquia Brown</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>12509</v>
+        <v>4392</v>
       </c>
       <c r="G143" t="n">
-        <v>1152</v>
+        <v>909</v>
       </c>
     </row>
     <row r="144">
@@ -6017,19 +6129,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Astra Estelle Gray</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>2236</v>
+        <v>25852</v>
       </c>
       <c r="G144" t="n">
-        <v>845</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="145">
@@ -6050,19 +6162,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>BELLA D_Nerelle 55%</t>
+          <t>PIA D_Sakura Mousse_55% UV</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>2292</v>
+        <v>12447</v>
       </c>
       <c r="G145" t="n">
-        <v>533</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="146">
@@ -6083,19 +6195,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>BELLA D_Silent Gray 55%</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>24628</v>
+        <v>635</v>
       </c>
       <c r="G146" t="n">
-        <v>2666</v>
+        <v>183</v>
       </c>
     </row>
     <row r="147">
@@ -6116,19 +6228,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>분리43호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>BELLA D_Nerelle 55%</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>33022</v>
+        <v>18113</v>
       </c>
       <c r="G147" t="n">
-        <v>7183</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="148">
@@ -6149,19 +6261,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>분리43호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>3129</v>
+        <v>9865</v>
       </c>
       <c r="G148" t="n">
-        <v>420</v>
+        <v>710</v>
       </c>
     </row>
     <row r="149">
@@ -6177,24 +6289,24 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리43호기</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1550</v>
+        <v>23437</v>
       </c>
       <c r="G149" t="n">
-        <v>387</v>
+        <v>3688</v>
       </c>
     </row>
     <row r="150">
@@ -6220,14 +6332,14 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PIA_Brown Fondue CP-1.25 Toric_UV</t>
+          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>8064</v>
+        <v>5507</v>
       </c>
       <c r="G150" t="n">
-        <v>1620</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="151">
@@ -6257,10 +6369,10 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>19507</v>
+        <v>5191</v>
       </c>
       <c r="G151" t="n">
-        <v>1862</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="152">
@@ -6286,14 +6398,14 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>Toric_CP-0.75_Halo Gray</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>12090</v>
+        <v>1812</v>
       </c>
       <c r="G152" t="n">
-        <v>1351</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="153">
@@ -6319,14 +6431,14 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>4584</v>
+        <v>2351</v>
       </c>
       <c r="G153" t="n">
-        <v>807</v>
+        <v>314</v>
       </c>
     </row>
     <row r="154">
@@ -6347,19 +6459,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1229</v>
+        <v>5082</v>
       </c>
       <c r="G154" t="n">
-        <v>462</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="155">
@@ -6375,24 +6487,24 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>분리22호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>36367</v>
+        <v>19284</v>
       </c>
       <c r="G155" t="n">
-        <v>6765</v>
+        <v>5855</v>
       </c>
     </row>
     <row r="156">
@@ -6413,7 +6525,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>분리23호기</t>
+          <t>분리22호기</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -6422,10 +6534,10 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>35503</v>
+        <v>36156</v>
       </c>
       <c r="G156" t="n">
-        <v>9606</v>
+        <v>6866</v>
       </c>
     </row>
     <row r="157">
@@ -6446,7 +6558,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>분리25호기</t>
+          <t>분리23호기</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -6455,10 +6567,10 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>36267</v>
+        <v>35631</v>
       </c>
       <c r="G157" t="n">
-        <v>7884</v>
+        <v>8306</v>
       </c>
     </row>
     <row r="158">
@@ -6479,7 +6591,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리25호기</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6488,10 +6600,10 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>41946</v>
+        <v>44431</v>
       </c>
       <c r="G158" t="n">
-        <v>10013</v>
+        <v>6589</v>
       </c>
     </row>
     <row r="159">
@@ -6507,24 +6619,24 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Cherish Brown_PIA_M_(중)_14.2</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>3437</v>
+        <v>41519</v>
       </c>
       <c r="G159" t="n">
-        <v>1439</v>
+        <v>11591</v>
       </c>
     </row>
     <row r="160">
@@ -6554,10 +6666,10 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>8506</v>
+        <v>1590</v>
       </c>
       <c r="G160" t="n">
-        <v>1878</v>
+        <v>409</v>
       </c>
     </row>
     <row r="161">
@@ -6583,14 +6695,14 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>MARIGOLD_PIA_M</t>
+          <t>Tarte Tatin_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>791</v>
+        <v>3122</v>
       </c>
       <c r="G161" t="n">
-        <v>4186</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="162">
@@ -6601,29 +6713,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Uniform Black_PIA_M(Y)</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>2414</v>
+        <v>3540</v>
       </c>
       <c r="G162" t="n">
-        <v>366</v>
+        <v>50</v>
       </c>
     </row>
     <row r="163">
@@ -6649,14 +6761,14 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>3325</v>
+        <v>6450</v>
       </c>
       <c r="G163" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
     </row>
     <row r="164">
@@ -6682,14 +6794,14 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>9865</v>
+        <v>3420</v>
       </c>
       <c r="G164" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
     </row>
     <row r="165">
@@ -6715,14 +6827,14 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>4795</v>
+        <v>3820</v>
       </c>
       <c r="G165" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="166">
@@ -6748,14 +6860,14 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>2673</v>
+        <v>4171</v>
       </c>
       <c r="G166" t="n">
-        <v>632</v>
+        <v>584</v>
       </c>
     </row>
     <row r="167">
@@ -6781,14 +6893,14 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA_SARANG BROWN</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>4620</v>
+        <v>10145</v>
       </c>
       <c r="G167" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="168">
@@ -6814,14 +6926,14 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>2370</v>
+        <v>3400</v>
       </c>
       <c r="G168" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="169">
@@ -6842,19 +6954,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>4565</v>
+        <v>18470</v>
       </c>
       <c r="G169" t="n">
-        <v>105</v>
+        <v>290</v>
       </c>
     </row>
     <row r="170">
@@ -6875,19 +6987,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>3820</v>
+        <v>4495</v>
       </c>
       <c r="G170" t="n">
-        <v>65</v>
+        <v>170</v>
       </c>
     </row>
     <row r="171">
@@ -6913,14 +7025,14 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1060</v>
+        <v>3115</v>
       </c>
       <c r="G171" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="172">
@@ -6946,14 +7058,14 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>6373</v>
+        <v>12072</v>
       </c>
       <c r="G172" t="n">
-        <v>572</v>
+        <v>678</v>
       </c>
     </row>
     <row r="173">
@@ -6979,14 +7091,14 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>10655</v>
+        <v>3070</v>
       </c>
       <c r="G173" t="n">
-        <v>185</v>
+        <v>70</v>
       </c>
     </row>
     <row r="174">
@@ -7012,14 +7124,14 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>PIA_SARANG BROWN</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3450</v>
+        <v>6500</v>
       </c>
       <c r="G174" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="175">
@@ -7045,14 +7157,14 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2920</v>
+        <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -7073,19 +7185,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>(NEW)1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>10850</v>
+        <v>6030</v>
       </c>
       <c r="G176" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="177">
@@ -7106,19 +7218,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>5245</v>
+        <v>29589</v>
       </c>
       <c r="G177" t="n">
-        <v>130</v>
+        <v>661</v>
       </c>
     </row>
     <row r="178">
@@ -7144,14 +7256,14 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>990</v>
+        <v>5895</v>
       </c>
       <c r="G178" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="179">
@@ -7177,14 +7289,14 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>2900</v>
+        <v>2785</v>
       </c>
       <c r="G179" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
     </row>
     <row r="180">
@@ -7210,14 +7322,14 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>8290</v>
+        <v>9650</v>
       </c>
       <c r="G180" t="n">
-        <v>360</v>
+        <v>100</v>
       </c>
     </row>
     <row r="181">
@@ -7243,14 +7355,14 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>PIA D_Cherish Brown_55% UV 14.2</t>
+          <t>PIA_SARANG BROWN</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>18635</v>
+        <v>2805</v>
       </c>
       <c r="G181" t="n">
-        <v>285</v>
+        <v>45</v>
       </c>
     </row>
     <row r="182">
@@ -7271,19 +7383,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>Astra Glitter</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1751</v>
+        <v>1105</v>
       </c>
       <c r="G182" t="n">
-        <v>1074</v>
+        <v>35</v>
       </c>
     </row>
     <row r="183">
@@ -7304,19 +7416,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>BELLA D_Silent Gray 55%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>15540</v>
+        <v>7900</v>
       </c>
       <c r="G183" t="n">
-        <v>135</v>
+        <v>60</v>
       </c>
     </row>
     <row r="184">
@@ -7337,19 +7449,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>BELLA D_VENUS 55%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3265</v>
+        <v>3700</v>
       </c>
       <c r="G184" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
     </row>
     <row r="185">
@@ -7370,19 +7482,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>5770</v>
+        <v>20010</v>
       </c>
       <c r="G185" t="n">
-        <v>160</v>
+        <v>185</v>
       </c>
     </row>
     <row r="186">
@@ -7403,19 +7515,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>BELLA D_MARS 55%</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>5550</v>
+        <v>36560</v>
       </c>
       <c r="G186" t="n">
-        <v>305</v>
+        <v>635</v>
       </c>
     </row>
     <row r="187">
@@ -7436,19 +7548,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>BELLA D_Silent Gray 55%</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>6690</v>
+        <v>23807</v>
       </c>
       <c r="G187" t="n">
-        <v>80</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="188">
@@ -7469,19 +7581,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>BELLA D_Siren Bronze 55%</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1940</v>
+        <v>26550</v>
       </c>
       <c r="G188" t="n">
-        <v>35</v>
+        <v>465</v>
       </c>
     </row>
     <row r="189">
@@ -7502,19 +7614,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>BELLA D_VENUS 55%</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>4867</v>
+        <v>9803</v>
       </c>
       <c r="G189" t="n">
-        <v>1783</v>
+        <v>617</v>
       </c>
     </row>
     <row r="190">
@@ -7535,19 +7647,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_One&amp;Only Kristin Plus Brown 14.2_38%</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>9935</v>
+        <v>5865</v>
       </c>
       <c r="G190" t="n">
-        <v>230</v>
+        <v>65</v>
       </c>
     </row>
     <row r="191">
@@ -7568,19 +7680,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Sincere D_Neutral Brown_UV_38% 14.2</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>595</v>
+        <v>3100</v>
       </c>
       <c r="G191" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="192">
@@ -7601,19 +7713,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>33285</v>
+        <v>4175</v>
       </c>
       <c r="G192" t="n">
-        <v>470</v>
+        <v>50</v>
       </c>
     </row>
     <row r="193">
@@ -7634,19 +7746,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>25274</v>
+        <v>14680</v>
       </c>
       <c r="G193" t="n">
-        <v>1056</v>
+        <v>155</v>
       </c>
     </row>
     <row r="194">
@@ -7667,19 +7779,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>38934</v>
+        <v>3135</v>
       </c>
       <c r="G194" t="n">
-        <v>1786</v>
+        <v>35</v>
       </c>
     </row>
     <row r="195">
@@ -7700,19 +7812,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA_SARANG BROWN</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>20710</v>
+        <v>13030</v>
       </c>
       <c r="G195" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="196">
@@ -7738,14 +7850,14 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>4325</v>
+        <v>6540</v>
       </c>
       <c r="G196" t="n">
-        <v>220</v>
+        <v>75</v>
       </c>
     </row>
     <row r="197">
@@ -7766,19 +7878,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>10570</v>
+        <v>41884</v>
       </c>
       <c r="G197" t="n">
-        <v>95</v>
+        <v>951</v>
       </c>
     </row>
     <row r="198">
@@ -7799,19 +7911,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>7015</v>
+        <v>14350</v>
       </c>
       <c r="G198" t="n">
-        <v>315</v>
+        <v>290</v>
       </c>
     </row>
     <row r="199">
@@ -7832,19 +7944,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>8010</v>
+        <v>18185</v>
       </c>
       <c r="G199" t="n">
-        <v>65</v>
+        <v>265</v>
       </c>
     </row>
     <row r="200">
@@ -7865,19 +7977,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>9450</v>
+        <v>18385</v>
       </c>
       <c r="G200" t="n">
-        <v>185</v>
+        <v>415</v>
       </c>
     </row>
     <row r="201">
@@ -7898,19 +8010,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>BELLA D_MARS 55%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>2494</v>
+        <v>695</v>
       </c>
       <c r="G201" t="n">
-        <v>831</v>
+        <v>70</v>
       </c>
     </row>
     <row r="202">
@@ -7931,19 +8043,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>BELLA D_Nerelle 55%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>5925</v>
+        <v>4467</v>
       </c>
       <c r="G202" t="n">
-        <v>75</v>
+        <v>333</v>
       </c>
     </row>
     <row r="203">
@@ -7964,19 +8076,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>BELLA D_Silent Gray 55%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>6425</v>
+        <v>1934</v>
       </c>
       <c r="G203" t="n">
-        <v>115</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="204">
@@ -7997,16 +8109,16 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>BELLA D_VENUS 55%</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>2915</v>
+        <v>515</v>
       </c>
       <c r="G204" t="n">
         <v>55</v>
@@ -8030,19 +8142,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>BELLA_1-Day_Almond Brown(8년)</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>29498</v>
+        <v>465</v>
       </c>
       <c r="G205" t="n">
-        <v>1172</v>
+        <v>35</v>
       </c>
     </row>
     <row r="206">
@@ -8063,19 +8175,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>BELLA_1-Day_Platinum Grey(8년)</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>21908</v>
+        <v>550</v>
       </c>
       <c r="G206" t="n">
-        <v>2312</v>
+        <v>45</v>
       </c>
     </row>
     <row r="207">
@@ -8096,19 +8208,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Plus Gray 14.2_55% UV</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>5965</v>
+        <v>12110</v>
       </c>
       <c r="G207" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
     </row>
     <row r="208">
@@ -8129,19 +8241,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>19935</v>
+        <v>4085</v>
       </c>
       <c r="G208" t="n">
-        <v>300</v>
+        <v>110</v>
       </c>
     </row>
     <row r="209">
@@ -8162,19 +8274,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>21905</v>
+        <v>3090</v>
       </c>
       <c r="G209" t="n">
-        <v>650</v>
+        <v>25</v>
       </c>
     </row>
     <row r="210">
@@ -8200,14 +8312,14 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
+          <t>Rina_Choco Brown_1-Day</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>15279</v>
+        <v>800</v>
       </c>
       <c r="G210" t="n">
-        <v>2321</v>
+        <v>25</v>
       </c>
     </row>
     <row r="211">
@@ -8233,14 +8345,14 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>Rina_Crystal Gray_1-Day</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>30405</v>
+        <v>4215</v>
       </c>
       <c r="G211" t="n">
-        <v>435</v>
+        <v>55</v>
       </c>
     </row>
     <row r="212">
@@ -8266,14 +8378,14 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>Rina_Mocha Brown_1-Day</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>9915</v>
+        <v>1205</v>
       </c>
       <c r="G212" t="n">
-        <v>145</v>
+        <v>15</v>
       </c>
     </row>
     <row r="213">
@@ -8299,14 +8411,14 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>IRIS_Soul Brown(NEW)</t>
+          <t>PIA D_Jelly Gray_38% UV</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>6135</v>
+        <v>8145</v>
       </c>
       <c r="G213" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
     </row>
     <row r="214">
@@ -8332,14 +8444,14 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Gray_38% UV</t>
+          <t>PIA D_Pomme Canele_38% UV</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>13690</v>
+        <v>2380</v>
       </c>
       <c r="G214" t="n">
-        <v>150</v>
+        <v>45</v>
       </c>
     </row>
     <row r="215">
@@ -8365,14 +8477,14 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>PIA D_Pomme Canele_38% UV</t>
+          <t>PIA D_Sugar Donut_38% UV</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>17960</v>
+        <v>4180</v>
       </c>
       <c r="G215" t="n">
-        <v>315</v>
+        <v>80</v>
       </c>
     </row>
     <row r="216">
@@ -8393,19 +8505,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>PIA D_Puree Greige_38% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>12195</v>
+        <v>14425</v>
       </c>
       <c r="G216" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
     </row>
     <row r="217">
@@ -8426,19 +8538,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>PIA D_Sugar Donut_38% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>2785</v>
+        <v>29312</v>
       </c>
       <c r="G217" t="n">
-        <v>50</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="218">
@@ -8459,19 +8571,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>16925</v>
+        <v>11975</v>
       </c>
       <c r="G218" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
     <row r="219">
@@ -8492,19 +8604,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F219" t="n">
-        <v>2770</v>
+        <v>15560</v>
       </c>
       <c r="G219" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
     </row>
     <row r="220">
@@ -8525,19 +8637,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>15235</v>
+        <v>23581</v>
       </c>
       <c r="G220" t="n">
-        <v>265</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="221">
@@ -8558,19 +8670,19 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>29386</v>
+        <v>57411</v>
       </c>
       <c r="G221" t="n">
-        <v>1304</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="222">
@@ -8591,16 +8703,16 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Astra Estelle Gray</t>
         </is>
       </c>
       <c r="F222" t="n">
-        <v>5890</v>
+        <v>2145</v>
       </c>
       <c r="G222" t="n">
         <v>65</v>
@@ -8624,19 +8736,19 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>JEWEL MOON D_Amber Moon_55%</t>
         </is>
       </c>
       <c r="F223" t="n">
-        <v>5750</v>
+        <v>3292</v>
       </c>
       <c r="G223" t="n">
-        <v>140</v>
+        <v>293</v>
       </c>
     </row>
     <row r="224">
@@ -8657,19 +8769,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Gemhour D_Liz Brown_Keira</t>
+          <t>JEWEL MOON D_Emerald Moon_55%</t>
         </is>
       </c>
       <c r="F224" t="n">
-        <v>2815</v>
+        <v>3832</v>
       </c>
       <c r="G224" t="n">
-        <v>60</v>
+        <v>338</v>
       </c>
     </row>
     <row r="225">
@@ -8690,19 +8802,19 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>JEWEL MOON D_Pearl Moon_55%</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>9605</v>
+        <v>398</v>
       </c>
       <c r="G225" t="n">
-        <v>205</v>
+        <v>137</v>
       </c>
     </row>
     <row r="226">
@@ -8723,19 +8835,19 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>JEWEL MOON D_Sapphire Moon_55%</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>8790</v>
+        <v>5940</v>
       </c>
       <c r="G226" t="n">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="227">
@@ -8756,19 +8868,19 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>55935</v>
+        <v>7915</v>
       </c>
       <c r="G227" t="n">
-        <v>1155</v>
+        <v>185</v>
       </c>
     </row>
     <row r="228">
@@ -8798,10 +8910,10 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>2720</v>
+        <v>8280</v>
       </c>
       <c r="G228" t="n">
-        <v>50</v>
+        <v>205</v>
       </c>
     </row>
     <row r="229">
@@ -8831,10 +8943,10 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>8805</v>
+        <v>5245</v>
       </c>
       <c r="G229" t="n">
-        <v>1340</v>
+        <v>110</v>
       </c>
     </row>
     <row r="230">
@@ -8860,14 +8972,14 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>3830</v>
+        <v>1500</v>
       </c>
       <c r="G230" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="231">
@@ -8893,14 +9005,14 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F231" t="n">
-        <v>1305</v>
+        <v>43283</v>
       </c>
       <c r="G231" t="n">
-        <v>20</v>
+        <v>987</v>
       </c>
     </row>
     <row r="232">
@@ -8926,14 +9038,14 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F232" t="n">
-        <v>25451</v>
+        <v>1872</v>
       </c>
       <c r="G232" t="n">
-        <v>574</v>
+        <v>443</v>
       </c>
     </row>
     <row r="233">
@@ -8959,14 +9071,14 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F233" t="n">
-        <v>2965</v>
+        <v>3475</v>
       </c>
       <c r="G233" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="234">
@@ -8982,24 +9094,24 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F234" t="n">
-        <v>2265</v>
+        <v>19984</v>
       </c>
       <c r="G234" t="n">
-        <v>35</v>
+        <v>926</v>
       </c>
     </row>
     <row r="235">
@@ -9020,19 +9132,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F235" t="n">
-        <v>0</v>
+        <v>10155</v>
       </c>
       <c r="G235" t="n">
-        <v>825</v>
+        <v>110</v>
       </c>
     </row>
     <row r="236">
@@ -9058,14 +9170,14 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>9250</v>
+        <v>10165</v>
       </c>
       <c r="G236" t="n">
-        <v>155</v>
+        <v>210</v>
       </c>
     </row>
     <row r="237">
@@ -9086,19 +9198,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>2915</v>
+        <v>6095</v>
       </c>
       <c r="G237" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="238">
@@ -9128,10 +9240,10 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>3150</v>
+        <v>1510</v>
       </c>
       <c r="G238" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
     </row>
     <row r="239">
@@ -9161,10 +9273,10 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>1220</v>
+        <v>7840</v>
       </c>
       <c r="G239" t="n">
-        <v>20</v>
+        <v>185</v>
       </c>
     </row>
     <row r="240">
@@ -9180,24 +9292,24 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_M/F</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Gray</t>
+          <t>Bi-focal D_8.40_55%</t>
         </is>
       </c>
       <c r="F240" t="n">
-        <v>11090</v>
+        <v>15345</v>
       </c>
       <c r="G240" t="n">
-        <v>160</v>
+        <v>450</v>
       </c>
     </row>
     <row r="241">
@@ -9213,24 +9325,24 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Gray</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F241" t="n">
-        <v>11060</v>
+        <v>15933</v>
       </c>
       <c r="G241" t="n">
-        <v>155</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="242">
@@ -9246,24 +9358,24 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>1-Day_SOLEKO(5년)</t>
         </is>
       </c>
       <c r="F242" t="n">
-        <v>13525</v>
+        <v>11220</v>
       </c>
       <c r="G242" t="n">
-        <v>185</v>
+        <v>375</v>
       </c>
     </row>
     <row r="243">
@@ -9279,24 +9391,24 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>1-Day_SOLEKO(5년)</t>
         </is>
       </c>
       <c r="F243" t="n">
-        <v>6170</v>
+        <v>36045</v>
       </c>
       <c r="G243" t="n">
-        <v>105</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="244">
@@ -9312,24 +9424,24 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F244" t="n">
-        <v>8310</v>
+        <v>24114</v>
       </c>
       <c r="G244" t="n">
-        <v>225</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="245">
@@ -9345,24 +9457,24 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>1-Day_58_M</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>2755</v>
+        <v>21730</v>
       </c>
       <c r="G245" t="n">
-        <v>40</v>
+        <v>550</v>
       </c>
     </row>
     <row r="246">
@@ -9378,101 +9490,101 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>PIA_Opal CP-0.75 Toric_UV</t>
+          <t>1-Day_SOLEKO(5년)</t>
         </is>
       </c>
       <c r="F246" t="n">
-        <v>7405</v>
+        <v>11315</v>
       </c>
       <c r="G246" t="n">
-        <v>250</v>
+        <v>465</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>B형 조립중합8호기</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>PIA_Opal CP-1.25 Toric_UV</t>
+          <t>Clalen D_Canola Brown</t>
         </is>
       </c>
       <c r="F247" t="n">
-        <v>1505</v>
+        <v>7502</v>
       </c>
       <c r="G247" t="n">
-        <v>40</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>B형 조립중합8호기</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>Clalen D_Pink Tulip Brown</t>
         </is>
       </c>
       <c r="F248" t="n">
-        <v>19540</v>
+        <v>12109</v>
       </c>
       <c r="G248" t="n">
-        <v>430</v>
+        <v>827</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9482,19 +9594,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>23895</v>
+        <v>17843</v>
       </c>
       <c r="G249" t="n">
-        <v>2140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -9524,7 +9636,7 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>17456</v>
+        <v>23298</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -9548,19 +9660,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>B형 조립중합4호기</t>
+          <t>B형 조립중합5호기</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>11236</v>
+        <v>16336</v>
       </c>
       <c r="G251" t="n">
-        <v>2316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -9581,19 +9693,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>B형 조립중합5호기</t>
+          <t>B형 조립중합6호기</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>O2O2 D_Ash Brown EX</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>43666</v>
+        <v>23540</v>
       </c>
       <c r="G252" t="n">
-        <v>3630</v>
+        <v>4532</v>
       </c>
     </row>
     <row r="253">
@@ -9609,24 +9721,24 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>B형 조립중합6호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Gray EX</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>7870</v>
+        <v>22390</v>
       </c>
       <c r="G253" t="n">
-        <v>4722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -9647,7 +9759,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -9656,7 +9768,7 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>39861</v>
+        <v>21742</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
@@ -9670,29 +9782,29 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>CAM분리2호기</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen D_Canola Brown</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>41135</v>
+        <v>3777</v>
       </c>
       <c r="G255" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
     </row>
     <row r="256">
@@ -9708,24 +9820,24 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>CAM분리1호기</t>
+          <t>CAM분리2호기</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Sincere D_Clear_38%</t>
+          <t>Clalen D_Pink Tulip Brown</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>12697</v>
+        <v>6479</v>
       </c>
       <c r="G256" t="n">
-        <v>4031</v>
+        <v>856</v>
       </c>
     </row>
     <row r="257">
@@ -9741,24 +9853,24 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>CAM분리4호기</t>
+          <t>CAM분리3호기</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Sincere D_Clear_38%</t>
+          <t>Clalen D_Canola Brown</t>
         </is>
       </c>
       <c r="F257" t="n">
-        <v>19161</v>
+        <v>790</v>
       </c>
       <c r="G257" t="n">
-        <v>4097</v>
+        <v>213</v>
       </c>
     </row>
     <row r="258">
@@ -9774,24 +9886,24 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>CAM분리3호기</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen D_Pink Tulip Brown</t>
         </is>
       </c>
       <c r="F258" t="n">
-        <v>7077</v>
+        <v>1427</v>
       </c>
       <c r="G258" t="n">
-        <v>1653</v>
+        <v>190</v>
       </c>
     </row>
     <row r="259">
@@ -9807,24 +9919,24 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>CAM분리3호기</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F259" t="n">
-        <v>4275</v>
+        <v>2124</v>
       </c>
       <c r="G259" t="n">
-        <v>527</v>
+        <v>107</v>
       </c>
     </row>
     <row r="260">
@@ -9840,24 +9952,24 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>CAM분리4호기</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Sincere D_Clear_38%</t>
         </is>
       </c>
       <c r="F260" t="n">
-        <v>4798</v>
+        <v>15506</v>
       </c>
       <c r="G260" t="n">
-        <v>951</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="261">
@@ -9878,7 +9990,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>B형 분리수화접착6호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -9887,10 +9999,10 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>2122</v>
+        <v>7012</v>
       </c>
       <c r="G261" t="n">
-        <v>377</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="262">
@@ -9911,19 +10023,19 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>B형 분리수화접착6호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F262" t="n">
-        <v>12582</v>
+        <v>621</v>
       </c>
       <c r="G262" t="n">
-        <v>1710</v>
+        <v>203</v>
       </c>
     </row>
     <row r="263">
@@ -9944,19 +10056,19 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F263" t="n">
-        <v>8773</v>
+        <v>10445</v>
       </c>
       <c r="G263" t="n">
-        <v>2799</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="264">
@@ -9977,19 +10089,19 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>B형 분리수화접착6호기</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F264" t="n">
-        <v>553</v>
+        <v>569</v>
       </c>
       <c r="G264" t="n">
-        <v>484</v>
+        <v>264</v>
       </c>
     </row>
     <row r="265">
@@ -10010,19 +10122,19 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>B형 분리수화접착6호기</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F265" t="n">
-        <v>18481</v>
+        <v>16491</v>
       </c>
       <c r="G265" t="n">
-        <v>2632</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="266">
@@ -10038,24 +10150,24 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F266" t="n">
-        <v>13338</v>
+        <v>5022</v>
       </c>
       <c r="G266" t="n">
-        <v>1182</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="267">
@@ -10071,24 +10183,24 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F267" t="n">
-        <v>14299</v>
+        <v>1524</v>
       </c>
       <c r="G267" t="n">
-        <v>882</v>
+        <v>147</v>
       </c>
     </row>
     <row r="268">
@@ -10104,24 +10216,24 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>O2O2 D_Ash Brown EX</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>10206</v>
+        <v>4909</v>
       </c>
       <c r="G268" t="n">
-        <v>1597</v>
+        <v>962</v>
       </c>
     </row>
     <row r="269">
@@ -10137,24 +10249,24 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>O2O2 D_Ash Gray EX</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>13341</v>
+        <v>19997</v>
       </c>
       <c r="G269" t="n">
-        <v>1338</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="270">
@@ -10165,29 +10277,29 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Clalen D_Canola Brown</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>2800</v>
+        <v>24388</v>
       </c>
       <c r="G270" t="n">
-        <v>50</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="271">
@@ -10198,29 +10310,29 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Clalen D_Mimosa Brown</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>4855</v>
+        <v>29608</v>
       </c>
       <c r="G271" t="n">
-        <v>90</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="272">
@@ -10231,29 +10343,29 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>B형 분리수화접착3호기</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>sincere Natural 1day</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>5625</v>
+        <v>10209</v>
       </c>
       <c r="G272" t="n">
-        <v>45</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="273">
@@ -10264,29 +10376,29 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>B형 분리수화접착4호기</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>sincere Natural 1day</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F273" t="n">
-        <v>16446</v>
+        <v>13443</v>
       </c>
       <c r="G273" t="n">
-        <v>1251</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="274">
@@ -10302,24 +10414,24 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen oneday A(O2 Edition)</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>6962</v>
+        <v>5305</v>
       </c>
       <c r="G274" t="n">
-        <v>1350</v>
+        <v>251</v>
       </c>
     </row>
     <row r="275">
@@ -10335,24 +10447,24 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>sincere Natural 1day</t>
         </is>
       </c>
       <c r="F275" t="n">
-        <v>6290</v>
+        <v>24425</v>
       </c>
       <c r="G275" t="n">
-        <v>650</v>
+        <v>807</v>
       </c>
     </row>
     <row r="276">
@@ -10378,14 +10490,14 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>26840</v>
+        <v>19170</v>
       </c>
       <c r="G276" t="n">
-        <v>1034</v>
+        <v>405</v>
       </c>
     </row>
     <row r="277">
@@ -10406,19 +10518,19 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F277" t="n">
-        <v>3295</v>
+        <v>5770</v>
       </c>
       <c r="G277" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="278">
@@ -10439,19 +10551,19 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>2854</v>
+        <v>19796</v>
       </c>
       <c r="G278" t="n">
-        <v>535</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="279">
@@ -10477,14 +10589,14 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>2359</v>
+        <v>13465</v>
       </c>
       <c r="G279" t="n">
-        <v>305</v>
+        <v>339</v>
       </c>
     </row>
     <row r="280">
@@ -10505,19 +10617,19 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>2640</v>
+        <v>5800</v>
       </c>
       <c r="G280" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
     </row>
     <row r="281">
@@ -10538,19 +10650,19 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>1730</v>
+        <v>4485</v>
       </c>
       <c r="G281" t="n">
-        <v>29</v>
+        <v>224</v>
       </c>
     </row>
     <row r="282">
@@ -10576,14 +10688,14 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F282" t="n">
-        <v>7035</v>
+        <v>1815</v>
       </c>
       <c r="G282" t="n">
-        <v>379</v>
+        <v>27</v>
       </c>
     </row>
     <row r="283">
@@ -10599,24 +10711,24 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>A형 인라인6호기</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F283" t="n">
-        <v>38423</v>
+        <v>1555</v>
       </c>
       <c r="G283" t="n">
-        <v>1268</v>
+        <v>22</v>
       </c>
     </row>
     <row r="284">
@@ -10637,7 +10749,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -10646,10 +10758,10 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>45712</v>
+        <v>38875</v>
       </c>
       <c r="G284" t="n">
-        <v>1847</v>
+        <v>872</v>
       </c>
     </row>
     <row r="285">
@@ -10670,7 +10782,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -10679,10 +10791,10 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>11830</v>
+        <v>37161</v>
       </c>
       <c r="G285" t="n">
-        <v>208</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="286">
@@ -10703,7 +10815,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -10712,43 +10824,10 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>7215</v>
+        <v>19525</v>
       </c>
       <c r="G286" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>A형 인라인6호기</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
-        </is>
-      </c>
-      <c r="F287" t="n">
-        <v>22630</v>
-      </c>
-      <c r="G287" t="n">
-        <v>497</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/생산실적현황(설비운영현황).xlsx
+++ b/생산실적현황(설비운영현황).xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>US55-2(M)</t>
+          <t>(NEW)S38-Dry-14.2</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -565,11 +565,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Toric</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -577,7 +577,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>O2O2 Spherical(DK70)_K2-SMD</t>
+          <t>O2O2 D_UV_Toric_SMD</t>
         </is>
       </c>
     </row>
@@ -589,23 +589,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Si_1-Day_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>O2O2 D_UV_Toric_SMD</t>
+          <t>(UV_NEW)CS30_8.60</t>
         </is>
       </c>
     </row>
@@ -625,15 +625,15 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>T55_소사각</t>
         </is>
       </c>
     </row>
@@ -645,23 +645,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>Bella Diamond_14.5_중사각</t>
         </is>
       </c>
     </row>
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bella-Natural_중사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
     </row>
@@ -705,19 +705,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Metha_55_중사각</t>
+          <t>T38_금캡(UV포함)</t>
         </is>
       </c>
     </row>
@@ -733,67 +733,67 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>T38_금캡(UV포함)</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Silicone relax_소사각</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
     </row>
@@ -817,19 +817,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Coffee Jelly_PIA_M(Y)</t>
         </is>
       </c>
     </row>
@@ -841,23 +841,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
     </row>
@@ -869,23 +869,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cream Rose_PIA_M</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
     </row>
@@ -905,15 +905,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>Cream Rose_PIA_M</t>
         </is>
       </c>
     </row>
@@ -953,23 +953,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
     </row>
@@ -989,15 +989,15 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
     </row>
@@ -1017,31 +1017,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
     </row>
@@ -1073,15 +1073,15 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Clalen D_Pink Tulip Brown</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sincere D_Clear_38%</t>
+          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Brown EX</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1149,23 +1149,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Sincere D_Clear_38%</t>
         </is>
       </c>
     </row>
@@ -1185,15 +1185,15 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Clalen D_Pink Tulip Brown</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
     </row>
@@ -1213,15 +1213,15 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sincere D_Clear_38%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1233,23 +1233,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen D_Canola Brown</t>
         </is>
       </c>
     </row>
@@ -1261,23 +1261,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>sincere Natural 1day</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>sincere Natural 1day</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
     </row>
@@ -1325,41 +1325,13 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>3</v>
       </c>
       <c r="F32" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>6</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F33" t="inlineStr">
         <is>
           <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
@@ -1376,12 +1348,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G286"/>
+  <dimension ref="A1:G302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="56" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -1443,19 +1415,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>조립30호기</t>
+          <t>조립1호기</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>1-Day_Metha</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>96527</v>
+        <v>16764</v>
       </c>
       <c r="G2" t="n">
-        <v>582</v>
+        <v>491</v>
       </c>
     </row>
     <row r="3">
@@ -1476,7 +1448,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>조립31호기</t>
+          <t>조립30호기</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1485,10 +1457,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>44984</v>
+        <v>51428</v>
       </c>
       <c r="G3" t="n">
-        <v>2115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1509,7 +1481,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>조립32호기</t>
+          <t>조립31호기</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1518,10 +1490,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>47065</v>
+        <v>50063</v>
       </c>
       <c r="G4" t="n">
-        <v>1385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1537,24 +1509,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>조립1호기</t>
+          <t>조립32호기</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>US55-2(M)</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>20180</v>
+        <v>97909</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="6">
@@ -1575,19 +1547,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>조립3호기</t>
+          <t>조립8호기</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S55_8.60</t>
+          <t>(NEW)S38-Dry-14.2</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>18927</v>
+        <v>37399</v>
       </c>
       <c r="G6" t="n">
-        <v>576</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7">
@@ -1603,24 +1575,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>조립8호기</t>
+          <t>조립2호기</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(NEW)S38-Dry-14.2</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>19166</v>
+        <v>7661</v>
       </c>
       <c r="G7" t="n">
-        <v>404</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="8">
@@ -1636,21 +1608,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>Si_1-Day_Toric</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>조립8호기</t>
+          <t>조립7호기</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(NEW)S38-HD-Dry-14.0</t>
+          <t>O2O2 D_UV_Toric_SMD</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>17766</v>
+        <v>4269</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1664,29 +1636,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>조립2호기</t>
+          <t>분리10호기</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>CS30-Dry</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3208</v>
+        <v>12356</v>
       </c>
       <c r="G9" t="n">
-        <v>1075</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="10">
@@ -1697,29 +1669,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>조립4호기</t>
+          <t>분리11호기</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>O2O2 Spherical(DK70)_K2-SMD</t>
+          <t>(UV_NEW)CS30_8.60</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>18256</v>
+        <v>15487</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="11">
@@ -1730,29 +1702,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Si_1-Day_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>조립7호기</t>
+          <t>분리14호기</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>O2O2 D_UV_Toric_SMD</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4177</v>
+        <v>8887</v>
       </c>
       <c r="G11" t="n">
-        <v>597</v>
+        <v>830</v>
       </c>
     </row>
     <row r="12">
@@ -1773,19 +1745,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>분리10호기</t>
+          <t>분리4호기</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS30-Dry</t>
+          <t>(NEW)S38-HD-Dry-14.0</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>12882</v>
+        <v>12168</v>
       </c>
       <c r="G12" t="n">
-        <v>1796</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="13">
@@ -1806,19 +1778,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>분리11호기</t>
+          <t>분리5호기</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(UV_NEW)CS30_8.60</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>14893</v>
+        <v>3581</v>
       </c>
       <c r="G13" t="n">
-        <v>1543</v>
+        <v>859</v>
       </c>
     </row>
     <row r="14">
@@ -1839,19 +1811,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>분리14호기</t>
+          <t>분리5호기</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>US55-2(M)</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5882</v>
+        <v>8167</v>
       </c>
       <c r="G14" t="n">
-        <v>1444</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="15">
@@ -1867,24 +1839,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>분리4호기</t>
+          <t>분리3호기</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(NEW)S38-HD-Dry-14.0</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>9998</v>
+        <v>2605</v>
       </c>
       <c r="G15" t="n">
-        <v>2747</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="16">
@@ -1895,29 +1867,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>분리5호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>Baby Espresso_PIA_M_중사각(Y)</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>10778</v>
+        <v>1633</v>
       </c>
       <c r="G16" t="n">
-        <v>4330</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1928,29 +1900,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>분리5호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>US55-2(M)</t>
+          <t>Brulee Pearl_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1740</v>
+        <v>1406</v>
       </c>
       <c r="G17" t="n">
-        <v>727</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
@@ -1961,29 +1933,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>분리3호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2107</v>
+        <v>498</v>
       </c>
       <c r="G18" t="n">
-        <v>2413</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
@@ -2009,14 +1981,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
+          <t>Date Topaz_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1274</v>
+        <v>2258</v>
       </c>
       <c r="G19" t="n">
-        <v>36</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20">
@@ -2042,14 +2014,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FLAMINGO_PIA_M_(중)(Y)</t>
+          <t>Garnet_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1479</v>
+        <v>720</v>
       </c>
       <c r="G20" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -2075,14 +2047,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oolong Tea_PIA_M_중사각(Y)</t>
+          <t>Strawberry Quartz_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>940</v>
+        <v>732</v>
       </c>
       <c r="G21" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
@@ -2108,14 +2080,14 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Princess Chocolat_PIA_M_(중)_14.5</t>
+          <t>Tiramisu Ring_PIA_M_중사각(Y)</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>948</v>
+        <v>1431</v>
       </c>
       <c r="G22" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -2136,19 +2108,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
+          <t>Uniform Black_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>934</v>
+        <v>1196</v>
       </c>
       <c r="G23" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
@@ -2169,19 +2141,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Date Topaz_PIA_M_(중)(Y)</t>
+          <t>Bella-Highlight_원형</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1882</v>
+        <v>151</v>
       </c>
       <c r="G24" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2202,19 +2174,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sakura Smore_PIA_M_(중)(Y)</t>
+          <t>Bella-SnowWhite_14.5_원형</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>402</v>
+        <v>212</v>
       </c>
       <c r="G25" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2235,19 +2207,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tiramisu Ring_PIA_M_중사각(Y)</t>
+          <t>CLC-30_원형</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1436</v>
+        <v>321</v>
       </c>
       <c r="G26" t="n">
-        <v>76</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -2273,14 +2245,14 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CLC-30_원형</t>
+          <t>Clalen Iris_Claire Brown_원형</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="G27" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2306,14 +2278,14 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NewFusion_원형</t>
+          <t>Clalen Iris_Claire Gray_원형</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="G28" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2334,19 +2306,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bella Diamond_14.5_중사각</t>
+          <t>Clalen Iris_GRA_3302_원형</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>420</v>
+        <v>72</v>
       </c>
       <c r="G29" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2367,19 +2339,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bella Glow_중사각</t>
+          <t>Desio color_원형</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>466</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2400,19 +2372,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bella-Contour_중사각</t>
+          <t>Festival-II-Color_원형</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>402</v>
+        <v>205</v>
       </c>
       <c r="G31" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2433,19 +2405,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bella-Elite_14.5_중사각</t>
+          <t>Intensive 55_원형</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>968</v>
+        <v>170</v>
       </c>
       <c r="G32" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2466,19 +2438,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bella-Natural_중사각</t>
+          <t>KBS-C_원형</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2200</v>
+        <v>70</v>
       </c>
       <c r="G33" t="n">
-        <v>759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2499,19 +2471,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Clalen 6M_WEIGUANG_38%_(중)</t>
+          <t>Neon Color_원형</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>136</v>
+        <v>239</v>
       </c>
       <c r="G34" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2532,19 +2504,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dazzle Beige_2T_(PBT)PIA_M(Y)</t>
+          <t>NewFusion_원형</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>400</v>
+        <v>353</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36">
@@ -2570,11 +2542,11 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MARIGOLD_PIA_M_(중)(Y)</t>
+          <t>Affogato_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>72</v>
+        <v>337</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2603,14 +2575,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tiramisu Ring_PIA_M_중사각(Y)</t>
+          <t>Bella Diamond_14.5_중사각</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>349</v>
+        <v>3414</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38">
@@ -2631,19 +2603,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bella Diamond_14.5_중사각</t>
+          <t>Bella Glow_중사각</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>768</v>
+        <v>1898</v>
       </c>
       <c r="G38" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
@@ -2664,19 +2636,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bella Glow_중사각</t>
+          <t>Bella-Contour_중사각</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="G39" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2697,19 +2669,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bella-Contour_중사각</t>
+          <t>Bella-Elite_14.5_중사각</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>514</v>
+        <v>1580</v>
       </c>
       <c r="G40" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41">
@@ -2730,7 +2702,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2739,10 +2711,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1180</v>
+        <v>362</v>
       </c>
       <c r="G41" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
@@ -2763,19 +2735,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bella-Natural_중사각</t>
+          <t>Clalen 1M_Planet_Gray Moon</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>576</v>
+        <v>80</v>
       </c>
       <c r="G42" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -2796,19 +2768,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CLC-30_원형</t>
+          <t>Clalen 1M_Planet_Mercury Blue</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>776</v>
+        <v>193</v>
       </c>
       <c r="G43" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2829,19 +2801,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KBS-C_원형</t>
+          <t>Clalen 1M_Planet_Venus Brown</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="G44" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45">
@@ -2862,19 +2834,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NewFusion_원형</t>
+          <t>NewFusion_소사각</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>708</v>
+        <v>56</v>
       </c>
       <c r="G45" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2895,19 +2867,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CLC-30_바이알</t>
+          <t>Clalen 6M_YOUYU_38%_(중)</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1249</v>
+        <v>260</v>
       </c>
       <c r="G46" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47">
@@ -2928,19 +2900,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Festival-II-Color_은캡</t>
+          <t>CLC-30_원형</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1629</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>167</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48">
@@ -2956,24 +2928,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>CLC-30_바이알</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>4176</v>
+        <v>1259</v>
       </c>
       <c r="G48" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -2989,24 +2961,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>Festival-II-Color_은캡</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>4686</v>
+        <v>2439</v>
       </c>
       <c r="G49" t="n">
-        <v>329</v>
+        <v>356</v>
       </c>
     </row>
     <row r="50">
@@ -3027,7 +2999,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3036,10 +3008,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>3590</v>
+        <v>5338</v>
       </c>
       <c r="G50" t="n">
-        <v>30</v>
+        <v>141</v>
       </c>
     </row>
     <row r="51">
@@ -3060,7 +3032,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3069,10 +3041,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2024</v>
+        <v>1850</v>
       </c>
       <c r="G51" t="n">
-        <v>20</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52">
@@ -3093,19 +3065,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Metha_55_중사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1200</v>
+        <v>3236</v>
       </c>
       <c r="G52" t="n">
-        <v>197</v>
+        <v>64</v>
       </c>
     </row>
     <row r="53">
@@ -3126,19 +3098,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Metha_55_중사각</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>11476</v>
+        <v>6048</v>
       </c>
       <c r="G53" t="n">
-        <v>96</v>
+        <v>201</v>
       </c>
     </row>
     <row r="54">
@@ -3159,19 +3131,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>Metha_55_중사각</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1744</v>
+        <v>1190</v>
       </c>
       <c r="G54" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
@@ -3192,19 +3164,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Metha_55_원형</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1784</v>
+        <v>1468</v>
       </c>
       <c r="G55" t="n">
-        <v>33</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56">
@@ -3220,24 +3192,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>680</v>
+        <v>1868</v>
       </c>
       <c r="G56" t="n">
-        <v>467</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57">
@@ -3253,24 +3225,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>Metha_55_원형</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1132</v>
+        <v>2863</v>
       </c>
       <c r="G57" t="n">
-        <v>121</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58">
@@ -3286,24 +3258,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>Metha_55_중사각</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>440</v>
+        <v>263</v>
       </c>
       <c r="G58" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3319,7 +3291,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3329,14 +3301,14 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>964</v>
+        <v>1963</v>
       </c>
       <c r="G59" t="n">
-        <v>238</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60">
@@ -3352,24 +3324,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>T38_금캡(UV포함)</t>
+          <t>Metha_55_중사각</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3457</v>
+        <v>4074</v>
       </c>
       <c r="G60" t="n">
-        <v>756</v>
+        <v>384</v>
       </c>
     </row>
     <row r="61">
@@ -3385,24 +3357,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
+          <t>S38_은캡(BLUE TINT)</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1034</v>
+        <v>367</v>
       </c>
       <c r="G61" t="n">
-        <v>297</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
@@ -3418,24 +3390,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>396</v>
+        <v>224</v>
       </c>
       <c r="G62" t="n">
-        <v>59</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63">
@@ -3451,24 +3423,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1674</v>
+        <v>466</v>
       </c>
       <c r="G63" t="n">
-        <v>179</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64">
@@ -3484,7 +3456,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3494,14 +3466,14 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Silicone relax_소사각</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3788</v>
+        <v>248</v>
       </c>
       <c r="G64" t="n">
-        <v>497</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65">
@@ -3517,24 +3489,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>T38_금캡</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>6074</v>
+        <v>544</v>
       </c>
       <c r="G65" t="n">
-        <v>933</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66">
@@ -3550,24 +3522,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>T38_금캡(UV포함)</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1060</v>
+        <v>3513</v>
       </c>
       <c r="G66" t="n">
-        <v>456</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="67">
@@ -3583,24 +3555,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>Si_FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>O2O2 M_Mysti Gray EX_(중)</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>3263</v>
+        <v>424</v>
       </c>
       <c r="G67" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3616,288 +3588,288 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Si_FRP_Toric</t>
+          <t>Si_FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>O2O2 M_UV_Toric_SMD_(소)</t>
+          <t>O2O2 M_Mysti Khaki EX_(중)</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>673</v>
+        <v>429</v>
       </c>
       <c r="G68" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>조립10호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1-Day_iris_Latin</t>
+          <t>O2O2 M_Natural Brown EX_(중)</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>27174</v>
+        <v>506</v>
       </c>
       <c r="G69" t="n">
-        <v>665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>조립11호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PIA D_Sakana_55% UV</t>
+          <t>O2O2 M_Natural Chocolat EX_(중)</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>27901</v>
+        <v>101</v>
       </c>
       <c r="G70" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>조립12호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>O2O2 M_Natural Gray EX_(중)</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>27332</v>
+        <v>343</v>
       </c>
       <c r="G71" t="n">
-        <v>921</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>조립14호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>Silicone relax_소사각</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>23280</v>
+        <v>2666</v>
       </c>
       <c r="G72" t="n">
-        <v>4920</v>
+        <v>250</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>조립14호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>22147</v>
+        <v>362</v>
       </c>
       <c r="G73" t="n">
-        <v>3100</v>
+        <v>138</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>조립15호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>19654</v>
+        <v>7215</v>
       </c>
       <c r="G74" t="n">
-        <v>3340</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>조립16호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>26495</v>
+        <v>7247</v>
       </c>
       <c r="G75" t="n">
-        <v>1542</v>
+        <v>743</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Toric</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>조립19호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>O2O2 M_UV_Toric_SMD_(소)</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>23921</v>
+        <v>284</v>
       </c>
       <c r="G76" t="n">
-        <v>2100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="77">
@@ -3918,19 +3890,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>조립20호기</t>
+          <t>조립10호기</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>20704</v>
+        <v>39942</v>
       </c>
       <c r="G77" t="n">
-        <v>3939</v>
+        <v>82</v>
       </c>
     </row>
     <row r="78">
@@ -3951,19 +3923,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>조립24호기</t>
+          <t>조립11호기</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Sakana_55% UV</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>32851</v>
+        <v>25410</v>
       </c>
       <c r="G78" t="n">
-        <v>2055</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="79">
@@ -3984,19 +3956,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>조립25호기</t>
+          <t>조립12호기</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>25668</v>
+        <v>26436</v>
       </c>
       <c r="G79" t="n">
-        <v>2595</v>
+        <v>182</v>
       </c>
     </row>
     <row r="80">
@@ -4017,19 +3989,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>조립26호기</t>
+          <t>조립13호기</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>BELLA D_VENUS 55%</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>14945</v>
+        <v>60936</v>
       </c>
       <c r="G80" t="n">
-        <v>1240</v>
+        <v>999</v>
       </c>
     </row>
     <row r="81">
@@ -4050,19 +4022,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>조립27호기</t>
+          <t>조립14호기</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>23764</v>
+        <v>27492</v>
       </c>
       <c r="G81" t="n">
-        <v>3520</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -4083,19 +4055,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>조립40호기</t>
+          <t>조립15호기</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>38711</v>
+        <v>36810</v>
       </c>
       <c r="G82" t="n">
-        <v>1547</v>
+        <v>2852</v>
       </c>
     </row>
     <row r="83">
@@ -4116,19 +4088,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>조립42호기</t>
+          <t>조립16호기</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>26094</v>
+        <v>22576</v>
       </c>
       <c r="G83" t="n">
-        <v>1735</v>
+        <v>41</v>
       </c>
     </row>
     <row r="84">
@@ -4149,19 +4121,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>조립44호기</t>
+          <t>조립19호기</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_First Love Kristin Brown 14.2_38% UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>7066</v>
+        <v>18660</v>
       </c>
       <c r="G84" t="n">
-        <v>6257</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="85">
@@ -4182,19 +4154,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>조립45호기</t>
+          <t>조립23호기</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1-Day_iris_Latin</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>28357</v>
+        <v>46177</v>
       </c>
       <c r="G85" t="n">
-        <v>2000</v>
+        <v>4003</v>
       </c>
     </row>
     <row r="86">
@@ -4215,19 +4187,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>조립47호기</t>
+          <t>조립25호기</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>22481</v>
+        <v>21678</v>
       </c>
       <c r="G86" t="n">
-        <v>5402</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="87">
@@ -4248,19 +4220,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>조립48호기</t>
+          <t>조립26호기</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>BELLA D_MARS 55%</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>25120</v>
+        <v>11830</v>
       </c>
       <c r="G87" t="n">
-        <v>75</v>
+        <v>172</v>
       </c>
     </row>
     <row r="88">
@@ -4281,19 +4253,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>조립49호기</t>
+          <t>조립27호기</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>38488</v>
+        <v>32760</v>
       </c>
       <c r="G88" t="n">
-        <v>9827</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="89">
@@ -4314,19 +4286,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>조립50호기</t>
+          <t>조립42호기</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>27917</v>
+        <v>35393</v>
       </c>
       <c r="G89" t="n">
-        <v>172</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="90">
@@ -4347,19 +4319,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>조립51호기</t>
+          <t>조립44호기</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>HAPA(PIA) D_First Love Kristin Brown 14.2_38% UV</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>57451</v>
+        <v>16606</v>
       </c>
       <c r="G90" t="n">
-        <v>50</v>
+        <v>8858</v>
       </c>
     </row>
     <row r="91">
@@ -4380,19 +4352,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>조립52호기</t>
+          <t>조립45호기</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>1-Day_iris_Latin</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>37000</v>
+        <v>30781</v>
       </c>
       <c r="G91" t="n">
-        <v>5858</v>
+        <v>608</v>
       </c>
     </row>
     <row r="92">
@@ -4413,19 +4385,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>조립54호기</t>
+          <t>조립47호기</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>PIA D_Glow Brown_38% UV</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Beige 14.2_55% UV</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>17274</v>
+        <v>16134</v>
       </c>
       <c r="G92" t="n">
-        <v>3325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -4446,19 +4418,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>조립56호기</t>
+          <t>조립47호기</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>28796</v>
+        <v>24678</v>
       </c>
       <c r="G93" t="n">
-        <v>534</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="94">
@@ -4479,19 +4451,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>조립57호기</t>
+          <t>조립48호기</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PIA D_Air Gray_55% UV</t>
+          <t>PIA D_Sakura Mousse_55% UV</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>28628</v>
+        <v>51527</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>5233</v>
       </c>
     </row>
     <row r="95">
@@ -4512,19 +4484,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>조립58호기</t>
+          <t>조립49호기</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>19513</v>
+        <v>10709</v>
       </c>
       <c r="G95" t="n">
-        <v>2690</v>
+        <v>5281</v>
       </c>
     </row>
     <row r="96">
@@ -4545,19 +4517,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>조립59호기</t>
+          <t>조립50호기</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>30208</v>
+        <v>58183</v>
       </c>
       <c r="G96" t="n">
-        <v>594</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97">
@@ -4573,24 +4545,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립52호기</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-0.75 Brown Bunny_55% UV</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1370</v>
+        <v>24589</v>
       </c>
       <c r="G97" t="n">
-        <v>604</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="98">
@@ -4606,24 +4578,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립56호기</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>11920</v>
+        <v>28995</v>
       </c>
       <c r="G98" t="n">
-        <v>1863</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="99">
@@ -4639,24 +4611,24 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립57호기</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>PIA D_Air Gray_55% UV</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>12797</v>
+        <v>23909</v>
       </c>
       <c r="G99" t="n">
-        <v>800</v>
+        <v>420</v>
       </c>
     </row>
     <row r="100">
@@ -4672,24 +4644,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립58호기</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>7783</v>
+        <v>56598</v>
       </c>
       <c r="G100" t="n">
-        <v>400</v>
+        <v>714</v>
       </c>
     </row>
     <row r="101">
@@ -4705,24 +4677,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립59호기</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Gray</t>
+          <t>PIA_TAMA KONNYAKU_55%</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>9404</v>
+        <v>28326</v>
       </c>
       <c r="G101" t="n">
-        <v>689</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="102">
@@ -4743,19 +4715,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Gray</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>4886</v>
+        <v>10117</v>
       </c>
       <c r="G102" t="n">
-        <v>1282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -4776,19 +4748,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>11868</v>
+        <v>1442</v>
       </c>
       <c r="G103" t="n">
-        <v>500</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="104">
@@ -4809,19 +4781,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>10886</v>
+        <v>10319</v>
       </c>
       <c r="G104" t="n">
-        <v>2352</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="105">
@@ -4837,24 +4809,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>조립46호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Coffee Jelly_PIA_M(Y)</t>
+          <t>Toric_CP-0.75_Halo Brown</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>5178</v>
+        <v>2748</v>
       </c>
       <c r="G105" t="n">
-        <v>6834</v>
+        <v>934</v>
       </c>
     </row>
     <row r="106">
@@ -4870,24 +4842,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>조립53호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Oolong Tea_PIA_M_중사각(Y)</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>9910</v>
+        <v>25635</v>
       </c>
       <c r="G106" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -4908,19 +4880,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>조립55호기</t>
+          <t>조립46호기</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cream Rose_PIA_M</t>
+          <t>Coffee Jelly_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>13598</v>
+        <v>15975</v>
       </c>
       <c r="G107" t="n">
-        <v>1087</v>
+        <v>3688</v>
       </c>
     </row>
     <row r="108">
@@ -4931,29 +4903,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>조립53호기</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>Twinkle Brown_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>37218</v>
+        <v>15557</v>
       </c>
       <c r="G108" t="n">
-        <v>4341</v>
+        <v>672</v>
       </c>
     </row>
     <row r="109">
@@ -4964,29 +4936,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>조립55호기</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Mirror Gray_3T_(PBT)PIA_M(Y)</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>17188</v>
+        <v>7234</v>
       </c>
       <c r="G109" t="n">
-        <v>3910</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="110">
@@ -5007,19 +4979,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>BELLA D_VENUS 55%</t>
+          <t>1-Day_iris_Latin</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>10366</v>
+        <v>24301</v>
       </c>
       <c r="G110" t="n">
-        <v>1130</v>
+        <v>4101</v>
       </c>
     </row>
     <row r="111">
@@ -5040,19 +5012,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>BELLA D_MARS 55%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>20416</v>
+        <v>8138</v>
       </c>
       <c r="G111" t="n">
-        <v>2038</v>
+        <v>744</v>
       </c>
     </row>
     <row r="112">
@@ -5073,19 +5045,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PIA D_Sakana_55% UV</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>20266</v>
+        <v>9125</v>
       </c>
       <c r="G112" t="n">
-        <v>2808</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="113">
@@ -5106,19 +5078,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>BELLA D_VENUS 55%</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>30262</v>
+        <v>3169</v>
       </c>
       <c r="G113" t="n">
-        <v>3840</v>
+        <v>280</v>
       </c>
     </row>
     <row r="114">
@@ -5139,19 +5111,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>7986</v>
+        <v>40243</v>
       </c>
       <c r="G114" t="n">
-        <v>1220</v>
+        <v>4975</v>
       </c>
     </row>
     <row r="115">
@@ -5172,19 +5144,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1-Day_iris_Latin</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>25020</v>
+        <v>5964</v>
       </c>
       <c r="G115" t="n">
-        <v>2749</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="116">
@@ -5205,19 +5177,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>PIA D_Sakana_55% UV</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>14899</v>
+        <v>22600</v>
       </c>
       <c r="G116" t="n">
-        <v>1465</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="117">
@@ -5238,19 +5210,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>분리19호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>27443</v>
+        <v>26955</v>
       </c>
       <c r="G117" t="n">
-        <v>3052</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="118">
@@ -5271,19 +5243,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>분리19호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>9554</v>
+        <v>9720</v>
       </c>
       <c r="G118" t="n">
-        <v>1445</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="119">
@@ -5304,19 +5276,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>1-Day_iris_Latin</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>42142</v>
+        <v>24344</v>
       </c>
       <c r="G119" t="n">
-        <v>5212</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="120">
@@ -5337,19 +5309,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>37847</v>
+        <v>16155</v>
       </c>
       <c r="G120" t="n">
-        <v>5742</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="121">
@@ -5370,19 +5342,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>분리19호기</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1-Day_iris_Latin</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>19229</v>
+        <v>2574</v>
       </c>
       <c r="G121" t="n">
-        <v>3927</v>
+        <v>218</v>
       </c>
     </row>
     <row r="122">
@@ -5403,19 +5375,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>분리19호기</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>16844</v>
+        <v>38810</v>
       </c>
       <c r="G122" t="n">
-        <v>1755</v>
+        <v>5705</v>
       </c>
     </row>
     <row r="123">
@@ -5436,19 +5408,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>2635</v>
+        <v>25619</v>
       </c>
       <c r="G123" t="n">
-        <v>426</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="124">
@@ -5469,19 +5441,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>21097</v>
+        <v>6889</v>
       </c>
       <c r="G124" t="n">
-        <v>4478</v>
+        <v>814</v>
       </c>
     </row>
     <row r="125">
@@ -5502,19 +5474,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>HOYA_Casual Ash</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>3650</v>
+        <v>19504</v>
       </c>
       <c r="G125" t="n">
-        <v>1774</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="126">
@@ -5535,19 +5507,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>30855</v>
+        <v>17995</v>
       </c>
       <c r="G126" t="n">
-        <v>9516</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="127">
@@ -5568,19 +5540,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>39093</v>
+        <v>24559</v>
       </c>
       <c r="G127" t="n">
-        <v>6233</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="128">
@@ -5601,19 +5573,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2671</v>
+        <v>15384</v>
       </c>
       <c r="G128" t="n">
-        <v>547</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="129">
@@ -5634,7 +5606,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5643,10 +5615,10 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>9657</v>
+        <v>20241</v>
       </c>
       <c r="G129" t="n">
-        <v>1097</v>
+        <v>4362</v>
       </c>
     </row>
     <row r="130">
@@ -5667,19 +5639,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>HOYA_Maquia Brown</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>129</v>
+        <v>9375</v>
       </c>
       <c r="G130" t="n">
-        <v>626</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="131">
@@ -5700,19 +5672,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>14389</v>
+        <v>14656</v>
       </c>
       <c r="G131" t="n">
-        <v>1624</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="132">
@@ -5733,19 +5705,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>24318</v>
+        <v>19170</v>
       </c>
       <c r="G132" t="n">
-        <v>1430</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="133">
@@ -5766,19 +5738,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>18636</v>
+        <v>2570</v>
       </c>
       <c r="G133" t="n">
-        <v>931</v>
+        <v>351</v>
       </c>
     </row>
     <row r="134">
@@ -5799,19 +5771,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>19792</v>
+        <v>7776</v>
       </c>
       <c r="G134" t="n">
-        <v>3986</v>
+        <v>641</v>
       </c>
     </row>
     <row r="135">
@@ -5832,19 +5804,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>PIA D_Uniform Black_55% UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>14173</v>
+        <v>19739</v>
       </c>
       <c r="G135" t="n">
-        <v>2376</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="136">
@@ -5865,19 +5837,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_First Love Kristin Brown 14.2_38% UV</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>9912</v>
+        <v>9810</v>
       </c>
       <c r="G136" t="n">
-        <v>4891</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="137">
@@ -5898,19 +5870,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>PIA D_Cream Rose_38% UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>6811</v>
+        <v>24441</v>
       </c>
       <c r="G137" t="n">
-        <v>1477</v>
+        <v>7070</v>
       </c>
     </row>
     <row r="138">
@@ -5931,19 +5903,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>PIA D_Glow Brown_38% UV</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>15449</v>
+        <v>16524</v>
       </c>
       <c r="G138" t="n">
-        <v>3408</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="139">
@@ -5964,7 +5936,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5973,10 +5945,10 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>17864</v>
+        <v>25038</v>
       </c>
       <c r="G139" t="n">
-        <v>1418</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="140">
@@ -5997,19 +5969,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>HOYA_Casual Ash</t>
+          <t>PIA D_Uniform Black_55% UV</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1610</v>
+        <v>1573</v>
       </c>
       <c r="G140" t="n">
-        <v>702</v>
+        <v>219</v>
       </c>
     </row>
     <row r="141">
@@ -6030,19 +6002,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>HOYA_Maquia Brown</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>374</v>
+        <v>22139</v>
       </c>
       <c r="G141" t="n">
-        <v>719</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="142">
@@ -6063,19 +6035,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>HAPA(PIA) D_First Love Kristin Brown 14.2_38% UV</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>7902</v>
+        <v>1380</v>
       </c>
       <c r="G142" t="n">
-        <v>593</v>
+        <v>356</v>
       </c>
     </row>
     <row r="143">
@@ -6096,19 +6068,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>HOYA_Maquia Brown</t>
+          <t>PIA D_Glow Brown_38% UV</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>4392</v>
+        <v>12787</v>
       </c>
       <c r="G143" t="n">
-        <v>909</v>
+        <v>4487</v>
       </c>
     </row>
     <row r="144">
@@ -6129,19 +6101,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA D_Sakura Mousse_55% UV</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>25852</v>
+        <v>18415</v>
       </c>
       <c r="G144" t="n">
-        <v>4002</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="145">
@@ -6162,19 +6134,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>12447</v>
+        <v>29997</v>
       </c>
       <c r="G145" t="n">
-        <v>1746</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="146">
@@ -6195,19 +6167,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Air Gray_55% UV</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>635</v>
+        <v>2828</v>
       </c>
       <c r="G146" t="n">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="147">
@@ -6228,19 +6200,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>BELLA D_Nerelle 55%</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>18113</v>
+        <v>12882</v>
       </c>
       <c r="G147" t="n">
-        <v>1762</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="148">
@@ -6261,19 +6233,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>9865</v>
+        <v>21865</v>
       </c>
       <c r="G148" t="n">
-        <v>710</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="149">
@@ -6294,19 +6266,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>분리43호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Sakura Mousse_55% UV</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>23437</v>
+        <v>14016</v>
       </c>
       <c r="G149" t="n">
-        <v>3688</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="150">
@@ -6322,24 +6294,24 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>5507</v>
+        <v>8955</v>
       </c>
       <c r="G150" t="n">
-        <v>1140</v>
+        <v>806</v>
       </c>
     </row>
     <row r="151">
@@ -6355,24 +6327,24 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>PIA D_Air Gray_55% UV</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>5191</v>
+        <v>26829</v>
       </c>
       <c r="G151" t="n">
-        <v>1025</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="152">
@@ -6388,24 +6360,24 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Gray</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1812</v>
+        <v>8246</v>
       </c>
       <c r="G152" t="n">
-        <v>1325</v>
+        <v>833</v>
       </c>
     </row>
     <row r="153">
@@ -6421,24 +6393,24 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리43호기</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2351</v>
+        <v>30258</v>
       </c>
       <c r="G153" t="n">
-        <v>314</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="154">
@@ -6464,14 +6436,14 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>PIA D Toric_CP-0.75 Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>5082</v>
+        <v>773</v>
       </c>
       <c r="G154" t="n">
-        <v>1407</v>
+        <v>597</v>
       </c>
     </row>
     <row r="155">
@@ -6497,14 +6469,14 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>PIA D Toric_CP-1.25 Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>19284</v>
+        <v>4357</v>
       </c>
       <c r="G155" t="n">
-        <v>5855</v>
+        <v>916</v>
       </c>
     </row>
     <row r="156">
@@ -6520,24 +6492,24 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>분리22호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>36156</v>
+        <v>10733</v>
       </c>
       <c r="G156" t="n">
-        <v>6866</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="157">
@@ -6553,24 +6525,24 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>분리23호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>35631</v>
+        <v>6174</v>
       </c>
       <c r="G157" t="n">
-        <v>8306</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="158">
@@ -6586,24 +6558,24 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>분리25호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Toric_CP-1.25_Halo Gray</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>44431</v>
+        <v>5430</v>
       </c>
       <c r="G158" t="n">
-        <v>6589</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="159">
@@ -6619,24 +6591,24 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>41519</v>
+        <v>1165</v>
       </c>
       <c r="G159" t="n">
-        <v>11591</v>
+        <v>391</v>
       </c>
     </row>
     <row r="160">
@@ -6652,24 +6624,24 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Date Topaz_PIA_M(Y)</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1590</v>
+        <v>10318</v>
       </c>
       <c r="G160" t="n">
-        <v>409</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="161">
@@ -6685,24 +6657,24 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리22호기</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Tarte Tatin_PIA_M(Y)</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>3122</v>
+        <v>35134</v>
       </c>
       <c r="G161" t="n">
-        <v>1476</v>
+        <v>7250</v>
       </c>
     </row>
     <row r="162">
@@ -6713,29 +6685,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리23호기</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>3540</v>
+        <v>30263</v>
       </c>
       <c r="G162" t="n">
-        <v>50</v>
+        <v>6376</v>
       </c>
     </row>
     <row r="163">
@@ -6746,29 +6718,29 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리25호기</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>6450</v>
+        <v>44634</v>
       </c>
       <c r="G163" t="n">
-        <v>90</v>
+        <v>9419</v>
       </c>
     </row>
     <row r="164">
@@ -6779,29 +6751,29 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>3420</v>
+        <v>43605</v>
       </c>
       <c r="G164" t="n">
-        <v>70</v>
+        <v>10144</v>
       </c>
     </row>
     <row r="165">
@@ -6812,29 +6784,29 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>Coffee Jelly_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>3820</v>
+        <v>2836</v>
       </c>
       <c r="G165" t="n">
-        <v>20</v>
+        <v>755</v>
       </c>
     </row>
     <row r="166">
@@ -6845,29 +6817,29 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>Cream Rose_PIA_M</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>4171</v>
+        <v>10986</v>
       </c>
       <c r="G166" t="n">
-        <v>584</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="167">
@@ -6878,29 +6850,29 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>PIA_SARANG BROWN</t>
+          <t>Mirror Gray_3T_(PBT)PIA_M(Y)</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>10145</v>
+        <v>1232</v>
       </c>
       <c r="G167" t="n">
-        <v>60</v>
+        <v>292</v>
       </c>
     </row>
     <row r="168">
@@ -6911,29 +6883,29 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>Oolong Tea_PIA_M_중사각(Y)</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>3400</v>
+        <v>3987</v>
       </c>
       <c r="G168" t="n">
-        <v>50</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="169">
@@ -6944,29 +6916,29 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>Sakura Smore_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>18470</v>
+        <v>760</v>
       </c>
       <c r="G169" t="n">
-        <v>290</v>
+        <v>226</v>
       </c>
     </row>
     <row r="170">
@@ -6977,29 +6949,29 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>Twinkle Brown_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>4495</v>
+        <v>1757</v>
       </c>
       <c r="G170" t="n">
-        <v>170</v>
+        <v>260</v>
       </c>
     </row>
     <row r="171">
@@ -7010,29 +6982,29 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>Uniform Black_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>3115</v>
+        <v>2404</v>
       </c>
       <c r="G171" t="n">
-        <v>40</v>
+        <v>369</v>
       </c>
     </row>
     <row r="172">
@@ -7053,19 +7025,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>12072</v>
+        <v>3135</v>
       </c>
       <c r="G172" t="n">
-        <v>678</v>
+        <v>70</v>
       </c>
     </row>
     <row r="173">
@@ -7086,19 +7058,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3070</v>
+        <v>2970</v>
       </c>
       <c r="G173" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="174">
@@ -7119,16 +7091,16 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PIA_SARANG BROWN</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>6500</v>
+        <v>3185</v>
       </c>
       <c r="G174" t="n">
         <v>50</v>
@@ -7152,19 +7124,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>0</v>
+        <v>1330</v>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="176">
@@ -7185,19 +7157,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>(NEW)1-Day_iris_Suzy Brown</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>6030</v>
+        <v>3120</v>
       </c>
       <c r="G176" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="177">
@@ -7218,19 +7190,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA_SARANG BROWN</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>29589</v>
+        <v>6355</v>
       </c>
       <c r="G177" t="n">
-        <v>661</v>
+        <v>115</v>
       </c>
     </row>
     <row r="178">
@@ -7251,19 +7223,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>5895</v>
+        <v>3500</v>
       </c>
       <c r="G178" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="179">
@@ -7284,19 +7256,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>2785</v>
+        <v>10300</v>
       </c>
       <c r="G179" t="n">
-        <v>35</v>
+        <v>205</v>
       </c>
     </row>
     <row r="180">
@@ -7317,19 +7289,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>9650</v>
+        <v>3050</v>
       </c>
       <c r="G180" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="181">
@@ -7350,19 +7322,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>PIA_SARANG BROWN</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2805</v>
+        <v>15200</v>
       </c>
       <c r="G181" t="n">
-        <v>45</v>
+        <v>235</v>
       </c>
     </row>
     <row r="182">
@@ -7383,19 +7355,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Astra Glitter</t>
+          <t>PIA_SARANG BROWN</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1105</v>
+        <v>5600</v>
       </c>
       <c r="G182" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
     </row>
     <row r="183">
@@ -7416,19 +7388,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>BELLA D_Silent Gray 55%</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>7900</v>
+        <v>9709</v>
       </c>
       <c r="G183" t="n">
-        <v>60</v>
+        <v>706</v>
       </c>
     </row>
     <row r="184">
@@ -7449,19 +7421,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>BELLA D_VENUS 55%</t>
+          <t>(NEW)1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3700</v>
+        <v>5905</v>
       </c>
       <c r="G184" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="185">
@@ -7482,19 +7454,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>20010</v>
+        <v>53930</v>
       </c>
       <c r="G185" t="n">
-        <v>185</v>
+        <v>540</v>
       </c>
     </row>
     <row r="186">
@@ -7515,19 +7487,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>BELLA D_MARS 55%</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>36560</v>
+        <v>2585</v>
       </c>
       <c r="G186" t="n">
-        <v>635</v>
+        <v>90</v>
       </c>
     </row>
     <row r="187">
@@ -7548,19 +7520,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>BELLA D_Silent Gray 55%</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>23807</v>
+        <v>2415</v>
       </c>
       <c r="G187" t="n">
-        <v>2613</v>
+        <v>635</v>
       </c>
     </row>
     <row r="188">
@@ -7581,19 +7553,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>26550</v>
+        <v>4775</v>
       </c>
       <c r="G188" t="n">
-        <v>465</v>
+        <v>80</v>
       </c>
     </row>
     <row r="189">
@@ -7614,19 +7586,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>9803</v>
+        <v>44236</v>
       </c>
       <c r="G189" t="n">
-        <v>617</v>
+        <v>794</v>
       </c>
     </row>
     <row r="190">
@@ -7647,19 +7619,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>5865</v>
+        <v>16455</v>
       </c>
       <c r="G190" t="n">
-        <v>65</v>
+        <v>175</v>
       </c>
     </row>
     <row r="191">
@@ -7680,19 +7652,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>PIA D_Tiramisu Ring_55% UV</t>
+          <t>1-Day_iris_Latin</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>3100</v>
+        <v>6270</v>
       </c>
       <c r="G191" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="192">
@@ -7713,19 +7685,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>4175</v>
+        <v>35365</v>
       </c>
       <c r="G192" t="n">
-        <v>50</v>
+        <v>445</v>
       </c>
     </row>
     <row r="193">
@@ -7746,19 +7718,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>14680</v>
+        <v>17245</v>
       </c>
       <c r="G193" t="n">
-        <v>155</v>
+        <v>285</v>
       </c>
     </row>
     <row r="194">
@@ -7784,14 +7756,14 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>PIA_MS6 Sakura Petal_2T</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>3135</v>
+        <v>5215</v>
       </c>
       <c r="G194" t="n">
-        <v>35</v>
+        <v>455</v>
       </c>
     </row>
     <row r="195">
@@ -7817,14 +7789,14 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>PIA_SARANG BROWN</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>13030</v>
+        <v>3555</v>
       </c>
       <c r="G195" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
     </row>
     <row r="196">
@@ -7850,14 +7822,14 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>6540</v>
+        <v>7945</v>
       </c>
       <c r="G196" t="n">
-        <v>75</v>
+        <v>155</v>
       </c>
     </row>
     <row r="197">
@@ -7878,19 +7850,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>41884</v>
+        <v>5220</v>
       </c>
       <c r="G197" t="n">
-        <v>951</v>
+        <v>55</v>
       </c>
     </row>
     <row r="198">
@@ -7911,19 +7883,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Uniform Black_55% UV</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>14350</v>
+        <v>2460</v>
       </c>
       <c r="G198" t="n">
-        <v>290</v>
+        <v>65</v>
       </c>
     </row>
     <row r="199">
@@ -7944,19 +7916,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>18185</v>
+        <v>14210</v>
       </c>
       <c r="G199" t="n">
-        <v>265</v>
+        <v>205</v>
       </c>
     </row>
     <row r="200">
@@ -7977,19 +7949,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA_SARANG BROWN</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>18385</v>
+        <v>10620</v>
       </c>
       <c r="G200" t="n">
-        <v>415</v>
+        <v>100</v>
       </c>
     </row>
     <row r="201">
@@ -8010,19 +7982,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>BELLA D_MARS 55%</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>695</v>
+        <v>9955</v>
       </c>
       <c r="G201" t="n">
-        <v>70</v>
+        <v>115</v>
       </c>
     </row>
     <row r="202">
@@ -8043,19 +8015,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>BELLA D_Nerelle 55%</t>
+          <t>1-Day_iris_Latin</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>4467</v>
+        <v>3260</v>
       </c>
       <c r="G202" t="n">
-        <v>333</v>
+        <v>15</v>
       </c>
     </row>
     <row r="203">
@@ -8076,19 +8048,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>BELLA D_Silent Gray 55%</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1934</v>
+        <v>31450</v>
       </c>
       <c r="G203" t="n">
-        <v>1536</v>
+        <v>440</v>
       </c>
     </row>
     <row r="204">
@@ -8109,19 +8081,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>BELLA D_VENUS 55%</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>515</v>
+        <v>21066</v>
       </c>
       <c r="G204" t="n">
-        <v>55</v>
+        <v>719</v>
       </c>
     </row>
     <row r="205">
@@ -8147,14 +8119,14 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>BELLA_1-Day_Almond Brown(8년)</t>
+          <t>BELLA D_Nerelle 55%</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>465</v>
+        <v>15400</v>
       </c>
       <c r="G205" t="n">
-        <v>35</v>
+        <v>175</v>
       </c>
     </row>
     <row r="206">
@@ -8180,14 +8152,14 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>BELLA_1-Day_Platinum Grey(8년)</t>
+          <t>BELLA D_VENUS 55%</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>550</v>
+        <v>10390</v>
       </c>
       <c r="G206" t="n">
-        <v>45</v>
+        <v>330</v>
       </c>
     </row>
     <row r="207">
@@ -8208,19 +8180,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Plus Gray 14.2_55% UV</t>
+          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>12110</v>
+        <v>2970</v>
       </c>
       <c r="G207" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
     </row>
     <row r="208">
@@ -8241,19 +8213,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>4085</v>
+        <v>6574</v>
       </c>
       <c r="G208" t="n">
-        <v>110</v>
+        <v>266</v>
       </c>
     </row>
     <row r="209">
@@ -8274,19 +8246,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>3090</v>
+        <v>13890</v>
       </c>
       <c r="G209" t="n">
-        <v>25</v>
+        <v>145</v>
       </c>
     </row>
     <row r="210">
@@ -8312,14 +8284,14 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Rina_Choco Brown_1-Day</t>
+          <t>ALENSA_1-DAY BL Metha</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>800</v>
+        <v>6700</v>
       </c>
       <c r="G210" t="n">
-        <v>25</v>
+        <v>355</v>
       </c>
     </row>
     <row r="211">
@@ -8340,19 +8312,19 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Rina_Crystal Gray_1-Day</t>
+          <t>PIA D_Cream Rose_38% UV</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>4215</v>
+        <v>16461</v>
       </c>
       <c r="G211" t="n">
-        <v>55</v>
+        <v>509</v>
       </c>
     </row>
     <row r="212">
@@ -8373,19 +8345,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Rina_Mocha Brown_1-Day</t>
+          <t>PIA D_Garnet_38% UV</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1205</v>
+        <v>6625</v>
       </c>
       <c r="G212" t="n">
-        <v>15</v>
+        <v>240</v>
       </c>
     </row>
     <row r="213">
@@ -8411,14 +8383,14 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Gray_38% UV</t>
+          <t>PIA D_Glow Brown_38% UV</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>8145</v>
+        <v>15055</v>
       </c>
       <c r="G213" t="n">
-        <v>95</v>
+        <v>350</v>
       </c>
     </row>
     <row r="214">
@@ -8444,14 +8416,14 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>PIA D_Pomme Canele_38% UV</t>
+          <t>PIA D_Grege Quartz 38% UV</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>2380</v>
+        <v>20093</v>
       </c>
       <c r="G214" t="n">
-        <v>45</v>
+        <v>937</v>
       </c>
     </row>
     <row r="215">
@@ -8472,19 +8444,19 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>PIA D_Sugar Donut_38% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>4180</v>
+        <v>13130</v>
       </c>
       <c r="G215" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="216">
@@ -8510,14 +8482,14 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>14425</v>
+        <v>14400</v>
       </c>
       <c r="G216" t="n">
-        <v>160</v>
+        <v>235</v>
       </c>
     </row>
     <row r="217">
@@ -8543,14 +8515,14 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>IRIS_Soul Brown(NEW)</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>29312</v>
+        <v>8315</v>
       </c>
       <c r="G217" t="n">
-        <v>1273</v>
+        <v>155</v>
       </c>
     </row>
     <row r="218">
@@ -8571,19 +8543,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
+          <t>PIA D_Air Gray_55% UV</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>11975</v>
+        <v>3039</v>
       </c>
       <c r="G218" t="n">
-        <v>270</v>
+        <v>316</v>
       </c>
     </row>
     <row r="219">
@@ -8604,19 +8576,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F219" t="n">
-        <v>15560</v>
+        <v>1200</v>
       </c>
       <c r="G219" t="n">
-        <v>290</v>
+        <v>35</v>
       </c>
     </row>
     <row r="220">
@@ -8637,19 +8609,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>23581</v>
+        <v>3025</v>
       </c>
       <c r="G220" t="n">
-        <v>1044</v>
+        <v>30</v>
       </c>
     </row>
     <row r="221">
@@ -8670,19 +8642,19 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>57411</v>
+        <v>2440</v>
       </c>
       <c r="G221" t="n">
-        <v>2739</v>
+        <v>10</v>
       </c>
     </row>
     <row r="222">
@@ -8703,19 +8675,19 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Astra Estelle Gray</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F222" t="n">
-        <v>2145</v>
+        <v>2950</v>
       </c>
       <c r="G222" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
     </row>
     <row r="223">
@@ -8736,19 +8708,19 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Amber Moon_55%</t>
+          <t>PIA_Sheer Black_55%_1-DAY</t>
         </is>
       </c>
       <c r="F223" t="n">
-        <v>3292</v>
+        <v>1955</v>
       </c>
       <c r="G223" t="n">
-        <v>293</v>
+        <v>25</v>
       </c>
     </row>
     <row r="224">
@@ -8769,19 +8741,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Emerald Moon_55%</t>
+          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F224" t="n">
-        <v>3832</v>
+        <v>15970</v>
       </c>
       <c r="G224" t="n">
-        <v>338</v>
+        <v>480</v>
       </c>
     </row>
     <row r="225">
@@ -8802,19 +8774,19 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Pearl Moon_55%</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>398</v>
+        <v>33154</v>
       </c>
       <c r="G225" t="n">
-        <v>137</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="226">
@@ -8835,19 +8807,19 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Sapphire Moon_55%</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>5940</v>
+        <v>5620</v>
       </c>
       <c r="G226" t="n">
-        <v>175</v>
+        <v>60</v>
       </c>
     </row>
     <row r="227">
@@ -8868,19 +8840,19 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>PIA D_Cat Pearl_55%_14.5 UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>7915</v>
+        <v>50977</v>
       </c>
       <c r="G227" t="n">
-        <v>185</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="228">
@@ -8906,14 +8878,14 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>HAPA(PIA) D_First Love Kristin Brown 14.2_38% UV</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>8280</v>
+        <v>10885</v>
       </c>
       <c r="G228" t="n">
-        <v>205</v>
+        <v>420</v>
       </c>
     </row>
     <row r="229">
@@ -8939,14 +8911,14 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>5245</v>
+        <v>17948</v>
       </c>
       <c r="G229" t="n">
-        <v>110</v>
+        <v>557</v>
       </c>
     </row>
     <row r="230">
@@ -8967,19 +8939,19 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Plus Gray 14.2_55% UV</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>1500</v>
+        <v>22355</v>
       </c>
       <c r="G230" t="n">
-        <v>60</v>
+        <v>535</v>
       </c>
     </row>
     <row r="231">
@@ -9000,19 +8972,19 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>JEWEL MOON D_Emerald Moon_55%</t>
         </is>
       </c>
       <c r="F231" t="n">
-        <v>43283</v>
+        <v>1815</v>
       </c>
       <c r="G231" t="n">
-        <v>987</v>
+        <v>30</v>
       </c>
     </row>
     <row r="232">
@@ -9033,19 +9005,19 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>JEWEL MOON D_Sapphire Moon_55%</t>
         </is>
       </c>
       <c r="F232" t="n">
-        <v>1872</v>
+        <v>775</v>
       </c>
       <c r="G232" t="n">
-        <v>443</v>
+        <v>30</v>
       </c>
     </row>
     <row r="233">
@@ -9066,19 +9038,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>PIA_Sheer Black_55%_1-DAY</t>
+          <t>JEWEL MOON D_Sunstone Moon_55%</t>
         </is>
       </c>
       <c r="F233" t="n">
-        <v>3475</v>
+        <v>1385</v>
       </c>
       <c r="G233" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="234">
@@ -9094,24 +9066,24 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>PIA D_Air Gray_55% UV</t>
         </is>
       </c>
       <c r="F234" t="n">
-        <v>19984</v>
+        <v>2980</v>
       </c>
       <c r="G234" t="n">
-        <v>926</v>
+        <v>155</v>
       </c>
     </row>
     <row r="235">
@@ -9127,24 +9099,24 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F235" t="n">
-        <v>10155</v>
+        <v>8845</v>
       </c>
       <c r="G235" t="n">
-        <v>110</v>
+        <v>210</v>
       </c>
     </row>
     <row r="236">
@@ -9160,24 +9132,24 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>10165</v>
+        <v>7065</v>
       </c>
       <c r="G236" t="n">
-        <v>210</v>
+        <v>100</v>
       </c>
     </row>
     <row r="237">
@@ -9193,24 +9165,24 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>6095</v>
+        <v>3370</v>
       </c>
       <c r="G237" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="238">
@@ -9226,24 +9198,24 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>PIA_Brown Fondue CP-0.75 Toric_UV</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F238" t="n">
-        <v>1510</v>
+        <v>21859</v>
       </c>
       <c r="G238" t="n">
-        <v>35</v>
+        <v>476</v>
       </c>
     </row>
     <row r="239">
@@ -9259,24 +9231,24 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>PIA_Brown Fondue CP-1.25 Toric_UV</t>
+          <t>PIA D_Tiramisu Ring_55% UV</t>
         </is>
       </c>
       <c r="F239" t="n">
-        <v>7840</v>
+        <v>2375</v>
       </c>
       <c r="G239" t="n">
-        <v>185</v>
+        <v>50</v>
       </c>
     </row>
     <row r="240">
@@ -9292,24 +9264,24 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>1-Day_M/F</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Bi-focal D_8.40_55%</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F240" t="n">
-        <v>15345</v>
+        <v>2125</v>
       </c>
       <c r="G240" t="n">
-        <v>450</v>
+        <v>30</v>
       </c>
     </row>
     <row r="241">
@@ -9325,24 +9297,24 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>1-DAY58_Micure</t>
+          <t>PIA_Espresso_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F241" t="n">
-        <v>15933</v>
+        <v>3085</v>
       </c>
       <c r="G241" t="n">
-        <v>1332</v>
+        <v>35</v>
       </c>
     </row>
     <row r="242">
@@ -9358,24 +9330,24 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>PIA_MS6 Sakura Petal_2T</t>
         </is>
       </c>
       <c r="F242" t="n">
-        <v>11220</v>
+        <v>5870</v>
       </c>
       <c r="G242" t="n">
-        <v>375</v>
+        <v>100</v>
       </c>
     </row>
     <row r="243">
@@ -9391,24 +9363,24 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F243" t="n">
-        <v>36045</v>
+        <v>8520</v>
       </c>
       <c r="G243" t="n">
-        <v>1025</v>
+        <v>110</v>
       </c>
     </row>
     <row r="244">
@@ -9424,24 +9396,24 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>1-DAY58_Micure</t>
+          <t>Toric_CP-0.75_Halo Gray</t>
         </is>
       </c>
       <c r="F244" t="n">
-        <v>24114</v>
+        <v>1795</v>
       </c>
       <c r="G244" t="n">
-        <v>1401</v>
+        <v>10</v>
       </c>
     </row>
     <row r="245">
@@ -9457,24 +9429,24 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>1-Day_58_M</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>21730</v>
+        <v>8560</v>
       </c>
       <c r="G245" t="n">
-        <v>550</v>
+        <v>130</v>
       </c>
     </row>
     <row r="246">
@@ -9490,387 +9462,387 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F246" t="n">
-        <v>11315</v>
+        <v>5140</v>
       </c>
       <c r="G246" t="n">
-        <v>465</v>
+        <v>95</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>B형 조립중합8호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Clalen D_Canola Brown</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F247" t="n">
-        <v>7502</v>
+        <v>13765</v>
       </c>
       <c r="G247" t="n">
-        <v>1562</v>
+        <v>115</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>B형 조립중합8호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Clalen D_Pink Tulip Brown</t>
+          <t>Hapa D Toric_Glazed choco_CP-1.75</t>
         </is>
       </c>
       <c r="F248" t="n">
-        <v>12109</v>
+        <v>1175</v>
       </c>
       <c r="G248" t="n">
-        <v>827</v>
+        <v>25</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>17843</v>
+        <v>2390</v>
       </c>
       <c r="G249" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Sincere D_Clear_38%</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>23298</v>
+        <v>1600</v>
       </c>
       <c r="G250" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_M/F</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>B형 조립중합5호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Bi-focal D_8.40_55%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>16336</v>
+        <v>870</v>
       </c>
       <c r="G251" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>B형 조립중합6호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Brown EX</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>23540</v>
+        <v>18720</v>
       </c>
       <c r="G252" t="n">
-        <v>4532</v>
+        <v>465</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>1-DAY_58(PDI)</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>22390</v>
+        <v>3617</v>
       </c>
       <c r="G253" t="n">
-        <v>0</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>21742</v>
+        <v>4860</v>
       </c>
       <c r="G254" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>CAM분리2호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Clalen D_Canola Brown</t>
+          <t>Metha_Daily</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3777</v>
+        <v>11760</v>
       </c>
       <c r="G255" t="n">
-        <v>570</v>
+        <v>620</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>CAM분리2호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Clalen D_Pink Tulip Brown</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>6479</v>
+        <v>59395</v>
       </c>
       <c r="G256" t="n">
-        <v>856</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>CAM분리3호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Clalen D_Canola Brown</t>
+          <t>1-Day_58(NEW)</t>
         </is>
       </c>
       <c r="F257" t="n">
-        <v>790</v>
+        <v>1898</v>
       </c>
       <c r="G257" t="n">
-        <v>213</v>
+        <v>432</v>
       </c>
     </row>
     <row r="258">
@@ -9881,29 +9853,29 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>CAM분리3호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Clalen D_Pink Tulip Brown</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F258" t="n">
-        <v>1427</v>
+        <v>33273</v>
       </c>
       <c r="G258" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -9914,29 +9886,29 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>CAM분리3호기</t>
+          <t>B형 조립중합4호기</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F259" t="n">
-        <v>2124</v>
+        <v>5399</v>
       </c>
       <c r="G259" t="n">
-        <v>107</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="260">
@@ -9947,29 +9919,29 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>CAM분리4호기</t>
+          <t>B형 조립중합5호기</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Sincere D_Clear_38%</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F260" t="n">
-        <v>15506</v>
+        <v>31591</v>
       </c>
       <c r="G260" t="n">
-        <v>3866</v>
+        <v>833</v>
       </c>
     </row>
     <row r="261">
@@ -9980,29 +9952,29 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F261" t="n">
-        <v>7012</v>
+        <v>17225</v>
       </c>
       <c r="G261" t="n">
-        <v>2806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -10013,29 +9985,29 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F262" t="n">
-        <v>621</v>
+        <v>58497</v>
       </c>
       <c r="G262" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -10046,29 +10018,29 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F263" t="n">
-        <v>10445</v>
+        <v>42853</v>
       </c>
       <c r="G263" t="n">
-        <v>1630</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -10084,24 +10056,24 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>B형 분리수화접착6호기</t>
+          <t>CAM분리1호기</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Sincere D_Clear_38%</t>
         </is>
       </c>
       <c r="F264" t="n">
-        <v>569</v>
+        <v>1508</v>
       </c>
       <c r="G264" t="n">
-        <v>264</v>
+        <v>674</v>
       </c>
     </row>
     <row r="265">
@@ -10117,24 +10089,24 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>B형 분리수화접착6호기</t>
+          <t>CAM분리3호기</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F265" t="n">
-        <v>16491</v>
+        <v>9229</v>
       </c>
       <c r="G265" t="n">
-        <v>2121</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="266">
@@ -10150,24 +10122,24 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>CAM분리4호기</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Sincere D_Clear_38%</t>
         </is>
       </c>
       <c r="F266" t="n">
-        <v>5022</v>
+        <v>19098</v>
       </c>
       <c r="G266" t="n">
-        <v>1775</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="267">
@@ -10188,19 +10160,19 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F267" t="n">
-        <v>1524</v>
+        <v>1570</v>
       </c>
       <c r="G267" t="n">
-        <v>147</v>
+        <v>239</v>
       </c>
     </row>
     <row r="268">
@@ -10221,19 +10193,19 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Brown EX</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>4909</v>
+        <v>962</v>
       </c>
       <c r="G268" t="n">
-        <v>962</v>
+        <v>167</v>
       </c>
     </row>
     <row r="269">
@@ -10254,19 +10226,19 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Gray EX</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>19997</v>
+        <v>17868</v>
       </c>
       <c r="G269" t="n">
-        <v>2355</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="270">
@@ -10282,24 +10254,24 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착6호기</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>24388</v>
+        <v>959</v>
       </c>
       <c r="G270" t="n">
-        <v>1590</v>
+        <v>83</v>
       </c>
     </row>
     <row r="271">
@@ -10315,24 +10287,24 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>B형 분리수화접착6호기</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>29608</v>
+        <v>17742</v>
       </c>
       <c r="G271" t="n">
-        <v>1492</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="272">
@@ -10348,24 +10320,24 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>10209</v>
+        <v>743</v>
       </c>
       <c r="G272" t="n">
-        <v>1990</v>
+        <v>187</v>
       </c>
     </row>
     <row r="273">
@@ -10381,24 +10353,24 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F273" t="n">
-        <v>13443</v>
+        <v>9526</v>
       </c>
       <c r="G273" t="n">
-        <v>1303</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="274">
@@ -10409,29 +10381,29 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Clalen oneday A(O2 Edition)</t>
+          <t>O2O2 D_Ash Gray EX</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>5305</v>
+        <v>1633</v>
       </c>
       <c r="G274" t="n">
-        <v>251</v>
+        <v>281</v>
       </c>
     </row>
     <row r="275">
@@ -10442,29 +10414,29 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>sincere Natural 1day</t>
+          <t>O2O2 D_Ash Gray EX</t>
         </is>
       </c>
       <c r="F275" t="n">
-        <v>24425</v>
+        <v>21888</v>
       </c>
       <c r="G275" t="n">
-        <v>807</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="276">
@@ -10475,29 +10447,29 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착3호기</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>19170</v>
+        <v>2102</v>
       </c>
       <c r="G276" t="n">
-        <v>405</v>
+        <v>70</v>
       </c>
     </row>
     <row r="277">
@@ -10508,12 +10480,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -10523,14 +10495,14 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F277" t="n">
-        <v>5770</v>
+        <v>36906</v>
       </c>
       <c r="G277" t="n">
-        <v>124</v>
+        <v>3164</v>
       </c>
     </row>
     <row r="278">
@@ -10541,29 +10513,29 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>19796</v>
+        <v>29270</v>
       </c>
       <c r="G278" t="n">
-        <v>1343</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="279">
@@ -10574,29 +10546,29 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>B형 분리수화접착3호기</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 Spherical(DK70)_K2-SMD</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>13465</v>
+        <v>4791</v>
       </c>
       <c r="G279" t="n">
-        <v>339</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="280">
@@ -10607,29 +10579,29 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>B형 분리수화접착3호기</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>5800</v>
+        <v>12550</v>
       </c>
       <c r="G280" t="n">
-        <v>96</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="281">
@@ -10640,29 +10612,29 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>B형 분리수화접착4호기</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>4485</v>
+        <v>7036</v>
       </c>
       <c r="G281" t="n">
-        <v>224</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="282">
@@ -10673,29 +10645,29 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Toric</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>B형 분리수화접착4호기</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 D_UV_Toric_SMD</t>
         </is>
       </c>
       <c r="F282" t="n">
-        <v>1815</v>
+        <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -10711,24 +10683,24 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Clalen D_Canola Brown</t>
         </is>
       </c>
       <c r="F283" t="n">
-        <v>1555</v>
+        <v>712</v>
       </c>
       <c r="G283" t="n">
-        <v>22</v>
+        <v>253</v>
       </c>
     </row>
     <row r="284">
@@ -10744,24 +10716,24 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+          <t>Clalen D_Mimosa Brown</t>
         </is>
       </c>
       <c r="F284" t="n">
-        <v>38875</v>
+        <v>3970</v>
       </c>
       <c r="G284" t="n">
-        <v>872</v>
+        <v>90</v>
       </c>
     </row>
     <row r="285">
@@ -10777,24 +10749,24 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+          <t>Clalen D_Pink Tulip Brown</t>
         </is>
       </c>
       <c r="F285" t="n">
-        <v>37161</v>
+        <v>1105</v>
       </c>
       <c r="G285" t="n">
-        <v>3626</v>
+        <v>395</v>
       </c>
     </row>
     <row r="286">
@@ -10810,24 +10782,552 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
+          <t>1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>A형 인라인6호기</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Clalen D_Canola Brown</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>9592</v>
+      </c>
+      <c r="G286" t="n">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>A형 인라인6호기</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Clalen D_Mimosa Brown</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>5301</v>
+      </c>
+      <c r="G287" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>A형 인라인5호기</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>sincere Natural 1day</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>19225</v>
+      </c>
+      <c r="G288" t="n">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>16670</v>
+      </c>
+      <c r="G289" t="n">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>1165</v>
+      </c>
+      <c r="G290" t="n">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>13924</v>
+      </c>
+      <c r="G291" t="n">
+        <v>3317</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>O2O2 D_Ash Brown EX</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>1490</v>
+      </c>
+      <c r="G292" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>O2O2 D_Ash Gray EX</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>5795</v>
+      </c>
+      <c r="G293" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Toric</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>A형 인라인6호기</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>O2O2 D Toric_Sepia Choco EX</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>7</v>
+      </c>
+      <c r="G294" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Si_1-Day_M/F</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>A형 인라인2호기</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>O2O2_Multifocal_K2_SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>1835</v>
+      </c>
+      <c r="G295" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Si_1-Day_M/F</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>A형 인라인3호기</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>O2O2_Multifocal_K2_SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>3790</v>
+      </c>
+      <c r="G296" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Si_1-Day_M/F</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>A형 인라인5호기</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>O2O2_Multifocal_K2_SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>2010</v>
+      </c>
+      <c r="G297" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
           <t>Si_1-Day_Sph</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr">
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>A형 인라인2호기</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>31475</v>
+      </c>
+      <c r="G298" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>A형 인라인3호기</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>44120</v>
+      </c>
+      <c r="G299" t="n">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
         <is>
           <t>A형 인라인4호기</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr">
+      <c r="E300" t="inlineStr">
         <is>
           <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
-      <c r="F286" t="n">
-        <v>19525</v>
-      </c>
-      <c r="G286" t="n">
-        <v>285</v>
+      <c r="F300" t="n">
+        <v>38070</v>
+      </c>
+      <c r="G300" t="n">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>A형 인라인5호기</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>15323</v>
+      </c>
+      <c r="G301" t="n">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>A형 인라인6호기</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>11975</v>
+      </c>
+      <c r="G302" t="n">
+        <v>271</v>
       </c>
     </row>
   </sheetData>

--- a/생산실적현황(설비운영현황).xlsx
+++ b/생산실적현황(설비운영현황).xlsx
@@ -426,13 +426,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.2</t>
+          <t>Metha_55</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>T38_(UV포함)</t>
         </is>
       </c>
     </row>
@@ -565,11 +565,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Toric</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -577,7 +577,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>O2O2 Spherical(DK70)_K2-SMD</t>
+          <t>O2O2 D_UV_Toric_SMD</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.4</t>
+          <t>(NEW)S43-HD-Dry-14.2</t>
         </is>
       </c>
     </row>
@@ -645,23 +645,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>(NEW)MG M_No.1 Hazel_GLAM_(중)</t>
+          <t>T55_소사각</t>
         </is>
       </c>
     </row>
@@ -673,23 +673,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>Silicone relax</t>
         </is>
       </c>
     </row>
@@ -709,15 +709,15 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>(NEW)MG M_No.1 Hazel_GLAM_(중)</t>
         </is>
       </c>
     </row>
@@ -737,15 +737,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Silicone relax_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -773,35 +773,35 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>T38_금캡(UV포함)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
     </row>
@@ -817,19 +817,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
     </row>
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dazzle Gray_2T_(PBT)PIA_M(Y)</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -953,23 +953,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
         </is>
       </c>
     </row>
@@ -989,35 +989,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
     </row>
@@ -1045,15 +1045,15 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
     </row>
@@ -1073,15 +1073,15 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
     </row>
@@ -1093,23 +1093,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1129,15 +1129,15 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
     </row>
@@ -1157,15 +1157,15 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
     </row>
@@ -1177,23 +1177,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C27" t="n">
+        <v>11</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
         <v>6</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Cherry Moon</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>sincere Natural 1day</t>
+          <t>Clalen oneday A(O2 Edition)</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1269,41 +1269,13 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Toric</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" t="inlineStr">
-        <is>
-          <t>O2O2 D Toric_Sepia Choco EX</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>6</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="inlineStr">
         <is>
           <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
@@ -1320,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G293"/>
+  <dimension ref="A1:G301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1387,19 +1359,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>조립1호기</t>
+          <t>조립30호기</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1-Day_Metha</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>31404</v>
+        <v>32547</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="3">
@@ -1420,7 +1392,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>조립30호기</t>
+          <t>조립31호기</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1429,10 +1401,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>43471</v>
+        <v>49760</v>
       </c>
       <c r="G3" t="n">
-        <v>939</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1453,7 +1425,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>조립31호기</t>
+          <t>조립32호기</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1462,10 +1434,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>90730</v>
+        <v>51166</v>
       </c>
       <c r="G4" t="n">
-        <v>857</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="5">
@@ -1481,24 +1453,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>조립32호기</t>
+          <t>조립1호기</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Metha_55</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>76365</v>
+        <v>20654</v>
       </c>
       <c r="G5" t="n">
-        <v>1570</v>
+        <v>624</v>
       </c>
     </row>
     <row r="6">
@@ -1519,19 +1491,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>조립3호기</t>
+          <t>조립8호기</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S55_8.60</t>
+          <t>S55-Dry</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>11282</v>
+        <v>20606</v>
       </c>
       <c r="G6" t="n">
-        <v>449</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1547,24 +1519,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>조립3호기</t>
+          <t>조립2호기</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S55_8.80</t>
+          <t>T38_(UV포함)</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>15973</v>
+        <v>2796</v>
       </c>
       <c r="G7" t="n">
-        <v>471</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="8">
@@ -1580,24 +1552,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>Si_1-Day_Toric</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>조립8호기</t>
+          <t>조립7호기</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.2</t>
+          <t>O2O2 D_UV_Toric_SMD</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>40376</v>
+        <v>4789</v>
       </c>
       <c r="G8" t="n">
-        <v>2043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1608,29 +1580,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>조립2호기</t>
+          <t>분리14호기</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>1-Day_Metha</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6557</v>
+        <v>13167</v>
       </c>
       <c r="G9" t="n">
-        <v>1014</v>
+        <v>7249</v>
       </c>
     </row>
     <row r="10">
@@ -1641,29 +1613,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>조립4호기</t>
+          <t>분리5호기</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>O2O2 Spherical(DK70)_K2-SMD</t>
+          <t>1-Day_Metha</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>35932</v>
+        <v>980</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>606</v>
       </c>
     </row>
     <row r="11">
@@ -1679,24 +1651,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>분리14호기</t>
+          <t>분리10호기</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1-Day_Metha</t>
+          <t>(NEW)S38-Dry-14.2</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>24707</v>
+        <v>2179</v>
       </c>
       <c r="G11" t="n">
-        <v>5403</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -1722,14 +1694,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(NEW)S38-Dry-14.2</t>
+          <t>(NEW)S43-HD-Dry-14.2</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>11404</v>
+        <v>7266</v>
       </c>
       <c r="G12" t="n">
-        <v>725</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="13">
@@ -1755,14 +1727,14 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.4</t>
+          <t>(NEW)S38-Dry-14.2</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>13777</v>
+        <v>6069</v>
       </c>
       <c r="G13" t="n">
-        <v>1820</v>
+        <v>748</v>
       </c>
     </row>
     <row r="14">
@@ -1783,19 +1755,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>분리4호기</t>
+          <t>분리11호기</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(NEW)S38-HD-Dry-14.0</t>
+          <t>(NEW)S43-HD-Dry-14.2</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>8608</v>
+        <v>4470</v>
       </c>
       <c r="G14" t="n">
-        <v>2162</v>
+        <v>836</v>
       </c>
     </row>
     <row r="15">
@@ -1806,29 +1778,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>분리11호기</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NewFusion_소사각</t>
+          <t>(NEW)S43-HD-Dry-14.4</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>108</v>
+        <v>1800</v>
       </c>
       <c r="G15" t="n">
-        <v>92</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16">
@@ -1839,29 +1811,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>분리14호기</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NewFusion_소사각</t>
+          <t>Metha</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>272</v>
+        <v>2166</v>
       </c>
       <c r="G16" t="n">
-        <v>217</v>
+        <v>513</v>
       </c>
     </row>
     <row r="17">
@@ -1872,29 +1844,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>검사15호기</t>
+          <t>분리4호기</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(NEW)MG M_No.1 Hazel_GLAM_(중)</t>
+          <t>(NEW)S38-HD-Dry-14.0</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3592</v>
+        <v>1050</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>650</v>
       </c>
     </row>
     <row r="18">
@@ -1905,29 +1877,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>분리4호기</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bella Diamond_14.5_중사각</t>
+          <t>(NEW)S43-HD-Dry-14.4</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>188</v>
+        <v>1494</v>
       </c>
       <c r="G18" t="n">
-        <v>9</v>
+        <v>906</v>
       </c>
     </row>
     <row r="19">
@@ -1938,29 +1910,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>분리3호기</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bella Glow_중사각</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>862</v>
+        <v>3671</v>
       </c>
       <c r="G19" t="n">
-        <v>35</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="20">
@@ -1971,29 +1943,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>분리42호기(초음파)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bella-Contour_중사각</t>
+          <t>Silicone relax</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>34</v>
+        <v>15838</v>
       </c>
       <c r="G20" t="n">
-        <v>61</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="21">
@@ -2014,19 +1986,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>검사15호기</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bella-Elite_14.5_중사각</t>
+          <t>(NEW)MG M_No.1 Hazel_GLAM_(중)</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1796</v>
+        <v>9223</v>
       </c>
       <c r="G21" t="n">
-        <v>139</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22">
@@ -2052,14 +2024,14 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Clalen 1M_Planet_Gray Moon</t>
+          <t>Affogato_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>316</v>
+        <v>442</v>
       </c>
       <c r="G22" t="n">
-        <v>179</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -2085,14 +2057,14 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Clalen 1M_Planet_Mercury Blue</t>
+          <t>Lady Black_PIA_M_(중)_14.5</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>420</v>
+        <v>282</v>
       </c>
       <c r="G23" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -2118,14 +2090,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NewFusion_중사각</t>
+          <t>Oolong Tea_PIA_M_중사각(Y)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>558</v>
+        <v>916</v>
       </c>
       <c r="G24" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25">
@@ -2146,19 +2118,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Affogato_PIA_M_(중)(Y)</t>
+          <t>Princess Chocolat_PIA_M_(중)_14.5</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1924</v>
+        <v>982</v>
       </c>
       <c r="G25" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -2179,19 +2151,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
+          <t>Sakura Smore_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>950</v>
+        <v>603</v>
       </c>
       <c r="G26" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -2217,14 +2189,14 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oolong Tea_PIA_M_중사각(Y)</t>
+          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1518</v>
+        <v>3192</v>
       </c>
       <c r="G27" t="n">
-        <v>33</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28">
@@ -2245,19 +2217,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brulee Pearl_PIA_M_(중)(Y)</t>
+          <t>Cream Rose_PIA_M_(중)</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1472</v>
+        <v>2864</v>
       </c>
       <c r="G28" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29">
@@ -2278,19 +2250,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oolong Tea_PIA_M_중사각(Y)</t>
+          <t>Clalen Iris_GRA_2902_원형</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1134</v>
+        <v>386</v>
       </c>
       <c r="G29" t="n">
-        <v>66</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30">
@@ -2311,19 +2283,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tarte Tatin_PIA_M_(중)(Y)</t>
+          <t>NewFusion_원형</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1554</v>
+        <v>1574</v>
       </c>
       <c r="G30" t="n">
-        <v>77</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="31">
@@ -2344,19 +2316,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Advance_CB_원형</t>
+          <t>Affogato_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>186</v>
+        <v>1526</v>
       </c>
       <c r="G31" t="n">
-        <v>832</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32">
@@ -2377,19 +2349,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bella-SnowWhite_14.5_원형</t>
+          <t>Bella Diamond_14.5_중사각</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>174</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2410,19 +2382,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>NewFusion_원형</t>
+          <t>Clalen 1M_Planet_Gray Moon</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1550</v>
+        <v>49</v>
       </c>
       <c r="G33" t="n">
-        <v>407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2438,24 +2410,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1940</v>
+        <v>822</v>
       </c>
       <c r="G34" t="n">
-        <v>27</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35">
@@ -2471,24 +2443,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>Dazzle Gray_2T_(PBT)PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1310</v>
+        <v>606</v>
       </c>
       <c r="G35" t="n">
-        <v>87</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36">
@@ -2504,24 +2476,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>Twinkle Brown_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4464</v>
+        <v>1624</v>
       </c>
       <c r="G36" t="n">
-        <v>318</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37">
@@ -2537,24 +2509,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>NewFusion_소사각</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4284</v>
+        <v>108</v>
       </c>
       <c r="G37" t="n">
-        <v>492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2570,24 +2542,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>Baby Espresso_PIA_M_중사각(Y)</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1054</v>
+        <v>1018</v>
       </c>
       <c r="G38" t="n">
-        <v>163</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39">
@@ -2603,24 +2575,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(UV)CS30_원형_8.60</t>
+          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>248</v>
+        <v>1208</v>
       </c>
       <c r="G39" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40">
@@ -2636,24 +2608,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CS30_원형_8.60</t>
+          <t>Date Topaz_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>7488</v>
+        <v>784</v>
       </c>
       <c r="G40" t="n">
-        <v>196</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -2669,24 +2641,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Metha_55_원형</t>
+          <t>Garnet_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1746</v>
+        <v>934</v>
       </c>
       <c r="G41" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42">
@@ -2702,24 +2674,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>Oolong Tea_PIA_M_중사각(Y)</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1948</v>
+        <v>1088</v>
       </c>
       <c r="G42" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43">
@@ -2735,24 +2707,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사7호기</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>Brulee Pearl_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1428</v>
+        <v>1234</v>
       </c>
       <c r="G43" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44">
@@ -2768,24 +2740,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>검사23호기</t>
+          <t>검사7호기</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Metha_55_원형</t>
+          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1652</v>
+        <v>2036</v>
       </c>
       <c r="G44" t="n">
-        <v>174</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
@@ -2801,24 +2773,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사7호기</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Metha_55_중사각</t>
+          <t>Mirror Gray_3T_(PBT)PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>912</v>
+        <v>1048</v>
       </c>
       <c r="G45" t="n">
-        <v>202</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46">
@@ -2834,24 +2806,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사7호기</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Metha_55_원형</t>
+          <t>Oolong Tea_PIA_M_중사각(Y)</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>5308</v>
+        <v>1018</v>
       </c>
       <c r="G46" t="n">
-        <v>160</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47">
@@ -2867,24 +2839,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>검사9호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Metha_55_원형</t>
+          <t>NewFusion_원형</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1160</v>
+        <v>994</v>
       </c>
       <c r="G47" t="n">
-        <v>35</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="48">
@@ -2900,7 +2872,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2910,14 +2882,14 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>292</v>
+        <v>1490</v>
       </c>
       <c r="G48" t="n">
-        <v>51</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49">
@@ -2933,24 +2905,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>US55-2(M)_소사각</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>64</v>
+        <v>3540</v>
       </c>
       <c r="G49" t="n">
-        <v>109</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50">
@@ -2966,24 +2938,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1170</v>
+        <v>4090</v>
       </c>
       <c r="G50" t="n">
-        <v>228</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51">
@@ -2999,24 +2971,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>516</v>
+        <v>2482</v>
       </c>
       <c r="G51" t="n">
-        <v>93</v>
+        <v>188</v>
       </c>
     </row>
     <row r="52">
@@ -3032,7 +3004,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3042,14 +3014,14 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Silicone relax_소사각</t>
+          <t>US55-2(M)_소사각</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3102</v>
+        <v>3781</v>
       </c>
       <c r="G52" t="n">
-        <v>479</v>
+        <v>132</v>
       </c>
     </row>
     <row r="53">
@@ -3065,24 +3037,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Silicone relax_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3210</v>
+        <v>3236</v>
       </c>
       <c r="G53" t="n">
-        <v>402</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54">
@@ -3098,24 +3070,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Silicone relax_소사각</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3950</v>
+        <v>3370</v>
       </c>
       <c r="G54" t="n">
-        <v>120</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55">
@@ -3131,24 +3103,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2750</v>
+        <v>3860</v>
       </c>
       <c r="G55" t="n">
-        <v>81</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56">
@@ -3164,7 +3136,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3174,344 +3146,344 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>4097</v>
+        <v>5650</v>
       </c>
       <c r="G56" t="n">
-        <v>319</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>조립10호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>27381</v>
+        <v>1828</v>
       </c>
       <c r="G57" t="n">
-        <v>1418</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>조립10호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>US55-2(M)_소사각</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>15231</v>
+        <v>1766</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>조립11호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>Metha_55_원형</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>30883</v>
+        <v>4884</v>
       </c>
       <c r="G59" t="n">
-        <v>1700</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>조립12호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>42371</v>
+        <v>4598</v>
       </c>
       <c r="G60" t="n">
-        <v>50</v>
+        <v>171</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>조립13호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>42302</v>
+        <v>1908</v>
       </c>
       <c r="G61" t="n">
-        <v>3452</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>조립14호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>US55-2(M)_소사각</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>53381</v>
+        <v>2260</v>
       </c>
       <c r="G62" t="n">
-        <v>3940</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>조립15호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PIA_1D 55% YakisobaPan_1T</t>
+          <t>Metha_55_원형</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>28114</v>
+        <v>2728</v>
       </c>
       <c r="G63" t="n">
-        <v>400</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>조립16호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>20591</v>
+        <v>20</v>
       </c>
       <c r="G64" t="n">
-        <v>1373</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>조립16호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lighly Rose Cacao(렌즈타운)</t>
+          <t>T38_금캡(UV포함)</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>9699</v>
+        <v>5122</v>
       </c>
       <c r="G65" t="n">
-        <v>1706</v>
+        <v>997</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>조립19호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>40346</v>
+        <v>5984</v>
       </c>
       <c r="G66" t="n">
-        <v>42</v>
+        <v>139</v>
       </c>
     </row>
     <row r="67">
@@ -3532,19 +3504,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>조립23호기</t>
+          <t>조립10호기</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>T-Garden D_Melty Time_55% UV 14.2</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>43273</v>
+        <v>27287</v>
       </c>
       <c r="G67" t="n">
-        <v>2285</v>
+        <v>500</v>
       </c>
     </row>
     <row r="68">
@@ -3565,19 +3537,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>조립24호기</t>
+          <t>조립11호기</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>20718</v>
+        <v>19282</v>
       </c>
       <c r="G68" t="n">
-        <v>1350</v>
+        <v>550</v>
       </c>
     </row>
     <row r="69">
@@ -3598,19 +3570,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>조립25호기</t>
+          <t>조립12호기</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>48436</v>
+        <v>26314</v>
       </c>
       <c r="G69" t="n">
-        <v>2437</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="70">
@@ -3631,19 +3603,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>조립26호기</t>
+          <t>조립13호기</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>30200</v>
+        <v>13785</v>
       </c>
       <c r="G70" t="n">
-        <v>3440</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -3664,19 +3636,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>조립27호기</t>
+          <t>조립15호기</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ALICIA BROWN(근시)</t>
+          <t>PIA_1D 55% YakisobaPan_1T</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>38124</v>
+        <v>13474</v>
       </c>
       <c r="G71" t="n">
-        <v>5110</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="72">
@@ -3697,19 +3669,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>조립40호기</t>
+          <t>조립16호기</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>22076</v>
+        <v>22776</v>
       </c>
       <c r="G72" t="n">
-        <v>1353</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="73">
@@ -3730,19 +3702,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>조립42호기</t>
+          <t>조립19호기</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>37639</v>
+        <v>22725</v>
       </c>
       <c r="G73" t="n">
-        <v>782</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="74">
@@ -3763,19 +3735,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>조립44호기</t>
+          <t>조립23호기</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ANW D_Art Gray_Dopewink 38%</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>9024</v>
+        <v>18221</v>
       </c>
       <c r="G74" t="n">
-        <v>5410</v>
+        <v>751</v>
       </c>
     </row>
     <row r="75">
@@ -3796,19 +3768,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>조립44호기</t>
+          <t>조립24호기</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ANW D_Spicy Gray_Dopewink 38%</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>24468</v>
+        <v>10176</v>
       </c>
       <c r="G75" t="n">
-        <v>2213</v>
+        <v>9226</v>
       </c>
     </row>
     <row r="76">
@@ -3829,19 +3801,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>조립47호기</t>
+          <t>조립25호기</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>30236</v>
+        <v>23396</v>
       </c>
       <c r="G76" t="n">
-        <v>7071</v>
+        <v>650</v>
       </c>
     </row>
     <row r="77">
@@ -3862,19 +3834,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>조립48호기</t>
+          <t>조립40호기</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>14163</v>
+        <v>14743</v>
       </c>
       <c r="G77" t="n">
-        <v>2261</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="78">
@@ -3895,19 +3867,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>조립48호기</t>
+          <t>조립42호기</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>23619</v>
+        <v>28031</v>
       </c>
       <c r="G78" t="n">
-        <v>4340</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="79">
@@ -3928,19 +3900,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>조립49호기</t>
+          <t>조립46호기</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Alcon D_Allure Grey_W3C</t>
+          <t>Alcon D_Jewel Gold_W3</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>37105</v>
+        <v>15205</v>
       </c>
       <c r="G79" t="n">
-        <v>4841</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="80">
@@ -3961,19 +3933,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>조립50호기</t>
+          <t>조립47호기</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>37645</v>
+        <v>3610</v>
       </c>
       <c r="G80" t="n">
-        <v>2300</v>
+        <v>3209</v>
       </c>
     </row>
     <row r="81">
@@ -3994,19 +3966,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>조립51호기</t>
+          <t>조립48호기</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PIA D_Cream Beige_14.4</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>14583</v>
+        <v>18206</v>
       </c>
       <c r="G81" t="n">
-        <v>12060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -4027,19 +3999,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>조립52호기</t>
+          <t>조립49호기</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>Alcon D_Allure Grey_W3C</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>56211</v>
+        <v>23274</v>
       </c>
       <c r="G82" t="n">
-        <v>1764</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="83">
@@ -4060,19 +4032,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>조립53호기</t>
+          <t>조립50호기</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PIA D_Baby Espresso_38% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>37370</v>
+        <v>22868</v>
       </c>
       <c r="G83" t="n">
-        <v>3983</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="84">
@@ -4093,19 +4065,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>조립54호기</t>
+          <t>조립51호기</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Cream Beige_14.4</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>39890</v>
+        <v>24255</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>3650</v>
       </c>
     </row>
     <row r="85">
@@ -4126,19 +4098,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>조립56호기</t>
+          <t>조립53호기</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>PIA D_Baby Espresso_38% UV</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>39731</v>
+        <v>16288</v>
       </c>
       <c r="G85" t="n">
-        <v>5910</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="86">
@@ -4159,19 +4131,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>조립57호기</t>
+          <t>조립54호기</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>23331</v>
+        <v>28284</v>
       </c>
       <c r="G86" t="n">
-        <v>3450</v>
+        <v>600</v>
       </c>
     </row>
     <row r="87">
@@ -4192,19 +4164,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>조립58호기</t>
+          <t>조립55호기</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PIA D_Pearl Cats Eye_38% UV</t>
+          <t>PIA D_Strawberry Quartz_38% UV</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>24905</v>
+        <v>9763</v>
       </c>
       <c r="G87" t="n">
-        <v>1118</v>
+        <v>10429</v>
       </c>
     </row>
     <row r="88">
@@ -4225,19 +4197,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>조립59호기</t>
+          <t>조립56호기</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>26069</v>
+        <v>9791</v>
       </c>
       <c r="G88" t="n">
-        <v>11455</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="89">
@@ -4253,24 +4225,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립57호기</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>10430</v>
+        <v>22688</v>
       </c>
       <c r="G89" t="n">
-        <v>756</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="90">
@@ -4291,19 +4263,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>Toric_CP-1.25_Halo Brown</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>13073</v>
+        <v>5978</v>
       </c>
       <c r="G90" t="n">
-        <v>660</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -4324,19 +4296,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>23424</v>
+        <v>16547</v>
       </c>
       <c r="G91" t="n">
-        <v>1421</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="92">
@@ -4347,29 +4319,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Brown</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3182</v>
+        <v>24434</v>
       </c>
       <c r="G92" t="n">
-        <v>5</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="93">
@@ -4380,29 +4352,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>31188</v>
+        <v>20241</v>
       </c>
       <c r="G93" t="n">
-        <v>1749</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="94">
@@ -4413,29 +4385,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>Alcon D_Allure Grey_W3C</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>16853</v>
+        <v>6381</v>
       </c>
       <c r="G94" t="n">
-        <v>128</v>
+        <v>919</v>
       </c>
     </row>
     <row r="95">
@@ -4446,29 +4418,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>조립45호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
+          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>11592</v>
+        <v>34918</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="96">
@@ -4479,29 +4451,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>조립46호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dazzle Gray_2T_(PBT)PIA_M(Y)</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>19977</v>
+        <v>16677</v>
       </c>
       <c r="G96" t="n">
-        <v>1902</v>
+        <v>4041</v>
       </c>
     </row>
     <row r="97">
@@ -4512,29 +4484,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>조립55호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Dollish Gray_PIA_M(Y)</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>7579</v>
+        <v>15149</v>
       </c>
       <c r="G97" t="n">
-        <v>5710</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="98">
@@ -4555,19 +4527,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>20327</v>
+        <v>19991</v>
       </c>
       <c r="G98" t="n">
-        <v>2367</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="99">
@@ -4588,19 +4560,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>T-Garden D_Melty Time_55% UV 14.2</t>
+          <t>PIA_1D 55% YakisobaPan_1T</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2882</v>
+        <v>14925</v>
       </c>
       <c r="G99" t="n">
-        <v>775</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="100">
@@ -4621,19 +4593,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>6450</v>
+        <v>20462</v>
       </c>
       <c r="G100" t="n">
-        <v>682</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="101">
@@ -4654,19 +4626,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>16264</v>
+        <v>13485</v>
       </c>
       <c r="G101" t="n">
-        <v>2198</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="102">
@@ -4687,19 +4659,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>Alcon D_Allure Grey_W3C</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>22761</v>
+        <v>9246</v>
       </c>
       <c r="G102" t="n">
-        <v>3510</v>
+        <v>938</v>
       </c>
     </row>
     <row r="103">
@@ -4720,19 +4692,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>분리19호기</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>22399</v>
+        <v>9421</v>
       </c>
       <c r="G103" t="n">
-        <v>3420</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="104">
@@ -4753,19 +4725,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>분리19호기</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PIA_1D 55% YakisobaPan_1T</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>14704</v>
+        <v>22820</v>
       </c>
       <c r="G104" t="n">
-        <v>2069</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="105">
@@ -4786,7 +4758,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4795,10 +4767,10 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>8832</v>
+        <v>34677</v>
       </c>
       <c r="G105" t="n">
-        <v>1413</v>
+        <v>3722</v>
       </c>
     </row>
     <row r="106">
@@ -4819,19 +4791,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>ALICIA BROWN(근시)</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>27169</v>
+        <v>2699</v>
       </c>
       <c r="G106" t="n">
-        <v>3289</v>
+        <v>318</v>
       </c>
     </row>
     <row r="107">
@@ -4852,19 +4824,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>분리19호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>36563</v>
+        <v>22836</v>
       </c>
       <c r="G107" t="n">
-        <v>5569</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="108">
@@ -4885,19 +4857,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ALICIA BROWN(근시)</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>13645</v>
+        <v>15604</v>
       </c>
       <c r="G108" t="n">
-        <v>3695</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="109">
@@ -4918,19 +4890,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>15331</v>
+        <v>37363</v>
       </c>
       <c r="G109" t="n">
-        <v>2031</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="110">
@@ -4951,19 +4923,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>ALICIA BROWN(근시)</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1670</v>
+        <v>6052</v>
       </c>
       <c r="G110" t="n">
-        <v>162</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="111">
@@ -4984,19 +4956,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>11990</v>
+        <v>23912</v>
       </c>
       <c r="G111" t="n">
-        <v>1098</v>
+        <v>6528</v>
       </c>
     </row>
     <row r="112">
@@ -5017,19 +4989,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>Lighly Rose Cacao(렌즈타운)</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2502</v>
+        <v>3962</v>
       </c>
       <c r="G112" t="n">
-        <v>401</v>
+        <v>566</v>
       </c>
     </row>
     <row r="113">
@@ -5050,7 +5022,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5059,10 +5031,10 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>25323</v>
+        <v>12227</v>
       </c>
       <c r="G113" t="n">
-        <v>2456</v>
+        <v>928</v>
       </c>
     </row>
     <row r="114">
@@ -5083,19 +5055,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA_TAMA KONNYAKU_55%</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>22435</v>
+        <v>22690</v>
       </c>
       <c r="G114" t="n">
-        <v>2752</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="115">
@@ -5116,19 +5088,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ALICIA BROWN(근시)</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1970</v>
+        <v>14071</v>
       </c>
       <c r="G115" t="n">
-        <v>64</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="116">
@@ -5149,19 +5121,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>14955</v>
+        <v>18875</v>
       </c>
       <c r="G116" t="n">
-        <v>1695</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="117">
@@ -5182,19 +5154,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA_TAMA KONNYAKU_55%</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>12818</v>
+        <v>2929</v>
       </c>
       <c r="G117" t="n">
-        <v>1759</v>
+        <v>302</v>
       </c>
     </row>
     <row r="118">
@@ -5215,7 +5187,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5224,10 +5196,10 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>15705</v>
+        <v>4516</v>
       </c>
       <c r="G118" t="n">
-        <v>2710</v>
+        <v>277</v>
       </c>
     </row>
     <row r="119">
@@ -5248,19 +5220,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>32203</v>
+        <v>34367</v>
       </c>
       <c r="G119" t="n">
-        <v>2675</v>
+        <v>4366</v>
       </c>
     </row>
     <row r="120">
@@ -5281,19 +5253,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>36196</v>
+        <v>51196</v>
       </c>
       <c r="G120" t="n">
-        <v>3768</v>
+        <v>3398</v>
       </c>
     </row>
     <row r="121">
@@ -5314,19 +5286,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Baby Espresso_38% UV</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>26384</v>
+        <v>15691</v>
       </c>
       <c r="G121" t="n">
-        <v>3815</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="122">
@@ -5347,19 +5319,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Lighly Rose Rose(렌즈타운)</t>
+          <t>PIA D_Cream Beige_14.4</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>10293</v>
+        <v>2261</v>
       </c>
       <c r="G122" t="n">
-        <v>1320</v>
+        <v>374</v>
       </c>
     </row>
     <row r="123">
@@ -5380,19 +5352,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Pearl Cats Eye_38% UV</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>23706</v>
+        <v>19054</v>
       </c>
       <c r="G123" t="n">
-        <v>3117</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="124">
@@ -5413,19 +5385,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>7552</v>
+        <v>19090</v>
       </c>
       <c r="G124" t="n">
-        <v>692</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="125">
@@ -5446,19 +5418,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>14983</v>
+        <v>25228</v>
       </c>
       <c r="G125" t="n">
-        <v>1216</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="126">
@@ -5479,19 +5451,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>PIA D_Sakura Mousse_55% UV</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>23202</v>
+        <v>12450</v>
       </c>
       <c r="G126" t="n">
-        <v>2358</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="127">
@@ -5512,19 +5484,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>PIA D_Baby Espresso_38% UV</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>16975</v>
+        <v>20585</v>
       </c>
       <c r="G127" t="n">
-        <v>4558</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="128">
@@ -5545,19 +5517,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>PIA D_Cream Beige_14.4</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3270</v>
+        <v>5695</v>
       </c>
       <c r="G128" t="n">
-        <v>391</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="129">
@@ -5578,19 +5550,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>PIA D_Honey Soda_38% UV</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>15286</v>
+        <v>28618</v>
       </c>
       <c r="G129" t="n">
-        <v>5190</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="130">
@@ -5606,24 +5578,24 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>PIA D_Pearl Cats Eye_38% UV</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>2487</v>
+        <v>8441</v>
       </c>
       <c r="G130" t="n">
-        <v>522</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="131">
@@ -5639,24 +5611,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>28723</v>
+        <v>11073</v>
       </c>
       <c r="G131" t="n">
-        <v>1753</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="132">
@@ -5672,24 +5644,24 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Beige 14.2_55% UV</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3709</v>
+        <v>15955</v>
       </c>
       <c r="G132" t="n">
-        <v>307</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="133">
@@ -5705,24 +5677,24 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리22호기</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>8896</v>
+        <v>37631</v>
       </c>
       <c r="G133" t="n">
-        <v>817</v>
+        <v>7876</v>
       </c>
     </row>
     <row r="134">
@@ -5738,24 +5710,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리23호기</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>ALICIA BROWN(근시)</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>11884</v>
+        <v>36020</v>
       </c>
       <c r="G134" t="n">
-        <v>1530</v>
+        <v>6721</v>
       </c>
     </row>
     <row r="135">
@@ -5771,24 +5743,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리25호기</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>6294</v>
+        <v>36735</v>
       </c>
       <c r="G135" t="n">
-        <v>866</v>
+        <v>9490</v>
       </c>
     </row>
     <row r="136">
@@ -5804,24 +5776,24 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>T-Garden D_Melty Time_55% UV 14.2</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>24123</v>
+        <v>38389</v>
       </c>
       <c r="G136" t="n">
-        <v>4337</v>
+        <v>11356</v>
       </c>
     </row>
     <row r="137">
@@ -5837,24 +5809,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리43호기</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>PIA D_Air Gray_55% UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>24346</v>
+        <v>37134</v>
       </c>
       <c r="G137" t="n">
-        <v>1863</v>
+        <v>7519</v>
       </c>
     </row>
     <row r="138">
@@ -5870,24 +5842,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>Brown Bunny_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>20362</v>
+        <v>1055</v>
       </c>
       <c r="G138" t="n">
-        <v>1199</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="139">
@@ -5903,24 +5875,24 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>Brulee Pearl_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>2341</v>
+        <v>3674</v>
       </c>
       <c r="G139" t="n">
-        <v>512</v>
+        <v>733</v>
       </c>
     </row>
     <row r="140">
@@ -5936,24 +5908,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>6853</v>
+        <v>7651</v>
       </c>
       <c r="G140" t="n">
-        <v>1757</v>
+        <v>3941</v>
       </c>
     </row>
     <row r="141">
@@ -5969,24 +5941,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>Dollish Gray_PIA_M</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>8700</v>
+        <v>1672</v>
       </c>
       <c r="G141" t="n">
-        <v>1657</v>
+        <v>380</v>
       </c>
     </row>
     <row r="142">
@@ -6002,24 +5974,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>Dollish Gray_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>15744</v>
+        <v>773</v>
       </c>
       <c r="G142" t="n">
-        <v>2121</v>
+        <v>895</v>
       </c>
     </row>
     <row r="143">
@@ -6035,24 +6007,24 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>Lady Black_PIA_M_(중)_14.5</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>7296</v>
+        <v>2191</v>
       </c>
       <c r="G143" t="n">
-        <v>2449</v>
+        <v>101</v>
       </c>
     </row>
     <row r="144">
@@ -6068,24 +6040,24 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>분리22호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Skin Grege_(신규)PIA_M_14.5(Y)</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>35409</v>
+        <v>1149</v>
       </c>
       <c r="G144" t="n">
-        <v>5805</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="145">
@@ -6101,24 +6073,24 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>분리23호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>water water_(신규)PIA_M(Y)</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>35923</v>
+        <v>481</v>
       </c>
       <c r="G145" t="n">
-        <v>5113</v>
+        <v>317</v>
       </c>
     </row>
     <row r="146">
@@ -6129,29 +6101,29 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>분리25호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>37476</v>
+        <v>10355</v>
       </c>
       <c r="G146" t="n">
-        <v>9041</v>
+        <v>175</v>
       </c>
     </row>
     <row r="147">
@@ -6162,29 +6134,29 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>43526</v>
+        <v>5800</v>
       </c>
       <c r="G147" t="n">
-        <v>8734</v>
+        <v>90</v>
       </c>
     </row>
     <row r="148">
@@ -6195,29 +6167,29 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>분리43호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>39184</v>
+        <v>1962</v>
       </c>
       <c r="G148" t="n">
-        <v>9803</v>
+        <v>568</v>
       </c>
     </row>
     <row r="149">
@@ -6228,29 +6200,29 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Dazzle Beige_2T_(PBT)PIA_M(Y)</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1070</v>
+        <v>5050</v>
       </c>
       <c r="G149" t="n">
-        <v>204</v>
+        <v>520</v>
       </c>
     </row>
     <row r="150">
@@ -6261,29 +6233,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Dazzle Gray_2T_(PBT)PIA_M(Y)</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2466</v>
+        <v>5550</v>
       </c>
       <c r="G150" t="n">
-        <v>604</v>
+        <v>130</v>
       </c>
     </row>
     <row r="151">
@@ -6294,29 +6266,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Dollish Gray_PIA_M(Y)</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1425</v>
+        <v>8748</v>
       </c>
       <c r="G151" t="n">
-        <v>256</v>
+        <v>722</v>
       </c>
     </row>
     <row r="152">
@@ -6337,19 +6309,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>PIA D_Air Gray_55% UV</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>4060</v>
+        <v>6125</v>
       </c>
       <c r="G152" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="153">
@@ -6370,7 +6342,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6379,10 +6351,10 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>10794</v>
+        <v>8870</v>
       </c>
       <c r="G153" t="n">
-        <v>641</v>
+        <v>125</v>
       </c>
     </row>
     <row r="154">
@@ -6403,7 +6375,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -6412,10 +6384,10 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>3005</v>
+        <v>6940</v>
       </c>
       <c r="G154" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
     </row>
     <row r="155">
@@ -6436,19 +6408,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>2910</v>
+        <v>2543</v>
       </c>
       <c r="G155" t="n">
-        <v>40</v>
+        <v>822</v>
       </c>
     </row>
     <row r="156">
@@ -6469,16 +6441,16 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>PIA D_Sakana_55% UV</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>5355</v>
+        <v>5985</v>
       </c>
       <c r="G156" t="n">
         <v>80</v>
@@ -6502,19 +6474,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>PIA D_Sakura Mousse_55% UV</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>3550</v>
+        <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -6535,7 +6507,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6544,10 +6516,10 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1762</v>
+        <v>2986</v>
       </c>
       <c r="G158" t="n">
-        <v>38</v>
+        <v>624</v>
       </c>
     </row>
     <row r="159">
@@ -6568,19 +6540,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>6060</v>
+        <v>3020</v>
       </c>
       <c r="G159" t="n">
-        <v>245</v>
+        <v>35</v>
       </c>
     </row>
     <row r="160">
@@ -6601,19 +6573,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>PIA D_Air Gray_55% UV</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>2715</v>
+        <v>5607</v>
       </c>
       <c r="G160" t="n">
-        <v>60</v>
+        <v>703</v>
       </c>
     </row>
     <row r="161">
@@ -6634,16 +6606,16 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>3335</v>
+        <v>5910</v>
       </c>
       <c r="G161" t="n">
         <v>45</v>
@@ -6667,19 +6639,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>PIA D_Sakana_55% UV</t>
+          <t>ALICIA BROWN(근시)</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>2840</v>
+        <v>3465</v>
       </c>
       <c r="G162" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
     </row>
     <row r="163">
@@ -6700,19 +6672,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>BELLA D_MARS 55%</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>9215</v>
+        <v>15130</v>
       </c>
       <c r="G163" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
     </row>
     <row r="164">
@@ -6733,19 +6705,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Beige 14.2_55% UV</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>17165</v>
+        <v>2970</v>
       </c>
       <c r="G164" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
     </row>
     <row r="165">
@@ -6766,19 +6738,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>Lighly Rose Rose(렌즈타운)</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>2585</v>
+        <v>13946</v>
       </c>
       <c r="G165" t="n">
-        <v>35</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="166">
@@ -6799,19 +6771,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>2415</v>
+        <v>47416</v>
       </c>
       <c r="G166" t="n">
-        <v>10</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="167">
@@ -6832,19 +6804,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1680</v>
+        <v>4793</v>
       </c>
       <c r="G167" t="n">
-        <v>35</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="168">
@@ -6865,19 +6837,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>2770</v>
+        <v>48260</v>
       </c>
       <c r="G168" t="n">
-        <v>45</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="169">
@@ -6898,19 +6870,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>2605</v>
+        <v>8527</v>
       </c>
       <c r="G169" t="n">
-        <v>35</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="170">
@@ -6931,19 +6903,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>PIA D_Air Gray_55% UV</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>2310</v>
+        <v>3985</v>
       </c>
       <c r="G170" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="171">
@@ -6964,19 +6936,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>49970</v>
+        <v>13907</v>
       </c>
       <c r="G171" t="n">
-        <v>590</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="172">
@@ -6997,19 +6969,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1-Day_iris_Latin</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>6875</v>
+        <v>14350</v>
       </c>
       <c r="G172" t="n">
-        <v>45</v>
+        <v>855</v>
       </c>
     </row>
     <row r="173">
@@ -7030,19 +7002,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>40385</v>
+        <v>3405</v>
       </c>
       <c r="G173" t="n">
-        <v>335</v>
+        <v>15</v>
       </c>
     </row>
     <row r="174">
@@ -7063,19 +7035,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Sakura Mousse_55% UV</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>5995</v>
+        <v>3020</v>
       </c>
       <c r="G174" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="175">
@@ -7096,19 +7068,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1-Day_iris_Latin</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3195</v>
+        <v>7125</v>
       </c>
       <c r="G175" t="n">
-        <v>25</v>
+        <v>110</v>
       </c>
     </row>
     <row r="176">
@@ -7129,19 +7101,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>40385</v>
+        <v>582</v>
       </c>
       <c r="G176" t="n">
-        <v>565</v>
+        <v>313</v>
       </c>
     </row>
     <row r="177">
@@ -7162,19 +7134,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>4445</v>
+        <v>5450</v>
       </c>
       <c r="G177" t="n">
-        <v>730</v>
+        <v>125</v>
       </c>
     </row>
     <row r="178">
@@ -7195,19 +7167,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>IRIS_Jazz black(NEW)</t>
+          <t>PIA_TAMA KONNYAKU_55%</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1420</v>
+        <v>3230</v>
       </c>
       <c r="G178" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="179">
@@ -7228,19 +7200,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>IRIS_Soul Brown(NEW)</t>
+          <t>(NEW)ALICIA BROWN(근시)</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>2450</v>
+        <v>10347</v>
       </c>
       <c r="G179" t="n">
-        <v>50</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="180">
@@ -7261,19 +7233,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>PIA D_Air Gray_55% UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>2460</v>
+        <v>14915</v>
       </c>
       <c r="G180" t="n">
-        <v>20</v>
+        <v>175</v>
       </c>
     </row>
     <row r="181">
@@ -7294,19 +7266,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA D_Coco Truffle_38% UV</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>7665</v>
+        <v>1415</v>
       </c>
       <c r="G181" t="n">
-        <v>195</v>
+        <v>70</v>
       </c>
     </row>
     <row r="182">
@@ -7327,19 +7299,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Honey Soda_38% UV</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>6725</v>
+        <v>14805</v>
       </c>
       <c r="G182" t="n">
-        <v>80</v>
+        <v>435</v>
       </c>
     </row>
     <row r="183">
@@ -7360,19 +7332,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2630</v>
+        <v>12894</v>
       </c>
       <c r="G183" t="n">
-        <v>15</v>
+        <v>351</v>
       </c>
     </row>
     <row r="184">
@@ -7393,19 +7365,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>8590</v>
+        <v>13673</v>
       </c>
       <c r="G184" t="n">
-        <v>135</v>
+        <v>382</v>
       </c>
     </row>
     <row r="185">
@@ -7426,19 +7398,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>5300</v>
+        <v>6460</v>
       </c>
       <c r="G185" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="186">
@@ -7459,19 +7431,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>6300</v>
+        <v>3020</v>
       </c>
       <c r="G186" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
     </row>
     <row r="187">
@@ -7492,19 +7464,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>4445</v>
+        <v>5420</v>
       </c>
       <c r="G187" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="188">
@@ -7525,16 +7497,16 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1883</v>
+        <v>603</v>
       </c>
       <c r="G188" t="n">
         <v>242</v>
@@ -7558,19 +7530,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>2990</v>
+        <v>5215</v>
       </c>
       <c r="G189" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
     </row>
     <row r="190">
@@ -7591,19 +7563,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA_TAMA KONNYAKU_55%</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>51275</v>
+        <v>3285</v>
       </c>
       <c r="G190" t="n">
-        <v>750</v>
+        <v>55</v>
       </c>
     </row>
     <row r="191">
@@ -7624,19 +7596,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>BELLA D_MARS 55%</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>27995</v>
+        <v>5080</v>
       </c>
       <c r="G191" t="n">
-        <v>335</v>
+        <v>115</v>
       </c>
     </row>
     <row r="192">
@@ -7657,19 +7629,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>HOYA_Ruby brown(Maquia Brown)</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>13805</v>
+        <v>1286</v>
       </c>
       <c r="G192" t="n">
-        <v>245</v>
+        <v>214</v>
       </c>
     </row>
     <row r="193">
@@ -7695,14 +7667,14 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>1-Day_iris_Latin</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>2735</v>
+        <v>12295</v>
       </c>
       <c r="G193" t="n">
-        <v>35</v>
+        <v>565</v>
       </c>
     </row>
     <row r="194">
@@ -7728,14 +7700,14 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>3220</v>
+        <v>13005</v>
       </c>
       <c r="G194" t="n">
-        <v>20</v>
+        <v>425</v>
       </c>
     </row>
     <row r="195">
@@ -7761,14 +7733,14 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>2965</v>
+        <v>3310</v>
       </c>
       <c r="G195" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="196">
@@ -7794,14 +7766,14 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>BELLA D_MARS 55%</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>2348</v>
+        <v>3215</v>
       </c>
       <c r="G196" t="n">
-        <v>272</v>
+        <v>60</v>
       </c>
     </row>
     <row r="197">
@@ -7822,19 +7794,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>PIA D_Sakura Mousse_55% UV</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1250</v>
+        <v>1065</v>
       </c>
       <c r="G197" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="198">
@@ -7855,19 +7827,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA_1D 55% YakisobaPan_1T</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>23713</v>
+        <v>4895</v>
       </c>
       <c r="G198" t="n">
-        <v>1997</v>
+        <v>200</v>
       </c>
     </row>
     <row r="199">
@@ -7888,19 +7860,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>IRIS_Jazz black(NEW)</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>4285</v>
+        <v>2875</v>
       </c>
       <c r="G199" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="200">
@@ -7921,19 +7893,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>PIA D_Baby Espresso_38% UV</t>
+          <t>PIA_TAMA KONNYAKU_55%</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>8780</v>
+        <v>2955</v>
       </c>
       <c r="G200" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
     </row>
     <row r="201">
@@ -7954,19 +7926,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>49969</v>
+        <v>3675</v>
       </c>
       <c r="G201" t="n">
-        <v>1541</v>
+        <v>70</v>
       </c>
     </row>
     <row r="202">
@@ -7987,19 +7959,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>3120</v>
+        <v>800</v>
       </c>
       <c r="G202" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="203">
@@ -8020,19 +7992,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Air Gray_55% UV</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>2085</v>
+        <v>4010</v>
       </c>
       <c r="G203" t="n">
-        <v>240</v>
+        <v>50</v>
       </c>
     </row>
     <row r="204">
@@ -8053,19 +8025,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>PIA D_Baby Espresso_38% UV</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>13230</v>
+        <v>26649</v>
       </c>
       <c r="G204" t="n">
-        <v>150</v>
+        <v>966</v>
       </c>
     </row>
     <row r="205">
@@ -8086,19 +8058,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Cream Beige_14.4</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>2215</v>
+        <v>8135</v>
       </c>
       <c r="G205" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
     </row>
     <row r="206">
@@ -8119,19 +8091,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>PIA_BROWN MANEGE</t>
+          <t>PIA D_Pearl Cats Eye_38% UV</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>2395</v>
+        <v>2450</v>
       </c>
       <c r="G206" t="n">
-        <v>800</v>
+        <v>30</v>
       </c>
     </row>
     <row r="207">
@@ -8152,19 +8124,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>8195</v>
+        <v>4930</v>
       </c>
       <c r="G207" t="n">
-        <v>100</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="208">
@@ -8185,19 +8157,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>2515</v>
+        <v>2235</v>
       </c>
       <c r="G208" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="209">
@@ -8218,19 +8190,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>14510</v>
+        <v>2600</v>
       </c>
       <c r="G209" t="n">
-        <v>455</v>
+        <v>30</v>
       </c>
     </row>
     <row r="210">
@@ -8251,19 +8223,19 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>1580</v>
+        <v>3605</v>
       </c>
       <c r="G210" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
     </row>
     <row r="211">
@@ -8284,19 +8256,19 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>PIA D_Air Gray_55% UV</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>2765</v>
+        <v>7827</v>
       </c>
       <c r="G211" t="n">
-        <v>35</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="212">
@@ -8317,19 +8289,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA_1D 55% YakisobaPan_1T</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>8140</v>
+        <v>5490</v>
       </c>
       <c r="G212" t="n">
-        <v>115</v>
+        <v>150</v>
       </c>
     </row>
     <row r="213">
@@ -8350,19 +8322,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>3730</v>
+        <v>4545</v>
       </c>
       <c r="G213" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
     </row>
     <row r="214">
@@ -8383,19 +8355,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>9651</v>
+        <v>9570</v>
       </c>
       <c r="G214" t="n">
-        <v>504</v>
+        <v>210</v>
       </c>
     </row>
     <row r="215">
@@ -8416,19 +8388,19 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Air Gray_55% UV</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>2090</v>
+        <v>4095</v>
       </c>
       <c r="G215" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="216">
@@ -8449,19 +8421,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>2560</v>
+        <v>2925</v>
       </c>
       <c r="G216" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="217">
@@ -8482,19 +8454,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>PIA_Espresso_55%_14.5_1-DAY</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>2870</v>
+        <v>12189</v>
       </c>
       <c r="G217" t="n">
-        <v>40</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="218">
@@ -8515,19 +8487,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>8210</v>
+        <v>8285</v>
       </c>
       <c r="G218" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
     </row>
     <row r="219">
@@ -8548,19 +8520,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>PIA D_Sakura Mousse_55% UV</t>
         </is>
       </c>
       <c r="F219" t="n">
-        <v>5235</v>
+        <v>1015</v>
       </c>
       <c r="G219" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
     </row>
     <row r="220">
@@ -8581,19 +8553,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>PIA D_Air Gray_55% UV</t>
+          <t>PIA_BROWN MANEGE</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1302</v>
+        <v>3155</v>
       </c>
       <c r="G220" t="n">
-        <v>2778</v>
+        <v>35</v>
       </c>
     </row>
     <row r="221">
@@ -8614,19 +8586,19 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>2600</v>
+        <v>9635</v>
       </c>
       <c r="G221" t="n">
-        <v>30</v>
+        <v>140</v>
       </c>
     </row>
     <row r="222">
@@ -8647,19 +8619,19 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>PIA D_Brulee Pearl_55%_14.2 UV</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F222" t="n">
-        <v>2625</v>
+        <v>1115</v>
       </c>
       <c r="G222" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
     </row>
     <row r="223">
@@ -8680,19 +8652,19 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F223" t="n">
-        <v>5770</v>
+        <v>14308</v>
       </c>
       <c r="G223" t="n">
-        <v>40</v>
+        <v>587</v>
       </c>
     </row>
     <row r="224">
@@ -8713,19 +8685,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA_TAMA KONNYAKU_55%</t>
         </is>
       </c>
       <c r="F224" t="n">
-        <v>1965</v>
+        <v>2640</v>
       </c>
       <c r="G224" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="225">
@@ -8746,19 +8718,19 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>PIA D_Air Gray_55% UV</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>7065</v>
+        <v>11855</v>
       </c>
       <c r="G225" t="n">
-        <v>90</v>
+        <v>175</v>
       </c>
     </row>
     <row r="226">
@@ -8779,19 +8751,19 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>3235</v>
+        <v>1900</v>
       </c>
       <c r="G226" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="227">
@@ -8812,19 +8784,19 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>6275</v>
+        <v>7130</v>
       </c>
       <c r="G227" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="228">
@@ -8845,19 +8817,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>13960</v>
+        <v>3240</v>
       </c>
       <c r="G228" t="n">
-        <v>165</v>
+        <v>40</v>
       </c>
     </row>
     <row r="229">
@@ -8878,19 +8850,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>(NEW)ALICIA BROWN(근시)</t>
+          <t>PIA_TAMA KONNYAKU_55%</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>15485</v>
+        <v>3180</v>
       </c>
       <c r="G229" t="n">
-        <v>680</v>
+        <v>75</v>
       </c>
     </row>
     <row r="230">
@@ -8911,19 +8883,19 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>1-Day_iris_Latin</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>5500</v>
+        <v>21365</v>
       </c>
       <c r="G230" t="n">
-        <v>75</v>
+        <v>195</v>
       </c>
     </row>
     <row r="231">
@@ -8944,19 +8916,19 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
         </is>
       </c>
       <c r="F231" t="n">
-        <v>26490</v>
+        <v>4961</v>
       </c>
       <c r="G231" t="n">
-        <v>350</v>
+        <v>724</v>
       </c>
     </row>
     <row r="232">
@@ -8977,19 +8949,19 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Air Gray_55% UV</t>
         </is>
       </c>
       <c r="F232" t="n">
-        <v>3085</v>
+        <v>4025</v>
       </c>
       <c r="G232" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="233">
@@ -9010,19 +8982,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Lighly Rose Rose(렌즈타운)</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F233" t="n">
-        <v>2730</v>
+        <v>7910</v>
       </c>
       <c r="G233" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
     </row>
     <row r="234">
@@ -9043,19 +9015,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>PIA D_Air Gray_55% UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F234" t="n">
-        <v>5340</v>
+        <v>5675</v>
       </c>
       <c r="G234" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="235">
@@ -9076,19 +9048,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F235" t="n">
-        <v>2185</v>
+        <v>2340</v>
       </c>
       <c r="G235" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
     </row>
     <row r="236">
@@ -9109,19 +9081,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>5950</v>
+        <v>535</v>
       </c>
       <c r="G236" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="237">
@@ -9142,19 +9114,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA_TAMA KONNYAKU_55%</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>9280</v>
+        <v>3215</v>
       </c>
       <c r="G237" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="238">
@@ -9175,19 +9147,19 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>PIA D_Sakana_55% UV</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F238" t="n">
-        <v>6085</v>
+        <v>15545</v>
       </c>
       <c r="G238" t="n">
-        <v>65</v>
+        <v>145</v>
       </c>
     </row>
     <row r="239">
@@ -9208,19 +9180,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
         </is>
       </c>
       <c r="F239" t="n">
-        <v>10195</v>
+        <v>8846</v>
       </c>
       <c r="G239" t="n">
-        <v>105</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="240">
@@ -9241,19 +9213,19 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>(NEW)ALICIA BROWN(근시)</t>
         </is>
       </c>
       <c r="F240" t="n">
-        <v>2400</v>
+        <v>2460</v>
       </c>
       <c r="G240" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="241">
@@ -9274,19 +9246,19 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>ADRIA_Blue_1-Day</t>
         </is>
       </c>
       <c r="F241" t="n">
-        <v>5525</v>
+        <v>540</v>
       </c>
       <c r="G241" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="242">
@@ -9307,19 +9279,19 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>ADRIA_Pearl_1-Day</t>
         </is>
       </c>
       <c r="F242" t="n">
-        <v>2795</v>
+        <v>720</v>
       </c>
       <c r="G242" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="243">
@@ -9335,24 +9307,24 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F243" t="n">
-        <v>7040</v>
+        <v>3865</v>
       </c>
       <c r="G243" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
     </row>
     <row r="244">
@@ -9368,24 +9340,24 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F244" t="n">
-        <v>10814</v>
+        <v>8205</v>
       </c>
       <c r="G244" t="n">
-        <v>546</v>
+        <v>140</v>
       </c>
     </row>
     <row r="245">
@@ -9401,24 +9373,24 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>PIA_Sheer Brown_55%_1-DAY</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>3110</v>
+        <v>9820</v>
       </c>
       <c r="G245" t="n">
-        <v>75</v>
+        <v>295</v>
       </c>
     </row>
     <row r="246">
@@ -9434,24 +9406,24 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F246" t="n">
-        <v>1895</v>
+        <v>13220</v>
       </c>
       <c r="G246" t="n">
-        <v>35</v>
+        <v>200</v>
       </c>
     </row>
     <row r="247">
@@ -9467,24 +9439,24 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F247" t="n">
-        <v>8095</v>
+        <v>10413</v>
       </c>
       <c r="G247" t="n">
-        <v>120</v>
+        <v>367</v>
       </c>
     </row>
     <row r="248">
@@ -9500,387 +9472,387 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>PIA D_Dark Peony_55% UV</t>
         </is>
       </c>
       <c r="F248" t="n">
-        <v>30180</v>
+        <v>5598</v>
       </c>
       <c r="G248" t="n">
-        <v>915</v>
+        <v>542</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>PIA D_Sakura Mousse_55% UV</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>16694</v>
+        <v>1010</v>
       </c>
       <c r="G249" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>B형 조립중합5호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>35408</v>
+        <v>3010</v>
       </c>
       <c r="G250" t="n">
-        <v>160</v>
+        <v>40</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>B형 조립중합6호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Brown EX</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>15880</v>
+        <v>3190</v>
       </c>
       <c r="G251" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>B형 조립중합6호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>O2O2 D_Sepia Choco EX</t>
+          <t>PIA_TAMA KONNYAKU_55%</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>17576</v>
+        <v>17270</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>41734</v>
+        <v>2310</v>
       </c>
       <c r="G253" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>41072</v>
+        <v>9845</v>
       </c>
       <c r="G254" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>21132</v>
+        <v>25040</v>
       </c>
       <c r="G255" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>CAM분리2호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>Toric_CP-1.25_Halo Brown</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>16119</v>
+        <v>3000</v>
       </c>
       <c r="G256" t="n">
-        <v>3034</v>
+        <v>35</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>CAM분리3호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>Toric_CP-1.25_Halo Brown</t>
         </is>
       </c>
       <c r="F257" t="n">
-        <v>18210</v>
+        <v>8565</v>
       </c>
       <c r="G257" t="n">
-        <v>3111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
       <c r="F258" t="n">
-        <v>6192</v>
+        <v>6651</v>
       </c>
       <c r="G258" t="n">
-        <v>1216</v>
+        <v>639</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F259" t="n">
-        <v>2499</v>
+        <v>23135</v>
       </c>
       <c r="G259" t="n">
-        <v>253</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="260">
@@ -9891,29 +9863,29 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>B형 분리수화접착6호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F260" t="n">
-        <v>4521</v>
+        <v>18736</v>
       </c>
       <c r="G260" t="n">
-        <v>1148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -9924,7 +9896,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9934,19 +9906,19 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>B형 분리수화접착6호기</t>
+          <t>B형 조립중합4호기</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F261" t="n">
-        <v>2737</v>
+        <v>14311</v>
       </c>
       <c r="G261" t="n">
-        <v>940</v>
+        <v>872</v>
       </c>
     </row>
     <row r="262">
@@ -9957,7 +9929,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9967,7 +9939,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>B형 조립중합5호기</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -9976,10 +9948,10 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>11150</v>
+        <v>14411</v>
       </c>
       <c r="G262" t="n">
-        <v>2367</v>
+        <v>720</v>
       </c>
     </row>
     <row r="263">
@@ -9990,29 +9962,29 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F263" t="n">
-        <v>2630</v>
+        <v>46701</v>
       </c>
       <c r="G263" t="n">
-        <v>829</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -10023,29 +9995,29 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Brown EX</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F264" t="n">
-        <v>8802</v>
+        <v>38383</v>
       </c>
       <c r="G264" t="n">
-        <v>2333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -10056,29 +10028,29 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Gray EX</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F265" t="n">
-        <v>11195</v>
+        <v>27460</v>
       </c>
       <c r="G265" t="n">
-        <v>2832</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -10094,24 +10066,24 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>CAM분리2호기</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F266" t="n">
-        <v>29071</v>
+        <v>1660</v>
       </c>
       <c r="G266" t="n">
-        <v>1621</v>
+        <v>485</v>
       </c>
     </row>
     <row r="267">
@@ -10127,24 +10099,24 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>CAM분리3호기</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F267" t="n">
-        <v>34152</v>
+        <v>11624</v>
       </c>
       <c r="G267" t="n">
-        <v>1100</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="268">
@@ -10160,24 +10132,24 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>29282</v>
+        <v>1669</v>
       </c>
       <c r="G268" t="n">
-        <v>3192</v>
+        <v>541</v>
       </c>
     </row>
     <row r="269">
@@ -10193,24 +10165,24 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>O2O2 Spherical(DK70)_K2-SMD</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>3644</v>
+        <v>573</v>
       </c>
       <c r="G269" t="n">
-        <v>1111</v>
+        <v>264</v>
       </c>
     </row>
     <row r="270">
@@ -10226,24 +10198,24 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>B형 분리수화접착6호기</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>7769</v>
+        <v>11164</v>
       </c>
       <c r="G270" t="n">
-        <v>2655</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="271">
@@ -10259,24 +10231,24 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>B형 분리수화접착6호기</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>O2O2 Spherical(DK70)_K2-SMD</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>6331</v>
+        <v>669</v>
       </c>
       <c r="G271" t="n">
-        <v>1399</v>
+        <v>175</v>
       </c>
     </row>
     <row r="272">
@@ -10292,24 +10264,24 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>9554</v>
+        <v>609</v>
       </c>
       <c r="G272" t="n">
-        <v>2746</v>
+        <v>86</v>
       </c>
     </row>
     <row r="273">
@@ -10320,29 +10292,29 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Clalen D_Mimosa Brown</t>
+          <t>O2O2 D_Ash Brown EX</t>
         </is>
       </c>
       <c r="F273" t="n">
-        <v>3300</v>
+        <v>5421</v>
       </c>
       <c r="G273" t="n">
-        <v>119</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="274">
@@ -10353,29 +10325,29 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Cherry Moon</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>23982</v>
+        <v>24100</v>
       </c>
       <c r="G274" t="n">
-        <v>3214</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="275">
@@ -10386,29 +10358,29 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Creamy Moon</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F275" t="n">
-        <v>6890</v>
+        <v>32734</v>
       </c>
       <c r="G275" t="n">
-        <v>216</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="276">
@@ -10419,29 +10391,29 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Ice gray Moon</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>2820</v>
+        <v>13837</v>
       </c>
       <c r="G276" t="n">
-        <v>74</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="277">
@@ -10452,29 +10424,29 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>B형 분리수화접착3호기</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Clalen oneday A(O2 Edition)</t>
+          <t>O2O2 Spherical(DK70)_K2-SMD</t>
         </is>
       </c>
       <c r="F277" t="n">
-        <v>2685</v>
+        <v>1739</v>
       </c>
       <c r="G277" t="n">
-        <v>1349</v>
+        <v>413</v>
       </c>
     </row>
     <row r="278">
@@ -10485,29 +10457,29 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>B형 분리수화접착3호기</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>sincere Natural 1day</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>19645</v>
+        <v>9936</v>
       </c>
       <c r="G278" t="n">
-        <v>326</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="279">
@@ -10518,29 +10490,29 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>B형 분리수화접착4호기</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Clalen oneday A(O2 Edition)</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>16675</v>
+        <v>25429</v>
       </c>
       <c r="G279" t="n">
-        <v>1698</v>
+        <v>4756</v>
       </c>
     </row>
     <row r="280">
@@ -10551,29 +10523,29 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>1525</v>
+        <v>19209</v>
       </c>
       <c r="G280" t="n">
-        <v>36</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="281">
@@ -10584,29 +10556,29 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착6호기</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>4213</v>
+        <v>2492</v>
       </c>
       <c r="G281" t="n">
-        <v>941</v>
+        <v>311</v>
       </c>
     </row>
     <row r="282">
@@ -10617,29 +10589,29 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Toric</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착3호기</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Brown EX</t>
+          <t>O2O2 D_UV_Toric_SMD</t>
         </is>
       </c>
       <c r="F282" t="n">
-        <v>3345</v>
+        <v>145</v>
       </c>
       <c r="G282" t="n">
-        <v>114</v>
+        <v>407</v>
       </c>
     </row>
     <row r="283">
@@ -10655,24 +10627,24 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Gray EX</t>
+          <t>JEWEL MOON D_Cherry Moon</t>
         </is>
       </c>
       <c r="F283" t="n">
-        <v>3581</v>
+        <v>3200</v>
       </c>
       <c r="G283" t="n">
-        <v>2014</v>
+        <v>406</v>
       </c>
     </row>
     <row r="284">
@@ -10688,7 +10660,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -10698,14 +10670,14 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>JEWEL MOON D_Cherry Moon</t>
         </is>
       </c>
       <c r="F284" t="n">
-        <v>771</v>
+        <v>356</v>
       </c>
       <c r="G284" t="n">
-        <v>3219</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="285">
@@ -10721,24 +10693,24 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Clalen oneday A(O2 Edition)</t>
         </is>
       </c>
       <c r="F285" t="n">
-        <v>269</v>
+        <v>21634</v>
       </c>
       <c r="G285" t="n">
-        <v>1111</v>
+        <v>4552</v>
       </c>
     </row>
     <row r="286">
@@ -10759,19 +10731,19 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F286" t="n">
-        <v>27352</v>
+        <v>1660</v>
       </c>
       <c r="G286" t="n">
-        <v>5680</v>
+        <v>43</v>
       </c>
     </row>
     <row r="287">
@@ -10787,7 +10759,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Toric</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -10797,14 +10769,14 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>O2O2 D Toric_Ash Brown EX</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F287" t="n">
-        <v>584</v>
+        <v>970</v>
       </c>
       <c r="G287" t="n">
-        <v>1713</v>
+        <v>26</v>
       </c>
     </row>
     <row r="288">
@@ -10820,7 +10792,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Toric</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -10830,14 +10802,14 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>O2O2 D Toric_Sepia Choco EX</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F288" t="n">
-        <v>18449</v>
+        <v>4300</v>
       </c>
       <c r="G288" t="n">
-        <v>1851</v>
+        <v>203</v>
       </c>
     </row>
     <row r="289">
@@ -10853,24 +10825,24 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMDH_WHITE_OPHTALMIC</t>
+          <t>O2O2 D_Ash Gray EX</t>
         </is>
       </c>
       <c r="F289" t="n">
-        <v>1360</v>
+        <v>3340</v>
       </c>
       <c r="G289" t="n">
-        <v>30</v>
+        <v>246</v>
       </c>
     </row>
     <row r="290">
@@ -10886,24 +10858,24 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>A형 인라인6호기</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F290" t="n">
-        <v>43385</v>
+        <v>12595</v>
       </c>
       <c r="G290" t="n">
-        <v>1288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="291">
@@ -10919,24 +10891,24 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>A형 인라인6호기</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F291" t="n">
-        <v>14225</v>
+        <v>1325</v>
       </c>
       <c r="G291" t="n">
-        <v>124</v>
+        <v>48</v>
       </c>
     </row>
     <row r="292">
@@ -10952,24 +10924,24 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>A형 인라인6호기</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F292" t="n">
-        <v>9515</v>
+        <v>12810</v>
       </c>
       <c r="G292" t="n">
-        <v>247</v>
+        <v>388</v>
       </c>
     </row>
     <row r="293">
@@ -10985,24 +10957,288 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>A형 인라인6호기</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>O2O2 D_Ash Brown EX</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>4544</v>
+      </c>
+      <c r="G293" t="n">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>A형 인라인6호기</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>O2O2 D_Ash Gray EX</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G294" t="n">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Toric</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>O2O2 D Toric_Ash Brown EX</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>1645</v>
+      </c>
+      <c r="G295" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Toric</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>O2O2 D Toric_Sepia Choco EX</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>1455</v>
+      </c>
+      <c r="G296" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Si_1-Day_M/F</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>O2O2_Multifocal_K2_SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>535</v>
+      </c>
+      <c r="G297" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
           <t>Si_1-Day_Sph</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr">
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>9380</v>
+      </c>
+      <c r="G298" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>A형 인라인2호기</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>24908</v>
+      </c>
+      <c r="G299" t="n">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>A형 인라인4호기</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>15953</v>
+      </c>
+      <c r="G300" t="n">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
         <is>
           <t>A형 인라인5호기</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr">
+      <c r="E301" t="inlineStr">
         <is>
           <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
-      <c r="F293" t="n">
-        <v>5955</v>
-      </c>
-      <c r="G293" t="n">
-        <v>1191</v>
+      <c r="F301" t="n">
+        <v>20584</v>
+      </c>
+      <c r="G301" t="n">
+        <v>1308</v>
       </c>
     </row>
   </sheetData>

--- a/생산실적현황(설비운영현황).xlsx
+++ b/생산실적현황(설비운영현황).xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_M/F</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Metha_55</t>
+          <t>Bi-focal_8.40</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -565,11 +565,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Si_1-Day_Toric</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -577,7 +577,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>O2O2 D_UV_Toric_SMD</t>
+          <t>O2O2_Multifocal_K2_SMD</t>
         </is>
       </c>
     </row>
@@ -589,23 +589,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Toric</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1-Day_Metha</t>
+          <t>O2O2 D_UV_Toric_SMD</t>
         </is>
       </c>
     </row>
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.2</t>
+          <t>1-Day_Metha</t>
         </is>
       </c>
     </row>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>(NEW)S38-Dry-14.2</t>
         </is>
       </c>
     </row>
@@ -673,23 +673,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Silicone relax</t>
+          <t>NewFusion_원형</t>
         </is>
       </c>
     </row>
@@ -705,19 +705,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>(NEW)MG M_No.1 Hazel_GLAM_(중)</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
     </row>
@@ -733,19 +733,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>T55_소사각</t>
         </is>
       </c>
     </row>
@@ -761,11 +761,11 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -773,35 +773,35 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>T38_금캡(UV포함)</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
     </row>
@@ -817,19 +817,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
     </row>
@@ -845,11 +845,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -857,7 +857,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>Coffee Jelly_PIA_M(Y)</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -909,11 +909,11 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>Toric_CP-1.25_Halo Brown</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -953,23 +953,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
+          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
         </is>
       </c>
     </row>
@@ -985,39 +985,39 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
     </row>
@@ -1073,15 +1073,15 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1125,19 +1125,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
     </row>
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1245,11 +1245,11 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1292,14 +1292,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G301"/>
+  <dimension ref="A1:G291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="43" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1359,19 +1359,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>조립30호기</t>
+          <t>조립1호기</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>1-Day_Metha</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>32547</v>
+        <v>34116</v>
       </c>
       <c r="G2" t="n">
-        <v>3573</v>
+        <v>3898</v>
       </c>
     </row>
     <row r="3">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>조립31호기</t>
+          <t>조립30호기</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>49760</v>
+        <v>84119</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>637</v>
       </c>
     </row>
     <row r="4">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>조립32호기</t>
+          <t>조립31호기</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>51166</v>
+        <v>96478</v>
       </c>
       <c r="G4" t="n">
-        <v>2554</v>
+        <v>563</v>
       </c>
     </row>
     <row r="5">
@@ -1453,24 +1453,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>조립1호기</t>
+          <t>조립32호기</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Metha_55</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>20654</v>
+        <v>49148</v>
       </c>
       <c r="G5" t="n">
-        <v>624</v>
+        <v>881</v>
       </c>
     </row>
     <row r="6">
@@ -1486,21 +1486,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>조립8호기</t>
+          <t>조립5호기</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S55-Dry</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>20606</v>
+        <v>36717</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1519,24 +1519,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_M/F</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>조립2호기</t>
+          <t>조립8호기</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>T38_(UV포함)</t>
+          <t>Bi-focal_8.40</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2796</v>
+        <v>31776</v>
       </c>
       <c r="G7" t="n">
-        <v>1715</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="8">
@@ -1552,24 +1552,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Si_1-Day_Toric</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>조립7호기</t>
+          <t>조립2호기</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>O2O2 D_UV_Toric_SMD</t>
+          <t>T38_(UV포함)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4789</v>
+        <v>7235</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="9">
@@ -1580,29 +1580,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>분리14호기</t>
+          <t>조립4호기</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1-Day_Metha</t>
+          <t>O2O2_Multifocal_K2_SMD</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>13167</v>
+        <v>7596</v>
       </c>
       <c r="G9" t="n">
-        <v>7249</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="10">
@@ -1613,29 +1613,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Toric</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>분리5호기</t>
+          <t>조립7호기</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1-Day_Metha</t>
+          <t>O2O2 D_UV_Toric_SMD</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>980</v>
+        <v>7714</v>
       </c>
       <c r="G10" t="n">
-        <v>606</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="11">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>분리10호기</t>
+          <t>분리14호기</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(NEW)S38-Dry-14.2</t>
+          <t>1-Day_Metha</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2179</v>
+        <v>16585</v>
       </c>
       <c r="G11" t="n">
-        <v>256</v>
+        <v>4445</v>
       </c>
     </row>
     <row r="12">
@@ -1694,14 +1694,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.2</t>
+          <t>(NEW)S38-Dry-14.2</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>7266</v>
+        <v>4081</v>
       </c>
       <c r="G12" t="n">
-        <v>1485</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13">
@@ -1722,19 +1722,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>분리11호기</t>
+          <t>분리10호기</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(NEW)S38-Dry-14.2</t>
+          <t>(NEW)S43-HD-Dry-14.4</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6069</v>
+        <v>6463</v>
       </c>
       <c r="G13" t="n">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="14">
@@ -1755,19 +1755,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>분리11호기</t>
+          <t>분리10호기</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.2</t>
+          <t>S43-Dry-14.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4470</v>
+        <v>5098</v>
       </c>
       <c r="G14" t="n">
-        <v>836</v>
+        <v>821</v>
       </c>
     </row>
     <row r="15">
@@ -1793,14 +1793,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.4</t>
+          <t>(NEW)S38-Dry-14.2</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1800</v>
+        <v>15617</v>
       </c>
       <c r="G15" t="n">
-        <v>180</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="16">
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2166</v>
+        <v>4368</v>
       </c>
       <c r="G16" t="n">
-        <v>513</v>
+        <v>758</v>
       </c>
     </row>
     <row r="17">
@@ -1854,19 +1854,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>분리4호기</t>
+          <t>분리14호기</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(NEW)S38-HD-Dry-14.0</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1050</v>
+        <v>8237</v>
       </c>
       <c r="G17" t="n">
-        <v>650</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="18">
@@ -1892,14 +1892,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.4</t>
+          <t>(NEW)S43-HD-Dry-14.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1494</v>
+        <v>4908</v>
       </c>
       <c r="G18" t="n">
-        <v>906</v>
+        <v>840</v>
       </c>
     </row>
     <row r="19">
@@ -1915,24 +1915,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>분리3호기</t>
+          <t>분리4호기</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>(NEW)S43-HD-Dry-14.4</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3671</v>
+        <v>4393</v>
       </c>
       <c r="G19" t="n">
-        <v>1693</v>
+        <v>407</v>
       </c>
     </row>
     <row r="20">
@@ -1948,24 +1948,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>분리42호기(초음파)</t>
+          <t>분리4호기</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Silicone relax</t>
+          <t>S43-Dry-14.5</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>15838</v>
+        <v>4117</v>
       </c>
       <c r="G20" t="n">
-        <v>1322</v>
+        <v>693</v>
       </c>
     </row>
     <row r="21">
@@ -1976,29 +1976,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>검사15호기</t>
+          <t>분리4호기</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(NEW)MG M_No.1 Hazel_GLAM_(중)</t>
+          <t>S55-Dry</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>9223</v>
+        <v>2135</v>
       </c>
       <c r="G21" t="n">
-        <v>68</v>
+        <v>443</v>
       </c>
     </row>
     <row r="22">
@@ -2009,29 +2009,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>분리5호기</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Affogato_PIA_M_(중)(Y)</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>442</v>
+        <v>3571</v>
       </c>
       <c r="G22" t="n">
-        <v>12</v>
+        <v>577</v>
       </c>
     </row>
     <row r="23">
@@ -2042,29 +2042,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>분리5호기</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lady Black_PIA_M_(중)_14.5</t>
+          <t>US55-2(M)</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>282</v>
+        <v>11873</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>4108</v>
       </c>
     </row>
     <row r="24">
@@ -2090,14 +2090,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oolong Tea_PIA_M_중사각(Y)</t>
+          <t>BELLA M_Moon_14.5_(중)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>916</v>
+        <v>486</v>
       </c>
       <c r="G24" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -2123,14 +2123,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Princess Chocolat_PIA_M_(중)_14.5</t>
+          <t>Bella Diamond_14.5_중사각</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>982</v>
+        <v>1022</v>
       </c>
       <c r="G25" t="n">
-        <v>18</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26">
@@ -2156,14 +2156,14 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sakura Smore_PIA_M_(중)(Y)</t>
+          <t>Bella Glow_중사각</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>603</v>
+        <v>284</v>
       </c>
       <c r="G26" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
@@ -2184,19 +2184,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
+          <t>Bella-Contour_중사각</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3192</v>
+        <v>450</v>
       </c>
       <c r="G27" t="n">
-        <v>166</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28">
@@ -2217,19 +2217,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cream Rose_PIA_M_(중)</t>
+          <t>Bella-Elite_14.5_중사각</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2864</v>
+        <v>3066</v>
       </c>
       <c r="G28" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29">
@@ -2250,19 +2250,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Clalen Iris_GRA_2902_원형</t>
+          <t>Affogato_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>386</v>
+        <v>974</v>
       </c>
       <c r="G29" t="n">
-        <v>129</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -2283,19 +2283,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>NewFusion_원형</t>
+          <t>Bella Glow_중사각</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1574</v>
+        <v>100</v>
       </c>
       <c r="G30" t="n">
-        <v>1957</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
@@ -2316,19 +2316,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Affogato_PIA_M_(중)(Y)</t>
+          <t>Bella-Natural_중사각</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1526</v>
+        <v>156</v>
       </c>
       <c r="G31" t="n">
-        <v>85</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32">
@@ -2349,19 +2349,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bella Diamond_14.5_중사각</t>
+          <t>Cream Rose_PIA_M_(중)</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>976</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
@@ -2382,19 +2382,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Clalen 1M_Planet_Gray Moon</t>
+          <t>Lady Black_PIA_M_(중)_14.5</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>49</v>
+        <v>1490</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34">
@@ -2415,19 +2415,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
+          <t>NewFusion_중사각</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>822</v>
+        <v>568</v>
       </c>
       <c r="G34" t="n">
-        <v>199</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35">
@@ -2448,19 +2448,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dazzle Gray_2T_(PBT)PIA_M_(중)(Y)</t>
+          <t>Aquarella M_Samba Green_원형</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>606</v>
+        <v>654</v>
       </c>
       <c r="G35" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2481,19 +2481,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Twinkle Brown_PIA_M_(중)(Y)</t>
+          <t>Aquarella_Amazonia Green_원형</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1624</v>
+        <v>1428</v>
       </c>
       <c r="G36" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2514,16 +2514,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>NewFusion_소사각</t>
+          <t>Aquarella_Dandara Hazel_원형</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>108</v>
+        <v>1398</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2547,19 +2547,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Baby Espresso_PIA_M_중사각(Y)</t>
+          <t>CLC-30_원형</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1018</v>
+        <v>174</v>
       </c>
       <c r="G38" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39">
@@ -2580,19 +2580,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
+          <t>Clalen Iris_GRA_2902_원형</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1208</v>
+        <v>402</v>
       </c>
       <c r="G39" t="n">
-        <v>56</v>
+        <v>413</v>
       </c>
     </row>
     <row r="40">
@@ -2613,19 +2613,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Date Topaz_PIA_M_(중)(Y)</t>
+          <t>Festival-II-Color_원형</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>784</v>
+        <v>1045</v>
       </c>
       <c r="G40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2646,19 +2646,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Garnet_PIA_M_(중)(Y)</t>
+          <t>NewFusion_원형</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>934</v>
+        <v>4057</v>
       </c>
       <c r="G41" t="n">
-        <v>61</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
@@ -2679,19 +2679,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oolong Tea_PIA_M_중사각(Y)</t>
+          <t>Rainbow_원형</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1088</v>
+        <v>227</v>
       </c>
       <c r="G42" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2712,19 +2712,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>검사7호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brulee Pearl_PIA_M_(중)(Y)</t>
+          <t>BELLA M_Moon_14.5_(중)</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1234</v>
+        <v>2386</v>
       </c>
       <c r="G43" t="n">
-        <v>29</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44">
@@ -2745,16 +2745,16 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>검사7호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
+          <t>Bella Diamond_14.5_중사각</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2036</v>
+        <v>936</v>
       </c>
       <c r="G44" t="n">
         <v>21</v>
@@ -2778,19 +2778,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>검사7호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mirror Gray_3T_(PBT)PIA_M_(중)(Y)</t>
+          <t>Bella-Contour_중사각</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1048</v>
+        <v>362</v>
       </c>
       <c r="G45" t="n">
-        <v>184</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46">
@@ -2811,19 +2811,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>검사7호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Oolong Tea_PIA_M_중사각(Y)</t>
+          <t>Bella-Elite_14.5_중사각</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1018</v>
+        <v>480</v>
       </c>
       <c r="G46" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
@@ -2844,19 +2844,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사7호기</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>NewFusion_원형</t>
+          <t>Bella Glow_중사각</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>994</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>1838</v>
+        <v>200</v>
       </c>
     </row>
     <row r="48">
@@ -2872,24 +2872,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>검사7호기</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>Bella-Natural_14.5_중사각</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1490</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>18</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49">
@@ -2905,24 +2905,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>Advance_CB_원형</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3540</v>
+        <v>718</v>
       </c>
       <c r="G49" t="n">
-        <v>153</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="50">
@@ -2938,24 +2938,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>CLC-30_원형</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>4090</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>119</v>
+        <v>296</v>
       </c>
     </row>
     <row r="51">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>Clalen Iris_GRA_2902_원형</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2482</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>188</v>
+        <v>297</v>
       </c>
     </row>
     <row r="52">
@@ -3004,24 +3004,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>Clalen Iris_GRA_3302_원형</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3781</v>
+        <v>242</v>
       </c>
       <c r="G52" t="n">
-        <v>132</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53">
@@ -3037,24 +3037,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>NewFusion_원형</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3236</v>
+        <v>32</v>
       </c>
       <c r="G53" t="n">
-        <v>185</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="54">
@@ -3070,24 +3070,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>CLC-30_바이알</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3370</v>
+        <v>927</v>
       </c>
       <c r="G54" t="n">
-        <v>164</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55">
@@ -3103,24 +3103,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>NewFusion_금캡</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3860</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>149</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56">
@@ -3136,24 +3136,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_M/F</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>HD-X55_소사각</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>5650</v>
+        <v>1428</v>
       </c>
       <c r="G56" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3174,19 +3174,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1828</v>
+        <v>12462</v>
       </c>
       <c r="G57" t="n">
-        <v>85</v>
+        <v>585</v>
       </c>
     </row>
     <row r="58">
@@ -3207,19 +3207,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1766</v>
+        <v>6746</v>
       </c>
       <c r="G58" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59">
@@ -3240,19 +3240,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Metha_55_원형</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>4884</v>
+        <v>6224</v>
       </c>
       <c r="G59" t="n">
-        <v>78</v>
+        <v>292</v>
       </c>
     </row>
     <row r="60">
@@ -3273,19 +3273,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>Metha_55_원형</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>4598</v>
+        <v>1704</v>
       </c>
       <c r="G60" t="n">
-        <v>171</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61">
@@ -3306,19 +3306,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>Metha_55_중사각</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1908</v>
+        <v>4702</v>
       </c>
       <c r="G61" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>US55-2(M)_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2260</v>
+        <v>3718</v>
       </c>
       <c r="G62" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63">
@@ -3372,19 +3372,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Metha_55_원형</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2728</v>
+        <v>1982</v>
       </c>
       <c r="G63" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -3400,24 +3400,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사7호기</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>Metha_55_중사각</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>20</v>
+        <v>1128</v>
       </c>
       <c r="G64" t="n">
-        <v>10</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65">
@@ -3433,24 +3433,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>T38_금캡(UV포함)</t>
+          <t>Metha_55_원형</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>5122</v>
+        <v>1764</v>
       </c>
       <c r="G65" t="n">
-        <v>997</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66">
@@ -3466,255 +3466,255 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>S38_은캡(BLUE TINT)</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>5984</v>
+        <v>9859</v>
       </c>
       <c r="G66" t="n">
-        <v>139</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>조립10호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>27287</v>
+        <v>2826</v>
       </c>
       <c r="G67" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>조립11호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>19282</v>
+        <v>544</v>
       </c>
       <c r="G68" t="n">
-        <v>550</v>
+        <v>92</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>조립12호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>O2O2 M_Mysti Gray EX_(중)</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>26314</v>
+        <v>26</v>
       </c>
       <c r="G69" t="n">
-        <v>1200</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>조립13호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>13785</v>
+        <v>1664</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>조립15호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PIA_1D 55% YakisobaPan_1T</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>13474</v>
+        <v>11482</v>
       </c>
       <c r="G71" t="n">
-        <v>4700</v>
+        <v>365</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>조립16호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>22776</v>
+        <v>3654</v>
       </c>
       <c r="G72" t="n">
-        <v>1500</v>
+        <v>33</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>조립19호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>22725</v>
+        <v>2150</v>
       </c>
       <c r="G73" t="n">
-        <v>1343</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74">
@@ -3735,19 +3735,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>조립23호기</t>
+          <t>조립10호기</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>T-Garden D_Melty Time_55% UV 14.2</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>18221</v>
+        <v>22001</v>
       </c>
       <c r="G74" t="n">
-        <v>751</v>
+        <v>5911</v>
       </c>
     </row>
     <row r="75">
@@ -3768,19 +3768,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>조립24호기</t>
+          <t>조립11호기</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>10176</v>
+        <v>10323</v>
       </c>
       <c r="G75" t="n">
-        <v>9226</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="76">
@@ -3801,19 +3801,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>조립25호기</t>
+          <t>조립12호기</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>1-Day_iris_Blue Moon</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>23396</v>
+        <v>32288</v>
       </c>
       <c r="G76" t="n">
-        <v>650</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="77">
@@ -3834,19 +3834,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>조립40호기</t>
+          <t>조립13호기</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>14743</v>
+        <v>25070</v>
       </c>
       <c r="G77" t="n">
-        <v>1883</v>
+        <v>900</v>
       </c>
     </row>
     <row r="78">
@@ -3867,19 +3867,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>조립42호기</t>
+          <t>조립14호기</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>28031</v>
+        <v>37642</v>
       </c>
       <c r="G78" t="n">
-        <v>1800</v>
+        <v>7980</v>
       </c>
     </row>
     <row r="79">
@@ -3900,19 +3900,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>조립46호기</t>
+          <t>조립15호기</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Gold_W3</t>
+          <t>HOYA_Casual Ash</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>15205</v>
+        <v>14361</v>
       </c>
       <c r="G79" t="n">
-        <v>1950</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="80">
@@ -3933,19 +3933,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>조립47호기</t>
+          <t>조립16호기</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3610</v>
+        <v>25584</v>
       </c>
       <c r="G80" t="n">
-        <v>3209</v>
+        <v>500</v>
       </c>
     </row>
     <row r="81">
@@ -3966,19 +3966,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>조립48호기</t>
+          <t>조립19호기</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>18206</v>
+        <v>28046</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="82">
@@ -3999,19 +3999,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>조립49호기</t>
+          <t>조립23호기</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Alcon D_Allure Grey_W3C</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>23274</v>
+        <v>15879</v>
       </c>
       <c r="G82" t="n">
-        <v>1635</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="83">
@@ -4032,19 +4032,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>조립50호기</t>
+          <t>조립24호기</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>22868</v>
+        <v>26426</v>
       </c>
       <c r="G83" t="n">
-        <v>6100</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="84">
@@ -4065,19 +4065,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>조립51호기</t>
+          <t>조립25호기</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PIA D_Cream Beige_14.4</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>24255</v>
+        <v>45908</v>
       </c>
       <c r="G84" t="n">
-        <v>3650</v>
+        <v>749</v>
       </c>
     </row>
     <row r="85">
@@ -4098,19 +4098,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>조립53호기</t>
+          <t>조립26호기</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PIA D_Baby Espresso_38% UV</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>16288</v>
+        <v>29367</v>
       </c>
       <c r="G85" t="n">
-        <v>1792</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86">
@@ -4131,19 +4131,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>조립54호기</t>
+          <t>조립27호기</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>28284</v>
+        <v>29251</v>
       </c>
       <c r="G86" t="n">
-        <v>600</v>
+        <v>778</v>
       </c>
     </row>
     <row r="87">
@@ -4164,19 +4164,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>조립55호기</t>
+          <t>조립42호기</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PIA D_Strawberry Quartz_38% UV</t>
+          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>9763</v>
+        <v>27222</v>
       </c>
       <c r="G87" t="n">
-        <v>10429</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="88">
@@ -4197,19 +4197,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>조립56호기</t>
+          <t>조립46호기</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>Alcon D_Jewel Gold_W3</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>9791</v>
+        <v>30635</v>
       </c>
       <c r="G88" t="n">
-        <v>2160</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="89">
@@ -4230,19 +4230,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>조립57호기</t>
+          <t>조립47호기</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>22688</v>
+        <v>31073</v>
       </c>
       <c r="G89" t="n">
-        <v>2730</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="90">
@@ -4258,24 +4258,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립48호기</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>5978</v>
+        <v>18501</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="91">
@@ -4291,24 +4291,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립51호기</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>PIA D_Cream Grege_14.4</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>16547</v>
+        <v>43904</v>
       </c>
       <c r="G91" t="n">
-        <v>1247</v>
+        <v>10776</v>
       </c>
     </row>
     <row r="92">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4329,19 +4329,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>조립52호기</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>24434</v>
+        <v>27510</v>
       </c>
       <c r="G92" t="n">
-        <v>2693</v>
+        <v>500</v>
       </c>
     </row>
     <row r="93">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4362,19 +4362,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>조립54호기</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>20241</v>
+        <v>31794</v>
       </c>
       <c r="G93" t="n">
-        <v>2445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4395,19 +4395,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>조립57호기</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Alcon D_Allure Grey_W3C</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>6381</v>
+        <v>53255</v>
       </c>
       <c r="G94" t="n">
-        <v>919</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="95">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4428,19 +4428,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>조립58호기</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
+          <t>PIA D_Date Topaz_38% UV</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>34918</v>
+        <v>23812</v>
       </c>
       <c r="G95" t="n">
-        <v>2923</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="96">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4461,19 +4461,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>조립59호기</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>16677</v>
+        <v>58685</v>
       </c>
       <c r="G96" t="n">
-        <v>4041</v>
+        <v>682</v>
       </c>
     </row>
     <row r="97">
@@ -4484,29 +4484,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>15149</v>
+        <v>1100</v>
       </c>
       <c r="G97" t="n">
-        <v>2582</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">
@@ -4517,29 +4517,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>19991</v>
+        <v>28153</v>
       </c>
       <c r="G98" t="n">
-        <v>2634</v>
+        <v>7565</v>
       </c>
     </row>
     <row r="99">
@@ -4550,29 +4550,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>PIA_1D 55% YakisobaPan_1T</t>
+          <t>Toric_CP-0.75_Halo Brown</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>14925</v>
+        <v>2675</v>
       </c>
       <c r="G99" t="n">
-        <v>2773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -4583,29 +4583,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>Toric_CP-1.25_Halo Brown</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>20462</v>
+        <v>7983</v>
       </c>
       <c r="G100" t="n">
-        <v>3313</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -4616,29 +4616,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>13485</v>
+        <v>9637</v>
       </c>
       <c r="G101" t="n">
-        <v>1698</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="102">
@@ -4649,29 +4649,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>조립55호기</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Alcon D_Allure Grey_W3C</t>
+          <t>Coffee Jelly_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>9246</v>
+        <v>5859</v>
       </c>
       <c r="G102" t="n">
-        <v>938</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="103">
@@ -4692,19 +4692,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>분리19호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>9421</v>
+        <v>29189</v>
       </c>
       <c r="G103" t="n">
-        <v>1799</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="104">
@@ -4725,19 +4725,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>분리19호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>T-Garden D_Melty Time_55% UV 14.2</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>22820</v>
+        <v>25163</v>
       </c>
       <c r="G104" t="n">
-        <v>3617</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="105">
@@ -4758,19 +4758,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>34677</v>
+        <v>34531</v>
       </c>
       <c r="G105" t="n">
-        <v>3722</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="106">
@@ -4791,19 +4791,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ALICIA BROWN(근시)</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2699</v>
+        <v>3888</v>
       </c>
       <c r="G106" t="n">
-        <v>318</v>
+        <v>519</v>
       </c>
     </row>
     <row r="107">
@@ -4824,19 +4824,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>HOYA_Noble Ash</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>22836</v>
+        <v>7696</v>
       </c>
       <c r="G107" t="n">
-        <v>2539</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="108">
@@ -4857,19 +4857,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>15604</v>
+        <v>22171</v>
       </c>
       <c r="G108" t="n">
-        <v>2595</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="109">
@@ -4890,19 +4890,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA_1D 55% YakisobaPan_1T</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>37363</v>
+        <v>5017</v>
       </c>
       <c r="G109" t="n">
-        <v>2682</v>
+        <v>702</v>
       </c>
     </row>
     <row r="110">
@@ -4923,19 +4923,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ALICIA BROWN(근시)</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>6052</v>
+        <v>20445</v>
       </c>
       <c r="G110" t="n">
-        <v>1143</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="111">
@@ -4956,19 +4956,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>Alcon D_Allure Hazel_W3C</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>23912</v>
+        <v>21023</v>
       </c>
       <c r="G111" t="n">
-        <v>6528</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="112">
@@ -4989,19 +4989,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리19호기</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Lighly Rose Cacao(렌즈타운)</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3962</v>
+        <v>6493</v>
       </c>
       <c r="G112" t="n">
-        <v>566</v>
+        <v>815</v>
       </c>
     </row>
     <row r="113">
@@ -5022,19 +5022,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>12227</v>
+        <v>2872</v>
       </c>
       <c r="G113" t="n">
-        <v>928</v>
+        <v>265</v>
       </c>
     </row>
     <row r="114">
@@ -5055,19 +5055,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>22690</v>
+        <v>13825</v>
       </c>
       <c r="G114" t="n">
-        <v>2058</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="115">
@@ -5088,19 +5088,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>14071</v>
+        <v>18526</v>
       </c>
       <c r="G115" t="n">
-        <v>1804</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="116">
@@ -5121,19 +5121,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>18875</v>
+        <v>14579</v>
       </c>
       <c r="G116" t="n">
-        <v>1984</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="117">
@@ -5154,19 +5154,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>Alcon D_Jewel Gold_W3</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>2929</v>
+        <v>29597</v>
       </c>
       <c r="G117" t="n">
-        <v>302</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="118">
@@ -5187,19 +5187,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>4516</v>
+        <v>18436</v>
       </c>
       <c r="G118" t="n">
-        <v>277</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="119">
@@ -5220,19 +5220,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>34367</v>
+        <v>21929</v>
       </c>
       <c r="G119" t="n">
-        <v>4366</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="120">
@@ -5253,19 +5253,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>51196</v>
+        <v>8557</v>
       </c>
       <c r="G120" t="n">
-        <v>3398</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="121">
@@ -5286,19 +5286,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>PIA D_Baby Espresso_38% UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>15691</v>
+        <v>26959</v>
       </c>
       <c r="G121" t="n">
-        <v>5570</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="122">
@@ -5319,19 +5319,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>PIA D_Cream Beige_14.4</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>2261</v>
+        <v>10294</v>
       </c>
       <c r="G122" t="n">
-        <v>374</v>
+        <v>788</v>
       </c>
     </row>
     <row r="123">
@@ -5352,19 +5352,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>PIA D_Pearl Cats Eye_38% UV</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>19054</v>
+        <v>23158</v>
       </c>
       <c r="G123" t="n">
-        <v>2820</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="124">
@@ -5385,19 +5385,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>19090</v>
+        <v>5836</v>
       </c>
       <c r="G124" t="n">
-        <v>1433</v>
+        <v>760</v>
       </c>
     </row>
     <row r="125">
@@ -5418,19 +5418,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>25228</v>
+        <v>7826</v>
       </c>
       <c r="G125" t="n">
-        <v>2766</v>
+        <v>905</v>
       </c>
     </row>
     <row r="126">
@@ -5451,19 +5451,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>12450</v>
+        <v>5691</v>
       </c>
       <c r="G126" t="n">
-        <v>1713</v>
+        <v>471</v>
       </c>
     </row>
     <row r="127">
@@ -5484,19 +5484,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>PIA D_Baby Espresso_38% UV</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>20585</v>
+        <v>5736</v>
       </c>
       <c r="G127" t="n">
-        <v>3034</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="128">
@@ -5517,19 +5517,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>T-Garden D_Melty Time_55% UV 14.2</t>
+          <t>PIA D_Cream Beige_14.4</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>5695</v>
+        <v>21389</v>
       </c>
       <c r="G128" t="n">
-        <v>1021</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="129">
@@ -5550,19 +5550,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Cream Grege_14.4</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>28618</v>
+        <v>6258</v>
       </c>
       <c r="G129" t="n">
-        <v>2050</v>
+        <v>599</v>
       </c>
     </row>
     <row r="130">
@@ -5578,24 +5578,24 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>PIA D_Date Topaz_38% UV</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>8441</v>
+        <v>7379</v>
       </c>
       <c r="G130" t="n">
-        <v>1991</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="131">
@@ -5611,24 +5611,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>ANW D_Art Gray_Dopewink 38%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>11073</v>
+        <v>6734</v>
       </c>
       <c r="G131" t="n">
-        <v>1970</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="132">
@@ -5644,24 +5644,24 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>ANW D_Spicy Gray_Dopewink 38%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>15955</v>
+        <v>6783</v>
       </c>
       <c r="G132" t="n">
-        <v>2681</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="133">
@@ -5677,24 +5677,24 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>분리22호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Strawberry Quartz_38% UV</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>37631</v>
+        <v>16501</v>
       </c>
       <c r="G133" t="n">
-        <v>7876</v>
+        <v>3918</v>
       </c>
     </row>
     <row r="134">
@@ -5710,24 +5710,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>분리23호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>36020</v>
+        <v>41485</v>
       </c>
       <c r="G134" t="n">
-        <v>6721</v>
+        <v>7727</v>
       </c>
     </row>
     <row r="135">
@@ -5743,24 +5743,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>분리25호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>36735</v>
+        <v>10080</v>
       </c>
       <c r="G135" t="n">
-        <v>9490</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="136">
@@ -5776,24 +5776,24 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>38389</v>
+        <v>20799</v>
       </c>
       <c r="G136" t="n">
-        <v>11356</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="137">
@@ -5809,24 +5809,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>분리43호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>37134</v>
+        <v>40550</v>
       </c>
       <c r="G137" t="n">
-        <v>7519</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="138">
@@ -5842,24 +5842,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Brown Bunny_PIA_M(Y)</t>
+          <t>PIA_Date topaz CP-0.75 Toric_UV</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1055</v>
+        <v>5876</v>
       </c>
       <c r="G138" t="n">
-        <v>1155</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="139">
@@ -5875,24 +5875,24 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Brulee Pearl_PIA_M(Y)</t>
+          <t>PIA_Date topaz CP-1.25 Toric_UV</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>3674</v>
+        <v>3077</v>
       </c>
       <c r="G139" t="n">
-        <v>733</v>
+        <v>347</v>
       </c>
     </row>
     <row r="140">
@@ -5908,24 +5908,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
+          <t>Toric_CP-1.25_Halo Brown</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>7651</v>
+        <v>5417</v>
       </c>
       <c r="G140" t="n">
-        <v>3941</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="141">
@@ -5941,24 +5941,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Dollish Gray_PIA_M</t>
+          <t>Toric_CP-1.25_Halo Gray</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1672</v>
+        <v>437</v>
       </c>
       <c r="G141" t="n">
-        <v>380</v>
+        <v>82</v>
       </c>
     </row>
     <row r="142">
@@ -5974,24 +5974,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Dollish Gray_PIA_M(Y)</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>773</v>
+        <v>12362</v>
       </c>
       <c r="G142" t="n">
-        <v>895</v>
+        <v>4370</v>
       </c>
     </row>
     <row r="143">
@@ -6007,24 +6007,24 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Lady Black_PIA_M_(중)_14.5</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>2191</v>
+        <v>2353</v>
       </c>
       <c r="G143" t="n">
-        <v>101</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="144">
@@ -6040,24 +6040,24 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Skin Grege_(신규)PIA_M_14.5(Y)</t>
+          <t>Toric_CP-0.75_Halo Gray</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1149</v>
+        <v>7792</v>
       </c>
       <c r="G144" t="n">
-        <v>1213</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="145">
@@ -6073,24 +6073,24 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>water water_(신규)PIA_M(Y)</t>
+          <t>Toric_CP-1.25_Halo Brown</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>481</v>
+        <v>12301</v>
       </c>
       <c r="G145" t="n">
-        <v>317</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="146">
@@ -6101,29 +6101,29 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>Toric_CP-1.25_Halo Gray</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>10355</v>
+        <v>3583</v>
       </c>
       <c r="G146" t="n">
-        <v>175</v>
+        <v>784</v>
       </c>
     </row>
     <row r="147">
@@ -6134,29 +6134,29 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>5800</v>
+        <v>5651</v>
       </c>
       <c r="G147" t="n">
-        <v>90</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="148">
@@ -6167,29 +6167,29 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1962</v>
+        <v>3113</v>
       </c>
       <c r="G148" t="n">
-        <v>568</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="149">
@@ -6200,29 +6200,29 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>Toric_CP-0.75_Halo Brown</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>5050</v>
+        <v>2943</v>
       </c>
       <c r="G149" t="n">
-        <v>520</v>
+        <v>239</v>
       </c>
     </row>
     <row r="150">
@@ -6233,29 +6233,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>Toric_CP-1.25_Halo Brown</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>5550</v>
+        <v>2207</v>
       </c>
       <c r="G150" t="n">
-        <v>130</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="151">
@@ -6266,29 +6266,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>8748</v>
+        <v>945</v>
       </c>
       <c r="G151" t="n">
-        <v>722</v>
+        <v>602</v>
       </c>
     </row>
     <row r="152">
@@ -6299,29 +6299,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>6125</v>
+        <v>865</v>
       </c>
       <c r="G152" t="n">
-        <v>120</v>
+        <v>346</v>
       </c>
     </row>
     <row r="153">
@@ -6332,29 +6332,29 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리22호기</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>8870</v>
+        <v>35810</v>
       </c>
       <c r="G153" t="n">
-        <v>125</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="154">
@@ -6365,29 +6365,29 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리23호기</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>6940</v>
+        <v>34893</v>
       </c>
       <c r="G154" t="n">
-        <v>300</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="155">
@@ -6398,29 +6398,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리25호기</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>2543</v>
+        <v>42297</v>
       </c>
       <c r="G155" t="n">
-        <v>822</v>
+        <v>8448</v>
       </c>
     </row>
     <row r="156">
@@ -6431,29 +6431,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>분리43호기</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>5985</v>
+        <v>30121</v>
       </c>
       <c r="G156" t="n">
-        <v>80</v>
+        <v>8652</v>
       </c>
     </row>
     <row r="157">
@@ -6474,19 +6474,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사30호기</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>4065</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="158">
@@ -6507,19 +6507,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사30호기</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>PIA_TAMA KONNYAKU_55%</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>2986</v>
+        <v>1660</v>
       </c>
       <c r="G158" t="n">
-        <v>624</v>
+        <v>80</v>
       </c>
     </row>
     <row r="159">
@@ -6540,19 +6540,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사31호기</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>3020</v>
+        <v>6505</v>
       </c>
       <c r="G159" t="n">
-        <v>35</v>
+        <v>335</v>
       </c>
     </row>
     <row r="160">
@@ -6573,19 +6573,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사31호기</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA_TAMA KONNYAKU_55%</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>5607</v>
+        <v>2525</v>
       </c>
       <c r="G160" t="n">
-        <v>703</v>
+        <v>80</v>
       </c>
     </row>
     <row r="161">
@@ -6606,19 +6606,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>5910</v>
+        <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -6639,19 +6639,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>ALICIA BROWN(근시)</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>3465</v>
+        <v>4895</v>
       </c>
       <c r="G162" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="163">
@@ -6672,19 +6672,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>BELLA D_MARS 55%</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>15130</v>
+        <v>1845</v>
       </c>
       <c r="G163" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
     </row>
     <row r="164">
@@ -6705,19 +6705,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Beige 14.2_55% UV</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>2970</v>
+        <v>8630</v>
       </c>
       <c r="G164" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
     </row>
     <row r="165">
@@ -6738,19 +6738,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Lighly Rose Rose(렌즈타운)</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>13946</v>
+        <v>3775</v>
       </c>
       <c r="G165" t="n">
-        <v>1519</v>
+        <v>45</v>
       </c>
     </row>
     <row r="166">
@@ -6771,19 +6771,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>47416</v>
+        <v>1895</v>
       </c>
       <c r="G166" t="n">
-        <v>2319</v>
+        <v>20</v>
       </c>
     </row>
     <row r="167">
@@ -6804,19 +6804,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA_1D 55% YakisobaPan_1T</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>4793</v>
+        <v>1422</v>
       </c>
       <c r="G167" t="n">
-        <v>1102</v>
+        <v>523</v>
       </c>
     </row>
     <row r="168">
@@ -6837,19 +6837,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>48260</v>
+        <v>3582</v>
       </c>
       <c r="G168" t="n">
-        <v>2640</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="169">
@@ -6870,19 +6870,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>8527</v>
+        <v>820</v>
       </c>
       <c r="G169" t="n">
-        <v>1933</v>
+        <v>20</v>
       </c>
     </row>
     <row r="170">
@@ -6903,19 +6903,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>PIA D_Air Gray_55% UV</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>3985</v>
+        <v>8170</v>
       </c>
       <c r="G170" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
     </row>
     <row r="171">
@@ -6936,19 +6936,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA_TAMA KONNYAKU_55%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>13907</v>
+        <v>1260</v>
       </c>
       <c r="G171" t="n">
-        <v>1043</v>
+        <v>60</v>
       </c>
     </row>
     <row r="172">
@@ -6969,19 +6969,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>14350</v>
+        <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>855</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -7002,19 +7002,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3405</v>
+        <v>2675</v>
       </c>
       <c r="G173" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="174">
@@ -7035,19 +7035,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3020</v>
+        <v>28265</v>
       </c>
       <c r="G174" t="n">
-        <v>100</v>
+        <v>785</v>
       </c>
     </row>
     <row r="175">
@@ -7068,19 +7068,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>7125</v>
+        <v>4993</v>
       </c>
       <c r="G175" t="n">
-        <v>110</v>
+        <v>507</v>
       </c>
     </row>
     <row r="176">
@@ -7101,19 +7101,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>582</v>
+        <v>5515</v>
       </c>
       <c r="G176" t="n">
-        <v>313</v>
+        <v>100</v>
       </c>
     </row>
     <row r="177">
@@ -7134,19 +7134,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>5450</v>
+        <v>3365</v>
       </c>
       <c r="G177" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="178">
@@ -7167,19 +7167,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>3230</v>
+        <v>1815</v>
       </c>
       <c r="G178" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
     </row>
     <row r="179">
@@ -7200,19 +7200,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>(NEW)ALICIA BROWN(근시)</t>
+          <t>PIA_TAMA KONNYAKU_55%</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>10347</v>
+        <v>2535</v>
       </c>
       <c r="G179" t="n">
-        <v>1003</v>
+        <v>80</v>
       </c>
     </row>
     <row r="180">
@@ -7233,19 +7233,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>14915</v>
+        <v>59707</v>
       </c>
       <c r="G180" t="n">
-        <v>175</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="181">
@@ -7266,19 +7266,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>PIA D_Coco Truffle_38% UV</t>
+          <t>ALICIA BROWN(근시)</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1415</v>
+        <v>13655</v>
       </c>
       <c r="G181" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
     </row>
     <row r="182">
@@ -7299,19 +7299,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>PIA D_Honey Soda_38% UV</t>
+          <t>Alcon D_Allure Grey_W3C(APAC)</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>14805</v>
+        <v>2285</v>
       </c>
       <c r="G182" t="n">
-        <v>435</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="183">
@@ -7332,19 +7332,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>Alcon D_Allure Grey_W3C(KR)</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>12894</v>
+        <v>18765</v>
       </c>
       <c r="G183" t="n">
-        <v>351</v>
+        <v>220</v>
       </c>
     </row>
     <row r="184">
@@ -7365,19 +7365,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>Alcon D_Allure Hazel_W3C(KR)</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>13673</v>
+        <v>3080</v>
       </c>
       <c r="G184" t="n">
-        <v>382</v>
+        <v>45</v>
       </c>
     </row>
     <row r="185">
@@ -7398,19 +7398,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>6460</v>
+        <v>2290</v>
       </c>
       <c r="G185" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="186">
@@ -7431,19 +7431,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>PIA D_Moon Melt Brown_55%_14.5 UV</t>
+          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>3020</v>
+        <v>3765</v>
       </c>
       <c r="G186" t="n">
-        <v>65</v>
+        <v>375</v>
       </c>
     </row>
     <row r="187">
@@ -7464,19 +7464,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>5420</v>
+        <v>1970</v>
       </c>
       <c r="G187" t="n">
-        <v>110</v>
+        <v>35</v>
       </c>
     </row>
     <row r="188">
@@ -7497,19 +7497,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>603</v>
+        <v>2500</v>
       </c>
       <c r="G188" t="n">
-        <v>242</v>
+        <v>30</v>
       </c>
     </row>
     <row r="189">
@@ -7530,19 +7530,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>5215</v>
+        <v>54019</v>
       </c>
       <c r="G189" t="n">
-        <v>65</v>
+        <v>4576</v>
       </c>
     </row>
     <row r="190">
@@ -7563,19 +7563,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>PIA D_Baby Espresso_38% UV</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>3285</v>
+        <v>29268</v>
       </c>
       <c r="G190" t="n">
-        <v>55</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="191">
@@ -7596,19 +7596,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>BELLA D_MARS 55%</t>
+          <t>PIA D_Cream Beige_14.4</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>5080</v>
+        <v>19042</v>
       </c>
       <c r="G191" t="n">
-        <v>115</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="192">
@@ -7629,19 +7629,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>HOYA_Ruby brown(Maquia Brown)</t>
+          <t>PIA D_Pearl Cats Eye_38% UV</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1286</v>
+        <v>3470</v>
       </c>
       <c r="G192" t="n">
-        <v>214</v>
+        <v>105</v>
       </c>
     </row>
     <row r="193">
@@ -7662,19 +7662,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>12295</v>
+        <v>2265</v>
       </c>
       <c r="G193" t="n">
-        <v>565</v>
+        <v>30</v>
       </c>
     </row>
     <row r="194">
@@ -7695,19 +7695,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>13005</v>
+        <v>1865</v>
       </c>
       <c r="G194" t="n">
-        <v>425</v>
+        <v>15</v>
       </c>
     </row>
     <row r="195">
@@ -7728,19 +7728,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>3310</v>
+        <v>10990</v>
       </c>
       <c r="G195" t="n">
-        <v>55</v>
+        <v>175</v>
       </c>
     </row>
     <row r="196">
@@ -7761,19 +7761,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>3215</v>
+        <v>5985</v>
       </c>
       <c r="G196" t="n">
-        <v>60</v>
+        <v>535</v>
       </c>
     </row>
     <row r="197">
@@ -7794,19 +7794,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1065</v>
+        <v>6275</v>
       </c>
       <c r="G197" t="n">
-        <v>15</v>
+        <v>585</v>
       </c>
     </row>
     <row r="198">
@@ -7827,19 +7827,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>PIA_1D 55% YakisobaPan_1T</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>4895</v>
+        <v>3330</v>
       </c>
       <c r="G198" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
     </row>
     <row r="199">
@@ -7860,19 +7860,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>2875</v>
+        <v>10990</v>
       </c>
       <c r="G199" t="n">
-        <v>15</v>
+        <v>125</v>
       </c>
     </row>
     <row r="200">
@@ -7893,19 +7893,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>PIA_1D 55% YakisobaPan_1T</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>2955</v>
+        <v>4408</v>
       </c>
       <c r="G200" t="n">
-        <v>55</v>
+        <v>232</v>
       </c>
     </row>
     <row r="201">
@@ -7926,19 +7926,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3675</v>
+        <v>10495</v>
       </c>
       <c r="G201" t="n">
-        <v>70</v>
+        <v>125</v>
       </c>
     </row>
     <row r="202">
@@ -7959,19 +7959,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>800</v>
+        <v>1485</v>
       </c>
       <c r="G202" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="203">
@@ -7992,19 +7992,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>PIA D_Air Gray_55% UV</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>4010</v>
+        <v>4210</v>
       </c>
       <c r="G203" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
     </row>
     <row r="204">
@@ -8025,19 +8025,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>PIA D_Baby Espresso_38% UV</t>
+          <t>(NEW)ALICIA BROWN(근시)</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>26649</v>
+        <v>1595</v>
       </c>
       <c r="G204" t="n">
-        <v>966</v>
+        <v>45</v>
       </c>
     </row>
     <row r="205">
@@ -8058,19 +8058,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>PIA D_Cream Beige_14.4</t>
+          <t>Lighly Rose Cacao(렌즈타운)</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>8135</v>
+        <v>4430</v>
       </c>
       <c r="G205" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
     </row>
     <row r="206">
@@ -8091,19 +8091,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>PIA D_Pearl Cats Eye_38% UV</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>2450</v>
+        <v>415</v>
       </c>
       <c r="G206" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="207">
@@ -8124,19 +8124,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>4930</v>
+        <v>3805</v>
       </c>
       <c r="G207" t="n">
-        <v>1030</v>
+        <v>290</v>
       </c>
     </row>
     <row r="208">
@@ -8157,19 +8157,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>2235</v>
+        <v>14260</v>
       </c>
       <c r="G208" t="n">
-        <v>70</v>
+        <v>690</v>
       </c>
     </row>
     <row r="209">
@@ -8190,19 +8190,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>2600</v>
+        <v>19665</v>
       </c>
       <c r="G209" t="n">
-        <v>30</v>
+        <v>250</v>
       </c>
     </row>
     <row r="210">
@@ -8223,19 +8223,19 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>3605</v>
+        <v>2530</v>
       </c>
       <c r="G210" t="n">
-        <v>55</v>
+        <v>105</v>
       </c>
     </row>
     <row r="211">
@@ -8256,19 +8256,19 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>7827</v>
+        <v>9770</v>
       </c>
       <c r="G211" t="n">
-        <v>1183</v>
+        <v>135</v>
       </c>
     </row>
     <row r="212">
@@ -8294,14 +8294,14 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>PIA_1D 55% YakisobaPan_1T</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>5490</v>
+        <v>12470</v>
       </c>
       <c r="G212" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
     </row>
     <row r="213">
@@ -8327,14 +8327,14 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>4545</v>
+        <v>2950</v>
       </c>
       <c r="G213" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
     </row>
     <row r="214">
@@ -8360,14 +8360,14 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>Alcon D_Jewel Gold_W3(KR)</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>9570</v>
+        <v>5700</v>
       </c>
       <c r="G214" t="n">
-        <v>210</v>
+        <v>105</v>
       </c>
     </row>
     <row r="215">
@@ -8393,11 +8393,11 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>PIA D_Air Gray_55% UV</t>
+          <t>1-Day_iris_JazzBlack</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>4095</v>
+        <v>4040</v>
       </c>
       <c r="G215" t="n">
         <v>25</v>
@@ -8426,14 +8426,14 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>1-Day_iris_Rhapsody</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>2925</v>
+        <v>35726</v>
       </c>
       <c r="G216" t="n">
-        <v>50</v>
+        <v>644</v>
       </c>
     </row>
     <row r="217">
@@ -8459,14 +8459,14 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>12189</v>
+        <v>12910</v>
       </c>
       <c r="G217" t="n">
-        <v>1306</v>
+        <v>240</v>
       </c>
     </row>
     <row r="218">
@@ -8492,14 +8492,14 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>8285</v>
+        <v>5570</v>
       </c>
       <c r="G218" t="n">
-        <v>55</v>
+        <v>350</v>
       </c>
     </row>
     <row r="219">
@@ -8520,19 +8520,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1015</v>
+        <v>13125</v>
       </c>
       <c r="G219" t="n">
-        <v>10</v>
+        <v>885</v>
       </c>
     </row>
     <row r="220">
@@ -8553,19 +8553,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>PIA_BROWN MANEGE</t>
+          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>3155</v>
+        <v>19155</v>
       </c>
       <c r="G220" t="n">
-        <v>35</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="221">
@@ -8586,19 +8586,19 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>9635</v>
+        <v>23652</v>
       </c>
       <c r="G221" t="n">
-        <v>140</v>
+        <v>3668</v>
       </c>
     </row>
     <row r="222">
@@ -8619,19 +8619,19 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
         </is>
       </c>
       <c r="F222" t="n">
-        <v>1115</v>
+        <v>24040</v>
       </c>
       <c r="G222" t="n">
-        <v>15</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="223">
@@ -8652,19 +8652,19 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>Alcon D_Chic Caramel_W4(KR)</t>
         </is>
       </c>
       <c r="F223" t="n">
-        <v>14308</v>
+        <v>5115</v>
       </c>
       <c r="G223" t="n">
-        <v>587</v>
+        <v>90</v>
       </c>
     </row>
     <row r="224">
@@ -8685,19 +8685,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>Alcon D_Chic Smoke_W4(KR)</t>
         </is>
       </c>
       <c r="F224" t="n">
-        <v>2640</v>
+        <v>2375</v>
       </c>
       <c r="G224" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="225">
@@ -8718,19 +8718,19 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>PIA D_Air Gray_55% UV</t>
+          <t>Alcon D_Jewel Black_W3(KR)</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>11855</v>
+        <v>940</v>
       </c>
       <c r="G225" t="n">
-        <v>175</v>
+        <v>30</v>
       </c>
     </row>
     <row r="226">
@@ -8751,19 +8751,19 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>Alcon D_Jewel Gold_W3(KR)</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>1900</v>
+        <v>5680</v>
       </c>
       <c r="G226" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
     </row>
     <row r="227">
@@ -8784,19 +8784,19 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>Coastal_JazzBlack(신형리드지)</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>7130</v>
+        <v>1355</v>
       </c>
       <c r="G227" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
     </row>
     <row r="228">
@@ -8817,16 +8817,16 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>Coastal_SoulBrown(신형리드지)</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>3240</v>
+        <v>2920</v>
       </c>
       <c r="G228" t="n">
         <v>40</v>
@@ -8850,19 +8850,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>3180</v>
+        <v>1174</v>
       </c>
       <c r="G229" t="n">
-        <v>75</v>
+        <v>151</v>
       </c>
     </row>
     <row r="230">
@@ -8883,19 +8883,19 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>T-Garden D_Melty Time_55% UV 14.2</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>21365</v>
+        <v>3120</v>
       </c>
       <c r="G230" t="n">
-        <v>195</v>
+        <v>55</v>
       </c>
     </row>
     <row r="231">
@@ -8916,19 +8916,19 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F231" t="n">
-        <v>4961</v>
+        <v>2960</v>
       </c>
       <c r="G231" t="n">
-        <v>724</v>
+        <v>25</v>
       </c>
     </row>
     <row r="232">
@@ -8949,19 +8949,19 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>PIA D_Air Gray_55% UV</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F232" t="n">
-        <v>4025</v>
+        <v>8045</v>
       </c>
       <c r="G232" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
     </row>
     <row r="233">
@@ -8982,19 +8982,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA D_Sakura Mousse_55% UV</t>
         </is>
       </c>
       <c r="F233" t="n">
-        <v>7910</v>
+        <v>1770</v>
       </c>
       <c r="G233" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="234">
@@ -9015,19 +9015,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA_1D 55% YakisobaPan_1T</t>
         </is>
       </c>
       <c r="F234" t="n">
-        <v>5675</v>
+        <v>6195</v>
       </c>
       <c r="G234" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
     </row>
     <row r="235">
@@ -9048,19 +9048,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F235" t="n">
-        <v>2340</v>
+        <v>3300</v>
       </c>
       <c r="G235" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
     </row>
     <row r="236">
@@ -9081,16 +9081,16 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>535</v>
+        <v>1235</v>
       </c>
       <c r="G236" t="n">
         <v>10</v>
@@ -9114,19 +9114,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>3215</v>
+        <v>1580</v>
       </c>
       <c r="G237" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="238">
@@ -9142,24 +9142,24 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>T-Garden D_Melty Time_55% UV 14.2</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F238" t="n">
-        <v>15545</v>
+        <v>4060</v>
       </c>
       <c r="G238" t="n">
-        <v>145</v>
+        <v>30</v>
       </c>
     </row>
     <row r="239">
@@ -9175,24 +9175,24 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
+          <t>Toric_CP-0.75_Halo Gray</t>
         </is>
       </c>
       <c r="F239" t="n">
-        <v>8846</v>
+        <v>3607</v>
       </c>
       <c r="G239" t="n">
-        <v>1624</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="240">
@@ -9208,24 +9208,24 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>(NEW)ALICIA BROWN(근시)</t>
+          <t>Toric_CP-1.25_Halo Gray</t>
         </is>
       </c>
       <c r="F240" t="n">
-        <v>2460</v>
+        <v>5165</v>
       </c>
       <c r="G240" t="n">
-        <v>15</v>
+        <v>85</v>
       </c>
     </row>
     <row r="241">
@@ -9241,24 +9241,24 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>ADRIA_Blue_1-Day</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F241" t="n">
-        <v>540</v>
+        <v>2475</v>
       </c>
       <c r="G241" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="242">
@@ -9274,24 +9274,24 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>ADRIA_Pearl_1-Day</t>
+          <t>Toric_CP-0.75_Halo Brown</t>
         </is>
       </c>
       <c r="F242" t="n">
-        <v>720</v>
+        <v>2860</v>
       </c>
       <c r="G242" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="243">
@@ -9307,24 +9307,24 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>Toric_CP-1.25_Halo Brown</t>
         </is>
       </c>
       <c r="F243" t="n">
-        <v>3865</v>
+        <v>5615</v>
       </c>
       <c r="G243" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
     </row>
     <row r="244">
@@ -9340,24 +9340,24 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
       <c r="F244" t="n">
-        <v>8205</v>
+        <v>7094</v>
       </c>
       <c r="G244" t="n">
-        <v>140</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="245">
@@ -9373,24 +9373,24 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>PIA_Sheer Brown_55%_1-DAY</t>
+          <t>Toric_CP-1.25_Halo Brown</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>9820</v>
+        <v>12540</v>
       </c>
       <c r="G245" t="n">
-        <v>295</v>
+        <v>190</v>
       </c>
     </row>
     <row r="246">
@@ -9406,24 +9406,24 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
       <c r="F246" t="n">
-        <v>13220</v>
+        <v>11755</v>
       </c>
       <c r="G246" t="n">
-        <v>200</v>
+        <v>145</v>
       </c>
     </row>
     <row r="247">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -9449,14 +9449,14 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA_Date topaz CP-0.75 Toric_UV</t>
         </is>
       </c>
       <c r="F247" t="n">
-        <v>10413</v>
+        <v>14727</v>
       </c>
       <c r="G247" t="n">
-        <v>367</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="248">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -9482,14 +9482,14 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>PIA D_Dark Peony_55% UV</t>
+          <t>PIA_Date topaz CP-1.25 Toric_UV</t>
         </is>
       </c>
       <c r="F248" t="n">
-        <v>5598</v>
+        <v>9065</v>
       </c>
       <c r="G248" t="n">
-        <v>542</v>
+        <v>60</v>
       </c>
     </row>
     <row r="249">
@@ -9505,24 +9505,24 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>1010</v>
+        <v>54778</v>
       </c>
       <c r="G249" t="n">
-        <v>20</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="250">
@@ -9538,24 +9538,24 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>PIA D_Twinkle Brown_55%_14.5 UV</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3010</v>
+        <v>20430</v>
       </c>
       <c r="G250" t="n">
-        <v>40</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="251">
@@ -9571,24 +9571,24 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>1-DAY_58_공용_MD로고</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3190</v>
+        <v>10290</v>
       </c>
       <c r="G251" t="n">
-        <v>75</v>
+        <v>300</v>
       </c>
     </row>
     <row r="252">
@@ -9604,24 +9604,24 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>1-Day_Contakt(유효기간_8년)</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>17270</v>
+        <v>16028</v>
       </c>
       <c r="G252" t="n">
-        <v>310</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="253">
@@ -9637,24 +9637,24 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>1-Day_SOLEKO(5년)</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>2310</v>
+        <v>18220</v>
       </c>
       <c r="G253" t="n">
-        <v>30</v>
+        <v>320</v>
       </c>
     </row>
     <row r="254">
@@ -9670,24 +9670,24 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>9845</v>
+        <v>20088</v>
       </c>
       <c r="G254" t="n">
-        <v>200</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="255">
@@ -9703,24 +9703,24 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>25040</v>
+        <v>17392</v>
       </c>
       <c r="G255" t="n">
-        <v>280</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="256">
@@ -9736,24 +9736,24 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>1-Day_Metha_Coastal</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>3000</v>
+        <v>11805</v>
       </c>
       <c r="G256" t="n">
-        <v>35</v>
+        <v>265</v>
       </c>
     </row>
     <row r="257">
@@ -9769,90 +9769,90 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>Metha_Daily</t>
         </is>
       </c>
       <c r="F257" t="n">
-        <v>8565</v>
+        <v>4425</v>
       </c>
       <c r="G257" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F258" t="n">
-        <v>6651</v>
+        <v>18407</v>
       </c>
       <c r="G258" t="n">
-        <v>639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>B형 조립중합4호기</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>1-DAY58_Micure</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F259" t="n">
-        <v>23135</v>
+        <v>30689</v>
       </c>
       <c r="G259" t="n">
-        <v>2825</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="260">
@@ -9868,21 +9868,21 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>A형 인라인6호기</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F260" t="n">
-        <v>18736</v>
+        <v>16403</v>
       </c>
       <c r="G260" t="n">
         <v>0</v>
@@ -9901,24 +9901,24 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>B형 조립중합4호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F261" t="n">
-        <v>14311</v>
+        <v>42426</v>
       </c>
       <c r="G261" t="n">
-        <v>872</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -9934,24 +9934,24 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>B형 조립중합5호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F262" t="n">
-        <v>14411</v>
+        <v>40565</v>
       </c>
       <c r="G262" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -9981,7 +9981,7 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>46701</v>
+        <v>24193</v>
       </c>
       <c r="G263" t="n">
         <v>0</v>
@@ -9995,29 +9995,29 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>B형 분리수화접착6호기</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F264" t="n">
-        <v>38383</v>
+        <v>17394</v>
       </c>
       <c r="G264" t="n">
-        <v>0</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="265">
@@ -10028,29 +10028,29 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>O2O2 D_Ash Brown EX</t>
         </is>
       </c>
       <c r="F265" t="n">
-        <v>27460</v>
+        <v>17192</v>
       </c>
       <c r="G265" t="n">
-        <v>0</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="266">
@@ -10066,24 +10066,24 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>CAM분리2호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F266" t="n">
-        <v>1660</v>
+        <v>11251</v>
       </c>
       <c r="G266" t="n">
-        <v>485</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="267">
@@ -10099,24 +10099,24 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>CAM분리3호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>O2O2 D_Ash Brown EX</t>
         </is>
       </c>
       <c r="F267" t="n">
-        <v>11624</v>
+        <v>1601</v>
       </c>
       <c r="G267" t="n">
-        <v>3069</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="268">
@@ -10132,24 +10132,24 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>B형 분리수화접착3호기</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>1669</v>
+        <v>7494</v>
       </c>
       <c r="G268" t="n">
-        <v>541</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="269">
@@ -10165,24 +10165,24 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>B형 분리수화접착4호기</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>573</v>
+        <v>1937</v>
       </c>
       <c r="G269" t="n">
-        <v>264</v>
+        <v>135</v>
       </c>
     </row>
     <row r="270">
@@ -10198,24 +10198,24 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>B형 분리수화접착6호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>11164</v>
+        <v>14248</v>
       </c>
       <c r="G270" t="n">
-        <v>2106</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="271">
@@ -10231,24 +10231,24 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>B형 분리수화접착6호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>669</v>
+        <v>14632</v>
       </c>
       <c r="G271" t="n">
-        <v>175</v>
+        <v>822</v>
       </c>
     </row>
     <row r="272">
@@ -10264,24 +10264,24 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>609</v>
+        <v>17208</v>
       </c>
       <c r="G272" t="n">
-        <v>86</v>
+        <v>336</v>
       </c>
     </row>
     <row r="273">
@@ -10297,24 +10297,24 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>B형 분리수화접착3호기</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Brown EX</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F273" t="n">
-        <v>5421</v>
+        <v>16209</v>
       </c>
       <c r="G273" t="n">
-        <v>1613</v>
+        <v>3707</v>
       </c>
     </row>
     <row r="274">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착4호기</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -10344,10 +10344,10 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>24100</v>
+        <v>22153</v>
       </c>
       <c r="G274" t="n">
-        <v>1400</v>
+        <v>3649</v>
       </c>
     </row>
     <row r="275">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -10377,10 +10377,10 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>32734</v>
+        <v>9588</v>
       </c>
       <c r="G275" t="n">
-        <v>1078</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="276">
@@ -10391,29 +10391,29 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>JEWEL MOON D_Cherry Moon</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>13837</v>
+        <v>2391</v>
       </c>
       <c r="G276" t="n">
-        <v>1276</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="277">
@@ -10424,29 +10424,29 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>O2O2 Spherical(DK70)_K2-SMD</t>
+          <t>JEWEL MOON D_Cherry Moon</t>
         </is>
       </c>
       <c r="F277" t="n">
-        <v>1739</v>
+        <v>3720</v>
       </c>
       <c r="G277" t="n">
-        <v>413</v>
+        <v>739</v>
       </c>
     </row>
     <row r="278">
@@ -10457,29 +10457,29 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>JEWEL MOON D_Creamy Moon</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>9936</v>
+        <v>2637</v>
       </c>
       <c r="G278" t="n">
-        <v>2251</v>
+        <v>983</v>
       </c>
     </row>
     <row r="279">
@@ -10490,29 +10490,29 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>JEWEL MOON D_Ice gray Moon</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>25429</v>
+        <v>456</v>
       </c>
       <c r="G279" t="n">
-        <v>4756</v>
+        <v>974</v>
       </c>
     </row>
     <row r="280">
@@ -10523,29 +10523,29 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen oneday A(O2 Edition)</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>19209</v>
+        <v>33183</v>
       </c>
       <c r="G280" t="n">
-        <v>2133</v>
+        <v>869</v>
       </c>
     </row>
     <row r="281">
@@ -10556,29 +10556,29 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>B형 분리수화접착6호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>O2O2 D_Ash Brown EX</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>2492</v>
+        <v>10592</v>
       </c>
       <c r="G281" t="n">
-        <v>311</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="282">
@@ -10589,29 +10589,29 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Si_1-Day_Toric</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>O2O2 D_UV_Toric_SMD</t>
+          <t>O2O2 D_Ash Gray EX</t>
         </is>
       </c>
       <c r="F282" t="n">
-        <v>145</v>
+        <v>2543</v>
       </c>
       <c r="G282" t="n">
-        <v>407</v>
+        <v>4255</v>
       </c>
     </row>
     <row r="283">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -10637,14 +10637,14 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Cherry Moon</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F283" t="n">
-        <v>3200</v>
+        <v>36105</v>
       </c>
       <c r="G283" t="n">
-        <v>406</v>
+        <v>962</v>
       </c>
     </row>
     <row r="284">
@@ -10660,24 +10660,24 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Cherry Moon</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F284" t="n">
-        <v>356</v>
+        <v>3962</v>
       </c>
       <c r="G284" t="n">
-        <v>2614</v>
+        <v>301</v>
       </c>
     </row>
     <row r="285">
@@ -10693,24 +10693,24 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Clalen oneday A(O2 Edition)</t>
+          <t>Clalen O2O2 D_Mute Brown_45%</t>
         </is>
       </c>
       <c r="F285" t="n">
-        <v>21634</v>
+        <v>2480</v>
       </c>
       <c r="G285" t="n">
-        <v>4552</v>
+        <v>78</v>
       </c>
     </row>
     <row r="286">
@@ -10726,24 +10726,24 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2_Multifocal_K2_SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
       <c r="F286" t="n">
-        <v>1660</v>
+        <v>482</v>
       </c>
       <c r="G286" t="n">
-        <v>43</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="287">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -10769,14 +10769,14 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
       <c r="F287" t="n">
-        <v>970</v>
+        <v>25685</v>
       </c>
       <c r="G287" t="n">
-        <v>26</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="288">
@@ -10792,24 +10792,24 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
       <c r="F288" t="n">
-        <v>4300</v>
+        <v>41226</v>
       </c>
       <c r="G288" t="n">
-        <v>203</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="289">
@@ -10825,24 +10825,24 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Gray EX</t>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
       <c r="F289" t="n">
-        <v>3340</v>
+        <v>16490</v>
       </c>
       <c r="G289" t="n">
-        <v>246</v>
+        <v>293</v>
       </c>
     </row>
     <row r="290">
@@ -10858,24 +10858,24 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
       <c r="F290" t="n">
-        <v>12595</v>
+        <v>11315</v>
       </c>
       <c r="G290" t="n">
-        <v>294</v>
+        <v>321</v>
       </c>
     </row>
     <row r="291">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -10901,344 +10901,14 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
       <c r="F291" t="n">
-        <v>1325</v>
+        <v>20630</v>
       </c>
       <c r="G291" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>A형 인라인6호기</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
-        </is>
-      </c>
-      <c r="F292" t="n">
-        <v>12810</v>
-      </c>
-      <c r="G292" t="n">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>A형 인라인6호기</t>
-        </is>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>O2O2 D_Ash Brown EX</t>
-        </is>
-      </c>
-      <c r="F293" t="n">
-        <v>4544</v>
-      </c>
-      <c r="G293" t="n">
-        <v>1570</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>A형 인라인6호기</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>O2O2 D_Ash Gray EX</t>
-        </is>
-      </c>
-      <c r="F294" t="n">
-        <v>1425</v>
-      </c>
-      <c r="G294" t="n">
-        <v>1931</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Toric</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>A형 인라인1호기</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>O2O2 D Toric_Ash Brown EX</t>
-        </is>
-      </c>
-      <c r="F295" t="n">
-        <v>1645</v>
-      </c>
-      <c r="G295" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Toric</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>A형 인라인1호기</t>
-        </is>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>O2O2 D Toric_Sepia Choco EX</t>
-        </is>
-      </c>
-      <c r="F296" t="n">
-        <v>1455</v>
-      </c>
-      <c r="G296" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>Si_1-Day_M/F</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>A형 인라인1호기</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>O2O2_Multifocal_K2_SMDH_WHITE_OPHTALMIC</t>
-        </is>
-      </c>
-      <c r="F297" t="n">
-        <v>535</v>
-      </c>
-      <c r="G297" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>A형 인라인1호기</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
-        </is>
-      </c>
-      <c r="F298" t="n">
-        <v>9380</v>
-      </c>
-      <c r="G298" t="n">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>A형 인라인2호기</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
-        </is>
-      </c>
-      <c r="F299" t="n">
-        <v>24908</v>
-      </c>
-      <c r="G299" t="n">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>A형 인라인4호기</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
-        </is>
-      </c>
-      <c r="F300" t="n">
-        <v>15953</v>
-      </c>
-      <c r="G300" t="n">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>A형 인라인5호기</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
-        </is>
-      </c>
-      <c r="F301" t="n">
-        <v>20584</v>
-      </c>
-      <c r="G301" t="n">
-        <v>1308</v>
+        <v>641</v>
       </c>
     </row>
   </sheetData>

--- a/생산실적현황(설비운영현황).xlsx
+++ b/생산실적현황(설비운영현황).xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -537,11 +537,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -549,7 +549,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>T38_(UV포함)</t>
+          <t>O2O2_Multifocal_K2_SMD</t>
         </is>
       </c>
     </row>
@@ -565,11 +565,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_1-Day_Toric</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -577,7 +577,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMD</t>
+          <t>O2O2 D_UV_Toric_SMD</t>
         </is>
       </c>
     </row>
@@ -589,15 +589,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Si_1-Day_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -605,7 +605,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>O2O2 D_UV_Toric_SMD</t>
+          <t>1-Day_Metha</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>FRP_M/F</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1-Day_Metha</t>
+          <t>Bi-focal_8.40</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -685,11 +685,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NewFusion_원형</t>
+          <t>MG M_Perfect Brown_GLAM_(중)</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>T38_금캡(UV포함)</t>
         </is>
       </c>
     </row>
@@ -761,11 +761,11 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>Si_FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>O2O2 M_Mysti Gray EX_(중)</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>Toric_CP-0.75_Halo Brown</t>
         </is>
       </c>
     </row>
@@ -841,23 +841,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Coffee Jelly_PIA_M(Y)</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
     </row>
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
     </row>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
     </row>
@@ -925,23 +925,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
     </row>
@@ -961,15 +961,15 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 D_Blending Hazel EX</t>
         </is>
       </c>
     </row>
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1093,23 +1093,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1177,23 +1177,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>O2O2 D_Ash Brown EX</t>
         </is>
       </c>
     </row>
@@ -1209,73 +1209,17 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F28" t="inlineStr">
-        <is>
-          <t>Clalen oneday A(O2 Edition)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>6</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Color_Sph</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>S관(3공장)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>[55] 접착/멸균</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>6</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Si_1-Day_Sph</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>4</v>
-      </c>
-      <c r="F30" t="inlineStr">
         <is>
           <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
@@ -1299,9 +1243,9 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="43" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1368,10 +1312,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>34116</v>
+        <v>18287</v>
       </c>
       <c r="G2" t="n">
-        <v>3898</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3">
@@ -1401,10 +1345,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84119</v>
+        <v>44889</v>
       </c>
       <c r="G3" t="n">
-        <v>637</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1434,10 +1378,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>96478</v>
+        <v>50616</v>
       </c>
       <c r="G4" t="n">
-        <v>563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1467,10 +1411,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>49148</v>
+        <v>90892</v>
       </c>
       <c r="G5" t="n">
-        <v>881</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1500,7 +1444,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>36717</v>
+        <v>27946</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1533,10 +1477,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>31776</v>
+        <v>21196</v>
       </c>
       <c r="G7" t="n">
-        <v>1730</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1552,24 +1496,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>조립2호기</t>
+          <t>조립1호기</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>T38_(UV포함)</t>
+          <t>Metha_55</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7235</v>
+        <v>11788</v>
       </c>
       <c r="G8" t="n">
-        <v>1657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1599,10 +1543,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7596</v>
+        <v>8341</v>
       </c>
       <c r="G9" t="n">
-        <v>1137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1632,10 +1576,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7714</v>
+        <v>7871</v>
       </c>
       <c r="G10" t="n">
-        <v>1728</v>
+        <v>446</v>
       </c>
     </row>
     <row r="11">
@@ -1665,10 +1609,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>16585</v>
+        <v>21214</v>
       </c>
       <c r="G11" t="n">
-        <v>4445</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="12">
@@ -1684,24 +1628,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_M/F</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>분리10호기</t>
+          <t>분리5호기</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(NEW)S38-Dry-14.2</t>
+          <t>Bi-focal_8.40</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4081</v>
+        <v>7985</v>
       </c>
       <c r="G12" t="n">
-        <v>304</v>
+        <v>736</v>
       </c>
     </row>
     <row r="13">
@@ -1731,10 +1675,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6463</v>
+        <v>1914</v>
       </c>
       <c r="G13" t="n">
-        <v>735</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -1764,10 +1708,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5098</v>
+        <v>7864</v>
       </c>
       <c r="G14" t="n">
-        <v>821</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="15">
@@ -1797,10 +1741,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>15617</v>
+        <v>11072</v>
       </c>
       <c r="G15" t="n">
-        <v>1563</v>
+        <v>970</v>
       </c>
     </row>
     <row r="16">
@@ -1821,19 +1765,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>분리14호기</t>
+          <t>분리11호기</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metha</t>
+          <t>(NEW)S43-HD-Dry-14.4</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4368</v>
+        <v>3835</v>
       </c>
       <c r="G16" t="n">
-        <v>758</v>
+        <v>373</v>
       </c>
     </row>
     <row r="17">
@@ -1854,19 +1798,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>분리14호기</t>
+          <t>분리4호기</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>(NEW)S38-Dry-14.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>8237</v>
+        <v>2100</v>
       </c>
       <c r="G17" t="n">
-        <v>3588</v>
+        <v>456</v>
       </c>
     </row>
     <row r="18">
@@ -1892,14 +1836,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.2</t>
+          <t>S55-Dry</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4908</v>
+        <v>12356</v>
       </c>
       <c r="G18" t="n">
-        <v>840</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="19">
@@ -1920,19 +1864,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>분리4호기</t>
+          <t>분리5호기</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.4</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4393</v>
+        <v>4801</v>
       </c>
       <c r="G19" t="n">
-        <v>407</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="20">
@@ -1953,19 +1897,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>분리4호기</t>
+          <t>분리5호기</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S43-Dry-14.5</t>
+          <t>US55-2(M)</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4117</v>
+        <v>1691</v>
       </c>
       <c r="G20" t="n">
-        <v>693</v>
+        <v>849</v>
       </c>
     </row>
     <row r="21">
@@ -1976,29 +1920,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>분리4호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S55-Dry</t>
+          <t>Advance_EO_소사각</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2135</v>
+        <v>168</v>
       </c>
       <c r="G21" t="n">
-        <v>443</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -2009,29 +1953,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>분리5호기</t>
+          <t>검사15호기</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>MG M_Glow Hazel_GLAM_(중)</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3571</v>
+        <v>2274</v>
       </c>
       <c r="G22" t="n">
-        <v>577</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2042,29 +1986,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>분리5호기</t>
+          <t>검사15호기</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>US55-2(M)</t>
+          <t>MG M_Nature Brown_GLAM_(중)</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11873</v>
+        <v>1704</v>
       </c>
       <c r="G23" t="n">
-        <v>4108</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2085,19 +2029,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>검사15호기</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BELLA M_Moon_14.5_(중)</t>
+          <t>MG M_Perfect Brown_GLAM_(중)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>486</v>
+        <v>5307</v>
       </c>
       <c r="G24" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -2123,14 +2067,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bella Diamond_14.5_중사각</t>
+          <t>Bella Glow_중사각</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1022</v>
+        <v>487</v>
       </c>
       <c r="G25" t="n">
-        <v>155</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -2156,14 +2100,14 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bella Glow_중사각</t>
+          <t>Bella-Elite_14.5_중사각</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>284</v>
+        <v>390</v>
       </c>
       <c r="G26" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -2189,11 +2133,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bella-Contour_중사각</t>
+          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>450</v>
+        <v>1912</v>
       </c>
       <c r="G27" t="n">
         <v>46</v>
@@ -2217,19 +2161,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>검사7호기</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bella-Elite_14.5_중사각</t>
+          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3066</v>
+        <v>1876</v>
       </c>
       <c r="G28" t="n">
-        <v>96</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29">
@@ -2250,19 +2194,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Affogato_PIA_M_(중)(Y)</t>
+          <t>CLC-10_원형</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>974</v>
+        <v>1163</v>
       </c>
       <c r="G29" t="n">
-        <v>26</v>
+        <v>334</v>
       </c>
     </row>
     <row r="30">
@@ -2283,19 +2227,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bella Glow_중사각</t>
+          <t>Clalen Iris_GRA_2902_원형</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>100</v>
+        <v>437</v>
       </c>
       <c r="G30" t="n">
-        <v>50</v>
+        <v>458</v>
       </c>
     </row>
     <row r="31">
@@ -2316,19 +2260,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bella-Natural_중사각</t>
+          <t>Clalen Iris_GRA_3302_원형</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="G31" t="n">
-        <v>139</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32">
@@ -2349,19 +2293,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cream Rose_PIA_M_(중)</t>
+          <t>CLC-30_바이알</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>976</v>
+        <v>734</v>
       </c>
       <c r="G32" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33">
@@ -2382,19 +2326,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lady Black_PIA_M_(중)_14.5</t>
+          <t>Festival-II-Color_은캡</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1490</v>
+        <v>417</v>
       </c>
       <c r="G33" t="n">
-        <v>47</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34">
@@ -2410,24 +2354,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_M/F</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>NewFusion_중사각</t>
+          <t>HD-X55_소사각</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>568</v>
+        <v>1433</v>
       </c>
       <c r="G34" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2443,21 +2387,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_M/F</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aquarella M_Samba Green_원형</t>
+          <t>HD-X55_소사각</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>654</v>
+        <v>5611</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2476,24 +2420,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aquarella_Amazonia Green_원형</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1428</v>
+        <v>8442</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37">
@@ -2509,24 +2453,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aquarella_Dandara Hazel_원형</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1398</v>
+        <v>6370</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38">
@@ -2542,24 +2486,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CLC-30_원형</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>174</v>
+        <v>10370</v>
       </c>
       <c r="G38" t="n">
-        <v>26</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39">
@@ -2575,24 +2519,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Clalen Iris_GRA_2902_원형</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>402</v>
+        <v>4412</v>
       </c>
       <c r="G39" t="n">
-        <v>413</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40">
@@ -2608,24 +2552,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Festival-II-Color_원형</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1045</v>
+        <v>10912</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
     </row>
     <row r="41">
@@ -2641,7 +2585,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2651,14 +2595,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NewFusion_원형</t>
+          <t>(UV)CS30_원형_8.60</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>4057</v>
+        <v>376</v>
       </c>
       <c r="G41" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
@@ -2674,7 +2618,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2684,14 +2628,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rainbow_원형</t>
+          <t>CS30_원형_8.60</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>227</v>
+        <v>1212</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43">
@@ -2707,24 +2651,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>BELLA M_Moon_14.5_(중)</t>
+          <t>Metha_55_원형</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2386</v>
+        <v>1392</v>
       </c>
       <c r="G43" t="n">
-        <v>81</v>
+        <v>290</v>
       </c>
     </row>
     <row r="44">
@@ -2740,24 +2684,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bella Diamond_14.5_중사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>936</v>
+        <v>6326</v>
       </c>
       <c r="G44" t="n">
-        <v>21</v>
+        <v>199</v>
       </c>
     </row>
     <row r="45">
@@ -2773,24 +2717,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사6호기</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bella-Contour_중사각</t>
+          <t>Metha_55_중사각</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>362</v>
+        <v>1158</v>
       </c>
       <c r="G45" t="n">
-        <v>32</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46">
@@ -2806,24 +2750,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bella-Elite_14.5_중사각</t>
+          <t>Metha_55_원형</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>480</v>
+        <v>1070</v>
       </c>
       <c r="G46" t="n">
-        <v>19</v>
+        <v>676</v>
       </c>
     </row>
     <row r="47">
@@ -2839,24 +2783,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>검사7호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bella Glow_중사각</t>
+          <t>T38_금캡</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="G47" t="n">
-        <v>200</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
@@ -2872,24 +2816,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>검사7호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bella-Natural_14.5_중사각</t>
+          <t>T38_금캡(UV포함)</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>3389</v>
       </c>
       <c r="G48" t="n">
-        <v>200</v>
+        <v>553</v>
       </c>
     </row>
     <row r="49">
@@ -2905,24 +2849,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>Si_FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Advance_CB_원형</t>
+          <t>O2O2 M_Mysti Gray EX_(중)</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>718</v>
+        <v>905</v>
       </c>
       <c r="G49" t="n">
-        <v>1926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2938,24 +2882,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>Si_FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CLC-30_원형</t>
+          <t>O2O2 M_Natural Gray EX_(중)</t>
         </is>
       </c>
       <c r="F50" t="n">
+        <v>578</v>
+      </c>
+      <c r="G50" t="n">
         <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>296</v>
       </c>
     </row>
     <row r="51">
@@ -2971,24 +2915,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Clalen Iris_GRA_2902_원형</t>
+          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>4154</v>
       </c>
       <c r="G51" t="n">
-        <v>297</v>
+        <v>431</v>
       </c>
     </row>
     <row r="52">
@@ -3004,24 +2948,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Clalen Iris_GRA_3302_원형</t>
+          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>242</v>
+        <v>4522</v>
       </c>
       <c r="G52" t="n">
-        <v>94</v>
+        <v>591</v>
       </c>
     </row>
     <row r="53">
@@ -3037,24 +2981,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NewFusion_원형</t>
+          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>32</v>
+        <v>4027</v>
       </c>
       <c r="G53" t="n">
-        <v>2367</v>
+        <v>244</v>
       </c>
     </row>
     <row r="54">
@@ -3070,651 +3014,651 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CLC-30_바이알</t>
+          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>927</v>
+        <v>688</v>
       </c>
       <c r="G54" t="n">
-        <v>18</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>조립10호기</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>NewFusion_금캡</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>23158</v>
       </c>
       <c r="G55" t="n">
-        <v>100</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FRP_M/F</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>조립11호기</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HD-X55_소사각</t>
+          <t>PIA D_Princess Chocolat_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1428</v>
+        <v>27633</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>조립12호기</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>12462</v>
+        <v>29656</v>
       </c>
       <c r="G57" t="n">
-        <v>585</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>조립13호기</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>6746</v>
+        <v>31105</v>
       </c>
       <c r="G58" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>조립14호기</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>6224</v>
+        <v>19250</v>
       </c>
       <c r="G59" t="n">
-        <v>292</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>조립15호기</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Metha_55_원형</t>
+          <t>HOYA_Casual Ash</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1704</v>
+        <v>12956</v>
       </c>
       <c r="G60" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>조립16호기</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Metha_55_중사각</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>4702</v>
+        <v>14163</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>조립19호기</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3718</v>
+        <v>43932</v>
       </c>
       <c r="G62" t="n">
-        <v>80</v>
+        <v>751</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>조립23호기</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>Hapa D_Crush Brown_Secretive</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1982</v>
+        <v>9081</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>검사7호기</t>
+          <t>조립23호기</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Metha_55_중사각</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1128</v>
+        <v>23850</v>
       </c>
       <c r="G64" t="n">
-        <v>108</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>조립24호기</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Metha_55_원형</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1764</v>
+        <v>26593</v>
       </c>
       <c r="G65" t="n">
-        <v>86</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>조립25호기</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>S38_은캡(BLUE TINT)</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>9859</v>
+        <v>5416</v>
       </c>
       <c r="G66" t="n">
-        <v>1348</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>조립26호기</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2826</v>
+        <v>25119</v>
       </c>
       <c r="G67" t="n">
-        <v>502</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>조립27호기</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>544</v>
+        <v>53639</v>
       </c>
       <c r="G68" t="n">
-        <v>92</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Si_FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>검사19호기</t>
+          <t>조립42호기</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>O2O2 M_Mysti Gray EX_(중)</t>
+          <t>Clalen D_MIZONG_55%</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>26</v>
+        <v>19343</v>
       </c>
       <c r="G69" t="n">
-        <v>6</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>조립44호기</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
+          <t>PIA D_Baby Espresso_38% UV</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1664</v>
+        <v>13849</v>
       </c>
       <c r="G70" t="n">
-        <v>41</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>조립46호기</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>Alcon D_Jewel Gold_W3</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>11482</v>
+        <v>17854</v>
       </c>
       <c r="G71" t="n">
-        <v>365</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>조립48호기</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3654</v>
+        <v>22734</v>
       </c>
       <c r="G72" t="n">
-        <v>33</v>
+        <v>8037</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>조립49호기</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>Alcon D_Allure Blue_W3C</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2150</v>
+        <v>29209</v>
       </c>
       <c r="G73" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
     </row>
     <row r="74">
@@ -3735,19 +3679,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>조립10호기</t>
+          <t>조립50호기</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>22001</v>
+        <v>28963</v>
       </c>
       <c r="G74" t="n">
-        <v>5911</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="75">
@@ -3768,19 +3712,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>조립11호기</t>
+          <t>조립51호기</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>From D_(UV)Clear Beige_38%</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>10323</v>
+        <v>22932</v>
       </c>
       <c r="G75" t="n">
-        <v>2135</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="76">
@@ -3801,19 +3745,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>조립12호기</t>
+          <t>조립52호기</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1-Day_iris_Blue Moon</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>32288</v>
+        <v>26836</v>
       </c>
       <c r="G76" t="n">
-        <v>2120</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77">
@@ -3834,19 +3778,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>조립13호기</t>
+          <t>조립53호기</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>From D_(UV)Clear Beige Coral_38%</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>25070</v>
+        <v>11778</v>
       </c>
       <c r="G77" t="n">
-        <v>900</v>
+        <v>400</v>
       </c>
     </row>
     <row r="78">
@@ -3867,19 +3811,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>조립14호기</t>
+          <t>조립53호기</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Baby Espresso_38% UV</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>37642</v>
+        <v>23274</v>
       </c>
       <c r="G78" t="n">
-        <v>7980</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79">
@@ -3900,19 +3844,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>조립15호기</t>
+          <t>조립54호기</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>HOYA_Casual Ash</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>14361</v>
+        <v>31924</v>
       </c>
       <c r="G79" t="n">
-        <v>2000</v>
+        <v>745</v>
       </c>
     </row>
     <row r="80">
@@ -3933,19 +3877,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>조립16호기</t>
+          <t>조립55호기</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>ClearBeige Mini UV 14.2</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>25584</v>
+        <v>24229</v>
       </c>
       <c r="G80" t="n">
-        <v>500</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="81">
@@ -3966,19 +3910,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>조립19호기</t>
+          <t>조립56호기</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>28046</v>
+        <v>26190</v>
       </c>
       <c r="G81" t="n">
-        <v>1437</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82">
@@ -3999,19 +3943,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>조립23호기</t>
+          <t>조립57호기</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>T-Garden D_Melty Time_55% UV 14.2</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>15879</v>
+        <v>28343</v>
       </c>
       <c r="G82" t="n">
-        <v>1493</v>
+        <v>730</v>
       </c>
     </row>
     <row r="83">
@@ -4032,19 +3976,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>조립24호기</t>
+          <t>조립58호기</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA D_Date Topaz_38% UV</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>26426</v>
+        <v>49278</v>
       </c>
       <c r="G83" t="n">
-        <v>1140</v>
+        <v>4782</v>
       </c>
     </row>
     <row r="84">
@@ -4065,19 +4009,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>조립25호기</t>
+          <t>조립59호기</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>45908</v>
+        <v>25078</v>
       </c>
       <c r="G84" t="n">
-        <v>749</v>
+        <v>940</v>
       </c>
     </row>
     <row r="85">
@@ -4093,24 +4037,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>조립26호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>29367</v>
+        <v>4240</v>
       </c>
       <c r="G85" t="n">
-        <v>9</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="86">
@@ -4126,24 +4070,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>조립27호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>29251</v>
+        <v>9016</v>
       </c>
       <c r="G86" t="n">
-        <v>778</v>
+        <v>400</v>
       </c>
     </row>
     <row r="87">
@@ -4159,24 +4103,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>조립42호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>27222</v>
+        <v>9046</v>
       </c>
       <c r="G87" t="n">
-        <v>1748</v>
+        <v>400</v>
       </c>
     </row>
     <row r="88">
@@ -4192,24 +4136,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>조립46호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Gold_W3</t>
+          <t>Toric_CP-0.75_Halo Brown</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>30635</v>
+        <v>16415</v>
       </c>
       <c r="G88" t="n">
-        <v>5900</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="89">
@@ -4225,24 +4169,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>조립47호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>Toric_CP-1.25_Halo Brown</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>31073</v>
+        <v>3712</v>
       </c>
       <c r="G89" t="n">
-        <v>2030</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -4258,24 +4202,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>조립48호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>18501</v>
+        <v>7403</v>
       </c>
       <c r="G90" t="n">
-        <v>1300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -4286,7 +4230,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4296,19 +4240,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>조립51호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>PIA D_Cream Grege_14.4</t>
+          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>43904</v>
+        <v>11699</v>
       </c>
       <c r="G91" t="n">
-        <v>10776</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="92">
@@ -4319,7 +4263,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4329,19 +4273,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>조립52호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>27510</v>
+        <v>25629</v>
       </c>
       <c r="G92" t="n">
-        <v>500</v>
+        <v>3895</v>
       </c>
     </row>
     <row r="93">
@@ -4352,7 +4296,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4362,19 +4306,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>조립54호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Dayglow Gray_55% UV 14.2</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>31794</v>
+        <v>1871</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
     </row>
     <row r="94">
@@ -4385,7 +4329,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4395,19 +4339,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>조립57호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Starflare Beige_55% UV 14.2</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>53255</v>
+        <v>4119</v>
       </c>
       <c r="G94" t="n">
-        <v>3070</v>
+        <v>830</v>
       </c>
     </row>
     <row r="95">
@@ -4418,7 +4362,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4428,19 +4372,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>조립58호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>PIA D_Date Topaz_38% UV</t>
+          <t>1-Day_iris_Blue Moon</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>23812</v>
+        <v>14776</v>
       </c>
       <c r="G95" t="n">
-        <v>3000</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="96">
@@ -4451,7 +4395,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4461,19 +4405,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>조립59호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>PIA D_Melty Butter_55%_14.5 UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>58685</v>
+        <v>7008</v>
       </c>
       <c r="G96" t="n">
-        <v>682</v>
+        <v>904</v>
       </c>
     </row>
     <row r="97">
@@ -4484,29 +4428,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1100</v>
+        <v>25331</v>
       </c>
       <c r="G97" t="n">
-        <v>8</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="98">
@@ -4517,29 +4461,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>28153</v>
+        <v>10651</v>
       </c>
       <c r="G98" t="n">
-        <v>7565</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="99">
@@ -4550,29 +4494,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Brown</t>
+          <t>JEWEL MOON D_Sapphire Moon_55%</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2675</v>
+        <v>4884</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>707</v>
       </c>
     </row>
     <row r="100">
@@ -4583,29 +4527,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>7983</v>
+        <v>13505</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="101">
@@ -4616,29 +4560,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>9637</v>
+        <v>8812</v>
       </c>
       <c r="G101" t="n">
-        <v>1050</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="102">
@@ -4649,29 +4593,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>조립55호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Coffee Jelly_PIA_M(Y)</t>
+          <t>HOYA_Noble Ash</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>5859</v>
+        <v>14769</v>
       </c>
       <c r="G102" t="n">
-        <v>3246</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="103">
@@ -4692,19 +4636,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Dayglow Gray_55% UV 14.2</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>29189</v>
+        <v>6779</v>
       </c>
       <c r="G103" t="n">
-        <v>3132</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="104">
@@ -4725,19 +4669,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>25163</v>
+        <v>6811</v>
       </c>
       <c r="G104" t="n">
-        <v>1882</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="105">
@@ -4758,19 +4702,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>34531</v>
+        <v>18686</v>
       </c>
       <c r="G105" t="n">
-        <v>4088</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="106">
@@ -4791,19 +4735,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>Alcon D_Allure Blue_W3C</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3888</v>
+        <v>9945</v>
       </c>
       <c r="G106" t="n">
-        <v>519</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="107">
@@ -4824,19 +4768,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>HOYA_Noble Ash</t>
+          <t>PIA D_Iconic Brown_55% UV 14.2</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>7696</v>
+        <v>11046</v>
       </c>
       <c r="G107" t="n">
-        <v>1496</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="108">
@@ -4857,19 +4801,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>분리19호기</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>22171</v>
+        <v>36086</v>
       </c>
       <c r="G108" t="n">
-        <v>3507</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="109">
@@ -4890,19 +4834,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>PIA_1D 55% YakisobaPan_1T</t>
+          <t>1-Day_iris_Blue Moon</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>5017</v>
+        <v>14342</v>
       </c>
       <c r="G109" t="n">
-        <v>702</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="110">
@@ -4923,19 +4867,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>Alcon D_Jewel Gold_W3</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>20445</v>
+        <v>21597</v>
       </c>
       <c r="G110" t="n">
-        <v>2963</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="111">
@@ -4956,19 +4900,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Alcon D_Allure Hazel_W3C</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>21023</v>
+        <v>12386</v>
       </c>
       <c r="G111" t="n">
-        <v>1864</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="112">
@@ -4989,19 +4933,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>분리19호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>6493</v>
+        <v>13551</v>
       </c>
       <c r="G112" t="n">
-        <v>815</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="113">
@@ -5022,19 +4966,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Iconic Brown_55% UV 14.2</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>2872</v>
+        <v>3528</v>
       </c>
       <c r="G113" t="n">
-        <v>265</v>
+        <v>359</v>
       </c>
     </row>
     <row r="114">
@@ -5055,19 +4999,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>PIA D_Starflare Beige_55% UV 14.2</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>13825</v>
+        <v>2940</v>
       </c>
       <c r="G114" t="n">
-        <v>2431</v>
+        <v>859</v>
       </c>
     </row>
     <row r="115">
@@ -5088,19 +5032,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>T-Garden D_Melty Time_55% UV 14.2</t>
+          <t>PIA D_Starflare Gray_55% UV 14.2</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>18526</v>
+        <v>2656</v>
       </c>
       <c r="G115" t="n">
-        <v>2428</v>
+        <v>336</v>
       </c>
     </row>
     <row r="116">
@@ -5126,14 +5070,14 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>14579</v>
+        <v>21645</v>
       </c>
       <c r="G116" t="n">
-        <v>2042</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="117">
@@ -5154,7 +5098,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5163,10 +5107,10 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>29597</v>
+        <v>14043</v>
       </c>
       <c r="G117" t="n">
-        <v>2860</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="118">
@@ -5192,14 +5136,14 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>JEWEL MOON D_Sapphire Moon_55%</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>18436</v>
+        <v>13007</v>
       </c>
       <c r="G118" t="n">
-        <v>1538</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="119">
@@ -5225,14 +5169,14 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
+          <t>JEWEL MOON D_Sunstone Moon_55%</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>21929</v>
+        <v>1541</v>
       </c>
       <c r="G119" t="n">
-        <v>3410</v>
+        <v>103</v>
       </c>
     </row>
     <row r="120">
@@ -5253,19 +5197,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>JEWEL MOON D_Topaz Moon_55%</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>8557</v>
+        <v>651</v>
       </c>
       <c r="G120" t="n">
-        <v>1718</v>
+        <v>38</v>
       </c>
     </row>
     <row r="121">
@@ -5286,19 +5230,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>26959</v>
+        <v>17460</v>
       </c>
       <c r="G121" t="n">
-        <v>3163</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="122">
@@ -5319,19 +5263,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>10294</v>
+        <v>33220</v>
       </c>
       <c r="G122" t="n">
-        <v>788</v>
+        <v>7389</v>
       </c>
     </row>
     <row r="123">
@@ -5352,19 +5296,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>PIA D_Iconic Brown_55% UV 14.2</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>23158</v>
+        <v>6855</v>
       </c>
       <c r="G123" t="n">
-        <v>3047</v>
+        <v>727</v>
       </c>
     </row>
     <row r="124">
@@ -5385,19 +5329,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>T-Garden D_Melty Time_55% UV 14.2</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>5836</v>
+        <v>24133</v>
       </c>
       <c r="G124" t="n">
-        <v>760</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="125">
@@ -5418,19 +5362,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Starflare Gray_55% UV 14.2</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>7826</v>
+        <v>13640</v>
       </c>
       <c r="G125" t="n">
-        <v>905</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="126">
@@ -5451,19 +5395,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>5691</v>
+        <v>3406</v>
       </c>
       <c r="G126" t="n">
-        <v>471</v>
+        <v>341</v>
       </c>
     </row>
     <row r="127">
@@ -5484,19 +5428,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>PIA D_Baby Espresso_38% UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>5736</v>
+        <v>29513</v>
       </c>
       <c r="G127" t="n">
-        <v>1074</v>
+        <v>4509</v>
       </c>
     </row>
     <row r="128">
@@ -5517,19 +5461,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>PIA D_Cream Beige_14.4</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>21389</v>
+        <v>7892</v>
       </c>
       <c r="G128" t="n">
-        <v>3028</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="129">
@@ -5550,19 +5494,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>PIA D_Cream Grege_14.4</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>6258</v>
+        <v>16069</v>
       </c>
       <c r="G129" t="n">
-        <v>599</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="130">
@@ -5583,19 +5527,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>PIA D_Date Topaz_38% UV</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>7379</v>
+        <v>13420</v>
       </c>
       <c r="G130" t="n">
-        <v>1435</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="131">
@@ -5616,19 +5560,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ANW D_Art Gray_Dopewink 38%</t>
+          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>6734</v>
+        <v>6938</v>
       </c>
       <c r="G131" t="n">
-        <v>1905</v>
+        <v>819</v>
       </c>
     </row>
     <row r="132">
@@ -5649,19 +5593,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ANW D_Spicy Gray_Dopewink 38%</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>6783</v>
+        <v>31830</v>
       </c>
       <c r="G132" t="n">
-        <v>1473</v>
+        <v>3168</v>
       </c>
     </row>
     <row r="133">
@@ -5682,19 +5626,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>PIA D_Strawberry Quartz_38% UV</t>
+          <t>PIA D_Dayglow Gray_55% UV 14.2</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>16501</v>
+        <v>12367</v>
       </c>
       <c r="G133" t="n">
-        <v>3918</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="134">
@@ -5715,19 +5659,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>PIA D_Melty Butter_55%_14.5 UV</t>
+          <t>PIA D_Cream Grege_14.4</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>41485</v>
+        <v>18127</v>
       </c>
       <c r="G134" t="n">
-        <v>7727</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="135">
@@ -5748,19 +5692,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA D_Date Topaz_38% UV</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>10080</v>
+        <v>25636</v>
       </c>
       <c r="G135" t="n">
-        <v>1143</v>
+        <v>4676</v>
       </c>
     </row>
     <row r="136">
@@ -5781,19 +5725,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>PIA D_Baby Espresso_38% UV</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>20799</v>
+        <v>2230</v>
       </c>
       <c r="G136" t="n">
-        <v>3531</v>
+        <v>570</v>
       </c>
     </row>
     <row r="137">
@@ -5814,19 +5758,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Cream Grege_14.4</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>40550</v>
+        <v>14161</v>
       </c>
       <c r="G137" t="n">
-        <v>3677</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="138">
@@ -5842,24 +5786,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>PIA_Date topaz CP-0.75 Toric_UV</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>5876</v>
+        <v>32798</v>
       </c>
       <c r="G138" t="n">
-        <v>1002</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="139">
@@ -5875,24 +5819,24 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>PIA_Date topaz CP-1.25 Toric_UV</t>
+          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>3077</v>
+        <v>7211</v>
       </c>
       <c r="G139" t="n">
-        <v>347</v>
+        <v>519</v>
       </c>
     </row>
     <row r="140">
@@ -5908,24 +5852,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>JEWEL MOON D_Amber Moon_55%</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>5417</v>
+        <v>2192</v>
       </c>
       <c r="G140" t="n">
-        <v>1764</v>
+        <v>285</v>
       </c>
     </row>
     <row r="141">
@@ -5941,24 +5885,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Gray</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>437</v>
+        <v>15185</v>
       </c>
       <c r="G141" t="n">
-        <v>82</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="142">
@@ -5974,24 +5918,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>PIA D_Dayglow Gray_55% UV 14.2</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>12362</v>
+        <v>17248</v>
       </c>
       <c r="G142" t="n">
-        <v>4370</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="143">
@@ -6007,24 +5951,24 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>2353</v>
+        <v>11889</v>
       </c>
       <c r="G143" t="n">
-        <v>1162</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="144">
@@ -6040,7 +5984,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6050,14 +5994,14 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Gray</t>
+          <t>PIA D_Starflare Beige_55% UV 14.2</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>7792</v>
+        <v>19453</v>
       </c>
       <c r="G144" t="n">
-        <v>1914</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="145">
@@ -6073,24 +6017,24 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>JEWEL MOON D_Emerald Moon_55%</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>12301</v>
+        <v>6130</v>
       </c>
       <c r="G145" t="n">
-        <v>2254</v>
+        <v>597</v>
       </c>
     </row>
     <row r="146">
@@ -6106,24 +6050,24 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Gray</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>3583</v>
+        <v>27142</v>
       </c>
       <c r="G146" t="n">
-        <v>784</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="147">
@@ -6144,19 +6088,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>5651</v>
+        <v>3053</v>
       </c>
       <c r="G147" t="n">
-        <v>1161</v>
+        <v>454</v>
       </c>
     </row>
     <row r="148">
@@ -6177,19 +6121,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>3113</v>
+        <v>4718</v>
       </c>
       <c r="G148" t="n">
-        <v>1150</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="149">
@@ -6210,19 +6154,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Brown</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2943</v>
+        <v>11924</v>
       </c>
       <c r="G149" t="n">
-        <v>239</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="150">
@@ -6243,19 +6187,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2207</v>
+        <v>1683</v>
       </c>
       <c r="G150" t="n">
-        <v>1232</v>
+        <v>674</v>
       </c>
     </row>
     <row r="151">
@@ -6271,24 +6215,24 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리22호기</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>945</v>
+        <v>40818</v>
       </c>
       <c r="G151" t="n">
-        <v>602</v>
+        <v>6459</v>
       </c>
     </row>
     <row r="152">
@@ -6304,24 +6248,24 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리23호기</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>865</v>
+        <v>38222</v>
       </c>
       <c r="G152" t="n">
-        <v>346</v>
+        <v>7089</v>
       </c>
     </row>
     <row r="153">
@@ -6342,7 +6286,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>분리22호기</t>
+          <t>분리25호기</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6351,10 +6295,10 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>35810</v>
+        <v>41886</v>
       </c>
       <c r="G153" t="n">
-        <v>6301</v>
+        <v>9455</v>
       </c>
     </row>
     <row r="154">
@@ -6375,7 +6319,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>분리23호기</t>
+          <t>분리43호기</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -6384,10 +6328,10 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>34893</v>
+        <v>37685</v>
       </c>
       <c r="G154" t="n">
-        <v>5840</v>
+        <v>9402</v>
       </c>
     </row>
     <row r="155">
@@ -6403,24 +6347,24 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>분리25호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Coffee Jelly_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>42297</v>
+        <v>957</v>
       </c>
       <c r="G155" t="n">
-        <v>8448</v>
+        <v>337</v>
       </c>
     </row>
     <row r="156">
@@ -6436,24 +6380,24 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>분리43호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Coffee Jelly_PIA_M(Y)</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>30121</v>
+        <v>1958</v>
       </c>
       <c r="G156" t="n">
-        <v>8652</v>
+        <v>320</v>
       </c>
     </row>
     <row r="157">
@@ -6479,14 +6423,14 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>4065</v>
+        <v>1235</v>
       </c>
       <c r="G157" t="n">
-        <v>180</v>
+        <v>60</v>
       </c>
     </row>
     <row r="158">
@@ -6512,14 +6456,14 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>PIA_1D 55% YakisobaPan_1T</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1660</v>
+        <v>1025</v>
       </c>
       <c r="G158" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="159">
@@ -6540,19 +6484,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>검사31호기</t>
+          <t>검사30호기</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>6505</v>
+        <v>2235</v>
       </c>
       <c r="G159" t="n">
-        <v>335</v>
+        <v>110</v>
       </c>
     </row>
     <row r="160">
@@ -6578,14 +6522,14 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>2525</v>
+        <v>1570</v>
       </c>
       <c r="G160" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="161">
@@ -6606,19 +6550,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사31호기</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="162">
@@ -6639,19 +6583,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사31호기</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>4895</v>
+        <v>3715</v>
       </c>
       <c r="G162" t="n">
-        <v>150</v>
+        <v>195</v>
       </c>
     </row>
     <row r="163">
@@ -6677,14 +6621,14 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>PIA D_Melty Butter_55%_14.5 UV</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1845</v>
+        <v>12021</v>
       </c>
       <c r="G163" t="n">
-        <v>60</v>
+        <v>794</v>
       </c>
     </row>
     <row r="164">
@@ -6710,14 +6654,14 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>8630</v>
+        <v>9740</v>
       </c>
       <c r="G164" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="165">
@@ -6743,11 +6687,11 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>3775</v>
+        <v>3030</v>
       </c>
       <c r="G165" t="n">
         <v>45</v>
@@ -6776,11 +6720,11 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1895</v>
+        <v>3190</v>
       </c>
       <c r="G166" t="n">
         <v>20</v>
@@ -6809,14 +6753,14 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>PIA_1D 55% YakisobaPan_1T</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1422</v>
+        <v>2500</v>
       </c>
       <c r="G167" t="n">
-        <v>523</v>
+        <v>20</v>
       </c>
     </row>
     <row r="168">
@@ -6842,14 +6786,14 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>3582</v>
+        <v>2040</v>
       </c>
       <c r="G168" t="n">
-        <v>1588</v>
+        <v>20</v>
       </c>
     </row>
     <row r="169">
@@ -6875,14 +6819,14 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>820</v>
+        <v>6510</v>
       </c>
       <c r="G169" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="170">
@@ -6903,19 +6847,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>8170</v>
+        <v>6515</v>
       </c>
       <c r="G170" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
     </row>
     <row r="171">
@@ -6936,19 +6880,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1260</v>
+        <v>16470</v>
       </c>
       <c r="G171" t="n">
-        <v>60</v>
+        <v>215</v>
       </c>
     </row>
     <row r="172">
@@ -6974,14 +6918,14 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>0</v>
+        <v>2768</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>577</v>
       </c>
     </row>
     <row r="173">
@@ -7007,14 +6951,14 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2675</v>
+        <v>5578</v>
       </c>
       <c r="G173" t="n">
-        <v>50</v>
+        <v>892</v>
       </c>
     </row>
     <row r="174">
@@ -7040,14 +6984,14 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>28265</v>
+        <v>6445</v>
       </c>
       <c r="G174" t="n">
-        <v>785</v>
+        <v>75</v>
       </c>
     </row>
     <row r="175">
@@ -7073,14 +7017,14 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>4993</v>
+        <v>3220</v>
       </c>
       <c r="G175" t="n">
-        <v>507</v>
+        <v>20</v>
       </c>
     </row>
     <row r="176">
@@ -7106,14 +7050,14 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>5515</v>
+        <v>3265</v>
       </c>
       <c r="G176" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="177">
@@ -7134,19 +7078,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>3365</v>
+        <v>39530</v>
       </c>
       <c r="G177" t="n">
-        <v>120</v>
+        <v>665</v>
       </c>
     </row>
     <row r="178">
@@ -7167,19 +7111,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>Clalen D_XUYU_55%</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1815</v>
+        <v>14428</v>
       </c>
       <c r="G178" t="n">
-        <v>110</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="179">
@@ -7200,19 +7144,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>PIA_TAMA KONNYAKU_55%</t>
+          <t>Alcon D_Allure Grey_W3C(KR)</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>2535</v>
+        <v>10120</v>
       </c>
       <c r="G179" t="n">
-        <v>80</v>
+        <v>225</v>
       </c>
     </row>
     <row r="180">
@@ -7233,19 +7177,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>Alcon D_Allure Hazel_W3C(KR)</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>59707</v>
+        <v>13383</v>
       </c>
       <c r="G180" t="n">
-        <v>2508</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="181">
@@ -7271,14 +7215,14 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>ALICIA BROWN(근시)</t>
+          <t>Alcon D_Jewel Gold_W3(KR)</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>13655</v>
+        <v>18130</v>
       </c>
       <c r="G181" t="n">
-        <v>140</v>
+        <v>355</v>
       </c>
     </row>
     <row r="182">
@@ -7304,14 +7248,14 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Alcon D_Allure Grey_W3C(APAC)</t>
+          <t>HOYA_Olive ash(Noble Ash)</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2285</v>
+        <v>4710</v>
       </c>
       <c r="G182" t="n">
-        <v>1520</v>
+        <v>615</v>
       </c>
     </row>
     <row r="183">
@@ -7337,14 +7281,14 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Alcon D_Allure Grey_W3C(KR)</t>
+          <t>PIA D_Dayglow Gray_55% UV 14.2</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>18765</v>
+        <v>2243</v>
       </c>
       <c r="G183" t="n">
-        <v>220</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="184">
@@ -7365,19 +7309,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Alcon D_Allure Hazel_W3C(KR)</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3080</v>
+        <v>58342</v>
       </c>
       <c r="G184" t="n">
-        <v>45</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="185">
@@ -7398,19 +7342,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>T-Garden D_Melty Time_55% UV 14.2</t>
+          <t>PIA D_Baby Espresso_38% UV</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2290</v>
+        <v>5965</v>
       </c>
       <c r="G185" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="186">
@@ -7431,19 +7375,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
+          <t>PIA D_Cream Beige_14.4</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>3765</v>
+        <v>12710</v>
       </c>
       <c r="G186" t="n">
-        <v>375</v>
+        <v>140</v>
       </c>
     </row>
     <row r="187">
@@ -7464,19 +7408,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>PIA D_Cream Grege_14.4</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1970</v>
+        <v>13446</v>
       </c>
       <c r="G187" t="n">
-        <v>35</v>
+        <v>869</v>
       </c>
     </row>
     <row r="188">
@@ -7497,19 +7441,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Date Topaz_38% UV</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>2500</v>
+        <v>7180</v>
       </c>
       <c r="G188" t="n">
-        <v>30</v>
+        <v>145</v>
       </c>
     </row>
     <row r="189">
@@ -7530,19 +7474,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Pearl Cats Eye_38% UV</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>54019</v>
+        <v>1315</v>
       </c>
       <c r="G189" t="n">
-        <v>4576</v>
+        <v>25</v>
       </c>
     </row>
     <row r="190">
@@ -7568,14 +7512,14 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>PIA D_Baby Espresso_38% UV</t>
+          <t>PIA D_Strawberry Quartz_38% UV</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>29268</v>
+        <v>15775</v>
       </c>
       <c r="G190" t="n">
-        <v>1032</v>
+        <v>285</v>
       </c>
     </row>
     <row r="191">
@@ -7596,19 +7540,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>PIA D_Cream Beige_14.4</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>19042</v>
+        <v>6610</v>
       </c>
       <c r="G191" t="n">
-        <v>2538</v>
+        <v>65</v>
       </c>
     </row>
     <row r="192">
@@ -7629,19 +7573,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>PIA D_Pearl Cats Eye_38% UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>3470</v>
+        <v>2604</v>
       </c>
       <c r="G192" t="n">
-        <v>105</v>
+        <v>676</v>
       </c>
     </row>
     <row r="193">
@@ -7667,14 +7611,14 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>2265</v>
+        <v>3040</v>
       </c>
       <c r="G193" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="194">
@@ -7700,14 +7644,14 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1865</v>
+        <v>12630</v>
       </c>
       <c r="G194" t="n">
-        <v>15</v>
+        <v>135</v>
       </c>
     </row>
     <row r="195">
@@ -7733,14 +7677,14 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>10990</v>
+        <v>15275</v>
       </c>
       <c r="G195" t="n">
-        <v>175</v>
+        <v>105</v>
       </c>
     </row>
     <row r="196">
@@ -7766,14 +7710,14 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>PIA D_Melty Butter_55%_14.5 UV</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>5985</v>
+        <v>6270</v>
       </c>
       <c r="G196" t="n">
-        <v>535</v>
+        <v>60</v>
       </c>
     </row>
     <row r="197">
@@ -7799,14 +7743,14 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>6275</v>
+        <v>5355</v>
       </c>
       <c r="G197" t="n">
-        <v>585</v>
+        <v>40</v>
       </c>
     </row>
     <row r="198">
@@ -7832,14 +7776,14 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>3330</v>
+        <v>12490</v>
       </c>
       <c r="G198" t="n">
-        <v>95</v>
+        <v>175</v>
       </c>
     </row>
     <row r="199">
@@ -7860,19 +7804,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>10990</v>
+        <v>23569</v>
       </c>
       <c r="G199" t="n">
-        <v>125</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="200">
@@ -7893,19 +7837,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>PIA_1D 55% YakisobaPan_1T</t>
+          <t>Gemhour D_Lia Choco_Keira</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>4408</v>
+        <v>8690</v>
       </c>
       <c r="G200" t="n">
-        <v>232</v>
+        <v>75</v>
       </c>
     </row>
     <row r="201">
@@ -7926,19 +7870,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>10495</v>
+        <v>2980</v>
       </c>
       <c r="G201" t="n">
-        <v>125</v>
+        <v>55</v>
       </c>
     </row>
     <row r="202">
@@ -7959,19 +7903,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1485</v>
+        <v>3190</v>
       </c>
       <c r="G202" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="203">
@@ -7992,19 +7936,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>4210</v>
+        <v>6806</v>
       </c>
       <c r="G203" t="n">
-        <v>180</v>
+        <v>409</v>
       </c>
     </row>
     <row r="204">
@@ -8025,19 +7969,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>(NEW)ALICIA BROWN(근시)</t>
+          <t>1-Day_iris_Blue Moon</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>1595</v>
+        <v>3641</v>
       </c>
       <c r="G204" t="n">
-        <v>45</v>
+        <v>154</v>
       </c>
     </row>
     <row r="205">
@@ -8058,19 +8002,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Lighly Rose Cacao(렌즈타운)</t>
+          <t>Alcon D_Allure Grey_W3C(APAC)</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>4430</v>
+        <v>1080</v>
       </c>
       <c r="G205" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
     </row>
     <row r="206">
@@ -8091,19 +8035,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>JEWEL MOON D_Pearl Moon_55%</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>415</v>
+        <v>3300</v>
       </c>
       <c r="G206" t="n">
-        <v>25</v>
+        <v>185</v>
       </c>
     </row>
     <row r="207">
@@ -8124,19 +8068,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>T-Garden D_Melty Time_55% UV 14.2</t>
+          <t>JEWEL MOON D_Topaz Moon_55%</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>3805</v>
+        <v>3107</v>
       </c>
       <c r="G207" t="n">
-        <v>290</v>
+        <v>98</v>
       </c>
     </row>
     <row r="208">
@@ -8157,19 +8101,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>14260</v>
+        <v>6125</v>
       </c>
       <c r="G208" t="n">
-        <v>690</v>
+        <v>190</v>
       </c>
     </row>
     <row r="209">
@@ -8190,19 +8134,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>19665</v>
+        <v>5620</v>
       </c>
       <c r="G209" t="n">
-        <v>250</v>
+        <v>65</v>
       </c>
     </row>
     <row r="210">
@@ -8223,7 +8167,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -8232,10 +8176,10 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>2530</v>
+        <v>2340</v>
       </c>
       <c r="G210" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
     </row>
     <row r="211">
@@ -8256,19 +8200,19 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>PIA D_Uniform Black_55% UV</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>9770</v>
+        <v>3995</v>
       </c>
       <c r="G211" t="n">
-        <v>135</v>
+        <v>180</v>
       </c>
     </row>
     <row r="212">
@@ -8294,14 +8238,14 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA_1D 55% YakisobaPan_1T</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>12470</v>
+        <v>1860</v>
       </c>
       <c r="G212" t="n">
-        <v>125</v>
+        <v>45</v>
       </c>
     </row>
     <row r="213">
@@ -8322,19 +8266,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>2950</v>
+        <v>12744</v>
       </c>
       <c r="G213" t="n">
-        <v>35</v>
+        <v>901</v>
       </c>
     </row>
     <row r="214">
@@ -8355,19 +8299,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Gold_W3(KR)</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>5700</v>
+        <v>15965</v>
       </c>
       <c r="G214" t="n">
-        <v>105</v>
+        <v>230</v>
       </c>
     </row>
     <row r="215">
@@ -8393,14 +8337,14 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>1-Day_iris_JazzBlack</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>4040</v>
+        <v>6000</v>
       </c>
       <c r="G215" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="216">
@@ -8426,14 +8370,14 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>1-Day_iris_Rhapsody</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>35726</v>
+        <v>2850</v>
       </c>
       <c r="G216" t="n">
-        <v>644</v>
+        <v>10</v>
       </c>
     </row>
     <row r="217">
@@ -8459,14 +8403,14 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>12910</v>
+        <v>12700</v>
       </c>
       <c r="G217" t="n">
-        <v>240</v>
+        <v>160</v>
       </c>
     </row>
     <row r="218">
@@ -8492,14 +8436,14 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>5570</v>
+        <v>6590</v>
       </c>
       <c r="G218" t="n">
-        <v>350</v>
+        <v>25</v>
       </c>
     </row>
     <row r="219">
@@ -8525,14 +8469,14 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>T-Garden D_Melty Time_55% UV 14.2</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
         </is>
       </c>
       <c r="F219" t="n">
-        <v>13125</v>
+        <v>9295</v>
       </c>
       <c r="G219" t="n">
-        <v>885</v>
+        <v>465</v>
       </c>
     </row>
     <row r="220">
@@ -8558,14 +8502,14 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Beige 14.2_55% UV</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>19155</v>
+        <v>7295</v>
       </c>
       <c r="G220" t="n">
-        <v>1145</v>
+        <v>235</v>
       </c>
     </row>
     <row r="221">
@@ -8595,10 +8539,10 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>23652</v>
+        <v>26605</v>
       </c>
       <c r="G221" t="n">
-        <v>3668</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="222">
@@ -8628,10 +8572,10 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>24040</v>
+        <v>21045</v>
       </c>
       <c r="G222" t="n">
-        <v>1665</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="223">
@@ -8657,14 +8601,14 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Alcon D_Chic Caramel_W4(KR)</t>
+          <t>ANW D_Spicy Gray_Dopewink 38%</t>
         </is>
       </c>
       <c r="F223" t="n">
-        <v>5115</v>
+        <v>16130</v>
       </c>
       <c r="G223" t="n">
-        <v>90</v>
+        <v>3225</v>
       </c>
     </row>
     <row r="224">
@@ -8690,14 +8634,14 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Alcon D_Chic Smoke_W4(KR)</t>
+          <t>Sincere D_Little Brown_ITFA_38% UV</t>
         </is>
       </c>
       <c r="F224" t="n">
-        <v>2375</v>
+        <v>4565</v>
       </c>
       <c r="G224" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
     </row>
     <row r="225">
@@ -8718,19 +8662,19 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Black_W3(KR)</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>940</v>
+        <v>18055</v>
       </c>
       <c r="G225" t="n">
-        <v>30</v>
+        <v>245</v>
       </c>
     </row>
     <row r="226">
@@ -8751,19 +8695,19 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Gold_W3(KR)</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>5680</v>
+        <v>9745</v>
       </c>
       <c r="G226" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="227">
@@ -8784,19 +8728,19 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Coastal_JazzBlack(신형리드지)</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>1355</v>
+        <v>2980</v>
       </c>
       <c r="G227" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="228">
@@ -8817,19 +8761,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Coastal_SoulBrown(신형리드지)</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>2920</v>
+        <v>5960</v>
       </c>
       <c r="G228" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="229">
@@ -8855,14 +8799,14 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>1174</v>
+        <v>4345</v>
       </c>
       <c r="G229" t="n">
-        <v>151</v>
+        <v>100</v>
       </c>
     </row>
     <row r="230">
@@ -8888,14 +8832,14 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>3120</v>
+        <v>7225</v>
       </c>
       <c r="G230" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
     </row>
     <row r="231">
@@ -8921,14 +8865,14 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA_1D 55% YakisobaPan_1T</t>
         </is>
       </c>
       <c r="F231" t="n">
-        <v>2960</v>
+        <v>1875</v>
       </c>
       <c r="G231" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="232">
@@ -8954,14 +8898,14 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F232" t="n">
-        <v>8045</v>
+        <v>5535</v>
       </c>
       <c r="G232" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="233">
@@ -8977,21 +8921,21 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>PIA D_Sakura Mousse_55% UV</t>
+          <t>Toric_CP-0.75_Halo Brown</t>
         </is>
       </c>
       <c r="F233" t="n">
-        <v>1770</v>
+        <v>2915</v>
       </c>
       <c r="G233" t="n">
         <v>20</v>
@@ -9010,24 +8954,24 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>PIA_1D 55% YakisobaPan_1T</t>
+          <t>Toric_CP-0.75_Halo Gray</t>
         </is>
       </c>
       <c r="F234" t="n">
-        <v>6195</v>
+        <v>5540</v>
       </c>
       <c r="G234" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
     </row>
     <row r="235">
@@ -9043,24 +8987,24 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>Toric_CP-1.25_Halo Brown</t>
         </is>
       </c>
       <c r="F235" t="n">
-        <v>3300</v>
+        <v>1350</v>
       </c>
       <c r="G235" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="236">
@@ -9076,24 +9020,24 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>Toric_CP-1.25_Halo Gray</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>1235</v>
+        <v>1800</v>
       </c>
       <c r="G236" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="237">
@@ -9109,24 +9053,24 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>PIA_Shiny Brown_55%_14.5_1-DAY</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>1580</v>
+        <v>2085</v>
       </c>
       <c r="G237" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="238">
@@ -9147,19 +9091,19 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F238" t="n">
-        <v>4060</v>
+        <v>6160</v>
       </c>
       <c r="G238" t="n">
-        <v>30</v>
+        <v>135</v>
       </c>
     </row>
     <row r="239">
@@ -9180,19 +9124,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Gray</t>
+          <t>Toric_CP-0.75_Halo Brown</t>
         </is>
       </c>
       <c r="F239" t="n">
-        <v>3607</v>
+        <v>4880</v>
       </c>
       <c r="G239" t="n">
-        <v>2468</v>
+        <v>55</v>
       </c>
     </row>
     <row r="240">
@@ -9213,19 +9157,19 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Gray</t>
+          <t>Toric_CP-1.25_Halo Brown</t>
         </is>
       </c>
       <c r="F240" t="n">
-        <v>5165</v>
+        <v>21620</v>
       </c>
       <c r="G240" t="n">
-        <v>85</v>
+        <v>235</v>
       </c>
     </row>
     <row r="241">
@@ -9246,19 +9190,19 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
       <c r="F241" t="n">
-        <v>2475</v>
+        <v>23645</v>
       </c>
       <c r="G241" t="n">
-        <v>25</v>
+        <v>255</v>
       </c>
     </row>
     <row r="242">
@@ -9279,19 +9223,19 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Brown</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F242" t="n">
-        <v>2860</v>
+        <v>1705</v>
       </c>
       <c r="G242" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="243">
@@ -9307,24 +9251,24 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F243" t="n">
-        <v>5615</v>
+        <v>41675</v>
       </c>
       <c r="G243" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
     </row>
     <row r="244">
@@ -9340,24 +9284,24 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F244" t="n">
-        <v>7094</v>
+        <v>42089</v>
       </c>
       <c r="G244" t="n">
-        <v>1021</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="245">
@@ -9373,7 +9317,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -9383,14 +9327,14 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>1-Day_SOLEKO(5년)</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>12540</v>
+        <v>14935</v>
       </c>
       <c r="G245" t="n">
-        <v>190</v>
+        <v>505</v>
       </c>
     </row>
     <row r="246">
@@ -9406,24 +9350,24 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F246" t="n">
-        <v>11755</v>
+        <v>29650</v>
       </c>
       <c r="G246" t="n">
-        <v>145</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="247">
@@ -9439,24 +9383,24 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>PIA_Date topaz CP-0.75 Toric_UV</t>
+          <t>1-Day_Contakt(유효기간_8년)</t>
         </is>
       </c>
       <c r="F247" t="n">
-        <v>14727</v>
+        <v>4375</v>
       </c>
       <c r="G247" t="n">
-        <v>1938</v>
+        <v>110</v>
       </c>
     </row>
     <row r="248">
@@ -9472,24 +9416,24 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>PIA_Date topaz CP-1.25 Toric_UV</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F248" t="n">
-        <v>9065</v>
+        <v>13980</v>
       </c>
       <c r="G248" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
     </row>
     <row r="249">
@@ -9510,19 +9454,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>1-DAY58_Micure</t>
+          <t>1-Day_SOLEKO(5년)</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>54778</v>
+        <v>28055</v>
       </c>
       <c r="G249" t="n">
-        <v>1947</v>
+        <v>685</v>
       </c>
     </row>
     <row r="250">
@@ -9543,7 +9487,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -9552,10 +9496,10 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>20430</v>
+        <v>12780</v>
       </c>
       <c r="G250" t="n">
-        <v>1355</v>
+        <v>615</v>
       </c>
     </row>
     <row r="251">
@@ -9576,19 +9520,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>1-DAY_58_공용_MD로고</t>
+          <t>1-Day_Metha_Coastal</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>10290</v>
+        <v>6490</v>
       </c>
       <c r="G251" t="n">
-        <v>300</v>
+        <v>190</v>
       </c>
     </row>
     <row r="252">
@@ -9609,30 +9553,30 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>1-Day_Contakt(유효기간_8년)</t>
+          <t>1-Day_SOLEKO(5년)</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>16028</v>
+        <v>7905</v>
       </c>
       <c r="G252" t="n">
-        <v>2677</v>
+        <v>555</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9642,151 +9586,151 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>18220</v>
+        <v>37456</v>
       </c>
       <c r="G253" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>B형 조립중합3호기</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>1-DAY58_Micure</t>
+          <t>O2O2 D_Blending Hazel EX</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>20088</v>
+        <v>29560</v>
       </c>
       <c r="G254" t="n">
-        <v>1302</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>B형 조립중합4호기</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>1-DAY58_Micure</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>17392</v>
+        <v>28457</v>
       </c>
       <c r="G255" t="n">
-        <v>2178</v>
+        <v>4472</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>B형 조립중합6호기</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>1-Day_Metha_Coastal</t>
+          <t>O2O2 D_Ash Brown EX</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>11805</v>
+        <v>17805</v>
       </c>
       <c r="G256" t="n">
-        <v>265</v>
+        <v>705</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Metha_Daily</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F257" t="n">
-        <v>4425</v>
+        <v>20722</v>
       </c>
       <c r="G257" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -9802,21 +9746,21 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F258" t="n">
-        <v>18407</v>
+        <v>36605</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
@@ -9835,24 +9779,24 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>B형 조립중합4호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F259" t="n">
-        <v>30689</v>
+        <v>16791</v>
       </c>
       <c r="G259" t="n">
-        <v>1402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -9863,29 +9807,29 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>CAM분리2호기</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F260" t="n">
-        <v>16403</v>
+        <v>8640</v>
       </c>
       <c r="G260" t="n">
-        <v>0</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="261">
@@ -9896,29 +9840,29 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>CAM분리3호기</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F261" t="n">
-        <v>42426</v>
+        <v>17313</v>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
+        <v>3794</v>
       </c>
     </row>
     <row r="262">
@@ -9929,29 +9873,29 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>B형 분리수화접착6호기</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F262" t="n">
-        <v>40565</v>
+        <v>20096</v>
       </c>
       <c r="G262" t="n">
-        <v>0</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="263">
@@ -9962,29 +9906,29 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F263" t="n">
-        <v>24193</v>
+        <v>6296</v>
       </c>
       <c r="G263" t="n">
-        <v>0</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="264">
@@ -10005,19 +9949,19 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>B형 분리수화접착6호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 D_Ash Brown EX</t>
         </is>
       </c>
       <c r="F264" t="n">
-        <v>17394</v>
+        <v>2374</v>
       </c>
       <c r="G264" t="n">
-        <v>2095</v>
+        <v>233</v>
       </c>
     </row>
     <row r="265">
@@ -10038,19 +9982,19 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Brown EX</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F265" t="n">
-        <v>17192</v>
+        <v>1631</v>
       </c>
       <c r="G265" t="n">
-        <v>2781</v>
+        <v>371</v>
       </c>
     </row>
     <row r="266">
@@ -10076,14 +10020,14 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 D_Ash Brown EX</t>
         </is>
       </c>
       <c r="F266" t="n">
-        <v>11251</v>
+        <v>6113</v>
       </c>
       <c r="G266" t="n">
-        <v>2340</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="267">
@@ -10099,24 +10043,24 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Brown EX</t>
+          <t>O2O2_Multifocal_K2_SMD</t>
         </is>
       </c>
       <c r="F267" t="n">
-        <v>1601</v>
+        <v>3069</v>
       </c>
       <c r="G267" t="n">
-        <v>1579</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="268">
@@ -10132,24 +10076,24 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>7494</v>
+        <v>29501</v>
       </c>
       <c r="G268" t="n">
-        <v>1130</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="269">
@@ -10165,24 +10109,24 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>1937</v>
+        <v>44020</v>
       </c>
       <c r="G269" t="n">
-        <v>135</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="270">
@@ -10198,24 +10142,24 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMDH_OPHTALMIC</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>14248</v>
+        <v>22237</v>
       </c>
       <c r="G270" t="n">
-        <v>2226</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="271">
@@ -10236,7 +10180,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착3호기</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -10245,10 +10189,10 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>14632</v>
+        <v>10966</v>
       </c>
       <c r="G271" t="n">
-        <v>822</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="272">
@@ -10269,7 +10213,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>B형 분리수화접착4호기</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -10278,10 +10222,10 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>17208</v>
+        <v>11508</v>
       </c>
       <c r="G272" t="n">
-        <v>336</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="273">
@@ -10302,19 +10246,19 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>O2O2 Spherical(DK70)_K2-SMD</t>
         </is>
       </c>
       <c r="F273" t="n">
-        <v>16209</v>
+        <v>1682</v>
       </c>
       <c r="G273" t="n">
-        <v>3707</v>
+        <v>454</v>
       </c>
     </row>
     <row r="274">
@@ -10335,7 +10279,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -10344,10 +10288,10 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>22153</v>
+        <v>10036</v>
       </c>
       <c r="G274" t="n">
-        <v>3649</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="275">
@@ -10358,29 +10302,29 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>JEWEL MOON D_Cherry Moon</t>
         </is>
       </c>
       <c r="F275" t="n">
-        <v>9588</v>
+        <v>3220</v>
       </c>
       <c r="G275" t="n">
-        <v>1230</v>
+        <v>189</v>
       </c>
     </row>
     <row r="276">
@@ -10401,7 +10345,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -10410,10 +10354,10 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>2391</v>
+        <v>265</v>
       </c>
       <c r="G276" t="n">
-        <v>1024</v>
+        <v>50</v>
       </c>
     </row>
     <row r="277">
@@ -10439,14 +10383,14 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Cherry Moon</t>
+          <t>JEWEL MOON D_Creamy Moon</t>
         </is>
       </c>
       <c r="F277" t="n">
-        <v>3720</v>
+        <v>2895</v>
       </c>
       <c r="G277" t="n">
-        <v>739</v>
+        <v>45</v>
       </c>
     </row>
     <row r="278">
@@ -10472,14 +10416,14 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Creamy Moon</t>
+          <t>JEWEL MOON D_Ice gray Moon</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>2637</v>
+        <v>1940</v>
       </c>
       <c r="G278" t="n">
-        <v>983</v>
+        <v>74</v>
       </c>
     </row>
     <row r="279">
@@ -10495,24 +10439,24 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Ice gray Moon</t>
+          <t>Clalen oneday A(O2 Edition)</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>456</v>
+        <v>10855</v>
       </c>
       <c r="G279" t="n">
-        <v>974</v>
+        <v>275</v>
       </c>
     </row>
     <row r="280">
@@ -10528,24 +10472,24 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Clalen oneday A(O2 Edition)</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>33183</v>
+        <v>11741</v>
       </c>
       <c r="G280" t="n">
-        <v>869</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="281">
@@ -10571,14 +10515,14 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Brown EX</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>10592</v>
+        <v>655</v>
       </c>
       <c r="G281" t="n">
-        <v>1958</v>
+        <v>14</v>
       </c>
     </row>
     <row r="282">
@@ -10604,14 +10548,14 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Gray EX</t>
+          <t>O2O2 D_Ash Brown EX</t>
         </is>
       </c>
       <c r="F282" t="n">
-        <v>2543</v>
+        <v>21970</v>
       </c>
       <c r="G282" t="n">
-        <v>4255</v>
+        <v>620</v>
       </c>
     </row>
     <row r="283">
@@ -10632,19 +10576,19 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 D_Ash Gray EX</t>
         </is>
       </c>
       <c r="F283" t="n">
-        <v>36105</v>
+        <v>14775</v>
       </c>
       <c r="G283" t="n">
-        <v>962</v>
+        <v>425</v>
       </c>
     </row>
     <row r="284">
@@ -10670,14 +10614,14 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F284" t="n">
-        <v>3962</v>
+        <v>5500</v>
       </c>
       <c r="G284" t="n">
-        <v>301</v>
+        <v>190</v>
       </c>
     </row>
     <row r="285">
@@ -10703,14 +10647,14 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Mute Brown_45%</t>
+          <t>Clalen O2O2 D_Lake Gray_45%</t>
         </is>
       </c>
       <c r="F285" t="n">
-        <v>2480</v>
+        <v>1395</v>
       </c>
       <c r="G285" t="n">
-        <v>78</v>
+        <v>22</v>
       </c>
     </row>
     <row r="286">
@@ -10740,10 +10684,10 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>482</v>
+        <v>4203</v>
       </c>
       <c r="G286" t="n">
-        <v>1123</v>
+        <v>685</v>
       </c>
     </row>
     <row r="287">
@@ -10773,10 +10717,10 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>25685</v>
+        <v>2285</v>
       </c>
       <c r="G287" t="n">
-        <v>2536</v>
+        <v>163</v>
       </c>
     </row>
     <row r="288">
@@ -10806,10 +10750,10 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>41226</v>
+        <v>48810</v>
       </c>
       <c r="G288" t="n">
-        <v>1844</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="289">
@@ -10839,10 +10783,10 @@
         </is>
       </c>
       <c r="F289" t="n">
-        <v>16490</v>
+        <v>37562</v>
       </c>
       <c r="G289" t="n">
-        <v>293</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="290">
@@ -10863,7 +10807,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -10872,10 +10816,10 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>11315</v>
+        <v>22465</v>
       </c>
       <c r="G290" t="n">
-        <v>321</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="291">
@@ -10896,7 +10840,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>A형 인라인6호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -10905,10 +10849,10 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>20630</v>
+        <v>29639</v>
       </c>
       <c r="G291" t="n">
-        <v>641</v>
+        <v>2980</v>
       </c>
     </row>
   </sheetData>

--- a/생산실적현황(설비운영현황).xlsx
+++ b/생산실적현황(설비운영현황).xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -537,11 +537,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -549,7 +549,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMD</t>
+          <t>T38_(UV포함)</t>
         </is>
       </c>
     </row>
@@ -565,11 +565,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Si_1-Day_Toric</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -577,7 +577,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>O2O2 D_UV_Toric_SMD</t>
+          <t>O2O2_Multifocal_K2_SMD</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>(NEW)MG M_No.1 Hazel_GLAM_(중)</t>
+          <t>Date Topaz_PIA_M_(중)(Y)</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Si_FRP_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -745,35 +745,35 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>O2O2 M_Natural Chocolat EX_(중)</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A관(1공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
     </row>
@@ -789,19 +789,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
     </row>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -829,7 +829,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
         </is>
       </c>
     </row>
@@ -841,23 +841,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
     </row>
@@ -877,15 +877,15 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
     </row>
@@ -905,15 +905,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
     </row>
@@ -925,23 +925,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
     </row>
@@ -957,35 +957,35 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>S관(3공장)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
     </row>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
     </row>
@@ -1041,19 +1041,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1065,15 +1065,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
     </row>
@@ -1101,15 +1101,15 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
     </row>
@@ -1129,15 +1129,15 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2_Multifocal_K2_SMD</t>
         </is>
       </c>
     </row>
@@ -1157,15 +1157,15 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMD</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1177,23 +1177,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>BELLA D_Garnet</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G268"/>
+  <dimension ref="A1:G283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1300,8 +1300,8 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="56" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>96337</v>
+        <v>45266</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>102240</v>
+        <v>51742</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>51267</v>
+        <v>93710</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>조립5호기</t>
+          <t>조립8호기</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>18532</v>
+        <v>19267</v>
       </c>
       <c r="G5" t="n">
-        <v>2715</v>
+        <v>846</v>
       </c>
     </row>
     <row r="6">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>조립8호기</t>
+          <t>조립1호기</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Metha_55</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>17716</v>
+        <v>29551</v>
       </c>
       <c r="G6" t="n">
-        <v>1544</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="7">
@@ -1519,24 +1519,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>조립1호기</t>
+          <t>조립2호기</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Metha_55</t>
+          <t>T38_(UV포함)</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>32060</v>
+        <v>2980</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="8">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>8013</v>
+        <v>4458</v>
       </c>
       <c r="G8" t="n">
-        <v>540</v>
+        <v>640</v>
       </c>
     </row>
     <row r="9">
@@ -1580,29 +1580,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Si_1-Day_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>조립7호기</t>
+          <t>분리14호기</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>O2O2 D_UV_Toric_SMD</t>
+          <t>1-Day_Metha</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4342</v>
+        <v>1605</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
     </row>
     <row r="10">
@@ -1618,24 +1618,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>FRP_M/F</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>분리14호기</t>
+          <t>분리5호기</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1-Day_Metha</t>
+          <t>Bi-focal_8.40</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9354</v>
+        <v>13594</v>
       </c>
       <c r="G10" t="n">
-        <v>1333</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="11">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FRP_M/F</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1661,14 +1661,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bi-focal_8.40</t>
+          <t>Metha</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1717</v>
+        <v>28083</v>
       </c>
       <c r="G11" t="n">
-        <v>213</v>
+        <v>4173</v>
       </c>
     </row>
     <row r="12">
@@ -1684,24 +1684,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FRP_M/F</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>분리5호기</t>
+          <t>분리4호기</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bi-focal_8.40</t>
+          <t>S55-Dry</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14290</v>
+        <v>6374</v>
       </c>
       <c r="G12" t="n">
-        <v>1845</v>
+        <v>461</v>
       </c>
     </row>
     <row r="13">
@@ -1717,24 +1717,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>분리10호기</t>
+          <t>분리3호기</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.4</t>
+          <t>T38_(UV포함)</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5576</v>
+        <v>501</v>
       </c>
       <c r="G13" t="n">
-        <v>675</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -1750,24 +1750,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>분리11호기</t>
+          <t>분리3호기</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(NEW)S43-HD-Dry-14.4</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3755</v>
+        <v>1140</v>
       </c>
       <c r="G14" t="n">
-        <v>447</v>
+        <v>563</v>
       </c>
     </row>
     <row r="15">
@@ -1778,29 +1778,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>분리14호기</t>
+          <t>검사15호기</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Metha</t>
+          <t>(NEW)MG M_No.1 Hazel_GLAM_(중)</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>24035</v>
+        <v>155</v>
       </c>
       <c r="G15" t="n">
-        <v>2250</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -1811,29 +1811,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>분리4호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S55-Dry</t>
+          <t>Bella Diamond_14.5_중사각</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>12225</v>
+        <v>1026</v>
       </c>
       <c r="G16" t="n">
-        <v>1897</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
@@ -1844,29 +1844,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>분리3호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>Bella-Natural_중사각</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1704</v>
+        <v>68</v>
       </c>
       <c r="G17" t="n">
-        <v>607</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -1887,19 +1887,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>검사15호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(NEW)MG M_No.1 Hazel_GLAM_(중)</t>
+          <t>Cream Rose_PIA_M_(중)</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3242</v>
+        <v>2252</v>
       </c>
       <c r="G18" t="n">
-        <v>480</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
@@ -1920,19 +1920,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>검사15호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MG M_Glow Hazel_GLAM_(중)</t>
+          <t>Date Topaz_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1495</v>
+        <v>3830</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20">
@@ -1953,19 +1953,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>검사15호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MG M_Perfect Brown_GLAM_(중)</t>
+          <t>Aquarella_Amazonia Green_원형</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>173</v>
+        <v>301</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1986,19 +1986,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
+          <t>Aquarella_Dandara Hazel_원형</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>437</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2019,16 +2019,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Clalen 1M_Planet_Gray Moon</t>
+          <t>Festival-II-Color_원형</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>373</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -2052,19 +2052,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>검사6호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Coffee Jelly_PIA_M_(중)(Y)</t>
+          <t>NewFusion_원형</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>408</v>
+        <v>599</v>
       </c>
       <c r="G23" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2085,19 +2085,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Clalen Iris_GRA_2902_원형</t>
+          <t>Bella Diamond_14.5_중사각</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="G24" t="n">
-        <v>2556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2118,19 +2118,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Clalen Iris_GRA_3302_원형</t>
+          <t>Bella-Elite_14.5_중사각</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>90</v>
+        <v>1084</v>
       </c>
       <c r="G25" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2151,19 +2151,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CLC-30_바이알</t>
+          <t>Cream Rose_PIA_M_(중)</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2581</v>
+        <v>1354</v>
       </c>
       <c r="G26" t="n">
-        <v>235</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27">
@@ -2184,19 +2184,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Festival-II-Color_은캡</t>
+          <t>Date Topaz_PIA_M_(중)(Y)</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2987</v>
+        <v>1362</v>
       </c>
       <c r="G27" t="n">
-        <v>512</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28">
@@ -2212,24 +2212,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>Melty Butter_PIA_M_(중)</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>7281</v>
+        <v>1414</v>
       </c>
       <c r="G28" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29">
@@ -2245,24 +2245,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사21호기</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>Mocha Ring_PIA_M_(중)</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6704</v>
+        <v>1432</v>
       </c>
       <c r="G29" t="n">
-        <v>512</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30">
@@ -2278,24 +2278,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>MG M_Perfect Brown_원형</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>11594</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>159</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
@@ -2311,24 +2311,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Metha_55_중사각</t>
+          <t>CLC-30_바이알</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1298</v>
+        <v>1351</v>
       </c>
       <c r="G31" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5980</v>
+        <v>4966</v>
       </c>
       <c r="G32" t="n">
-        <v>79</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33">
@@ -2382,19 +2382,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>(UV)CS30_원형_8.60</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>178</v>
+        <v>6468</v>
       </c>
       <c r="G33" t="n">
-        <v>17</v>
+        <v>236</v>
       </c>
     </row>
     <row r="34">
@@ -2415,19 +2415,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CS30_원형_8.60</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>998</v>
+        <v>786</v>
       </c>
       <c r="G34" t="n">
-        <v>149</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
@@ -2448,19 +2448,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Metha_55_원형</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>7124</v>
+        <v>8904</v>
       </c>
       <c r="G35" t="n">
-        <v>282</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36">
@@ -2481,19 +2481,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>6802</v>
+        <v>2636</v>
       </c>
       <c r="G36" t="n">
-        <v>294</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37">
@@ -2514,19 +2514,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1990</v>
+        <v>5176</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38">
@@ -2547,19 +2547,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Metha_55_원형</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>10232</v>
+        <v>4544</v>
       </c>
       <c r="G38" t="n">
-        <v>255</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39">
@@ -2580,19 +2580,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>검사9호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Metha_55_원형</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>9896</v>
+        <v>8386</v>
       </c>
       <c r="G39" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40">
@@ -2613,19 +2613,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>S38_은캡(BLUE TINT)</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>966</v>
+        <v>3668</v>
       </c>
       <c r="G40" t="n">
-        <v>115</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41">
@@ -2641,24 +2641,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>Metha_55_원형</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>372</v>
+        <v>8486</v>
       </c>
       <c r="G41" t="n">
-        <v>63</v>
+        <v>347</v>
       </c>
     </row>
     <row r="42">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>T38_금캡</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>417</v>
+        <v>3468</v>
       </c>
       <c r="G42" t="n">
-        <v>22</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43">
@@ -2707,24 +2707,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>T38_금캡(UV포함)</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>4950</v>
+        <v>1032</v>
       </c>
       <c r="G43" t="n">
-        <v>1046</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44">
@@ -2740,24 +2740,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Si_FRP_Color_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>검사23호기</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>O2O2 M_Natural Chocolat EX_(중)</t>
+          <t>Metha_55_원형</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>7810</v>
+        <v>1456</v>
       </c>
       <c r="G44" t="n">
-        <v>810</v>
+        <v>319</v>
       </c>
     </row>
     <row r="45">
@@ -2773,24 +2773,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
+          <t>Metha_55_원형</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>892</v>
+        <v>4648</v>
       </c>
       <c r="G45" t="n">
-        <v>42</v>
+        <v>176</v>
       </c>
     </row>
     <row r="46">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
+          <t>S38 원형(Green)</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>958</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="47">
@@ -2839,24 +2839,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>검사9호기</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
+          <t>Metha_55_원형</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1038</v>
+        <v>5278</v>
       </c>
       <c r="G47" t="n">
-        <v>31</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48">
@@ -2872,24 +2872,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>S38_은캡(BLUE TINT)</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2746</v>
+        <v>349</v>
       </c>
       <c r="G48" t="n">
-        <v>722</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -2905,24 +2905,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3464</v>
+        <v>440</v>
       </c>
       <c r="G49" t="n">
-        <v>114</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50">
@@ -2938,24 +2938,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2953</v>
+        <v>498</v>
       </c>
       <c r="G50" t="n">
-        <v>437</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51">
@@ -2971,90 +2971,90 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>Si_FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사16호기</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>O2O2 M_Natural Chocolat EX_(중)</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>5018</v>
+        <v>670</v>
       </c>
       <c r="G51" t="n">
-        <v>1320</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>조립10호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Sapphire Moon_55%</t>
+          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>31448</v>
+        <v>364</v>
       </c>
       <c r="G52" t="n">
-        <v>3475</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>조립11호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PIA D_Princess Chocolat_55%_14.5 UV</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>25750</v>
+        <v>5566</v>
       </c>
       <c r="G53" t="n">
-        <v>1847</v>
+        <v>841</v>
       </c>
     </row>
     <row r="54">
@@ -3075,19 +3075,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>조립12호기</t>
+          <t>조립10호기</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>JEWEL MOON D_Sapphire Moon_55%</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>49483</v>
+        <v>14159</v>
       </c>
       <c r="G54" t="n">
-        <v>6162</v>
+        <v>4695</v>
       </c>
     </row>
     <row r="55">
@@ -3108,19 +3108,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>조립13호기</t>
+          <t>조립11호기</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA D_Princess Chocolat_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>26714</v>
+        <v>51249</v>
       </c>
       <c r="G55" t="n">
-        <v>2063</v>
+        <v>3899</v>
       </c>
     </row>
     <row r="56">
@@ -3141,19 +3141,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>조립14호기</t>
+          <t>조립12호기</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>54920</v>
+        <v>29077</v>
       </c>
       <c r="G56" t="n">
-        <v>7766</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="57">
@@ -3174,19 +3174,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>조립15호기</t>
+          <t>조립13호기</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HOYA_Maquia Brown</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>7807</v>
+        <v>27660</v>
       </c>
       <c r="G57" t="n">
-        <v>4471</v>
+        <v>4306</v>
       </c>
     </row>
     <row r="58">
@@ -3207,19 +3207,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>조립16호기</t>
+          <t>조립14호기</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>51244</v>
+        <v>30438</v>
       </c>
       <c r="G58" t="n">
-        <v>2849</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3240,19 +3240,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>조립19호기</t>
+          <t>조립15호기</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>27269</v>
+        <v>47828</v>
       </c>
       <c r="G59" t="n">
-        <v>1350</v>
+        <v>978</v>
       </c>
     </row>
     <row r="60">
@@ -3273,19 +3273,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>조립23호기</t>
+          <t>조립16호기</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hapa D_Crush Brown_Secretive</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>23209</v>
+        <v>25691</v>
       </c>
       <c r="G60" t="n">
-        <v>315</v>
+        <v>800</v>
       </c>
     </row>
     <row r="61">
@@ -3306,19 +3306,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>조립24호기</t>
+          <t>조립18호기</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>20231</v>
+        <v>10472</v>
       </c>
       <c r="G61" t="n">
-        <v>3654</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="62">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>조립25호기</t>
+          <t>조립19호기</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>13036</v>
+        <v>48560</v>
       </c>
       <c r="G62" t="n">
-        <v>511</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="63">
@@ -3372,19 +3372,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>조립26호기</t>
+          <t>조립23호기</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rina_Crystal Gray_1-Day</t>
+          <t>Hapa D_Glazed Kristin_Choco</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>25754</v>
+        <v>25539</v>
       </c>
       <c r="G63" t="n">
-        <v>36</v>
+        <v>700</v>
       </c>
     </row>
     <row r="64">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>조립27호기</t>
+          <t>조립24호기</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3414,10 +3414,10 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>26382</v>
+        <v>39494</v>
       </c>
       <c r="G64" t="n">
-        <v>5270</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="65">
@@ -3438,19 +3438,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>조립42호기</t>
+          <t>조립25호기</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Clalen D_XUYU_55%</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>17323</v>
+        <v>20788</v>
       </c>
       <c r="G65" t="n">
-        <v>596</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="66">
@@ -3471,19 +3471,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>조립44호기</t>
+          <t>조립26호기</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PIA D_Baby Espresso_38% UV</t>
+          <t>Rina_Crystal Gray_1-Day</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>21984</v>
+        <v>19038</v>
       </c>
       <c r="G66" t="n">
-        <v>2037</v>
+        <v>8393</v>
       </c>
     </row>
     <row r="67">
@@ -3504,19 +3504,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>조립45호기</t>
+          <t>조립27호기</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Black_W3</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>19320</v>
+        <v>11190</v>
       </c>
       <c r="G67" t="n">
-        <v>1300</v>
+        <v>800</v>
       </c>
     </row>
     <row r="68">
@@ -3537,19 +3537,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>조립46호기</t>
+          <t>조립42호기</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Gold_W3</t>
+          <t>JEWEL MOON D_Topaz Moon_55%</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>6666</v>
+        <v>21134</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="69">
@@ -3570,19 +3570,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>조립47호기</t>
+          <t>조립44호기</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PIA_Lemonade_55%_1-DAY</t>
+          <t>PIA D_Baby Espresso_38% UV</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>12991</v>
+        <v>29228</v>
       </c>
       <c r="G69" t="n">
-        <v>3407</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="70">
@@ -3603,19 +3603,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>조립48호기</t>
+          <t>조립45호기</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>Alcon D_Jewel Black_W3</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>24722</v>
+        <v>17940</v>
       </c>
       <c r="G70" t="n">
-        <v>2709</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="71">
@@ -3636,19 +3636,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>조립49호기</t>
+          <t>조립47호기</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Sunstone Moon_55%</t>
+          <t>PIA_Lemonade_55%_1-DAY</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>25189</v>
+        <v>39732</v>
       </c>
       <c r="G71" t="n">
-        <v>2000</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="72">
@@ -3669,19 +3669,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>조립50호기</t>
+          <t>조립48호기</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>59252</v>
+        <v>23292</v>
       </c>
       <c r="G72" t="n">
-        <v>130</v>
+        <v>3687</v>
       </c>
     </row>
     <row r="73">
@@ -3702,19 +3702,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>조립52호기</t>
+          <t>조립49호기</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>Gemhour D_Liz Brown_Keira</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>74105</v>
+        <v>23797</v>
       </c>
       <c r="G73" t="n">
-        <v>2877</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -3735,19 +3735,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>조립53호기</t>
+          <t>조립50호기</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>From D_(UV)Clear Beige Coral_38%</t>
+          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>26992</v>
+        <v>28536</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="75">
@@ -3768,19 +3768,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>조립54호기</t>
+          <t>조립51호기</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>From D_(UV)Clear Beige_38%</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>16878</v>
+        <v>28458</v>
       </c>
       <c r="G75" t="n">
-        <v>612</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="76">
@@ -3801,19 +3801,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>조립54호기</t>
+          <t>조립52호기</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>32032</v>
+        <v>20403</v>
       </c>
       <c r="G76" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77">
@@ -3834,19 +3834,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>조립55호기</t>
+          <t>조립53호기</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PIA D_Strawberry Quartz_38% UV</t>
+          <t>PIA D_Mocha Ring_38% UV</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>25421</v>
+        <v>29111</v>
       </c>
       <c r="G77" t="n">
-        <v>5912</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -3867,19 +3867,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>조립56호기</t>
+          <t>조립54호기</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>57546</v>
+        <v>51852</v>
       </c>
       <c r="G78" t="n">
-        <v>2608</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="79">
@@ -3900,19 +3900,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>조립57호기</t>
+          <t>조립55호기</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Strawberry Quartz_38% UV</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>20728</v>
+        <v>23118</v>
       </c>
       <c r="G79" t="n">
-        <v>3050</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="80">
@@ -3933,19 +3933,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>조립58호기</t>
+          <t>조립56호기</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>PIA D_Date Topaz_38% UV</t>
+          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>8277</v>
+        <v>25812</v>
       </c>
       <c r="G80" t="n">
-        <v>602</v>
+        <v>996</v>
       </c>
     </row>
     <row r="81">
@@ -3966,19 +3966,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>조립59호기</t>
+          <t>조립57호기</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PIA D_Melty Butter_55%_14.5 UV</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>25294</v>
+        <v>28572</v>
       </c>
       <c r="G81" t="n">
-        <v>3693</v>
+        <v>671</v>
       </c>
     </row>
     <row r="82">
@@ -3994,24 +3994,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립58호기</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>PIA D_Date Topaz_38% UV</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>15714</v>
+        <v>51606</v>
       </c>
       <c r="G82" t="n">
-        <v>833</v>
+        <v>3622</v>
       </c>
     </row>
     <row r="83">
@@ -4027,24 +4027,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립59호기</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>4839</v>
+        <v>57993</v>
       </c>
       <c r="G83" t="n">
-        <v>663</v>
+        <v>794</v>
       </c>
     </row>
     <row r="84">
@@ -4065,19 +4065,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Brown</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>8112</v>
+        <v>4933</v>
       </c>
       <c r="G84" t="n">
-        <v>1865</v>
+        <v>513</v>
       </c>
     </row>
     <row r="85">
@@ -4098,19 +4098,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Gray</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3874</v>
+        <v>10031</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>834</v>
       </c>
     </row>
     <row r="86">
@@ -4131,19 +4131,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>5317</v>
+        <v>4918</v>
       </c>
       <c r="G86" t="n">
-        <v>666</v>
+        <v>514</v>
       </c>
     </row>
     <row r="87">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>5230</v>
+        <v>4955</v>
       </c>
       <c r="G87" t="n">
-        <v>2585</v>
+        <v>3362</v>
       </c>
     </row>
     <row r="88">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1767</v>
+        <v>25400</v>
       </c>
       <c r="G88" t="n">
-        <v>2117</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="89">
@@ -4230,19 +4230,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>조립46호기</t>
+          <t>조립40호기</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
+          <t>Chai Cafe_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>21249</v>
+        <v>28331</v>
       </c>
       <c r="G89" t="n">
-        <v>1564</v>
+        <v>4146</v>
       </c>
     </row>
     <row r="90">
@@ -4253,29 +4253,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>조립46호기</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
+          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>24163</v>
+        <v>28958</v>
       </c>
       <c r="G90" t="n">
-        <v>3396</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="91">
@@ -4301,14 +4301,14 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>22455</v>
+        <v>14236</v>
       </c>
       <c r="G91" t="n">
-        <v>2881</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="92">
@@ -4329,19 +4329,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>Rina_Crystal Gray_1-Day</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>46735</v>
+        <v>31595</v>
       </c>
       <c r="G92" t="n">
-        <v>5192</v>
+        <v>3649</v>
       </c>
     </row>
     <row r="93">
@@ -4362,19 +4362,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>17764</v>
+        <v>14266</v>
       </c>
       <c r="G93" t="n">
-        <v>2123</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="94">
@@ -4395,19 +4395,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PIA D_Princess Chocolat_55%_14.5 UV</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>24809</v>
+        <v>10396</v>
       </c>
       <c r="G94" t="n">
-        <v>2824</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="95">
@@ -4428,19 +4428,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HOYA_Casual Ash</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>11924</v>
+        <v>13289</v>
       </c>
       <c r="G95" t="n">
-        <v>2074</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="96">
@@ -4461,19 +4461,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>19852</v>
+        <v>12733</v>
       </c>
       <c r="G96" t="n">
-        <v>3615</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="97">
@@ -4494,19 +4494,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>20310</v>
+        <v>17919</v>
       </c>
       <c r="G97" t="n">
-        <v>2848</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="98">
@@ -4527,19 +4527,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Alcon D_Allure Blue_W3C</t>
+          <t>HOYA_Casual Ash</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>16606</v>
+        <v>8888</v>
       </c>
       <c r="G98" t="n">
-        <v>1647</v>
+        <v>3907</v>
       </c>
     </row>
     <row r="99">
@@ -4560,19 +4560,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Sapphire Moon_55%</t>
+          <t>HOYA_Maquia Brown</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>8251</v>
+        <v>5184</v>
       </c>
       <c r="G99" t="n">
-        <v>1158</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="100">
@@ -4593,19 +4593,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>분리19호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>39250</v>
+        <v>2783</v>
       </c>
       <c r="G100" t="n">
-        <v>4832</v>
+        <v>586</v>
       </c>
     </row>
     <row r="101">
@@ -4626,19 +4626,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>분리19호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>JEWEL MOON D_Sapphire Moon_55%</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1410</v>
+        <v>17501</v>
       </c>
       <c r="G101" t="n">
-        <v>271</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="102">
@@ -4659,19 +4659,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>JEWEL MOON D_Sunstone Moon_55%</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>36800</v>
+        <v>22546</v>
       </c>
       <c r="G102" t="n">
-        <v>2611</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="103">
@@ -4692,19 +4692,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리19호기</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Gold_W3</t>
+          <t>Alcon D_Jewel Black_W3</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3202</v>
+        <v>16773</v>
       </c>
       <c r="G103" t="n">
-        <v>380</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="104">
@@ -4725,19 +4725,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>분리19호기</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>19579</v>
+        <v>15024</v>
       </c>
       <c r="G104" t="n">
-        <v>3014</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="105">
@@ -4758,19 +4758,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>6397</v>
+        <v>41736</v>
       </c>
       <c r="G105" t="n">
-        <v>753</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="106">
@@ -4791,19 +4791,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Gold_W3</t>
+          <t>Hapa D_Crush Brown_Secretive</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>23640</v>
+        <v>28094</v>
       </c>
       <c r="G106" t="n">
-        <v>1773</v>
+        <v>4131</v>
       </c>
     </row>
     <row r="107">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>17716</v>
+        <v>8146</v>
       </c>
       <c r="G107" t="n">
-        <v>3900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="108">
@@ -4857,19 +4857,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>14374</v>
+        <v>24687</v>
       </c>
       <c r="G108" t="n">
-        <v>3057</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="109">
@@ -4890,19 +4890,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>PIA D_Princess Chocolat_55%_14.5 UV</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>17118</v>
+        <v>5664</v>
       </c>
       <c r="G109" t="n">
-        <v>1698</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="110">
@@ -4923,19 +4923,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3499</v>
+        <v>12143</v>
       </c>
       <c r="G110" t="n">
-        <v>591</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="111">
@@ -4956,19 +4956,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>PIA D_Melty Butter_55%_14.5 UV</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>35183</v>
+        <v>33085</v>
       </c>
       <c r="G111" t="n">
-        <v>4651</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="112">
@@ -4989,19 +4989,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Princess Chocolat_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>19224</v>
+        <v>6198</v>
       </c>
       <c r="G112" t="n">
-        <v>2173</v>
+        <v>736</v>
       </c>
     </row>
     <row r="113">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>18417</v>
+        <v>23035</v>
       </c>
       <c r="G113" t="n">
-        <v>1846</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="114">
@@ -5055,19 +5055,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Clalen D_MIZONG_55%</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>16973</v>
+        <v>9366</v>
       </c>
       <c r="G114" t="n">
-        <v>2543</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="115">
@@ -5088,19 +5088,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Clalen D_XUYU_55%</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>11587</v>
+        <v>34007</v>
       </c>
       <c r="G115" t="n">
-        <v>1278</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="116">
@@ -5121,19 +5121,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>T-Garden D_Melty Time_55% UV 14.2</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>7334</v>
+        <v>4824</v>
       </c>
       <c r="G116" t="n">
-        <v>1079</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="117">
@@ -5154,19 +5154,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>Clalen D_XUYU_55%</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>38386</v>
+        <v>3871</v>
       </c>
       <c r="G117" t="n">
-        <v>4593</v>
+        <v>587</v>
       </c>
     </row>
     <row r="118">
@@ -5187,19 +5187,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>From D_(UV)Clear Beige_38%</t>
+          <t>PIA D_Princess Chocolat_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>2078</v>
+        <v>23347</v>
       </c>
       <c r="G118" t="n">
-        <v>749</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="119">
@@ -5220,19 +5220,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>PIA D_Date Topaz_38% UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>36968</v>
+        <v>21086</v>
       </c>
       <c r="G119" t="n">
-        <v>5865</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="120">
@@ -5253,19 +5253,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ClearBeige Mini UV 14.2</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>11336</v>
+        <v>16131</v>
       </c>
       <c r="G120" t="n">
-        <v>2267</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="121">
@@ -5286,19 +5286,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>From D_(UV)Clear Beige Coral_38%</t>
+          <t>ClearBeige Mini UV 14.2</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>6122</v>
+        <v>6018</v>
       </c>
       <c r="G121" t="n">
-        <v>990</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="122">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>2861</v>
+        <v>6206</v>
       </c>
       <c r="G122" t="n">
-        <v>638</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="123">
@@ -5352,19 +5352,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>PIA D_Baby Espresso_38% UV</t>
+          <t>PIA D_Date Topaz_38% UV</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>18635</v>
+        <v>7383</v>
       </c>
       <c r="G123" t="n">
-        <v>5701</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="124">
@@ -5385,19 +5385,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
+          <t>PIA D_Strawberry Quartz_38% UV</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>44403</v>
+        <v>21029</v>
       </c>
       <c r="G124" t="n">
-        <v>5095</v>
+        <v>4392</v>
       </c>
     </row>
     <row r="125">
@@ -5418,19 +5418,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>PIA_Lemonade_55%_1-DAY</t>
+          <t>ClearBeige Mini UV 14.2</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1869</v>
+        <v>2294</v>
       </c>
       <c r="G125" t="n">
-        <v>184</v>
+        <v>635</v>
       </c>
     </row>
     <row r="126">
@@ -5451,19 +5451,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>From D_(UV)Clear Beige Coral_38%</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>21135</v>
+        <v>17996</v>
       </c>
       <c r="G126" t="n">
-        <v>3163</v>
+        <v>3331</v>
       </c>
     </row>
     <row r="127">
@@ -5484,19 +5484,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>PIA D_Baby Espresso_38% UV</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>24366</v>
+        <v>17775</v>
       </c>
       <c r="G127" t="n">
-        <v>3711</v>
+        <v>5521</v>
       </c>
     </row>
     <row r="128">
@@ -5517,19 +5517,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>31153</v>
+        <v>28268</v>
       </c>
       <c r="G128" t="n">
-        <v>2545</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="129">
@@ -5545,24 +5545,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>PIA_Lemonade_55%_1-DAY</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1598</v>
+        <v>15359</v>
       </c>
       <c r="G129" t="n">
-        <v>271</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="130">
@@ -5578,24 +5578,24 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Brown</t>
+          <t>Alcon D_Jewel Black_W3</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>11727</v>
+        <v>15484</v>
       </c>
       <c r="G130" t="n">
-        <v>3172</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="131">
@@ -5611,24 +5611,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>8262</v>
+        <v>24180</v>
       </c>
       <c r="G131" t="n">
-        <v>3469</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="132">
@@ -5644,24 +5644,24 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2876</v>
+        <v>5032</v>
       </c>
       <c r="G132" t="n">
-        <v>619</v>
+        <v>944</v>
       </c>
     </row>
     <row r="133">
@@ -5677,24 +5677,24 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>14133</v>
+        <v>16277</v>
       </c>
       <c r="G133" t="n">
-        <v>2876</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="134">
@@ -5710,24 +5710,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>분리22호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>37957</v>
+        <v>12010</v>
       </c>
       <c r="G134" t="n">
-        <v>5994</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="135">
@@ -5743,24 +5743,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>분리23호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>32980</v>
+        <v>3786</v>
       </c>
       <c r="G135" t="n">
-        <v>5949</v>
+        <v>454</v>
       </c>
     </row>
     <row r="136">
@@ -5776,24 +5776,24 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>분리25호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Toric_CP-0.75_Halo Brown</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>35929</v>
+        <v>3023</v>
       </c>
       <c r="G136" t="n">
-        <v>10156</v>
+        <v>683</v>
       </c>
     </row>
     <row r="137">
@@ -5809,24 +5809,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>37448</v>
+        <v>26068</v>
       </c>
       <c r="G137" t="n">
-        <v>9053</v>
+        <v>5991</v>
       </c>
     </row>
     <row r="138">
@@ -5842,24 +5842,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>분리43호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>36618</v>
+        <v>11440</v>
       </c>
       <c r="G138" t="n">
-        <v>9606</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="139">
@@ -5870,29 +5870,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>검사30호기</t>
+          <t>분리22호기</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>2475</v>
+        <v>39407</v>
       </c>
       <c r="G139" t="n">
-        <v>300</v>
+        <v>4603</v>
       </c>
     </row>
     <row r="140">
@@ -5903,29 +5903,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>검사30호기</t>
+          <t>분리23호기</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>3095</v>
+        <v>37081</v>
       </c>
       <c r="G140" t="n">
-        <v>130</v>
+        <v>5666</v>
       </c>
     </row>
     <row r="141">
@@ -5936,29 +5936,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>검사31호기</t>
+          <t>분리25호기</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>2070</v>
+        <v>40947</v>
       </c>
       <c r="G141" t="n">
-        <v>110</v>
+        <v>9093</v>
       </c>
     </row>
     <row r="142">
@@ -5969,29 +5969,29 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>검사31호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>3890</v>
+        <v>37713</v>
       </c>
       <c r="G142" t="n">
-        <v>220</v>
+        <v>7582</v>
       </c>
     </row>
     <row r="143">
@@ -6002,29 +6002,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>검사31호기</t>
+          <t>분리43호기</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>2330</v>
+        <v>36528</v>
       </c>
       <c r="G143" t="n">
-        <v>75</v>
+        <v>9268</v>
       </c>
     </row>
     <row r="144">
@@ -6035,29 +6035,29 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
+          <t>Chai Cafe_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>8645</v>
+        <v>2742</v>
       </c>
       <c r="G144" t="n">
-        <v>175</v>
+        <v>670</v>
       </c>
     </row>
     <row r="145">
@@ -6068,29 +6068,29 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>6025</v>
+        <v>12865</v>
       </c>
       <c r="G145" t="n">
-        <v>65</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="146">
@@ -6111,19 +6111,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사30호기</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>9735</v>
+        <v>1260</v>
       </c>
       <c r="G146" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
     </row>
     <row r="147">
@@ -6144,19 +6144,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사30호기</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>9015</v>
+        <v>905</v>
       </c>
       <c r="G147" t="n">
-        <v>610</v>
+        <v>45</v>
       </c>
     </row>
     <row r="148">
@@ -6177,19 +6177,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사31호기</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>2835</v>
+        <v>2190</v>
       </c>
       <c r="G148" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
     </row>
     <row r="149">
@@ -6210,19 +6210,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사31호기</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2925</v>
+        <v>390</v>
       </c>
       <c r="G149" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150">
@@ -6243,19 +6243,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사31호기</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>9559</v>
+        <v>2215</v>
       </c>
       <c r="G150" t="n">
-        <v>766</v>
+        <v>70</v>
       </c>
     </row>
     <row r="151">
@@ -6276,19 +6276,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -6309,19 +6309,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>PIA D_Melty Butter_55%_14.5 UV</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>13300</v>
+        <v>6400</v>
       </c>
       <c r="G152" t="n">
-        <v>115</v>
+        <v>80</v>
       </c>
     </row>
     <row r="153">
@@ -6342,19 +6342,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>6395</v>
+        <v>9265</v>
       </c>
       <c r="G153" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
     </row>
     <row r="154">
@@ -6375,19 +6375,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>6680</v>
+        <v>2935</v>
       </c>
       <c r="G154" t="n">
-        <v>120</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155">
@@ -6408,19 +6408,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>3200</v>
+        <v>3215</v>
       </c>
       <c r="G155" t="n">
-        <v>425</v>
+        <v>25</v>
       </c>
     </row>
     <row r="156">
@@ -6441,19 +6441,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>6925</v>
+        <v>12653</v>
       </c>
       <c r="G156" t="n">
-        <v>105</v>
+        <v>777</v>
       </c>
     </row>
     <row r="157">
@@ -6474,19 +6474,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Clalen D_MIZONG_55%</t>
+          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>2470</v>
+        <v>2800</v>
       </c>
       <c r="G157" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="158">
@@ -6507,19 +6507,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Clalen D_XUYU_55%</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>29765</v>
+        <v>6240</v>
       </c>
       <c r="G158" t="n">
-        <v>545</v>
+        <v>115</v>
       </c>
     </row>
     <row r="159">
@@ -6540,19 +6540,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>PIA D_Dayglow Gray_55% UV 14.2</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>15460</v>
+        <v>10445</v>
       </c>
       <c r="G159" t="n">
-        <v>245</v>
+        <v>150</v>
       </c>
     </row>
     <row r="160">
@@ -6573,19 +6573,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>PIA D_Iconic Brown_55% UV 14.2</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>3430</v>
+        <v>6270</v>
       </c>
       <c r="G160" t="n">
-        <v>25</v>
+        <v>115</v>
       </c>
     </row>
     <row r="161">
@@ -6606,19 +6606,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>PIA D_Starflare Beige_55% UV 14.2</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>19082</v>
+        <v>6347</v>
       </c>
       <c r="G161" t="n">
-        <v>2038</v>
+        <v>488</v>
       </c>
     </row>
     <row r="162">
@@ -6639,19 +6639,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>PIA D_Starflare Gray_55% UV 14.2</t>
+          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>9105</v>
+        <v>3585</v>
       </c>
       <c r="G162" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
     </row>
     <row r="163">
@@ -6672,19 +6672,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>50044</v>
+        <v>6795</v>
       </c>
       <c r="G163" t="n">
-        <v>1281</v>
+        <v>105</v>
       </c>
     </row>
     <row r="164">
@@ -6705,19 +6705,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>PIA D_Cream Beige_14.4</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>600</v>
+        <v>42652</v>
       </c>
       <c r="G164" t="n">
-        <v>40</v>
+        <v>903</v>
       </c>
     </row>
     <row r="165">
@@ -6738,19 +6738,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>PIA D_Cream Grege_14.4</t>
+          <t>Clalen D_MIZONG_55%</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>15140</v>
+        <v>10065</v>
       </c>
       <c r="G165" t="n">
-        <v>105</v>
+        <v>155</v>
       </c>
     </row>
     <row r="166">
@@ -6771,19 +6771,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>PIA D_Date Topaz_38% UV</t>
+          <t>Clalen D_MIZONG_55%</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>28197</v>
+        <v>1940</v>
       </c>
       <c r="G166" t="n">
-        <v>613</v>
+        <v>25</v>
       </c>
     </row>
     <row r="167">
@@ -6804,19 +6804,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>Clalen D_XUYU_55%</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>5135</v>
+        <v>9930</v>
       </c>
       <c r="G167" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
     </row>
     <row r="168">
@@ -6837,19 +6837,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>ClearBeige Mini UV 14.2</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>25345</v>
+        <v>10759</v>
       </c>
       <c r="G168" t="n">
-        <v>210</v>
+        <v>341</v>
       </c>
     </row>
     <row r="169">
@@ -6870,19 +6870,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>From D_(UV)Clear Beige Coral_38%</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>5820</v>
+        <v>880</v>
       </c>
       <c r="G169" t="n">
-        <v>160</v>
+        <v>25</v>
       </c>
     </row>
     <row r="170">
@@ -6903,19 +6903,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>PIA D_Melty Butter_55%_14.5 UV</t>
+          <t>From D_(UV)Clear Beige_38%</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>9900</v>
+        <v>2352</v>
       </c>
       <c r="G170" t="n">
-        <v>130</v>
+        <v>503</v>
       </c>
     </row>
     <row r="171">
@@ -6936,19 +6936,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Dayglow Gray_55% UV 14.2</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>3220</v>
+        <v>6030</v>
       </c>
       <c r="G171" t="n">
-        <v>5</v>
+        <v>125</v>
       </c>
     </row>
     <row r="172">
@@ -6969,19 +6969,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
+          <t>PIA D_Iconic Brown_55% UV 14.2</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>6730</v>
+        <v>8660</v>
       </c>
       <c r="G172" t="n">
-        <v>450</v>
+        <v>160</v>
       </c>
     </row>
     <row r="173">
@@ -7002,19 +7002,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>PIA D_Starflare Beige_55% UV 14.2</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>4245</v>
+        <v>4180</v>
       </c>
       <c r="G173" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="174">
@@ -7035,19 +7035,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1-Day_iris_Blue Moon</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>18849</v>
+        <v>13885</v>
       </c>
       <c r="G174" t="n">
-        <v>761</v>
+        <v>240</v>
       </c>
     </row>
     <row r="175">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -7077,10 +7077,10 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>19890</v>
+        <v>35587</v>
       </c>
       <c r="G175" t="n">
-        <v>385</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="176">
@@ -7101,19 +7101,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
+          <t>PIA D_Baby Espresso_38% UV</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>5125</v>
+        <v>22103</v>
       </c>
       <c r="G176" t="n">
-        <v>95</v>
+        <v>647</v>
       </c>
     </row>
     <row r="177">
@@ -7134,19 +7134,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Beige 14.2_55% UV</t>
+          <t>PIA D_Cream Grege_14.4</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>5575</v>
+        <v>1105</v>
       </c>
       <c r="G177" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
     </row>
     <row r="178">
@@ -7167,19 +7167,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Plus Gray 14.2_55% UV</t>
+          <t>PIA D_Date Topaz_38% UV</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>2175</v>
+        <v>29970</v>
       </c>
       <c r="G178" t="n">
-        <v>35</v>
+        <v>230</v>
       </c>
     </row>
     <row r="179">
@@ -7200,19 +7200,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>60187</v>
+        <v>2920</v>
       </c>
       <c r="G179" t="n">
-        <v>1168</v>
+        <v>20</v>
       </c>
     </row>
     <row r="180">
@@ -7233,19 +7233,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1-Day_iris_Blue Moon</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>5555</v>
+        <v>18005</v>
       </c>
       <c r="G180" t="n">
-        <v>80</v>
+        <v>220</v>
       </c>
     </row>
     <row r="181">
@@ -7266,19 +7266,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Clalen D_XUYU_55%</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>4005</v>
+        <v>12495</v>
       </c>
       <c r="G181" t="n">
-        <v>100</v>
+        <v>220</v>
       </c>
     </row>
     <row r="182">
@@ -7299,19 +7299,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>PIA D_Dayglow Gray_55% UV 14.2</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>8410</v>
+        <v>8605</v>
       </c>
       <c r="G182" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
     </row>
     <row r="183">
@@ -7332,19 +7332,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>PIA D_Iconic Brown_55% UV 14.2</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>6380</v>
+        <v>3240</v>
       </c>
       <c r="G183" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="184">
@@ -7365,19 +7365,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PIA D_Starflare Gray_55% UV 14.2</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>6970</v>
+        <v>4615</v>
       </c>
       <c r="G184" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
     </row>
     <row r="185">
@@ -7398,19 +7398,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Amber Moon_55%</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3785</v>
+        <v>9340</v>
       </c>
       <c r="G185" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
     </row>
     <row r="186">
@@ -7431,19 +7431,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Emerald Moon_55%</t>
+          <t>1-Day_iris_Blue Moon</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>7470</v>
+        <v>5980</v>
       </c>
       <c r="G186" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -7464,19 +7464,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Pearl Moon_55%</t>
+          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>2335</v>
+        <v>720</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="188">
@@ -7497,19 +7497,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Sapphire Moon_55%</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>18489</v>
+        <v>15795</v>
       </c>
       <c r="G188" t="n">
-        <v>1046</v>
+        <v>215</v>
       </c>
     </row>
     <row r="189">
@@ -7530,19 +7530,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Sunstone Moon_55%</t>
+          <t>PIA D_Princess Chocolat_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1490</v>
+        <v>26188</v>
       </c>
       <c r="G189" t="n">
-        <v>45</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="190">
@@ -7563,19 +7563,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Topaz Moon_55%</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>610</v>
+        <v>52235</v>
       </c>
       <c r="G190" t="n">
-        <v>35</v>
+        <v>542</v>
       </c>
     </row>
     <row r="191">
@@ -7596,19 +7596,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>JEWEL MOON D_Topaz Moon_55%</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>2840</v>
+        <v>2290</v>
       </c>
       <c r="G191" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
     </row>
     <row r="192">
@@ -7629,19 +7629,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
+          <t>Alcon D_Allure Blue_W3C(APAC)</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>2815</v>
+        <v>3360</v>
       </c>
       <c r="G192" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="193">
@@ -7662,19 +7662,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>Alcon D_Allure Blue_W3C(KR)</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>3180</v>
+        <v>3175</v>
       </c>
       <c r="G193" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
     </row>
     <row r="194">
@@ -7695,19 +7695,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>Alcon D_Jewel Gold_W3(APAC)</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>5540</v>
+        <v>6950</v>
       </c>
       <c r="G194" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="195">
@@ -7728,19 +7728,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>PIA D_Melty Butter_55%_14.5 UV</t>
+          <t>Alcon D_Jewel Gold_W3(KR)</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>2830</v>
+        <v>1750</v>
       </c>
       <c r="G195" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
     </row>
     <row r="196">
@@ -7761,19 +7761,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>Gemhour D_Greta Black_Keira</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>4370</v>
+        <v>7868</v>
       </c>
       <c r="G196" t="n">
-        <v>130</v>
+        <v>537</v>
       </c>
     </row>
     <row r="197">
@@ -7794,19 +7794,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
+          <t>Gemhour D_Lia Choco_Keira</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>3555</v>
+        <v>2010</v>
       </c>
       <c r="G197" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
     </row>
     <row r="198">
@@ -7827,19 +7827,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>Gemhour D_Liz Brown_Keira</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>2170</v>
+        <v>1475</v>
       </c>
       <c r="G198" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="199">
@@ -7860,19 +7860,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>4695</v>
+        <v>17525</v>
       </c>
       <c r="G199" t="n">
-        <v>50</v>
+        <v>130</v>
       </c>
     </row>
     <row r="200">
@@ -7893,19 +7893,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
+          <t>PIA D_Princess Chocolat_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>4735</v>
+        <v>11570</v>
       </c>
       <c r="G200" t="n">
-        <v>95</v>
+        <v>190</v>
       </c>
     </row>
     <row r="201">
@@ -7926,19 +7926,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Beige 14.2_55% UV</t>
+          <t>T-Garden D_Melty Time_55% UV 14.2</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>5275</v>
+        <v>9940</v>
       </c>
       <c r="G201" t="n">
-        <v>35</v>
+        <v>320</v>
       </c>
     </row>
     <row r="202">
@@ -7959,19 +7959,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>T-Garden D_Melty Time_55% UV 14.2</t>
+          <t>Hapa D_Crush Brown_Secretive</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>27050</v>
+        <v>4499</v>
       </c>
       <c r="G202" t="n">
-        <v>1390</v>
+        <v>481</v>
       </c>
     </row>
     <row r="203">
@@ -7992,19 +7992,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>T-Garden D_Pule Shabon_55% UV 14.2</t>
+          <t>PIA D_Dayglow Gray_55% UV 14.2</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>25041</v>
+        <v>2755</v>
       </c>
       <c r="G203" t="n">
-        <v>2174</v>
+        <v>25</v>
       </c>
     </row>
     <row r="204">
@@ -8030,14 +8030,14 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>ANW D_Art Gray_Dopewink 38%</t>
+          <t>PIA D_Iconic Brown_55% UV 14.2</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>5430</v>
+        <v>2610</v>
       </c>
       <c r="G204" t="n">
-        <v>425</v>
+        <v>50</v>
       </c>
     </row>
     <row r="205">
@@ -8063,14 +8063,14 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>ANW D_Bitter Brown_Dopewink 38%</t>
+          <t>PIA D_Starflare Beige_55% UV 14.2</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>4580</v>
+        <v>1115</v>
       </c>
       <c r="G205" t="n">
-        <v>110</v>
+        <v>10</v>
       </c>
     </row>
     <row r="206">
@@ -8091,19 +8091,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>ANW D_Spicy Gray_Dopewink 38%</t>
+          <t>Alcon D_Jewel Gold_W3(APAC)</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>13687</v>
+        <v>4070</v>
       </c>
       <c r="G206" t="n">
-        <v>558</v>
+        <v>55</v>
       </c>
     </row>
     <row r="207">
@@ -8124,19 +8124,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>ANW D_Vesta Beige_Dopewink 38%</t>
+          <t>Alcon D_Jewel Gold_W3(KR)</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>14115</v>
+        <v>5980</v>
       </c>
       <c r="G207" t="n">
-        <v>565</v>
+        <v>75</v>
       </c>
     </row>
     <row r="208">
@@ -8162,14 +8162,14 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Alcon D_Allure Blue_W3C(KR)</t>
+          <t>HOYA_Amber ash(Casual Ash)</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>9840</v>
+        <v>6830</v>
       </c>
       <c r="G208" t="n">
-        <v>85</v>
+        <v>490</v>
       </c>
     </row>
     <row r="209">
@@ -8195,14 +8195,14 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Gold_W3(KR)</t>
+          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>13300</v>
+        <v>2840</v>
       </c>
       <c r="G209" t="n">
-        <v>225</v>
+        <v>15</v>
       </c>
     </row>
     <row r="210">
@@ -8228,14 +8228,14 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>HOYA_Olive ash(Noble Ash)</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>4980</v>
+        <v>11811</v>
       </c>
       <c r="G210" t="n">
-        <v>750</v>
+        <v>384</v>
       </c>
     </row>
     <row r="211">
@@ -8261,14 +8261,14 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>10360</v>
+        <v>5690</v>
       </c>
       <c r="G211" t="n">
-        <v>260</v>
+        <v>70</v>
       </c>
     </row>
     <row r="212">
@@ -8294,14 +8294,14 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>6020</v>
+        <v>9966</v>
       </c>
       <c r="G212" t="n">
-        <v>60</v>
+        <v>689</v>
       </c>
     </row>
     <row r="213">
@@ -8327,14 +8327,14 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>4760</v>
+        <v>2695</v>
       </c>
       <c r="G213" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="214">
@@ -8360,14 +8360,14 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>2185</v>
+        <v>1925</v>
       </c>
       <c r="G214" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="215">
@@ -8388,19 +8388,19 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>검사48호기</t>
+          <t>검사49호기</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>2420</v>
+        <v>4115</v>
       </c>
       <c r="G215" t="n">
-        <v>25</v>
+        <v>285</v>
       </c>
     </row>
     <row r="216">
@@ -8416,24 +8416,24 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사49호기</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>930</v>
+        <v>2440</v>
       </c>
       <c r="G216" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="217">
@@ -8449,24 +8449,24 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사49호기</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>6160</v>
+        <v>2280</v>
       </c>
       <c r="G217" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="218">
@@ -8482,24 +8482,24 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사50호기</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1500</v>
+        <v>9115</v>
       </c>
       <c r="G218" t="n">
-        <v>175</v>
+        <v>495</v>
       </c>
     </row>
     <row r="219">
@@ -8515,24 +8515,24 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사50호기</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Brown</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1860</v>
+        <v>1800</v>
       </c>
       <c r="G219" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="220">
@@ -8548,24 +8548,24 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사50호기</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1885</v>
+        <v>1575</v>
       </c>
       <c r="G220" t="n">
-        <v>345</v>
+        <v>115</v>
       </c>
     </row>
     <row r="221">
@@ -8581,24 +8581,24 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사50호기</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>7085</v>
+        <v>1415</v>
       </c>
       <c r="G221" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="222">
@@ -8619,19 +8619,19 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>Toric_CP-0.75_Halo Brown</t>
         </is>
       </c>
       <c r="F222" t="n">
-        <v>3000</v>
+        <v>2965</v>
       </c>
       <c r="G222" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="223">
@@ -8652,19 +8652,19 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>Toric_CP-1.25_Halo Brown</t>
         </is>
       </c>
       <c r="F223" t="n">
-        <v>1742</v>
+        <v>1725</v>
       </c>
       <c r="G223" t="n">
-        <v>1143</v>
+        <v>25</v>
       </c>
     </row>
     <row r="224">
@@ -8685,19 +8685,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
       <c r="F224" t="n">
-        <v>7415</v>
+        <v>2085</v>
       </c>
       <c r="G224" t="n">
-        <v>135</v>
+        <v>15</v>
       </c>
     </row>
     <row r="225">
@@ -8713,24 +8713,24 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>34400</v>
+        <v>1580</v>
       </c>
       <c r="G225" t="n">
-        <v>540</v>
+        <v>10</v>
       </c>
     </row>
     <row r="226">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -8756,14 +8756,14 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>1-DAY58_Micure</t>
+          <t>Toric_CP-0.75_Halo Brown</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>29886</v>
+        <v>9755</v>
       </c>
       <c r="G226" t="n">
-        <v>2349</v>
+        <v>95</v>
       </c>
     </row>
     <row r="227">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -8789,14 +8789,14 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1-Day_58(NEW)</t>
+          <t>Toric_CP-1.25_Halo Brown</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>1870</v>
+        <v>4210</v>
       </c>
       <c r="G227" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="228">
@@ -8812,24 +8812,24 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>1-DAY58_Micure</t>
+          <t>Toric_CP-1.75_Halo Brown</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>7495</v>
+        <v>4830</v>
       </c>
       <c r="G228" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
     </row>
     <row r="229">
@@ -8845,24 +8845,24 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>1-DAY58_Micure</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>9478</v>
+        <v>870</v>
       </c>
       <c r="G229" t="n">
-        <v>512</v>
+        <v>15</v>
       </c>
     </row>
     <row r="230">
@@ -8878,24 +8878,24 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>1-DAY58_Micure</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>10800</v>
+        <v>950</v>
       </c>
       <c r="G230" t="n">
-        <v>235</v>
+        <v>15</v>
       </c>
     </row>
     <row r="231">
@@ -8916,30 +8916,30 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F231" t="n">
-        <v>31280</v>
+        <v>7945</v>
       </c>
       <c r="G231" t="n">
-        <v>890</v>
+        <v>105</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8949,195 +8949,195 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>1-DAY_58(PDI)</t>
         </is>
       </c>
       <c r="F232" t="n">
-        <v>32955</v>
+        <v>9637</v>
       </c>
       <c r="G232" t="n">
-        <v>2240</v>
+        <v>863</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>B형 조립중합3호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>O2O2 D_Blending Hazel EX</t>
+          <t>1-Day_SOLEKO(5년)</t>
         </is>
       </c>
       <c r="F233" t="n">
-        <v>14613</v>
+        <v>27490</v>
       </c>
       <c r="G233" t="n">
-        <v>1176</v>
+        <v>530</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>B형 조립중합4호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F234" t="n">
-        <v>26838</v>
+        <v>31426</v>
       </c>
       <c r="G234" t="n">
-        <v>1726</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>1-Day_Contakt(유효기간_8년)</t>
         </is>
       </c>
       <c r="F235" t="n">
-        <v>46205</v>
+        <v>13662</v>
       </c>
       <c r="G235" t="n">
-        <v>0</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>1-Day_Metha_Coastal</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>32423</v>
+        <v>13460</v>
       </c>
       <c r="G236" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>39833</v>
+        <v>51956</v>
       </c>
       <c r="G237" t="n">
-        <v>0</v>
+        <v>974</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -9147,30 +9147,30 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>CAM분리1호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F238" t="n">
-        <v>4117</v>
+        <v>22199</v>
       </c>
       <c r="G238" t="n">
-        <v>2922</v>
+        <v>726</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -9180,30 +9180,30 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>CAM분리2호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>1-Day_SOLEKO(5년)</t>
         </is>
       </c>
       <c r="F239" t="n">
-        <v>11959</v>
+        <v>26855</v>
       </c>
       <c r="G239" t="n">
-        <v>3946</v>
+        <v>690</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -9213,52 +9213,52 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>CAM분리3호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F240" t="n">
-        <v>13850</v>
+        <v>30915</v>
       </c>
       <c r="G240" t="n">
-        <v>4093</v>
+        <v>620</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>1-Day_SOLEKO(5년)</t>
         </is>
       </c>
       <c r="F241" t="n">
-        <v>3692</v>
+        <v>8810</v>
       </c>
       <c r="G241" t="n">
-        <v>1329</v>
+        <v>115</v>
       </c>
     </row>
     <row r="242">
@@ -9269,29 +9269,29 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Brown EX</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F242" t="n">
-        <v>1563</v>
+        <v>13572</v>
       </c>
       <c r="G242" t="n">
-        <v>705</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -9312,19 +9312,19 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>B형 조립중합3호기</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Brown EX</t>
+          <t>O2O2 D_Blending Hazel EX</t>
         </is>
       </c>
       <c r="F243" t="n">
-        <v>7881</v>
+        <v>14069</v>
       </c>
       <c r="G243" t="n">
-        <v>1300</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="244">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>B형 조립중합4호기</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -9354,10 +9354,10 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>1649</v>
+        <v>29531</v>
       </c>
       <c r="G244" t="n">
-        <v>242</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="245">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -9378,19 +9378,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>B형 조립중합6호기</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>O2O2 D_Sepia Choco EX</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>537</v>
+        <v>11470</v>
       </c>
       <c r="G245" t="n">
-        <v>141</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="246">
@@ -9401,29 +9401,29 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>B형 분리수화접착6호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F246" t="n">
-        <v>2917</v>
+        <v>37439</v>
       </c>
       <c r="G246" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -9434,29 +9434,29 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F247" t="n">
-        <v>20538</v>
+        <v>41581</v>
       </c>
       <c r="G247" t="n">
-        <v>4095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -9467,29 +9467,29 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F248" t="n">
-        <v>17009</v>
+        <v>43048</v>
       </c>
       <c r="G248" t="n">
-        <v>1918</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -9505,24 +9505,24 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>B형 분리수화접착2호기</t>
+          <t>CAM분리2호기</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMD</t>
+          <t>Clalen D_Mimosa Brown</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>155</v>
+        <v>926</v>
       </c>
       <c r="G249" t="n">
-        <v>365</v>
+        <v>87</v>
       </c>
     </row>
     <row r="250">
@@ -9538,24 +9538,24 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>CAM분리3호기</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen D_Mimosa Brown</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>26950</v>
+        <v>915</v>
       </c>
       <c r="G250" t="n">
-        <v>1113</v>
+        <v>92</v>
       </c>
     </row>
     <row r="251">
@@ -9571,24 +9571,24 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>CAM분리1호기</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>23874</v>
+        <v>1668</v>
       </c>
       <c r="G251" t="n">
-        <v>1312</v>
+        <v>489</v>
       </c>
     </row>
     <row r="252">
@@ -9604,24 +9604,24 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>CAM분리2호기</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>14724</v>
+        <v>8238</v>
       </c>
       <c r="G252" t="n">
-        <v>1277</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="253">
@@ -9637,24 +9637,24 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>CAM분리3호기</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>11231</v>
+        <v>13823</v>
       </c>
       <c r="G253" t="n">
-        <v>2205</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="254">
@@ -9670,24 +9670,24 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>B형 분리수화접착3호기</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>14941</v>
+        <v>28429</v>
       </c>
       <c r="G254" t="n">
-        <v>1627</v>
+        <v>4958</v>
       </c>
     </row>
     <row r="255">
@@ -9698,29 +9698,29 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Cherry Moon</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3790</v>
+        <v>7853</v>
       </c>
       <c r="G255" t="n">
-        <v>186</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="256">
@@ -9731,29 +9731,29 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>B형 분리수화접착6호기</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Creamy Moon</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>10570</v>
+        <v>8931</v>
       </c>
       <c r="G256" t="n">
-        <v>269</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="257">
@@ -9764,29 +9764,29 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>A형 인라인4호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Ice gray Moon</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F257" t="n">
-        <v>810</v>
+        <v>26736</v>
       </c>
       <c r="G257" t="n">
-        <v>70</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="258">
@@ -9797,29 +9797,29 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Clalen oneday A(O2 Edition)</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F258" t="n">
-        <v>18195</v>
+        <v>24843</v>
       </c>
       <c r="G258" t="n">
-        <v>1436</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="259">
@@ -9830,29 +9830,29 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착2호기</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2_Multifocal_K2_SMD</t>
         </is>
       </c>
       <c r="F259" t="n">
-        <v>27290</v>
+        <v>6628</v>
       </c>
       <c r="G259" t="n">
-        <v>3107</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="260">
@@ -9863,12 +9863,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -9878,14 +9878,14 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Lake Gray_45%</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F260" t="n">
-        <v>550</v>
+        <v>24307</v>
       </c>
       <c r="G260" t="n">
-        <v>16</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="261">
@@ -9896,29 +9896,29 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>O2O2 D_Ash Brown EX</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F261" t="n">
-        <v>3989</v>
+        <v>29365</v>
       </c>
       <c r="G261" t="n">
-        <v>2650</v>
+        <v>319</v>
       </c>
     </row>
     <row r="262">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -9944,14 +9944,14 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMDH_WHITE_OPHTALMIC</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F262" t="n">
-        <v>18458</v>
+        <v>19958</v>
       </c>
       <c r="G262" t="n">
-        <v>1542</v>
+        <v>693</v>
       </c>
     </row>
     <row r="263">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9972,19 +9972,19 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>B형 분리수화접착2호기</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>O2O2 D_Spherical(DK70)_K2-SMD</t>
+          <t>O2O2 Spherical(DK70)_K2-SMD</t>
         </is>
       </c>
       <c r="F263" t="n">
-        <v>4864</v>
+        <v>5213</v>
       </c>
       <c r="G263" t="n">
-        <v>74</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="264">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -10005,19 +10005,19 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>B형 분리수화접착4호기</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F264" t="n">
-        <v>10815</v>
+        <v>31642</v>
       </c>
       <c r="G264" t="n">
-        <v>198</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="265">
@@ -10033,24 +10033,24 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+          <t>DYE D_LAVA</t>
         </is>
       </c>
       <c r="F265" t="n">
-        <v>25572</v>
+        <v>3638</v>
       </c>
       <c r="G265" t="n">
-        <v>1937</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="266">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -10076,14 +10076,14 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+          <t>BELLA D_Cove</t>
         </is>
       </c>
       <c r="F266" t="n">
-        <v>26959</v>
+        <v>9270</v>
       </c>
       <c r="G266" t="n">
-        <v>1009</v>
+        <v>270</v>
       </c>
     </row>
     <row r="267">
@@ -10099,24 +10099,24 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>A형 인라인4호기</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+          <t>BELLA D_Garnet</t>
         </is>
       </c>
       <c r="F267" t="n">
-        <v>13960</v>
+        <v>13085</v>
       </c>
       <c r="G267" t="n">
-        <v>924</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="268">
@@ -10132,24 +10132,519 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
+          <t>1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>A형 인라인4호기</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>JEWEL MOON D_Creamy Moon</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>555</v>
+      </c>
+      <c r="G268" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>A형 인라인5호기</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Clalen D_Pink Tulip Brown</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>10410</v>
+      </c>
+      <c r="G269" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>A형 인라인5호기</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>JEWEL MOON D_Ice gray Moon</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>689</v>
+      </c>
+      <c r="G270" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>A형 인라인2호기</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Clalen oneday A(O2 Edition)</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>11184</v>
+      </c>
+      <c r="G271" t="n">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>A형 인라인5호기</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Clalen oneday A(O2 Edition)</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>22320</v>
+      </c>
+      <c r="G272" t="n">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>21080</v>
+      </c>
+      <c r="G273" t="n">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>O2O2 D_Ash Brown EX</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>13215</v>
+      </c>
+      <c r="G274" t="n">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>O2O2 D_Blending Hazel EX</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>4528</v>
+      </c>
+      <c r="G275" t="n">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>A형 인라인1호기</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>O2O2 D_Blending Rose EX</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>2509</v>
+      </c>
+      <c r="G276" t="n">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>A형 인라인6호기</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>2410</v>
+      </c>
+      <c r="G277" t="n">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Si_1-Day_M/F</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>A형 인라인2호기</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>O2O2_Multifocal_K2_SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
+        <v>1625</v>
+      </c>
+      <c r="G278" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Si_1-Day_M/F</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>A형 인라인3호기</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>O2O2_Multifocal_K2_SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>1830</v>
+      </c>
+      <c r="G279" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
           <t>Si_1-Day_Sph</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr">
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>A형 인라인2호기</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>15080</v>
+      </c>
+      <c r="G280" t="n">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>A형 인라인3호기</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>44127</v>
+      </c>
+      <c r="G281" t="n">
+        <v>3898</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>A형 인라인4호기</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>17210</v>
+      </c>
+      <c r="G282" t="n">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Si_1-Day_Sph</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
         <is>
           <t>A형 인라인6호기</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
+      <c r="E283" t="inlineStr">
         <is>
           <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
       </c>
-      <c r="F268" t="n">
-        <v>27360</v>
-      </c>
-      <c r="G268" t="n">
-        <v>787</v>
+      <c r="F283" t="n">
+        <v>26330</v>
+      </c>
+      <c r="G283" t="n">
+        <v>1089</v>
       </c>
     </row>
   </sheetData>

--- a/생산실적현황(설비운영현황).xlsx
+++ b/생산실적현황(설비운영현황).xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -589,15 +589,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FRP_M/F</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -605,7 +605,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bi-focal_8.40</t>
+          <t>Silicone relax</t>
         </is>
       </c>
     </row>
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_M/F</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metha</t>
+          <t>Bi-focal_8.40</t>
         </is>
       </c>
     </row>
@@ -649,11 +649,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>Metha</t>
         </is>
       </c>
     </row>
@@ -673,23 +673,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Date Topaz_PIA_M_(중)(Y)</t>
+          <t>T38_(UV포함)</t>
         </is>
       </c>
     </row>
@@ -705,19 +705,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>CLC-20_원형</t>
         </is>
       </c>
     </row>
@@ -733,47 +733,47 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
     </row>
@@ -789,19 +789,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
     </row>
@@ -817,19 +817,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
     </row>
@@ -841,23 +841,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
         </is>
       </c>
     </row>
@@ -877,15 +877,15 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
     </row>
@@ -905,15 +905,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
     </row>
@@ -925,23 +925,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
     </row>
@@ -953,79 +953,79 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1-DAY58_Micure</t>
+          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S관(3공장)</t>
+          <t>C관(2공장)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
     </row>
@@ -1041,19 +1041,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>JEWEL MOON D_Creamy Moon</t>
         </is>
       </c>
     </row>
@@ -1065,11 +1065,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1093,11 +1093,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1121,23 +1121,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMD</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1157,15 +1157,15 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
     </row>
@@ -1177,23 +1177,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BELLA D_Garnet</t>
+          <t>O2O2 D_Sepia Choco EX</t>
         </is>
       </c>
     </row>
@@ -1205,23 +1205,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Clalen oneday A(O2 Edition)</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
     </row>
@@ -1241,15 +1241,15 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen D_Pink Tulip Brown</t>
         </is>
       </c>
     </row>
@@ -1269,13 +1269,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>Si_1-Day_Color_Sph</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S관(3공장)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>[55] 접착/멸균</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>Si_1-Day_Sph</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E31" t="n">
         <v>3</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>O2O2 Spherical_K2-SMDH_WHITE_OPHTALMIC</t>
         </is>
@@ -1292,16 +1320,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G283"/>
+  <dimension ref="A1:G291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="43" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1368,7 +1396,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>45266</v>
+        <v>50868</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1401,7 +1429,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>51742</v>
+        <v>50518</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1425,7 +1453,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>조립32호기</t>
+          <t>조립8호기</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1434,10 +1462,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>93710</v>
+        <v>33652</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5">
@@ -1453,24 +1481,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>FRP_Sph</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>조립8호기</t>
+          <t>조립1호기</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>Metha_55</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>19267</v>
+        <v>32188</v>
       </c>
       <c r="G5" t="n">
-        <v>846</v>
+        <v>790</v>
       </c>
     </row>
     <row r="6">
@@ -1486,24 +1514,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>조립1호기</t>
+          <t>조립2호기</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Metha_55</t>
+          <t>T38_(UV포함)</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>29551</v>
+        <v>7911</v>
       </c>
       <c r="G6" t="n">
-        <v>1163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1519,24 +1547,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>Si_1-Day_M/F</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>조립2호기</t>
+          <t>조립4호기</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>T38_(UV포함)</t>
+          <t>O2O2_Multifocal_K2_SMD</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2980</v>
+        <v>9183</v>
       </c>
       <c r="G7" t="n">
-        <v>1006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1552,24 +1580,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>조립4호기</t>
+          <t>조립3호기</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMD</t>
+          <t>Silicone relax</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4458</v>
+        <v>12172</v>
       </c>
       <c r="G8" t="n">
-        <v>640</v>
+        <v>856</v>
       </c>
     </row>
     <row r="9">
@@ -1599,10 +1627,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1605</v>
+        <v>3042</v>
       </c>
       <c r="G9" t="n">
-        <v>465</v>
+        <v>835</v>
       </c>
     </row>
     <row r="10">
@@ -1632,10 +1660,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>13594</v>
+        <v>9620</v>
       </c>
       <c r="G10" t="n">
-        <v>1861</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="11">
@@ -1665,10 +1693,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>28083</v>
+        <v>32526</v>
       </c>
       <c r="G11" t="n">
-        <v>4173</v>
+        <v>2704</v>
       </c>
     </row>
     <row r="12">
@@ -1684,24 +1712,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>분리4호기</t>
+          <t>분리3호기</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S55-Dry</t>
+          <t>T38_(UV포함)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6374</v>
+        <v>7704</v>
       </c>
       <c r="G12" t="n">
-        <v>461</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="13">
@@ -1727,14 +1755,14 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>T38_(UV포함)</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>501</v>
+        <v>1137</v>
       </c>
       <c r="G13" t="n">
-        <v>62</v>
+        <v>529</v>
       </c>
     </row>
     <row r="14">
@@ -1745,29 +1773,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FRP_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>분리3호기</t>
+          <t>검사15호기</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>T55_소사각</t>
+          <t>(NEW)MG M_No.1 Hazel_GLAM_(중)</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1140</v>
+        <v>7159</v>
       </c>
       <c r="G14" t="n">
-        <v>563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1793,14 +1821,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(NEW)MG M_No.1 Hazel_GLAM_(중)</t>
+          <t>Hapa M_First Love Kristin</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="G15" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1821,19 +1849,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>검사15호기</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bella Diamond_14.5_중사각</t>
+          <t>MG M_Glow Hazel_GLAM_(중)</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1026</v>
+        <v>1456</v>
       </c>
       <c r="G16" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1854,19 +1882,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bella-Natural_중사각</t>
+          <t>Bella Diamond_14.5_중사각</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>68</v>
+        <v>1030</v>
       </c>
       <c r="G17" t="n">
-        <v>24</v>
+        <v>343</v>
       </c>
     </row>
     <row r="18">
@@ -1887,19 +1915,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cream Rose_PIA_M_(중)</t>
+          <t>Cihan Sophistic_중사각</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2252</v>
+        <v>132</v>
       </c>
       <c r="G18" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1920,19 +1948,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Date Topaz_PIA_M_(중)(Y)</t>
+          <t>Advance_EO_원형</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3830</v>
+        <v>546</v>
       </c>
       <c r="G19" t="n">
-        <v>195</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20">
@@ -1958,11 +1986,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aquarella_Amazonia Green_원형</t>
+          <t>CLC-10_원형</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>301</v>
+        <v>7755</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1991,11 +2019,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aquarella_Dandara Hazel_원형</t>
+          <t>CLC-20_원형</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>43</v>
+        <v>10900</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2024,11 +2052,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Festival-II-Color_원형</t>
+          <t>Cihan Elegance_원형</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>373</v>
+        <v>157</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -2052,19 +2080,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사8호기</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>NewFusion_원형</t>
+          <t>Advance_CB_원형</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>599</v>
+        <v>526</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="24">
@@ -2085,19 +2113,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사9호기</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bella Diamond_14.5_중사각</t>
+          <t>Advance_EO_원형</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>245</v>
+        <v>1388</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
@@ -2118,19 +2146,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사9호기</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bella-Elite_14.5_중사각</t>
+          <t>Aquarella M_Alegria Gray_원형</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1084</v>
+        <v>120</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
@@ -2151,19 +2179,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사9호기</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cream Rose_PIA_M_(중)</t>
+          <t>Aquarella M_Bahia Green_원형</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1354</v>
+        <v>192</v>
       </c>
       <c r="G26" t="n">
-        <v>68</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -2184,19 +2212,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사9호기</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Date Topaz_PIA_M_(중)(Y)</t>
+          <t>Aquarella M_Noronha Blue_원형</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1362</v>
+        <v>176</v>
       </c>
       <c r="G27" t="n">
-        <v>79</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -2217,19 +2245,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사9호기</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Melty Butter_PIA_M_(중)</t>
+          <t>Aquarella_Bossa Nova Gray_원형</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1414</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>86</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -2250,19 +2278,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>검사21호기</t>
+          <t>검사9호기</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mocha Ring_PIA_M_(중)</t>
+          <t>NewFusion_원형</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1432</v>
+        <v>464</v>
       </c>
       <c r="G29" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
@@ -2283,19 +2311,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MG M_Perfect Brown_원형</t>
+          <t>CLC-30_바이알</t>
         </is>
       </c>
       <c r="F30" t="n">
+        <v>1646</v>
+      </c>
+      <c r="G30" t="n">
         <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="31">
@@ -2321,14 +2349,14 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CLC-30_바이알</t>
+          <t>Crazy_은캡</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1351</v>
+        <v>704</v>
       </c>
       <c r="G31" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2344,24 +2372,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_M/F</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>HD-X55_소사각</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4966</v>
+        <v>756</v>
       </c>
       <c r="G32" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2377,24 +2405,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_M/F</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>HD-X38_은캡</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6468</v>
+        <v>314</v>
       </c>
       <c r="G33" t="n">
-        <v>236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2415,19 +2443,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>검사11호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>786</v>
+        <v>7052</v>
       </c>
       <c r="G34" t="n">
-        <v>14</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35">
@@ -2448,19 +2476,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>8904</v>
+        <v>1374</v>
       </c>
       <c r="G35" t="n">
-        <v>91</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36">
@@ -2481,19 +2509,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>검사14호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>US55-2(M)_소사각</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2636</v>
+        <v>1268</v>
       </c>
       <c r="G36" t="n">
-        <v>61</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -2514,7 +2542,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>검사17호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2523,10 +2551,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>5176</v>
+        <v>10032</v>
       </c>
       <c r="G37" t="n">
-        <v>148</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38">
@@ -2552,14 +2580,14 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4544</v>
+        <v>9264</v>
       </c>
       <c r="G38" t="n">
-        <v>94</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39">
@@ -2580,19 +2608,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사17호기</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>8386</v>
+        <v>1120</v>
       </c>
       <c r="G39" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40">
@@ -2618,14 +2646,14 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3668</v>
+        <v>7779</v>
       </c>
       <c r="G40" t="n">
-        <v>145</v>
+        <v>199</v>
       </c>
     </row>
     <row r="41">
@@ -2646,19 +2674,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>검사20호기</t>
+          <t>검사19호기</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Metha_55_원형</t>
+          <t>US55-2(M)_중사각</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>8486</v>
+        <v>1306</v>
       </c>
       <c r="G41" t="n">
-        <v>347</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42">
@@ -2679,19 +2707,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사20호기</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Metha_55_소사각</t>
+          <t>(UV)CS30_원형_8.60</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3468</v>
+        <v>11004</v>
       </c>
       <c r="G42" t="n">
-        <v>64</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43">
@@ -2717,14 +2745,14 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>S55_소사각</t>
+          <t>Metha_55_소사각</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1032</v>
+        <v>2098</v>
       </c>
       <c r="G43" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44">
@@ -2745,19 +2773,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>검사23호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Metha_55_원형</t>
+          <t>S55_소사각</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1456</v>
+        <v>1678</v>
       </c>
       <c r="G44" t="n">
-        <v>319</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45">
@@ -2783,14 +2811,14 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Metha_55_원형</t>
+          <t>(UV)CS30_원형_8.60</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>4648</v>
+        <v>3890</v>
       </c>
       <c r="G45" t="n">
-        <v>176</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46">
@@ -2811,19 +2839,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>검사8호기</t>
+          <t>검사9호기</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>S38 원형(Green)</t>
+          <t>(UV)CS30_원형_8.60</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1954</v>
       </c>
       <c r="G46" t="n">
-        <v>300</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47">
@@ -2844,19 +2872,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>검사9호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Metha_55_원형</t>
+          <t>S38_은캡(BLUE TINT)</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>5278</v>
+        <v>2197</v>
       </c>
       <c r="G47" t="n">
-        <v>313</v>
+        <v>221</v>
       </c>
     </row>
     <row r="48">
@@ -2872,24 +2900,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>바이알캡핑기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>S38_은캡(BLUE TINT)</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>349</v>
+        <v>852</v>
       </c>
       <c r="G48" t="n">
-        <v>5</v>
+        <v>133</v>
       </c>
     </row>
     <row r="49">
@@ -2910,7 +2938,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>검사18호기</t>
+          <t>검사14호기</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2919,10 +2947,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>440</v>
+        <v>308</v>
       </c>
       <c r="G49" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50">
@@ -2943,7 +2971,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>검사22호기</t>
+          <t>검사18호기</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2952,10 +2980,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>498</v>
+        <v>556</v>
       </c>
       <c r="G50" t="n">
-        <v>35</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51">
@@ -2971,24 +2999,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Si_FRP_Color_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>검사16호기</t>
+          <t>검사22호기</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>O2O2 M_Natural Chocolat EX_(중)</t>
+          <t>T55_소사각</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>670</v>
+        <v>360</v>
       </c>
       <c r="G51" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52">
@@ -3004,24 +3032,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Si_FRP_M/F</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
+          <t>T38_금캡</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>364</v>
+        <v>470</v>
       </c>
       <c r="G52" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53">
@@ -3037,123 +3065,123 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Si_FRP_Sph</t>
+          <t>FRP_Toric</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>검사10호기</t>
+          <t>바이알캡핑기</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
+          <t>T38_금캡(UV포함)</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>5566</v>
+        <v>486</v>
       </c>
       <c r="G53" t="n">
-        <v>841</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>조립10호기</t>
+          <t>검사10호기</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Sapphire Moon_55%</t>
+          <t>Silicone relax_소사각</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>14159</v>
+        <v>1690</v>
       </c>
       <c r="G54" t="n">
-        <v>4695</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_M/F</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>조립11호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PIA D_Princess Chocolat_55%_14.5 UV</t>
+          <t>O2O2 M_Multifocal(Dk70)_K2_SMD_(소)</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>51249</v>
+        <v>554</v>
       </c>
       <c r="G55" t="n">
-        <v>3899</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C관(2공장)</t>
+          <t>A관(1공장)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_FRP_Sph</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>조립12호기</t>
+          <t>검사11호기</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>O2O2 M_Spherical(DK70)_K2-SMD_(소)</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>29077</v>
+        <v>6100</v>
       </c>
       <c r="G56" t="n">
-        <v>1200</v>
+        <v>889</v>
       </c>
     </row>
     <row r="57">
@@ -3174,19 +3202,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>조립13호기</t>
+          <t>조립10호기</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>Hapa D_Bam Brown_Dear Deer</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>27660</v>
+        <v>14874</v>
       </c>
       <c r="G57" t="n">
-        <v>4306</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="58">
@@ -3207,19 +3235,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>조립14호기</t>
+          <t>조립10호기</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>JEWEL MOON D_Amber Moon_55%</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>30438</v>
+        <v>10243</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="59">
@@ -3240,19 +3268,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>조립15호기</t>
+          <t>조립11호기</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Princess Chocolat_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>47828</v>
+        <v>50008</v>
       </c>
       <c r="G59" t="n">
-        <v>978</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="60">
@@ -3273,19 +3301,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>조립16호기</t>
+          <t>조립12호기</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>25691</v>
+        <v>55518</v>
       </c>
       <c r="G60" t="n">
-        <v>800</v>
+        <v>865</v>
       </c>
     </row>
     <row r="61">
@@ -3306,19 +3334,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>조립18호기</t>
+          <t>조립13호기</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PIA D_Brown Bunny_55% UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>10472</v>
+        <v>25156</v>
       </c>
       <c r="G61" t="n">
-        <v>4233</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3339,19 +3367,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>조립19호기</t>
+          <t>조립14호기</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>48560</v>
+        <v>18397</v>
       </c>
       <c r="G62" t="n">
-        <v>4490</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="63">
@@ -3372,19 +3400,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>조립23호기</t>
+          <t>조립15호기</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hapa D_Glazed Kristin_Choco</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>25539</v>
+        <v>9619</v>
       </c>
       <c r="G63" t="n">
-        <v>700</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="64">
@@ -3405,19 +3433,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>조립24호기</t>
+          <t>조립17호기</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>39494</v>
+        <v>27254</v>
       </c>
       <c r="G64" t="n">
-        <v>6150</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="65">
@@ -3438,19 +3466,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>조립25호기</t>
+          <t>조립19호기</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>20788</v>
+        <v>25711</v>
       </c>
       <c r="G65" t="n">
-        <v>3427</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="66">
@@ -3471,19 +3499,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>조립26호기</t>
+          <t>조립23호기</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rina_Crystal Gray_1-Day</t>
+          <t>Hapa D_Glazed Kristin_Choco</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>19038</v>
+        <v>14964</v>
       </c>
       <c r="G66" t="n">
-        <v>8393</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="67">
@@ -3504,19 +3532,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>조립27호기</t>
+          <t>조립25호기</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>11190</v>
+        <v>43442</v>
       </c>
       <c r="G67" t="n">
-        <v>800</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="68">
@@ -3537,19 +3565,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>조립42호기</t>
+          <t>조립27호기</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Topaz Moon_55%</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>21134</v>
+        <v>26981</v>
       </c>
       <c r="G68" t="n">
-        <v>1501</v>
+        <v>139</v>
       </c>
     </row>
     <row r="69">
@@ -3570,19 +3598,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>조립44호기</t>
+          <t>조립42호기</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PIA D_Baby Espresso_38% UV</t>
+          <t>JEWEL MOON D_Pearl Moon_55%</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>29228</v>
+        <v>14350</v>
       </c>
       <c r="G69" t="n">
-        <v>3215</v>
+        <v>3857</v>
       </c>
     </row>
     <row r="70">
@@ -3603,19 +3631,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>조립45호기</t>
+          <t>조립44호기</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Black_W3</t>
+          <t>PIA D_Baby Espresso_38% UV</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>17940</v>
+        <v>42258</v>
       </c>
       <c r="G70" t="n">
-        <v>3038</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="71">
@@ -3636,19 +3664,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>조립47호기</t>
+          <t>조립45호기</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PIA_Lemonade_55%_1-DAY</t>
+          <t>Alcon D_Chic Smoke_W4</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>39732</v>
+        <v>25439</v>
       </c>
       <c r="G71" t="n">
-        <v>3028</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="72">
@@ -3669,19 +3697,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>조립48호기</t>
+          <t>조립47호기</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>PIA_Lemonade_55%_1-DAY</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>23292</v>
+        <v>26940</v>
       </c>
       <c r="G72" t="n">
-        <v>3687</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="73">
@@ -3702,19 +3730,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>조립49호기</t>
+          <t>조립48호기</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gemhour D_Liz Brown_Keira</t>
+          <t>PIA D_Maria Ring_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>23797</v>
+        <v>54533</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="74">
@@ -3735,19 +3763,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>조립50호기</t>
+          <t>조립49호기</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
+          <t>Gemhour D_Lia Choco_Keira</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>28536</v>
+        <v>25068</v>
       </c>
       <c r="G74" t="n">
-        <v>1350</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="75">
@@ -3768,19 +3796,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>조립51호기</t>
+          <t>조립50호기</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>From D_(UV)Clear Beige_38%</t>
+          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>28458</v>
+        <v>31546</v>
       </c>
       <c r="G75" t="n">
-        <v>1215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3801,19 +3829,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>조립52호기</t>
+          <t>조립51호기</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>From D_(UV)Clear Beige_38%</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>20403</v>
+        <v>46388</v>
       </c>
       <c r="G76" t="n">
-        <v>77</v>
+        <v>4473</v>
       </c>
     </row>
     <row r="77">
@@ -3834,19 +3862,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>조립53호기</t>
+          <t>조립52호기</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PIA D_Mocha Ring_38% UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>29111</v>
+        <v>51332</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>868</v>
       </c>
     </row>
     <row r="78">
@@ -3867,19 +3895,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>조립54호기</t>
+          <t>조립53호기</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Mocha Ring_38% UV</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>51852</v>
+        <v>50681</v>
       </c>
       <c r="G78" t="n">
-        <v>2138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -3900,19 +3928,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>조립55호기</t>
+          <t>조립54호기</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PIA D_Strawberry Quartz_38% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>23118</v>
+        <v>28861</v>
       </c>
       <c r="G79" t="n">
-        <v>2203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -3933,19 +3961,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>조립56호기</t>
+          <t>조립55호기</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
+          <t>PIA D_Strawberry Quartz_38% UV</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>25812</v>
+        <v>21998</v>
       </c>
       <c r="G80" t="n">
-        <v>996</v>
+        <v>3982</v>
       </c>
     </row>
     <row r="81">
@@ -3966,19 +3994,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>조립57호기</t>
+          <t>조립56호기</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>28572</v>
+        <v>53888</v>
       </c>
       <c r="G81" t="n">
-        <v>671</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="82">
@@ -3999,19 +4027,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>조립58호기</t>
+          <t>조립57호기</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PIA D_Date Topaz_38% UV</t>
+          <t>PIA D_Bubble Blue_55% UV</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>51606</v>
+        <v>43789</v>
       </c>
       <c r="G82" t="n">
-        <v>3622</v>
+        <v>8261</v>
       </c>
     </row>
     <row r="83">
@@ -4032,19 +4060,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>조립59호기</t>
+          <t>조립58호기</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PIA D_Melty Butter_55%_14.5 UV</t>
+          <t>PIA D_Date Topaz_38% UV</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>57993</v>
+        <v>25372</v>
       </c>
       <c r="G83" t="n">
-        <v>794</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="84">
@@ -4060,24 +4088,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립59호기</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>4933</v>
+        <v>29628</v>
       </c>
       <c r="G84" t="n">
-        <v>513</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="85">
@@ -4098,19 +4126,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>Toric_CP-1.25_Halo Gray</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>10031</v>
+        <v>4340</v>
       </c>
       <c r="G85" t="n">
-        <v>834</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
@@ -4131,19 +4159,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>조립17호기</t>
+          <t>조립22호기</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>4918</v>
+        <v>38887</v>
       </c>
       <c r="G86" t="n">
-        <v>514</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="87">
@@ -4159,24 +4187,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립40호기</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Gray</t>
+          <t>Chai Cafe_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>4955</v>
+        <v>13005</v>
       </c>
       <c r="G87" t="n">
-        <v>3362</v>
+        <v>4665</v>
       </c>
     </row>
     <row r="88">
@@ -4192,24 +4220,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>조립22호기</t>
+          <t>조립46호기</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Gray</t>
+          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>25400</v>
+        <v>22204</v>
       </c>
       <c r="G88" t="n">
-        <v>3450</v>
+        <v>532</v>
       </c>
     </row>
     <row r="89">
@@ -4220,29 +4248,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>조립40호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Chai Cafe_PIA_M_(중)_14.2</t>
+          <t>JEWEL MOON D_Pearl Moon_55%</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>28331</v>
+        <v>10543</v>
       </c>
       <c r="G89" t="n">
-        <v>4146</v>
+        <v>801</v>
       </c>
     </row>
     <row r="90">
@@ -4253,29 +4281,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>[10] 사출조립</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>조립46호기</t>
+          <t>분리12호기</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
+          <t>JEWEL MOON D_Topaz Moon_55%</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>28958</v>
+        <v>19405</v>
       </c>
       <c r="G90" t="n">
-        <v>2310</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="91">
@@ -4301,14 +4329,14 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
+          <t>Rina_Crystal Gray_1-Day</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>14236</v>
+        <v>8678</v>
       </c>
       <c r="G91" t="n">
-        <v>2090</v>
+        <v>870</v>
       </c>
     </row>
     <row r="92">
@@ -4329,19 +4357,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>분리12호기</t>
+          <t>분리15호기</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rina_Crystal Gray_1-Day</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>31595</v>
+        <v>36506</v>
       </c>
       <c r="G92" t="n">
-        <v>3649</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="93">
@@ -4367,14 +4395,14 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>14266</v>
+        <v>12038</v>
       </c>
       <c r="G93" t="n">
-        <v>2612</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="94">
@@ -4395,19 +4423,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>10396</v>
+        <v>8184</v>
       </c>
       <c r="G94" t="n">
-        <v>1633</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="95">
@@ -4428,19 +4456,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>분리15호기</t>
+          <t>분리16호기</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Princess Chocolat_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>13289</v>
+        <v>22881</v>
       </c>
       <c r="G95" t="n">
-        <v>1329</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="96">
@@ -4461,7 +4489,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4470,10 +4498,10 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>12733</v>
+        <v>18262</v>
       </c>
       <c r="G96" t="n">
-        <v>2138</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="97">
@@ -4494,19 +4522,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>분리16호기</t>
+          <t>분리17호기</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>HOYA_Maquia Brown</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>17919</v>
+        <v>1355</v>
       </c>
       <c r="G97" t="n">
-        <v>2312</v>
+        <v>259</v>
       </c>
     </row>
     <row r="98">
@@ -4532,14 +4560,14 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>HOYA_Casual Ash</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>8888</v>
+        <v>9063</v>
       </c>
       <c r="G98" t="n">
-        <v>3907</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="99">
@@ -4560,19 +4588,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HOYA_Maquia Brown</t>
+          <t>Gemhour D_Liz Brown_Keira</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>5184</v>
+        <v>21435</v>
       </c>
       <c r="G99" t="n">
-        <v>1009</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="100">
@@ -4593,19 +4621,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>분리17호기</t>
+          <t>분리18호기</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>JEWEL MOON D_Amber Moon_55%</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>2783</v>
+        <v>5262</v>
       </c>
       <c r="G100" t="n">
-        <v>586</v>
+        <v>476</v>
       </c>
     </row>
     <row r="101">
@@ -4635,10 +4663,10 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>17501</v>
+        <v>13721</v>
       </c>
       <c r="G101" t="n">
-        <v>2748</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="102">
@@ -4659,19 +4687,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>분리18호기</t>
+          <t>분리19호기</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Sunstone Moon_55%</t>
+          <t>Hapa D_Glazed Kristin_Choco</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>22546</v>
+        <v>26813</v>
       </c>
       <c r="G102" t="n">
-        <v>2771</v>
+        <v>3278</v>
       </c>
     </row>
     <row r="103">
@@ -4692,19 +4720,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>분리19호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Black_W3</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>16773</v>
+        <v>40665</v>
       </c>
       <c r="G103" t="n">
-        <v>2428</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="104">
@@ -4725,7 +4753,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>분리19호기</t>
+          <t>분리20호기</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4734,10 +4762,10 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>15024</v>
+        <v>2023</v>
       </c>
       <c r="G104" t="n">
-        <v>1798</v>
+        <v>185</v>
       </c>
     </row>
     <row r="105">
@@ -4758,19 +4786,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>분리20호기</t>
+          <t>분리21호기</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>41736</v>
+        <v>25951</v>
       </c>
       <c r="G105" t="n">
-        <v>3325</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="106">
@@ -4796,14 +4824,14 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hapa D_Crush Brown_Secretive</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>28094</v>
+        <v>13633</v>
       </c>
       <c r="G106" t="n">
-        <v>4131</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="107">
@@ -4824,19 +4852,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>분리21호기</t>
+          <t>분리24호기</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>Alcon D_Chic Smoke_W4</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>8146</v>
+        <v>9824</v>
       </c>
       <c r="G107" t="n">
-        <v>640</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="108">
@@ -4862,14 +4890,14 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>24687</v>
+        <v>30784</v>
       </c>
       <c r="G108" t="n">
-        <v>2049</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="109">
@@ -4890,19 +4918,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>분리26호기</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>5664</v>
+        <v>31151</v>
       </c>
       <c r="G109" t="n">
-        <v>1642</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="110">
@@ -4923,19 +4951,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>분리24호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>12143</v>
+        <v>23748</v>
       </c>
       <c r="G110" t="n">
-        <v>1314</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="111">
@@ -4956,19 +4984,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리27호기</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>33085</v>
+        <v>15999</v>
       </c>
       <c r="G111" t="n">
-        <v>4492</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="112">
@@ -4989,19 +5017,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>분리26호기</t>
+          <t>분리28호기</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PIA D_Princess Chocolat_55%_14.5 UV</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>6198</v>
+        <v>34575</v>
       </c>
       <c r="G112" t="n">
-        <v>736</v>
+        <v>5512</v>
       </c>
     </row>
     <row r="113">
@@ -5022,19 +5050,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>Hapa D_Crush Brown_Secretive</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>23035</v>
+        <v>1575</v>
       </c>
       <c r="G113" t="n">
-        <v>2459</v>
+        <v>207</v>
       </c>
     </row>
     <row r="114">
@@ -5055,19 +5083,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>분리27호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>PIA D_Melty Butter_55%_14.5 UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>9366</v>
+        <v>24519</v>
       </c>
       <c r="G114" t="n">
-        <v>1172</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="115">
@@ -5088,19 +5116,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리30호기</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>34007</v>
+        <v>10020</v>
       </c>
       <c r="G115" t="n">
-        <v>3627</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="116">
@@ -5121,19 +5149,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>분리28호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA D_Date Topaz_38% UV</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>4824</v>
+        <v>20699</v>
       </c>
       <c r="G116" t="n">
-        <v>1389</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="117">
@@ -5154,19 +5182,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리31호기</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Clalen D_XUYU_55%</t>
+          <t>PIA D_Strawberry Quartz_38% UV</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>3871</v>
+        <v>19327</v>
       </c>
       <c r="G117" t="n">
-        <v>587</v>
+        <v>3791</v>
       </c>
     </row>
     <row r="118">
@@ -5187,19 +5215,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>PIA D_Princess Chocolat_55%_14.5 UV</t>
+          <t>From D_(UV)Clear Beige Coral_38%</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>23347</v>
+        <v>8272</v>
       </c>
       <c r="G118" t="n">
-        <v>2499</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="119">
@@ -5220,19 +5248,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리32호기</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>From D_(UV)Clear Beige_38%</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>21086</v>
+        <v>32780</v>
       </c>
       <c r="G119" t="n">
-        <v>1986</v>
+        <v>6021</v>
       </c>
     </row>
     <row r="120">
@@ -5253,19 +5281,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>분리30호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>PIA D_Melty Butter_55%_14.5 UV</t>
+          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>16131</v>
+        <v>25896</v>
       </c>
       <c r="G120" t="n">
-        <v>1987</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="121">
@@ -5286,19 +5314,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리33호기</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>ClearBeige Mini UV 14.2</t>
+          <t>PIA_Lemonade_55%_1-DAY</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>6018</v>
+        <v>19735</v>
       </c>
       <c r="G121" t="n">
-        <v>1824</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="122">
@@ -5319,19 +5347,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리34호기</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>From D_(UV)Clear Beige_38%</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>6206</v>
+        <v>44125</v>
       </c>
       <c r="G122" t="n">
-        <v>2392</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="123">
@@ -5352,19 +5380,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리37호기</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>PIA D_Date Topaz_38% UV</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>7383</v>
+        <v>9036</v>
       </c>
       <c r="G123" t="n">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="124">
@@ -5380,24 +5408,24 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>분리31호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>PIA D_Strawberry Quartz_38% UV</t>
+          <t>Toric_CP-0.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>21029</v>
+        <v>4379</v>
       </c>
       <c r="G124" t="n">
-        <v>4392</v>
+        <v>554</v>
       </c>
     </row>
     <row r="125">
@@ -5413,24 +5441,24 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ClearBeige Mini UV 14.2</t>
+          <t>Toric_CP-0.75_Halo Brown</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>2294</v>
+        <v>6492</v>
       </c>
       <c r="G125" t="n">
-        <v>635</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="126">
@@ -5446,24 +5474,24 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>From D_(UV)Clear Beige Coral_38%</t>
+          <t>Toric_CP-0.75_Halo Gray</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>17996</v>
+        <v>1500</v>
       </c>
       <c r="G126" t="n">
-        <v>3331</v>
+        <v>443</v>
       </c>
     </row>
     <row r="127">
@@ -5479,24 +5507,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>분리32호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>PIA D_Baby Espresso_38% UV</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>17775</v>
+        <v>2201</v>
       </c>
       <c r="G127" t="n">
-        <v>5521</v>
+        <v>501</v>
       </c>
     </row>
     <row r="128">
@@ -5512,24 +5540,24 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
+          <t>Toric_CP-1.25_Halo Brown</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>28268</v>
+        <v>4258</v>
       </c>
       <c r="G128" t="n">
-        <v>2496</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="129">
@@ -5545,24 +5573,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>분리33호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>PIA_Lemonade_55%_1-DAY</t>
+          <t>Toric_CP-1.25_Halo Gray</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>15359</v>
+        <v>1141</v>
       </c>
       <c r="G129" t="n">
-        <v>1488</v>
+        <v>983</v>
       </c>
     </row>
     <row r="130">
@@ -5578,24 +5606,24 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Black_W3</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>15484</v>
+        <v>4048</v>
       </c>
       <c r="G130" t="n">
-        <v>2456</v>
+        <v>870</v>
       </c>
     </row>
     <row r="131">
@@ -5611,24 +5639,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리35호기</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>Toric_CP-1.75_Halo Gray</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>24180</v>
+        <v>14586</v>
       </c>
       <c r="G131" t="n">
-        <v>2199</v>
+        <v>3963</v>
       </c>
     </row>
     <row r="132">
@@ -5644,24 +5672,24 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>분리34호기</t>
+          <t>분리22호기</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>5032</v>
+        <v>38853</v>
       </c>
       <c r="G132" t="n">
-        <v>944</v>
+        <v>5438</v>
       </c>
     </row>
     <row r="133">
@@ -5677,24 +5705,24 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리23호기</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>16277</v>
+        <v>36147</v>
       </c>
       <c r="G133" t="n">
-        <v>1497</v>
+        <v>5616</v>
       </c>
     </row>
     <row r="134">
@@ -5710,24 +5738,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>분리37호기</t>
+          <t>분리25호기</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>12010</v>
+        <v>40320</v>
       </c>
       <c r="G134" t="n">
-        <v>1233</v>
+        <v>11423</v>
       </c>
     </row>
     <row r="135">
@@ -5743,24 +5771,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리36호기</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>3786</v>
+        <v>42563</v>
       </c>
       <c r="G135" t="n">
-        <v>454</v>
+        <v>8807</v>
       </c>
     </row>
     <row r="136">
@@ -5776,24 +5804,24 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리43호기</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Brown</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>3023</v>
+        <v>41557</v>
       </c>
       <c r="G136" t="n">
-        <v>683</v>
+        <v>7659</v>
       </c>
     </row>
     <row r="137">
@@ -5809,24 +5837,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>Chai Cafe_PIA_M_(중)_14.2</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>26068</v>
+        <v>7819</v>
       </c>
       <c r="G137" t="n">
-        <v>5991</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="138">
@@ -5842,24 +5870,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>분리35호기</t>
+          <t>분리29호기</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>11440</v>
+        <v>28639</v>
       </c>
       <c r="G138" t="n">
-        <v>2445</v>
+        <v>4471</v>
       </c>
     </row>
     <row r="139">
@@ -5870,29 +5898,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>분리22호기</t>
+          <t>검사31호기</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>39407</v>
+        <v>1800</v>
       </c>
       <c r="G139" t="n">
-        <v>4603</v>
+        <v>95</v>
       </c>
     </row>
     <row r="140">
@@ -5903,29 +5931,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>분리23호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>37081</v>
+        <v>12705</v>
       </c>
       <c r="G140" t="n">
-        <v>5666</v>
+        <v>360</v>
       </c>
     </row>
     <row r="141">
@@ -5936,29 +5964,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>분리25호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>40947</v>
+        <v>5435</v>
       </c>
       <c r="G141" t="n">
-        <v>9093</v>
+        <v>60</v>
       </c>
     </row>
     <row r="142">
@@ -5969,29 +5997,29 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>분리36호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>37713</v>
+        <v>8363</v>
       </c>
       <c r="G142" t="n">
-        <v>7582</v>
+        <v>847</v>
       </c>
     </row>
     <row r="143">
@@ -6002,29 +6030,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>분리43호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>1-day_58_Kontaktni-HA</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>36528</v>
+        <v>928</v>
       </c>
       <c r="G143" t="n">
-        <v>9268</v>
+        <v>477</v>
       </c>
     </row>
     <row r="144">
@@ -6035,29 +6063,29 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Chai Cafe_PIA_M_(중)_14.2</t>
+          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>2742</v>
+        <v>3615</v>
       </c>
       <c r="G144" t="n">
-        <v>670</v>
+        <v>35</v>
       </c>
     </row>
     <row r="145">
@@ -6068,29 +6096,29 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[55] 접착/멸균</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>FRP_Color_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>분리29호기</t>
+          <t>검사32호기</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Coral Brown_2T_(PBT)PIA_M(Y)</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>12865</v>
+        <v>5210</v>
       </c>
       <c r="G145" t="n">
-        <v>3607</v>
+        <v>65</v>
       </c>
     </row>
     <row r="146">
@@ -6111,19 +6139,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>검사30호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1260</v>
+        <v>3630</v>
       </c>
       <c r="G146" t="n">
-        <v>135</v>
+        <v>50</v>
       </c>
     </row>
     <row r="147">
@@ -6144,19 +6172,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>검사30호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>905</v>
+        <v>14200</v>
       </c>
       <c r="G147" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
     </row>
     <row r="148">
@@ -6177,19 +6205,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>검사31호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>2190</v>
+        <v>3030</v>
       </c>
       <c r="G148" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="149">
@@ -6210,19 +6238,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>검사31호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>390</v>
+        <v>1925</v>
       </c>
       <c r="G149" t="n">
-        <v>20</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="150">
@@ -6243,19 +6271,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>검사31호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2215</v>
+        <v>6740</v>
       </c>
       <c r="G150" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="151">
@@ -6276,19 +6304,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>2550</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="152">
@@ -6309,19 +6337,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>6400</v>
+        <v>7105</v>
       </c>
       <c r="G152" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="153">
@@ -6342,19 +6370,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>9265</v>
+        <v>2920</v>
       </c>
       <c r="G153" t="n">
-        <v>120</v>
+        <v>35</v>
       </c>
     </row>
     <row r="154">
@@ -6375,19 +6403,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사33호기</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>PIA D_Melty Butter_55%_14.5 UV</t>
+          <t>PIA_Lemonade_55%_1-DAY</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>2935</v>
+        <v>2444</v>
       </c>
       <c r="G154" t="n">
-        <v>5</v>
+        <v>606</v>
       </c>
     </row>
     <row r="155">
@@ -6408,19 +6436,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>1-Day_iris_SoulBrown</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>3215</v>
+        <v>53765</v>
       </c>
       <c r="G155" t="n">
-        <v>25</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="156">
@@ -6441,19 +6469,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>검사32호기</t>
+          <t>검사34호기</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
+          <t>Clalen D_XUYU_55%</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>12653</v>
+        <v>2500</v>
       </c>
       <c r="G156" t="n">
-        <v>777</v>
+        <v>65</v>
       </c>
     </row>
     <row r="157">
@@ -6474,19 +6502,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
+          <t>Clalen D_XUYU_55%</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>2800</v>
+        <v>500</v>
       </c>
       <c r="G157" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="158">
@@ -6507,19 +6535,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>From D_(UV)Clear Beige Coral_38%</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>6240</v>
+        <v>10440</v>
       </c>
       <c r="G158" t="n">
-        <v>115</v>
+        <v>170</v>
       </c>
     </row>
     <row r="159">
@@ -6540,19 +6568,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>From D_(UV)Clear Beige_38%</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>10445</v>
+        <v>8070</v>
       </c>
       <c r="G159" t="n">
-        <v>150</v>
+        <v>195</v>
       </c>
     </row>
     <row r="160">
@@ -6573,19 +6601,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>PIA D_Coffee Jelly_55% UV</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>6270</v>
+        <v>16445</v>
       </c>
       <c r="G160" t="n">
-        <v>115</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="161">
@@ -6606,19 +6634,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>6347</v>
+        <v>2955</v>
       </c>
       <c r="G161" t="n">
-        <v>488</v>
+        <v>30</v>
       </c>
     </row>
     <row r="162">
@@ -6639,7 +6667,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6648,10 +6676,10 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>3585</v>
+        <v>13340</v>
       </c>
       <c r="G162" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="163">
@@ -6672,19 +6700,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>검사33호기</t>
+          <t>검사35호기</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>6795</v>
+        <v>437</v>
       </c>
       <c r="G163" t="n">
-        <v>105</v>
+        <v>788</v>
       </c>
     </row>
     <row r="164">
@@ -6705,19 +6733,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>1-Day_iris_SoulBrown</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>42652</v>
+        <v>31660</v>
       </c>
       <c r="G164" t="n">
-        <v>903</v>
+        <v>435</v>
       </c>
     </row>
     <row r="165">
@@ -6738,19 +6766,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>검사34호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Clalen D_MIZONG_55%</t>
+          <t>PIA D_Baby Espresso_38% UV</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>10065</v>
+        <v>13200</v>
       </c>
       <c r="G165" t="n">
-        <v>155</v>
+        <v>305</v>
       </c>
     </row>
     <row r="166">
@@ -6771,19 +6799,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Clalen D_MIZONG_55%</t>
+          <t>PIA D_Cream Grege_14.4</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1940</v>
+        <v>5015</v>
       </c>
       <c r="G166" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="167">
@@ -6804,19 +6832,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Clalen D_XUYU_55%</t>
+          <t>PIA D_Date Topaz_38% UV</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>9930</v>
+        <v>16035</v>
       </c>
       <c r="G167" t="n">
-        <v>115</v>
+        <v>150</v>
       </c>
     </row>
     <row r="168">
@@ -6837,19 +6865,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사37호기</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>ClearBeige Mini UV 14.2</t>
+          <t>PIA D_Strawberry Quartz_38% UV</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>10759</v>
+        <v>20665</v>
       </c>
       <c r="G168" t="n">
-        <v>341</v>
+        <v>560</v>
       </c>
     </row>
     <row r="169">
@@ -6870,19 +6898,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>From D_(UV)Clear Beige Coral_38%</t>
+          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>880</v>
+        <v>6645</v>
       </c>
       <c r="G169" t="n">
-        <v>25</v>
+        <v>110</v>
       </c>
     </row>
     <row r="170">
@@ -6903,19 +6931,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>From D_(UV)Clear Beige_38%</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>2352</v>
+        <v>16648</v>
       </c>
       <c r="G170" t="n">
-        <v>503</v>
+        <v>742</v>
       </c>
     </row>
     <row r="171">
@@ -6936,19 +6964,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PIA D_Dayglow Gray_55% UV 14.2</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>6030</v>
+        <v>12640</v>
       </c>
       <c r="G171" t="n">
-        <v>125</v>
+        <v>230</v>
       </c>
     </row>
     <row r="172">
@@ -6969,19 +6997,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PIA D_Iconic Brown_55% UV 14.2</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>8660</v>
+        <v>5370</v>
       </c>
       <c r="G172" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
     </row>
     <row r="173">
@@ -7002,19 +7030,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>검사35호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PIA D_Starflare Beige_55% UV 14.2</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>4180</v>
+        <v>6563</v>
       </c>
       <c r="G173" t="n">
-        <v>30</v>
+        <v>697</v>
       </c>
     </row>
     <row r="174">
@@ -7035,19 +7063,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>13885</v>
+        <v>2205</v>
       </c>
       <c r="G174" t="n">
-        <v>240</v>
+        <v>20</v>
       </c>
     </row>
     <row r="175">
@@ -7068,19 +7096,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>검사36호기</t>
+          <t>검사38호기</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Gray</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>35587</v>
+        <v>1405</v>
       </c>
       <c r="G175" t="n">
-        <v>1393</v>
+        <v>15</v>
       </c>
     </row>
     <row r="176">
@@ -7101,19 +7129,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>PIA D_Baby Espresso_38% UV</t>
+          <t>ClearBeige Mini UV 14.2</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>22103</v>
+        <v>5030</v>
       </c>
       <c r="G176" t="n">
-        <v>647</v>
+        <v>45</v>
       </c>
     </row>
     <row r="177">
@@ -7134,19 +7162,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>PIA D_Cream Grege_14.4</t>
+          <t>From D_(UV)Clear Beige Coral_38%</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1105</v>
+        <v>9986</v>
       </c>
       <c r="G177" t="n">
-        <v>40</v>
+        <v>909</v>
       </c>
     </row>
     <row r="178">
@@ -7167,19 +7195,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>검사37호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>PIA D_Date Topaz_38% UV</t>
+          <t>From D_(UV)Clear Beige_38%</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>29970</v>
+        <v>1646</v>
       </c>
       <c r="G178" t="n">
-        <v>230</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="179">
@@ -7200,19 +7228,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
+          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>2920</v>
+        <v>19320</v>
       </c>
       <c r="G179" t="n">
-        <v>20</v>
+        <v>275</v>
       </c>
     </row>
     <row r="180">
@@ -7233,19 +7261,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사39호기</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA D_Princess Chocolat_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>18005</v>
+        <v>15790</v>
       </c>
       <c r="G180" t="n">
-        <v>220</v>
+        <v>355</v>
       </c>
     </row>
     <row r="181">
@@ -7266,19 +7294,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사40호기</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>1-Day_iris_Suzy Brown</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>12495</v>
+        <v>56433</v>
       </c>
       <c r="G181" t="n">
-        <v>220</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="182">
@@ -7299,19 +7327,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>PIA D_Melty Butter_55%_14.5 UV</t>
+          <t>Alcon D_Jewel Black_W3(KR)</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>8605</v>
+        <v>10765</v>
       </c>
       <c r="G182" t="n">
-        <v>65</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="183">
@@ -7332,16 +7360,16 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>Alcon D_Jewel Gold_W3(KR)</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3240</v>
+        <v>635</v>
       </c>
       <c r="G183" t="n">
         <v>15</v>
@@ -7365,19 +7393,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>BELLA_Bluish Gray(8년)</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>4615</v>
+        <v>105</v>
       </c>
       <c r="G184" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185">
@@ -7398,19 +7426,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>검사38호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>Coastal_JazzBlack(신형리드지)</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>9340</v>
+        <v>195</v>
       </c>
       <c r="G185" t="n">
-        <v>95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186">
@@ -7431,19 +7459,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>1-Day_iris_Blue Moon</t>
+          <t>Freedom380</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>5980</v>
+        <v>4085</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
     </row>
     <row r="187">
@@ -7464,19 +7492,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사41호기</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>HAPA(PIA) D_Sugar High Kristin Ash Choco 14.2_55% UV</t>
+          <t>Soleko_Pearl</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>720</v>
+        <v>175</v>
       </c>
       <c r="G187" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="188">
@@ -7497,19 +7525,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>1-Day_iris_Suzy Gray</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>15795</v>
+        <v>8425</v>
       </c>
       <c r="G188" t="n">
-        <v>215</v>
+        <v>160</v>
       </c>
     </row>
     <row r="189">
@@ -7530,19 +7558,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>검사39호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>PIA D_Princess Chocolat_55%_14.5 UV</t>
+          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>26188</v>
+        <v>3285</v>
       </c>
       <c r="G189" t="n">
-        <v>1212</v>
+        <v>10</v>
       </c>
     </row>
     <row r="190">
@@ -7563,19 +7591,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>검사40호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>1-Day_iris_Suzy Brown</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>52235</v>
+        <v>9195</v>
       </c>
       <c r="G190" t="n">
-        <v>542</v>
+        <v>60</v>
       </c>
     </row>
     <row r="191">
@@ -7596,19 +7624,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>JEWEL MOON D_Topaz Moon_55%</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>2290</v>
+        <v>15997</v>
       </c>
       <c r="G191" t="n">
-        <v>120</v>
+        <v>533</v>
       </c>
     </row>
     <row r="192">
@@ -7629,19 +7657,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Alcon D_Allure Blue_W3C(APAC)</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>3360</v>
+        <v>3300</v>
       </c>
       <c r="G192" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
     </row>
     <row r="193">
@@ -7662,19 +7690,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Alcon D_Allure Blue_W3C(KR)</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>3175</v>
+        <v>5306</v>
       </c>
       <c r="G193" t="n">
-        <v>80</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="194">
@@ -7695,19 +7723,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Gold_W3(APAC)</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>6950</v>
+        <v>1730</v>
       </c>
       <c r="G194" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
     </row>
     <row r="195">
@@ -7728,19 +7756,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사46호기</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Gold_W3(KR)</t>
+          <t>Gemhour D_Greta Black_Keira</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1750</v>
+        <v>19977</v>
       </c>
       <c r="G195" t="n">
-        <v>80</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="196">
@@ -7766,14 +7794,14 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Gemhour D_Greta Black_Keira</t>
+          <t>Gemhour D_Lia Choco_Keira</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>7868</v>
+        <v>3230</v>
       </c>
       <c r="G196" t="n">
-        <v>537</v>
+        <v>45</v>
       </c>
     </row>
     <row r="197">
@@ -7799,14 +7827,14 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Gemhour D_Lia Choco_Keira</t>
+          <t>Gemhour D_Liz Brown_Keira</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>2010</v>
+        <v>19796</v>
       </c>
       <c r="G197" t="n">
-        <v>55</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="198">
@@ -7827,19 +7855,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Gemhour D_Liz Brown_Keira</t>
+          <t>Alcon D_Jewel Gold_W3(APAC)</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1475</v>
+        <v>1575</v>
       </c>
       <c r="G198" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="199">
@@ -7860,19 +7888,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>PIA D_Jelly Quartz_55% UV 14.2</t>
+          <t>Hapa D_Crush Brown_Secretive</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>17525</v>
+        <v>15190</v>
       </c>
       <c r="G199" t="n">
-        <v>130</v>
+        <v>245</v>
       </c>
     </row>
     <row r="200">
@@ -7893,19 +7921,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사47호기</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>PIA D_Princess Chocolat_55%_14.5 UV</t>
+          <t>Rina_Crystal Gray_1-Day</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>11570</v>
+        <v>10602</v>
       </c>
       <c r="G200" t="n">
-        <v>190</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="201">
@@ -7926,19 +7954,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>검사46호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>T-Garden D_Melty Time_55% UV 14.2</t>
+          <t>HOYA_Amber ash(Casual Ash)</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>9940</v>
+        <v>2730</v>
       </c>
       <c r="G201" t="n">
-        <v>320</v>
+        <v>240</v>
       </c>
     </row>
     <row r="202">
@@ -7959,19 +7987,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Hapa D_Crush Brown_Secretive</t>
+          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>4499</v>
+        <v>8545</v>
       </c>
       <c r="G202" t="n">
-        <v>481</v>
+        <v>65</v>
       </c>
     </row>
     <row r="203">
@@ -7992,19 +8020,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>PIA D_Dayglow Gray_55% UV 14.2</t>
+          <t>PIA D_Brown Bunny_55% UV</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>2755</v>
+        <v>945</v>
       </c>
       <c r="G203" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="204">
@@ -8025,19 +8053,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>PIA D_Iconic Brown_55% UV 14.2</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>2610</v>
+        <v>5440</v>
       </c>
       <c r="G204" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="205">
@@ -8058,19 +8086,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>PIA D_Starflare Beige_55% UV 14.2</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1115</v>
+        <v>5325</v>
       </c>
       <c r="G205" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
     </row>
     <row r="206">
@@ -8096,14 +8124,14 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Gold_W3(APAC)</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>4070</v>
+        <v>3055</v>
       </c>
       <c r="G206" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="207">
@@ -8129,14 +8157,14 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Alcon D_Jewel Gold_W3(KR)</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>5980</v>
+        <v>2735</v>
       </c>
       <c r="G207" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
     </row>
     <row r="208">
@@ -8162,14 +8190,14 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>HOYA_Amber ash(Casual Ash)</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>6830</v>
+        <v>5424</v>
       </c>
       <c r="G208" t="n">
-        <v>490</v>
+        <v>611</v>
       </c>
     </row>
     <row r="209">
@@ -8195,14 +8223,14 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>2840</v>
+        <v>540</v>
       </c>
       <c r="G209" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="210">
@@ -8228,14 +8256,14 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>PIA D_Chai Cafe_55% UV 14.2</t>
+          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>11811</v>
+        <v>5065</v>
       </c>
       <c r="G210" t="n">
-        <v>384</v>
+        <v>100</v>
       </c>
     </row>
     <row r="211">
@@ -8261,14 +8289,14 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>5690</v>
+        <v>7850</v>
       </c>
       <c r="G211" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="212">
@@ -8294,14 +8322,14 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>PIA D_Melty Butter_55%_14.5 UV</t>
+          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>9966</v>
+        <v>2605</v>
       </c>
       <c r="G212" t="n">
-        <v>689</v>
+        <v>85</v>
       </c>
     </row>
     <row r="213">
@@ -8327,14 +8355,14 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>PIA D_Melty Mist_55% UV</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>2695</v>
+        <v>1445</v>
       </c>
       <c r="G213" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="214">
@@ -8360,14 +8388,14 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA_Lemonade_55%_1-DAY</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>1925</v>
+        <v>3020</v>
       </c>
       <c r="G214" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="215">
@@ -8393,14 +8421,14 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
+          <t>PIA D_Almond Poodle_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>4115</v>
+        <v>11685</v>
       </c>
       <c r="G215" t="n">
-        <v>285</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="216">
@@ -8426,14 +8454,14 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>PIA D_Tarte Tatin_55% UV</t>
+          <t>PIA D_Chai Cafe_55% UV 14.2</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>2440</v>
+        <v>2485</v>
       </c>
       <c r="G216" t="n">
-        <v>45</v>
+        <v>115</v>
       </c>
     </row>
     <row r="217">
@@ -8459,14 +8487,14 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>2280</v>
+        <v>3040</v>
       </c>
       <c r="G217" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
     </row>
     <row r="218">
@@ -8487,19 +8515,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>검사50호기</t>
+          <t>검사49호기</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>PIA D_Choco Mist_55% UV 14.2</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>9115</v>
+        <v>2970</v>
       </c>
       <c r="G218" t="n">
-        <v>495</v>
+        <v>115</v>
       </c>
     </row>
     <row r="219">
@@ -8520,7 +8548,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>검사50호기</t>
+          <t>검사49호기</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -8529,10 +8557,10 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1800</v>
+        <v>3095</v>
       </c>
       <c r="G219" t="n">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="220">
@@ -8558,14 +8586,14 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>PIA_Cafe Mocha_1D_55%_14.5</t>
+          <t>PIA D_Choco Mist_55% UV 14.2</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1575</v>
+        <v>4340</v>
       </c>
       <c r="G220" t="n">
-        <v>115</v>
+        <v>60</v>
       </c>
     </row>
     <row r="221">
@@ -8591,11 +8619,11 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>PIA_HOJICHA LATTE_55%</t>
+          <t>PIA D_Coffee Jelly_55% UV</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1415</v>
+        <v>4275</v>
       </c>
       <c r="G221" t="n">
         <v>55</v>
@@ -8614,24 +8642,24 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사50호기</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Brown</t>
+          <t>PIA D_Melty Butter_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F222" t="n">
-        <v>2965</v>
+        <v>6165</v>
       </c>
       <c r="G222" t="n">
-        <v>15</v>
+        <v>85</v>
       </c>
     </row>
     <row r="223">
@@ -8647,24 +8675,24 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사50호기</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>PIA D_Melty Mist_55% UV</t>
         </is>
       </c>
       <c r="F223" t="n">
-        <v>1725</v>
+        <v>6510</v>
       </c>
       <c r="G223" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
     </row>
     <row r="224">
@@ -8680,24 +8708,24 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사50호기</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>PIA D_Pink Bomb_55%_14.5 UV</t>
         </is>
       </c>
       <c r="F224" t="n">
-        <v>2085</v>
+        <v>2920</v>
       </c>
       <c r="G224" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="225">
@@ -8713,24 +8741,24 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사50호기</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_ALICIA BROWN</t>
+          <t>PIA D_Sugar Pearl_55%_14.2 UV</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>1580</v>
+        <v>3605</v>
       </c>
       <c r="G225" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="226">
@@ -8746,24 +8774,24 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사50호기</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Toric_CP-0.75_Halo Brown</t>
+          <t>PIA D_Tarte Tatin_55% UV</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>9755</v>
+        <v>4175</v>
       </c>
       <c r="G226" t="n">
-        <v>95</v>
+        <v>170</v>
       </c>
     </row>
     <row r="227">
@@ -8779,24 +8807,24 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1-Day_Color_Toric</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사50호기</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_Halo Brown</t>
+          <t>PIA_HOJICHA LATTE_55%</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>4210</v>
+        <v>1320</v>
       </c>
       <c r="G227" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
     </row>
     <row r="228">
@@ -8817,19 +8845,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>검사42호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_Halo Brown</t>
+          <t>Toric_CP-1.25_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>4830</v>
+        <v>18910</v>
       </c>
       <c r="G228" t="n">
-        <v>40</v>
+        <v>245</v>
       </c>
     </row>
     <row r="229">
@@ -8850,19 +8878,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사36호기</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Toric_CP-1.25_ALICIA BROWN</t>
+          <t>Toric_CP-1.75_ALICIA BROWN</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>870</v>
+        <v>6870</v>
       </c>
       <c r="G229" t="n">
-        <v>15</v>
+        <v>165</v>
       </c>
     </row>
     <row r="230">
@@ -8888,14 +8916,14 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Toric_CP-1.75_ALICIA BROWN</t>
+          <t>Toric_CP-0.75_Halo Gray</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>950</v>
+        <v>2100</v>
       </c>
       <c r="G230" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="231">
@@ -8911,24 +8939,24 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Toric</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>검사41호기</t>
+          <t>검사48호기</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>1-DAY58_Micure</t>
+          <t>PIA_Date topaz CP-1.25 Toric_UV</t>
         </is>
       </c>
       <c r="F231" t="n">
-        <v>7945</v>
+        <v>2695</v>
       </c>
       <c r="G231" t="n">
-        <v>105</v>
+        <v>50</v>
       </c>
     </row>
     <row r="232">
@@ -8958,10 +8986,10 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>9637</v>
+        <v>4580</v>
       </c>
       <c r="G232" t="n">
-        <v>863</v>
+        <v>75</v>
       </c>
     </row>
     <row r="233">
@@ -8987,14 +9015,14 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F233" t="n">
-        <v>27490</v>
+        <v>24210</v>
       </c>
       <c r="G233" t="n">
-        <v>530</v>
+        <v>385</v>
       </c>
     </row>
     <row r="234">
@@ -9020,14 +9048,14 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>1-DAY58_Micure</t>
+          <t>1-DAY(OPTIC CENTER)</t>
         </is>
       </c>
       <c r="F234" t="n">
-        <v>31426</v>
+        <v>10826</v>
       </c>
       <c r="G234" t="n">
-        <v>1394</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="235">
@@ -9048,19 +9076,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>1-Day_Contakt(유효기간_8년)</t>
+          <t>1-DAY58_Micure</t>
         </is>
       </c>
       <c r="F235" t="n">
-        <v>13662</v>
+        <v>7660</v>
       </c>
       <c r="G235" t="n">
-        <v>1438</v>
+        <v>250</v>
       </c>
     </row>
     <row r="236">
@@ -9081,19 +9109,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>검사43호기</t>
+          <t>검사42호기</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>1-Day_Metha_Coastal</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>13460</v>
+        <v>25400</v>
       </c>
       <c r="G236" t="n">
-        <v>340</v>
+        <v>405</v>
       </c>
     </row>
     <row r="237">
@@ -9114,19 +9142,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>검사44호기</t>
+          <t>검사43호기</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>1-DAY58_Micure</t>
+          <t>1-Day_Contakt(유효기간_8년)</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>51956</v>
+        <v>53814</v>
       </c>
       <c r="G237" t="n">
-        <v>974</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="238">
@@ -9147,7 +9175,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>검사45호기</t>
+          <t>검사44호기</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -9156,10 +9184,10 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>22199</v>
+        <v>16545</v>
       </c>
       <c r="G238" t="n">
-        <v>726</v>
+        <v>410</v>
       </c>
     </row>
     <row r="239">
@@ -9185,14 +9213,14 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>1-DAY(OPTIC CENTER)</t>
         </is>
       </c>
       <c r="F239" t="n">
-        <v>26855</v>
+        <v>22400</v>
       </c>
       <c r="G239" t="n">
-        <v>690</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="240">
@@ -9213,7 +9241,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>검사47호기</t>
+          <t>검사45호기</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -9222,10 +9250,10 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>30915</v>
+        <v>27985</v>
       </c>
       <c r="G240" t="n">
-        <v>620</v>
+        <v>670</v>
       </c>
     </row>
     <row r="241">
@@ -9251,14 +9279,14 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>1-Day_SOLEKO(5년)</t>
+          <t>1-day_58_Kontaktni-HA</t>
         </is>
       </c>
       <c r="F241" t="n">
-        <v>8810</v>
+        <v>23605</v>
       </c>
       <c r="G241" t="n">
-        <v>115</v>
+        <v>415</v>
       </c>
     </row>
     <row r="242">
@@ -9274,24 +9302,24 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>A형 인라인5호기</t>
+          <t>B형 조립중합8호기</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>JEWEL MOON D_Creamy Moon</t>
         </is>
       </c>
       <c r="F242" t="n">
-        <v>13572</v>
+        <v>2892</v>
       </c>
       <c r="G242" t="n">
-        <v>0</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="243">
@@ -9307,24 +9335,24 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>B형 조립중합3호기</t>
+          <t>A형 인라인5호기</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>O2O2 D_Blending Hazel EX</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F243" t="n">
-        <v>14069</v>
+        <v>30957</v>
       </c>
       <c r="G243" t="n">
-        <v>2085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -9345,19 +9373,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>B형 조립중합4호기</t>
+          <t>B형 조립중합3호기</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 D_Blending Hazel EX</t>
         </is>
       </c>
       <c r="F244" t="n">
-        <v>29531</v>
+        <v>15853</v>
       </c>
       <c r="G244" t="n">
-        <v>2051</v>
+        <v>189</v>
       </c>
     </row>
     <row r="245">
@@ -9378,19 +9406,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>B형 조립중합6호기</t>
+          <t>B형 조립중합4호기</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>O2O2 D_Sepia Choco EX</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>11470</v>
+        <v>29381</v>
       </c>
       <c r="G245" t="n">
-        <v>1643</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="246">
@@ -9406,24 +9434,24 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 조립중합6호기</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>O2O2 D_Sepia Choco EX</t>
         </is>
       </c>
       <c r="F246" t="n">
-        <v>37439</v>
+        <v>6530</v>
       </c>
       <c r="G246" t="n">
-        <v>0</v>
+        <v>5421</v>
       </c>
     </row>
     <row r="247">
@@ -9444,7 +9472,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>A형 인라인1호기</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -9453,7 +9481,7 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>41581</v>
+        <v>42297</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -9477,7 +9505,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>A형 인라인2호기</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -9486,7 +9514,7 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>43048</v>
+        <v>42855</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -9500,29 +9528,29 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>CAM분리2호기</t>
+          <t>A형 인라인3호기</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Clalen D_Mimosa Brown</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>926</v>
+        <v>44033</v>
       </c>
       <c r="G249" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -9533,29 +9561,29 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Sph</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>CAM분리3호기</t>
+          <t>A형 인라인6호기</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Clalen D_Mimosa Brown</t>
+          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>915</v>
+        <v>18400</v>
       </c>
       <c r="G250" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -9566,29 +9594,29 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>[20] 분리</t>
+          <t>[10] 사출조립</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>Si_FRP_Color_Sph</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>CAM분리1호기</t>
+          <t>B형 조립중합4호기</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>O2O2 M_Natural Brown EX</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>1668</v>
+        <v>13624</v>
       </c>
       <c r="G251" t="n">
-        <v>489</v>
+        <v>3223</v>
       </c>
     </row>
     <row r="252">
@@ -9604,7 +9632,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -9614,14 +9642,14 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>JEWEL MOON D_Creamy Moon</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>8238</v>
+        <v>1186</v>
       </c>
       <c r="G252" t="n">
-        <v>3011</v>
+        <v>277</v>
       </c>
     </row>
     <row r="253">
@@ -9637,7 +9665,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>1-Day_Sph</t>
+          <t>1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -9647,14 +9675,14 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Clalen oneday A</t>
+          <t>JEWEL MOON D_Creamy Moon</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>13823</v>
+        <v>1321</v>
       </c>
       <c r="G253" t="n">
-        <v>1953</v>
+        <v>108</v>
       </c>
     </row>
     <row r="254">
@@ -9670,24 +9698,24 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>B형 분리수화접착3호기</t>
+          <t>CAM분리1호기</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>28429</v>
+        <v>1633</v>
       </c>
       <c r="G254" t="n">
-        <v>4958</v>
+        <v>317</v>
       </c>
     </row>
     <row r="255">
@@ -9703,24 +9731,24 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>B형 분리수화접착5호기</t>
+          <t>CAM분리2호기</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>7853</v>
+        <v>4597</v>
       </c>
       <c r="G255" t="n">
-        <v>1311</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="256">
@@ -9736,24 +9764,24 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Si_1-Day_Color_Sph</t>
+          <t>1-Day_Sph</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>B형 분리수화접착6호기</t>
+          <t>CAM분리3호기</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>Clalen oneday A</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>8931</v>
+        <v>4904</v>
       </c>
       <c r="G256" t="n">
-        <v>1349</v>
+        <v>816</v>
       </c>
     </row>
     <row r="257">
@@ -9774,7 +9802,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>B형 분리수화접착7호기</t>
+          <t>B형 분리수화접착3호기</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -9783,10 +9811,10 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>26736</v>
+        <v>1355</v>
       </c>
       <c r="G257" t="n">
-        <v>3510</v>
+        <v>247</v>
       </c>
     </row>
     <row r="258">
@@ -9807,19 +9835,19 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>B형 분리수화접착8호기</t>
+          <t>B형 분리수화접착3호기</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Clalen O2O2 D_Deep Black_45%</t>
+          <t>O2O2 D_Ash Brown EX</t>
         </is>
       </c>
       <c r="F258" t="n">
-        <v>24843</v>
+        <v>3352</v>
       </c>
       <c r="G258" t="n">
-        <v>2249</v>
+        <v>711</v>
       </c>
     </row>
     <row r="259">
@@ -9835,24 +9863,24 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Si_1-Day_M/F</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>B형 분리수화접착2호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>O2O2_Multifocal_K2_SMD</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F259" t="n">
-        <v>6628</v>
+        <v>2935</v>
       </c>
       <c r="G259" t="n">
-        <v>1186</v>
+        <v>710</v>
       </c>
     </row>
     <row r="260">
@@ -9868,24 +9896,24 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>A형 인라인1호기</t>
+          <t>B형 분리수화접착5호기</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>O2O2 D_Sepia Choco EX</t>
         </is>
       </c>
       <c r="F260" t="n">
-        <v>24307</v>
+        <v>19157</v>
       </c>
       <c r="G260" t="n">
-        <v>1661</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="261">
@@ -9901,24 +9929,24 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>B형 분리수화접착6호기</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>O2O2 D_Sepia Choco EX</t>
         </is>
       </c>
       <c r="F261" t="n">
-        <v>29365</v>
+        <v>19838</v>
       </c>
       <c r="G261" t="n">
-        <v>319</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="262">
@@ -9934,24 +9962,24 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>A형 인라인3호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>O2O2 D_Ash Brown EX</t>
         </is>
       </c>
       <c r="F262" t="n">
-        <v>19958</v>
+        <v>1349</v>
       </c>
       <c r="G262" t="n">
-        <v>693</v>
+        <v>698</v>
       </c>
     </row>
     <row r="263">
@@ -9967,24 +9995,24 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>B형 분리수화접착2호기</t>
+          <t>B형 분리수화접착7호기</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>O2O2 Spherical(DK70)_K2-SMD</t>
+          <t>O2O2 D_Blending Hazel EX</t>
         </is>
       </c>
       <c r="F263" t="n">
-        <v>5213</v>
+        <v>18311</v>
       </c>
       <c r="G263" t="n">
-        <v>1193</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="264">
@@ -10000,24 +10028,24 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Si_1-Day_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>B형 분리수화접착4호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>O2O2 Spherical_K2-SMDH_OPHTALMIC</t>
+          <t>Clalen O2O2 D_Deep Black_45%</t>
         </is>
       </c>
       <c r="F264" t="n">
-        <v>31642</v>
+        <v>8352</v>
       </c>
       <c r="G264" t="n">
-        <v>2826</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="265">
@@ -10028,29 +10056,29 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>[55] 접착/멸균</t>
+          <t>[20] 분리</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>1-Day_Color_Sph</t>
+          <t>Si_1-Day_Color_Sph</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>A형 인라인2호기</t>
+          <t>B형 분리수화접착8호기</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>DYE D_LAVA</t>
+          <t>O2O2 D_Ash Brown EX</t>
         </is>
       </c>
       <c r="F265" t="n">
-        <v>3638</v>
+        <v>11164</v>
       </c>
       <c r="G265" t="n">
-        <v>2229</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="266">
@@ -10061